--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -1,20 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="69">
   <si>
     <t>Date</t>
   </si>
@@ -103,6 +108,9 @@
     <t>2021-08-13</t>
   </si>
   <si>
+    <t>2025-08-04</t>
+  </si>
+  <si>
     <t>DG27001</t>
   </si>
   <si>
@@ -205,20 +213,26 @@
     <t>DG22003</t>
   </si>
   <si>
-    <t>0.084</t>
+    <t>3</t>
   </si>
   <si>
     <t>N41</t>
   </si>
   <si>
+    <t>R579</t>
+  </si>
+  <si>
     <t>2021/22</t>
+  </si>
+  <si>
+    <t>2025/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -281,6 +295,14 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -327,7 +349,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -359,9 +381,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -393,6 +416,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -568,11 +592,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K71"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:K72"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -607,18 +631,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -639,21 +663,21 @@
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -674,21 +698,21 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -706,21 +730,21 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>12</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -738,21 +762,21 @@
         <v>2</v>
       </c>
       <c r="K5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -770,21 +794,21 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -802,21 +826,21 @@
         <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -834,21 +858,21 @@
         <v>3</v>
       </c>
       <c r="K8" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -866,21 +890,21 @@
         <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -898,21 +922,21 @@
         <v>3</v>
       </c>
       <c r="K10" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C11">
-        <v>4.634</v>
+        <v>4.6340000000000003</v>
       </c>
       <c r="D11" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -930,21 +954,21 @@
         <v>4</v>
       </c>
       <c r="K11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C12">
         <v>3</v>
       </c>
       <c r="D12" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -962,21 +986,21 @@
         <v>3</v>
       </c>
       <c r="K12" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -994,21 +1018,21 @@
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1026,21 +1050,21 @@
         <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1058,21 +1082,21 @@
         <v>2</v>
       </c>
       <c r="K15" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1090,21 +1114,21 @@
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1122,21 +1146,21 @@
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1154,21 +1178,21 @@
         <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1186,21 +1210,21 @@
         <v>2</v>
       </c>
       <c r="K19" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1218,21 +1242,21 @@
         <v>2</v>
       </c>
       <c r="K20" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>17</v>
       </c>
       <c r="B21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1250,21 +1274,21 @@
         <v>2</v>
       </c>
       <c r="K21" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1282,21 +1306,21 @@
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23">
-        <v>0.452</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="D23" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1314,21 +1338,21 @@
         <v>1</v>
       </c>
       <c r="K23" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24">
         <v>3</v>
       </c>
       <c r="D24" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1346,21 +1370,21 @@
         <v>2</v>
       </c>
       <c r="K24" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>18</v>
       </c>
       <c r="B25" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1378,21 +1402,21 @@
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1410,21 +1434,21 @@
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1442,21 +1466,21 @@
         <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>19</v>
       </c>
       <c r="B28" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1474,21 +1498,21 @@
         <v>2</v>
       </c>
       <c r="K28" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1506,21 +1530,21 @@
         <v>2</v>
       </c>
       <c r="K29" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1538,21 +1562,21 @@
         <v>2</v>
       </c>
       <c r="K30" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C31">
-        <v>0.08400000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="D31" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1570,21 +1594,21 @@
         <v>1</v>
       </c>
       <c r="K31" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>20</v>
       </c>
       <c r="B32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C32">
         <v>3</v>
       </c>
       <c r="D32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1602,21 +1626,21 @@
         <v>2</v>
       </c>
       <c r="K32" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1634,21 +1658,21 @@
         <v>2</v>
       </c>
       <c r="K33" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1666,21 +1690,21 @@
         <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>21</v>
       </c>
       <c r="B35" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1698,21 +1722,21 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1730,21 +1754,21 @@
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C37">
-        <v>0.452</v>
+        <v>0.45200000000000001</v>
       </c>
       <c r="D37" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -1762,21 +1786,21 @@
         <v>1</v>
       </c>
       <c r="K37" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>22</v>
       </c>
       <c r="B38" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C38">
         <v>3</v>
       </c>
       <c r="D38" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -1794,21 +1818,21 @@
         <v>3</v>
       </c>
       <c r="K38" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1826,21 +1850,21 @@
         <v>3</v>
       </c>
       <c r="K39" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -1858,21 +1882,21 @@
         <v>3</v>
       </c>
       <c r="K40" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>23</v>
       </c>
       <c r="B41" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1890,21 +1914,21 @@
         <v>3</v>
       </c>
       <c r="K41" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1922,21 +1946,21 @@
         <v>3</v>
       </c>
       <c r="K42" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1951,21 +1975,21 @@
         <v>6</v>
       </c>
       <c r="K43" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1983,21 +2007,21 @@
         <v>3</v>
       </c>
       <c r="K44" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>24</v>
       </c>
       <c r="B45" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2015,21 +2039,21 @@
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2047,21 +2071,21 @@
         <v>3</v>
       </c>
       <c r="K46" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2079,21 +2103,21 @@
         <v>3</v>
       </c>
       <c r="K47" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2111,21 +2135,21 @@
         <v>3</v>
       </c>
       <c r="K48" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C49">
-        <v>0.845</v>
+        <v>0.84499999999999997</v>
       </c>
       <c r="D49" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2143,21 +2167,21 @@
         <v>1</v>
       </c>
       <c r="K49" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>25</v>
       </c>
       <c r="B50" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C50">
         <v>3</v>
       </c>
       <c r="D50" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2175,21 +2199,21 @@
         <v>3</v>
       </c>
       <c r="K50" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2207,21 +2231,21 @@
         <v>2</v>
       </c>
       <c r="K51" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2239,21 +2263,21 @@
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2271,21 +2295,21 @@
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C54">
-        <v>0.08400000000000001</v>
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="D54" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2303,21 +2327,21 @@
         <v>1</v>
       </c>
       <c r="K54" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C55">
         <v>3</v>
       </c>
       <c r="D55" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2335,21 +2359,21 @@
         <v>2</v>
       </c>
       <c r="K55" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2367,21 +2391,21 @@
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2399,21 +2423,21 @@
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2431,21 +2455,21 @@
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>26</v>
       </c>
       <c r="B59" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2463,21 +2487,21 @@
         <v>3</v>
       </c>
       <c r="K59" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2495,21 +2519,21 @@
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2527,21 +2551,21 @@
         <v>3</v>
       </c>
       <c r="K61" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C62">
-        <v>4.634</v>
+        <v>4.6340000000000003</v>
       </c>
       <c r="D62" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2559,21 +2583,21 @@
         <v>4</v>
       </c>
       <c r="K62" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>27</v>
       </c>
       <c r="B63" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C63">
         <v>3</v>
       </c>
       <c r="D63" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -2591,21 +2615,21 @@
         <v>2</v>
       </c>
       <c r="K63" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2623,21 +2647,21 @@
         <v>3</v>
       </c>
       <c r="K64" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2655,21 +2679,21 @@
         <v>2</v>
       </c>
       <c r="K65" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2687,21 +2711,21 @@
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>28</v>
       </c>
       <c r="B67" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2719,21 +2743,21 @@
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2751,21 +2775,21 @@
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2783,21 +2807,21 @@
         <v>2</v>
       </c>
       <c r="K69" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2815,21 +2839,21 @@
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>57</v>
-      </c>
-      <c r="C71" t="s">
-        <v>63</v>
+        <v>58</v>
+      </c>
+      <c r="C71">
+        <v>8.4000000000000005E-2</v>
       </c>
       <c r="D71" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -2847,7 +2871,42 @@
         <v>1</v>
       </c>
       <c r="K71" t="s">
-        <v>65</v>
+        <v>67</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>29</v>
+      </c>
+      <c r="B72" t="s">
+        <v>36</v>
+      </c>
+      <c r="C72" t="s">
+        <v>64</v>
+      </c>
+      <c r="D72" t="s">
+        <v>66</v>
+      </c>
+      <c r="E72">
+        <v>13</v>
+      </c>
+      <c r="F72">
+        <v>9</v>
+      </c>
+      <c r="G72">
+        <v>5</v>
+      </c>
+      <c r="H72">
+        <v>2</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="J72">
+        <v>12</v>
+      </c>
+      <c r="K72" t="s">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -1,25 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sibale\Desktop\Flask FarmManagementSystem\data\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="143">
   <si>
     <t>Date</t>
   </si>
@@ -108,7 +103,91 @@
     <t>2021-08-13</t>
   </si>
   <si>
-    <t>2025-08-04</t>
+    <t>2021-08-26</t>
+  </si>
+  <si>
+    <t>2021-09-01</t>
+  </si>
+  <si>
+    <t>2021-08-28</t>
+  </si>
+  <si>
+    <t>2024-09-01</t>
+  </si>
+  <si>
+    <t>2021-09-03</t>
+  </si>
+  <si>
+    <t>2021-09-04</t>
+  </si>
+  <si>
+    <t>2021-09-07</t>
+  </si>
+  <si>
+    <t>2021-09-08</t>
+  </si>
+  <si>
+    <t>2021-09-09</t>
+  </si>
+  <si>
+    <t>2021-09-11</t>
+  </si>
+  <si>
+    <t>2021-09-14</t>
+  </si>
+  <si>
+    <t>2021-09-19</t>
+  </si>
+  <si>
+    <t>2021-09-24</t>
+  </si>
+  <si>
+    <t>2021-09-18</t>
+  </si>
+  <si>
+    <t>2021-09-27</t>
+  </si>
+  <si>
+    <t>2021-09-28</t>
+  </si>
+  <si>
+    <t>2021-10-05</t>
+  </si>
+  <si>
+    <t>2021-10-06</t>
+  </si>
+  <si>
+    <t>2021-10-08</t>
+  </si>
+  <si>
+    <t>2021-10-14</t>
+  </si>
+  <si>
+    <t>2021-10-22</t>
+  </si>
+  <si>
+    <t>2021-10-01</t>
+  </si>
+  <si>
+    <t>2021-11-06</t>
+  </si>
+  <si>
+    <t>2021-11-08</t>
+  </si>
+  <si>
+    <t>2021-11-09</t>
+  </si>
+  <si>
+    <t>2021-11-10</t>
+  </si>
+  <si>
+    <t>2021-11-12</t>
+  </si>
+  <si>
+    <t>2021-11-13</t>
+  </si>
+  <si>
+    <t>2021-11-16</t>
   </si>
   <si>
     <t>DG27001</t>
@@ -120,6 +199,9 @@
     <t>DG27003</t>
   </si>
   <si>
+    <t>DG27004</t>
+  </si>
+  <si>
     <t>DG29001</t>
   </si>
   <si>
@@ -129,9 +211,6 @@
     <t>DG29003</t>
   </si>
   <si>
-    <t>DG27004</t>
-  </si>
-  <si>
     <t>DG31001</t>
   </si>
   <si>
@@ -213,7 +292,142 @@
     <t>DG22003</t>
   </si>
   <si>
-    <t>3</t>
+    <t>DG32005</t>
+  </si>
+  <si>
+    <t>DG32006</t>
+  </si>
+  <si>
+    <t>DG32007</t>
+  </si>
+  <si>
+    <t>DG33006</t>
+  </si>
+  <si>
+    <t>DG33007</t>
+  </si>
+  <si>
+    <t>DG33008</t>
+  </si>
+  <si>
+    <t>DG25001</t>
+  </si>
+  <si>
+    <t>DG25002</t>
+  </si>
+  <si>
+    <t>DG25003</t>
+  </si>
+  <si>
+    <t>DG33003</t>
+  </si>
+  <si>
+    <t>DG33004</t>
+  </si>
+  <si>
+    <t>DG33005</t>
+  </si>
+  <si>
+    <t>DG24001</t>
+  </si>
+  <si>
+    <t>DG24002</t>
+  </si>
+  <si>
+    <t>DG33001</t>
+  </si>
+  <si>
+    <t>DG33002</t>
+  </si>
+  <si>
+    <t>DG25004</t>
+  </si>
+  <si>
+    <t>DG25005</t>
+  </si>
+  <si>
+    <t>DG25006</t>
+  </si>
+  <si>
+    <t>DG24003</t>
+  </si>
+  <si>
+    <t>DG24004</t>
+  </si>
+  <si>
+    <t>DG24005</t>
+  </si>
+  <si>
+    <t>DG24006</t>
+  </si>
+  <si>
+    <t>DG24007</t>
+  </si>
+  <si>
+    <t>DG24008</t>
+  </si>
+  <si>
+    <t>DG24009</t>
+  </si>
+  <si>
+    <t>DG20001</t>
+  </si>
+  <si>
+    <t>DG20002</t>
+  </si>
+  <si>
+    <t>DG20003</t>
+  </si>
+  <si>
+    <t>DG20004</t>
+  </si>
+  <si>
+    <t>DG20005</t>
+  </si>
+  <si>
+    <t>DG39003</t>
+  </si>
+  <si>
+    <t>DG20006</t>
+  </si>
+  <si>
+    <t>DG20007</t>
+  </si>
+  <si>
+    <t>DG20008</t>
+  </si>
+  <si>
+    <t>DG35001</t>
+  </si>
+  <si>
+    <t>DG35002</t>
+  </si>
+  <si>
+    <t>DG35003</t>
+  </si>
+  <si>
+    <t>DG36001</t>
+  </si>
+  <si>
+    <t>DG36002</t>
+  </si>
+  <si>
+    <t>DG36003</t>
+  </si>
+  <si>
+    <t>DG36004</t>
+  </si>
+  <si>
+    <t>DG35004</t>
+  </si>
+  <si>
+    <t>DG39001</t>
+  </si>
+  <si>
+    <t>DG39002</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>N41</t>
@@ -222,17 +436,20 @@
     <t>R579</t>
   </si>
   <si>
+    <t>R570</t>
+  </si>
+  <si>
+    <t>97F1692</t>
+  </si>
+  <si>
     <t>2021/22</t>
-  </si>
-  <si>
-    <t>2025/26</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -295,14 +512,6 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -349,7 +558,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -381,10 +590,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -416,7 +624,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -592,11 +799,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K72"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:K193"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -631,18 +838,18 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -663,21 +870,21 @@
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>31</v>
+        <v>59</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -698,21 +905,21 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
       <c r="A4" t="s">
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>60</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -720,6 +927,9 @@
       <c r="F4">
         <v>3</v>
       </c>
+      <c r="G4">
+        <v>6</v>
+      </c>
       <c r="H4">
         <v>0</v>
       </c>
@@ -730,27 +940,30 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11">
       <c r="A5" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>61</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>4.634</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>3</v>
+        <v>5</v>
+      </c>
+      <c r="G5">
+        <v>9</v>
       </c>
       <c r="H5">
         <v>0</v>
@@ -759,24 +972,24 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
       <c r="A6" t="s">
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -784,6 +997,9 @@
       <c r="F6">
         <v>3</v>
       </c>
+      <c r="G6">
+        <v>6</v>
+      </c>
       <c r="H6">
         <v>0</v>
       </c>
@@ -794,21 +1010,21 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
       <c r="A7" t="s">
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -816,6 +1032,9 @@
       <c r="F7">
         <v>3</v>
       </c>
+      <c r="G7">
+        <v>6</v>
+      </c>
       <c r="H7">
         <v>0</v>
       </c>
@@ -826,53 +1045,56 @@
         <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>64</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="G8">
+        <v>6</v>
       </c>
       <c r="H8">
         <v>0</v>
       </c>
       <c r="I8">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
       <c r="A9" t="s">
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -880,6 +1102,9 @@
       <c r="F9">
         <v>8</v>
       </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
       <c r="H9">
         <v>0</v>
       </c>
@@ -890,21 +1115,21 @@
         <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -912,6 +1137,9 @@
       <c r="F10">
         <v>8</v>
       </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
       <c r="H10">
         <v>0</v>
       </c>
@@ -922,85 +1150,91 @@
         <v>3</v>
       </c>
       <c r="K10" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
       <c r="A11" t="s">
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>36</v>
+        <v>60</v>
       </c>
       <c r="C11">
-        <v>4.6340000000000003</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11">
+        <v>8</v>
+      </c>
+      <c r="G11">
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>6</v>
+      </c>
+      <c r="J11">
+        <v>3</v>
+      </c>
+      <c r="K11" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12">
+        <v>4.634</v>
+      </c>
+      <c r="D12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12">
         <v>12</v>
       </c>
-      <c r="H11">
-        <v>0</v>
-      </c>
-      <c r="I11">
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>0</v>
+      </c>
+      <c r="I12">
         <v>9</v>
       </c>
-      <c r="J11">
+      <c r="J12">
         <v>4</v>
       </c>
-      <c r="K11" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>14</v>
-      </c>
-      <c r="B12" t="s">
-        <v>33</v>
-      </c>
-      <c r="C12">
-        <v>3</v>
-      </c>
-      <c r="D12" t="s">
-        <v>65</v>
-      </c>
-      <c r="E12">
-        <v>0</v>
-      </c>
-      <c r="F12">
-        <v>8</v>
-      </c>
-      <c r="H12">
-        <v>0</v>
-      </c>
-      <c r="I12">
-        <v>6</v>
-      </c>
-      <c r="J12">
-        <v>3</v>
-      </c>
       <c r="K12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
       <c r="A13" t="s">
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1008,6 +1242,9 @@
       <c r="F13">
         <v>8</v>
       </c>
+      <c r="G13">
+        <v>0</v>
+      </c>
       <c r="H13">
         <v>0</v>
       </c>
@@ -1018,21 +1255,21 @@
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
       <c r="A14" t="s">
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1040,6 +1277,9 @@
       <c r="F14">
         <v>8</v>
       </c>
+      <c r="G14">
+        <v>0</v>
+      </c>
       <c r="H14">
         <v>0</v>
       </c>
@@ -1050,53 +1290,56 @@
         <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>37</v>
+        <v>64</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E15">
         <v>0</v>
       </c>
       <c r="F15">
-        <v>3</v>
+        <v>8</v>
+      </c>
+      <c r="G15">
+        <v>0</v>
       </c>
       <c r="H15">
         <v>0</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J15">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K15" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
       <c r="A16" t="s">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1104,6 +1347,9 @@
       <c r="F16">
         <v>3</v>
       </c>
+      <c r="G16">
+        <v>6</v>
+      </c>
       <c r="H16">
         <v>0</v>
       </c>
@@ -1114,21 +1360,21 @@
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
       <c r="A17" t="s">
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1136,6 +1382,9 @@
       <c r="F17">
         <v>3</v>
       </c>
+      <c r="G17">
+        <v>6</v>
+      </c>
       <c r="H17">
         <v>0</v>
       </c>
@@ -1146,21 +1395,21 @@
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
       <c r="A18" t="s">
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1168,6 +1417,9 @@
       <c r="F18">
         <v>3</v>
       </c>
+      <c r="G18">
+        <v>6</v>
+      </c>
       <c r="H18">
         <v>0</v>
       </c>
@@ -1178,21 +1430,21 @@
         <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
       <c r="A19" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1200,6 +1452,9 @@
       <c r="F19">
         <v>3</v>
       </c>
+      <c r="G19">
+        <v>6</v>
+      </c>
       <c r="H19">
         <v>0</v>
       </c>
@@ -1210,21 +1465,21 @@
         <v>2</v>
       </c>
       <c r="K19" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
       <c r="A20" t="s">
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1232,6 +1487,9 @@
       <c r="F20">
         <v>3</v>
       </c>
+      <c r="G20">
+        <v>6</v>
+      </c>
       <c r="H20">
         <v>0</v>
       </c>
@@ -1242,21 +1500,21 @@
         <v>2</v>
       </c>
       <c r="K20" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1264,6 +1522,9 @@
       <c r="F21">
         <v>3</v>
       </c>
+      <c r="G21">
+        <v>6</v>
+      </c>
       <c r="H21">
         <v>0</v>
       </c>
@@ -1274,21 +1535,21 @@
         <v>2</v>
       </c>
       <c r="K21" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
       <c r="A22" t="s">
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1296,6 +1557,9 @@
       <c r="F22">
         <v>3</v>
       </c>
+      <c r="G22">
+        <v>6</v>
+      </c>
       <c r="H22">
         <v>0</v>
       </c>
@@ -1306,27 +1570,30 @@
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
       <c r="A23" t="s">
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C23">
-        <v>0.45200000000000001</v>
+        <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E23">
         <v>0</v>
       </c>
       <c r="F23">
-        <v>1</v>
+        <v>3</v>
+      </c>
+      <c r="G23">
+        <v>6</v>
       </c>
       <c r="H23">
         <v>0</v>
@@ -1335,30 +1602,33 @@
         <v>0</v>
       </c>
       <c r="J23">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K23" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>46</v>
+        <v>73</v>
       </c>
       <c r="C24">
-        <v>3</v>
+        <v>0.452</v>
       </c>
       <c r="D24" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E24">
         <v>0</v>
       </c>
       <c r="F24">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>2</v>
       </c>
       <c r="H24">
         <v>0</v>
@@ -1367,24 +1637,24 @@
         <v>0</v>
       </c>
       <c r="J24">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
       <c r="A25" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>47</v>
+        <v>74</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1392,6 +1662,9 @@
       <c r="F25">
         <v>3</v>
       </c>
+      <c r="G25">
+        <v>6</v>
+      </c>
       <c r="H25">
         <v>0</v>
       </c>
@@ -1402,21 +1675,21 @@
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
       <c r="A26" t="s">
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1424,6 +1697,9 @@
       <c r="F26">
         <v>3</v>
       </c>
+      <c r="G26">
+        <v>6</v>
+      </c>
       <c r="H26">
         <v>0</v>
       </c>
@@ -1434,21 +1710,21 @@
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
       <c r="A27" t="s">
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>48</v>
+        <v>76</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1456,6 +1732,9 @@
       <c r="F27">
         <v>3</v>
       </c>
+      <c r="G27">
+        <v>6</v>
+      </c>
       <c r="H27">
         <v>0</v>
       </c>
@@ -1466,21 +1745,21 @@
         <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
       <c r="A28" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>49</v>
+        <v>76</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1488,6 +1767,9 @@
       <c r="F28">
         <v>3</v>
       </c>
+      <c r="G28">
+        <v>6</v>
+      </c>
       <c r="H28">
         <v>0</v>
       </c>
@@ -1498,21 +1780,21 @@
         <v>2</v>
       </c>
       <c r="K28" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
       <c r="A29" t="s">
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1520,6 +1802,9 @@
       <c r="F29">
         <v>3</v>
       </c>
+      <c r="G29">
+        <v>6</v>
+      </c>
       <c r="H29">
         <v>0</v>
       </c>
@@ -1530,21 +1815,21 @@
         <v>2</v>
       </c>
       <c r="K29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
       <c r="A30" t="s">
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1552,6 +1837,9 @@
       <c r="F30">
         <v>3</v>
       </c>
+      <c r="G30">
+        <v>6</v>
+      </c>
       <c r="H30">
         <v>0</v>
       </c>
@@ -1562,60 +1850,66 @@
         <v>2</v>
       </c>
       <c r="K30" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
       <c r="A31" t="s">
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C31">
-        <v>8.4000000000000005E-2</v>
+        <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E31">
         <v>0</v>
       </c>
       <c r="F31">
+        <v>3</v>
+      </c>
+      <c r="G31">
+        <v>6</v>
+      </c>
+      <c r="H31">
+        <v>0</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>2</v>
+      </c>
+      <c r="K31" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>19</v>
+      </c>
+      <c r="B32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="D32" t="s">
+        <v>138</v>
+      </c>
+      <c r="E32">
+        <v>0</v>
+      </c>
+      <c r="F32">
         <v>1</v>
       </c>
-      <c r="H31">
-        <v>0</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
+      <c r="G32">
         <v>1</v>
       </c>
-      <c r="K31" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>20</v>
-      </c>
-      <c r="B32" t="s">
-        <v>53</v>
-      </c>
-      <c r="C32">
-        <v>3</v>
-      </c>
-      <c r="D32" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32">
-        <v>0</v>
-      </c>
-      <c r="F32">
-        <v>3</v>
-      </c>
       <c r="H32">
         <v>0</v>
       </c>
@@ -1623,24 +1917,24 @@
         <v>0</v>
       </c>
       <c r="J32">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
       <c r="A33" t="s">
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1648,6 +1942,9 @@
       <c r="F33">
         <v>3</v>
       </c>
+      <c r="G33">
+        <v>6</v>
+      </c>
       <c r="H33">
         <v>0</v>
       </c>
@@ -1658,21 +1955,21 @@
         <v>2</v>
       </c>
       <c r="K33" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
       <c r="A34" t="s">
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1680,6 +1977,9 @@
       <c r="F34">
         <v>3</v>
       </c>
+      <c r="G34">
+        <v>6</v>
+      </c>
       <c r="H34">
         <v>0</v>
       </c>
@@ -1690,21 +1990,21 @@
         <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
       <c r="A35" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -1712,6 +2012,9 @@
       <c r="F35">
         <v>3</v>
       </c>
+      <c r="G35">
+        <v>6</v>
+      </c>
       <c r="H35">
         <v>0</v>
       </c>
@@ -1722,21 +2025,21 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
       <c r="A36" t="s">
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -1744,6 +2047,9 @@
       <c r="F36">
         <v>3</v>
       </c>
+      <c r="G36">
+        <v>6</v>
+      </c>
       <c r="H36">
         <v>0</v>
       </c>
@@ -1754,85 +2060,91 @@
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
       <c r="A37" t="s">
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C37">
-        <v>0.45200000000000001</v>
+        <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E37">
         <v>0</v>
       </c>
       <c r="F37">
+        <v>3</v>
+      </c>
+      <c r="G37">
+        <v>6</v>
+      </c>
+      <c r="H37">
+        <v>0</v>
+      </c>
+      <c r="I37">
+        <v>0</v>
+      </c>
+      <c r="J37">
+        <v>2</v>
+      </c>
+      <c r="K37" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" t="s">
+        <v>21</v>
+      </c>
+      <c r="B38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C38">
+        <v>0.452</v>
+      </c>
+      <c r="D38" t="s">
+        <v>138</v>
+      </c>
+      <c r="E38">
+        <v>0</v>
+      </c>
+      <c r="F38">
         <v>1</v>
       </c>
-      <c r="H37">
-        <v>0</v>
-      </c>
-      <c r="I37">
-        <v>0</v>
-      </c>
-      <c r="J37">
+      <c r="G38">
         <v>1</v>
       </c>
-      <c r="K37" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>22</v>
-      </c>
-      <c r="B38" t="s">
-        <v>30</v>
-      </c>
-      <c r="C38">
-        <v>3</v>
-      </c>
-      <c r="D38" t="s">
-        <v>65</v>
-      </c>
-      <c r="E38">
-        <v>0</v>
-      </c>
-      <c r="F38">
-        <v>5</v>
-      </c>
       <c r="H38">
         <v>0</v>
       </c>
       <c r="I38">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J38">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11">
       <c r="A39" t="s">
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>31</v>
+        <v>58</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -1840,37 +2152,43 @@
       <c r="F39">
         <v>5</v>
       </c>
+      <c r="G39">
+        <v>0</v>
+      </c>
       <c r="H39">
         <v>0</v>
       </c>
       <c r="I39">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="J39">
         <v>3</v>
       </c>
       <c r="K39" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11">
       <c r="A40" t="s">
         <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>32</v>
+        <v>59</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E40">
         <v>0</v>
       </c>
       <c r="F40">
         <v>5</v>
+      </c>
+      <c r="G40">
+        <v>0</v>
       </c>
       <c r="H40">
         <v>0</v>
@@ -1882,21 +2200,21 @@
         <v>3</v>
       </c>
       <c r="K40" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
       <c r="A41" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>37</v>
+        <v>60</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -1904,31 +2222,34 @@
       <c r="F41">
         <v>5</v>
       </c>
+      <c r="G41">
+        <v>0</v>
+      </c>
       <c r="H41">
         <v>0</v>
       </c>
       <c r="I41">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="J41">
         <v>3</v>
       </c>
       <c r="K41" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11">
       <c r="A42" t="s">
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -1936,6 +2257,9 @@
       <c r="F42">
         <v>5</v>
       </c>
+      <c r="G42">
+        <v>0</v>
+      </c>
       <c r="H42">
         <v>0</v>
       </c>
@@ -1946,21 +2270,21 @@
         <v>3</v>
       </c>
       <c r="K42" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="43" spans="1:11">
       <c r="A43" t="s">
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>39</v>
+        <v>66</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -1968,28 +2292,34 @@
       <c r="F43">
         <v>5</v>
       </c>
+      <c r="G43">
+        <v>0</v>
+      </c>
       <c r="H43">
         <v>0</v>
       </c>
       <c r="I43">
         <v>6</v>
       </c>
+      <c r="J43">
+        <v>3</v>
+      </c>
       <c r="K43" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
       <c r="A44" t="s">
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>40</v>
+        <v>67</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -1997,31 +2327,31 @@
       <c r="F44">
         <v>5</v>
       </c>
+      <c r="G44">
+        <v>0</v>
+      </c>
       <c r="H44">
         <v>0</v>
       </c>
       <c r="I44">
         <v>6</v>
       </c>
-      <c r="J44">
-        <v>3</v>
-      </c>
       <c r="K44" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
       <c r="A45" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2029,6 +2359,9 @@
       <c r="F45">
         <v>5</v>
       </c>
+      <c r="G45">
+        <v>0</v>
+      </c>
       <c r="H45">
         <v>0</v>
       </c>
@@ -2039,21 +2372,21 @@
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="46" spans="1:11">
       <c r="A46" t="s">
         <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>42</v>
+        <v>69</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2061,6 +2394,9 @@
       <c r="F46">
         <v>5</v>
       </c>
+      <c r="G46">
+        <v>0</v>
+      </c>
       <c r="H46">
         <v>0</v>
       </c>
@@ -2071,21 +2407,21 @@
         <v>3</v>
       </c>
       <c r="K46" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="47" spans="1:11">
       <c r="A47" t="s">
         <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>43</v>
+        <v>70</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2093,6 +2429,9 @@
       <c r="F47">
         <v>5</v>
       </c>
+      <c r="G47">
+        <v>0</v>
+      </c>
       <c r="H47">
         <v>0</v>
       </c>
@@ -2103,21 +2442,21 @@
         <v>3</v>
       </c>
       <c r="K47" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="48" spans="1:11">
       <c r="A48" t="s">
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>44</v>
+        <v>71</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2125,6 +2464,9 @@
       <c r="F48">
         <v>5</v>
       </c>
+      <c r="G48">
+        <v>0</v>
+      </c>
       <c r="H48">
         <v>0</v>
       </c>
@@ -2135,85 +2477,91 @@
         <v>3</v>
       </c>
       <c r="K48" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="49" spans="1:11">
       <c r="A49" t="s">
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>45</v>
+        <v>72</v>
       </c>
       <c r="C49">
-        <v>0.84499999999999997</v>
+        <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E49">
         <v>0</v>
       </c>
       <c r="F49">
+        <v>5</v>
+      </c>
+      <c r="G49">
+        <v>0</v>
+      </c>
+      <c r="H49">
+        <v>0</v>
+      </c>
+      <c r="I49">
+        <v>6</v>
+      </c>
+      <c r="J49">
+        <v>3</v>
+      </c>
+      <c r="K49" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="50" spans="1:11">
+      <c r="A50" t="s">
+        <v>24</v>
+      </c>
+      <c r="B50" t="s">
+        <v>73</v>
+      </c>
+      <c r="C50">
+        <v>0.845</v>
+      </c>
+      <c r="D50" t="s">
+        <v>138</v>
+      </c>
+      <c r="E50">
+        <v>0</v>
+      </c>
+      <c r="F50">
         <v>1</v>
       </c>
-      <c r="H49">
-        <v>0</v>
-      </c>
-      <c r="I49">
-        <v>2</v>
-      </c>
-      <c r="J49">
+      <c r="G50">
+        <v>0</v>
+      </c>
+      <c r="H50">
+        <v>0</v>
+      </c>
+      <c r="I50">
+        <v>2</v>
+      </c>
+      <c r="J50">
         <v>1</v>
       </c>
-      <c r="K49" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>25</v>
-      </c>
-      <c r="B50" t="s">
-        <v>46</v>
-      </c>
-      <c r="C50">
-        <v>3</v>
-      </c>
-      <c r="D50" t="s">
-        <v>65</v>
-      </c>
-      <c r="E50">
-        <v>0</v>
-      </c>
-      <c r="F50">
-        <v>5</v>
-      </c>
-      <c r="H50">
-        <v>0</v>
-      </c>
-      <c r="I50">
-        <v>6</v>
-      </c>
-      <c r="J50">
-        <v>3</v>
-      </c>
       <c r="K50" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="51" spans="1:11">
       <c r="A51" t="s">
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>49</v>
+        <v>74</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2221,6 +2569,9 @@
       <c r="F51">
         <v>5</v>
       </c>
+      <c r="G51">
+        <v>0</v>
+      </c>
       <c r="H51">
         <v>0</v>
       </c>
@@ -2228,24 +2579,24 @@
         <v>6</v>
       </c>
       <c r="J51">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K51" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="52" spans="1:11">
       <c r="A52" t="s">
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>50</v>
+        <v>77</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2253,6 +2604,9 @@
       <c r="F52">
         <v>5</v>
       </c>
+      <c r="G52">
+        <v>0</v>
+      </c>
       <c r="H52">
         <v>0</v>
       </c>
@@ -2263,21 +2617,21 @@
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="53" spans="1:11">
       <c r="A53" t="s">
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2285,6 +2639,9 @@
       <c r="F53">
         <v>5</v>
       </c>
+      <c r="G53">
+        <v>0</v>
+      </c>
       <c r="H53">
         <v>0</v>
       </c>
@@ -2295,85 +2652,91 @@
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="54" spans="1:11">
       <c r="A54" t="s">
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="C54">
-        <v>8.4000000000000005E-2</v>
+        <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E54">
         <v>0</v>
       </c>
       <c r="F54">
-        <v>1</v>
+        <v>5</v>
+      </c>
+      <c r="G54">
+        <v>0</v>
       </c>
       <c r="H54">
         <v>0</v>
       </c>
       <c r="I54">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J54">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="55" spans="1:11">
       <c r="A55" t="s">
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>59</v>
+        <v>80</v>
       </c>
       <c r="C55">
-        <v>3</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="D55" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E55">
         <v>0</v>
       </c>
       <c r="F55">
-        <v>3</v>
+        <v>1</v>
+      </c>
+      <c r="G55">
+        <v>0</v>
       </c>
       <c r="H55">
         <v>0</v>
       </c>
       <c r="I55">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J55">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:11">
       <c r="A56" t="s">
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>60</v>
+        <v>87</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2381,6 +2744,9 @@
       <c r="F56">
         <v>3</v>
       </c>
+      <c r="G56">
+        <v>6</v>
+      </c>
       <c r="H56">
         <v>0</v>
       </c>
@@ -2391,21 +2757,21 @@
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="57" spans="1:11">
       <c r="A57" t="s">
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>61</v>
+        <v>88</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2413,6 +2779,9 @@
       <c r="F57">
         <v>3</v>
       </c>
+      <c r="G57">
+        <v>6</v>
+      </c>
       <c r="H57">
         <v>0</v>
       </c>
@@ -2423,21 +2792,21 @@
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="58" spans="1:11">
       <c r="A58" t="s">
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>62</v>
+        <v>89</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2445,6 +2814,9 @@
       <c r="F58">
         <v>3</v>
       </c>
+      <c r="G58">
+        <v>6</v>
+      </c>
       <c r="H58">
         <v>0</v>
       </c>
@@ -2455,59 +2827,65 @@
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="59" spans="1:11">
       <c r="A59" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>33</v>
+        <v>90</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E59">
         <v>0</v>
       </c>
       <c r="F59">
-        <v>5</v>
+        <v>3</v>
+      </c>
+      <c r="G59">
+        <v>6</v>
       </c>
       <c r="H59">
         <v>0</v>
       </c>
       <c r="I59">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J59">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="60" spans="1:11">
       <c r="A60" t="s">
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>34</v>
+        <v>62</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E60">
         <v>0</v>
       </c>
       <c r="F60">
         <v>5</v>
+      </c>
+      <c r="G60">
+        <v>0</v>
       </c>
       <c r="H60">
         <v>0</v>
@@ -2519,27 +2897,30 @@
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="61" spans="1:11">
       <c r="A61" t="s">
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>35</v>
+        <v>63</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E61">
         <v>0</v>
       </c>
       <c r="F61">
         <v>5</v>
+      </c>
+      <c r="G61">
+        <v>0</v>
       </c>
       <c r="H61">
         <v>0</v>
@@ -2551,85 +2932,91 @@
         <v>3</v>
       </c>
       <c r="K61" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="62" spans="1:11">
       <c r="A62" t="s">
         <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>36</v>
+        <v>64</v>
       </c>
       <c r="C62">
-        <v>4.6340000000000003</v>
+        <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E62">
         <v>0</v>
       </c>
       <c r="F62">
+        <v>5</v>
+      </c>
+      <c r="G62">
+        <v>0</v>
+      </c>
+      <c r="H62">
+        <v>0</v>
+      </c>
+      <c r="I62">
+        <v>9</v>
+      </c>
+      <c r="J62">
+        <v>3</v>
+      </c>
+      <c r="K62" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="63" spans="1:11">
+      <c r="A63" t="s">
+        <v>26</v>
+      </c>
+      <c r="B63" t="s">
+        <v>61</v>
+      </c>
+      <c r="C63">
+        <v>4.634</v>
+      </c>
+      <c r="D63" t="s">
+        <v>138</v>
+      </c>
+      <c r="E63">
+        <v>0</v>
+      </c>
+      <c r="F63">
         <v>7</v>
       </c>
-      <c r="H62">
-        <v>0</v>
-      </c>
-      <c r="I62">
+      <c r="G63">
+        <v>0</v>
+      </c>
+      <c r="H63">
+        <v>0</v>
+      </c>
+      <c r="I63">
         <v>14</v>
       </c>
-      <c r="J62">
+      <c r="J63">
         <v>4</v>
       </c>
-      <c r="K62" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>27</v>
-      </c>
-      <c r="B63" t="s">
-        <v>47</v>
-      </c>
-      <c r="C63">
-        <v>3</v>
-      </c>
-      <c r="D63" t="s">
-        <v>65</v>
-      </c>
-      <c r="E63">
-        <v>0</v>
-      </c>
-      <c r="F63">
-        <v>5</v>
-      </c>
-      <c r="H63">
-        <v>0</v>
-      </c>
-      <c r="I63">
-        <v>6</v>
-      </c>
-      <c r="J63">
-        <v>2</v>
-      </c>
       <c r="K63" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="64" spans="1:11">
       <c r="A64" t="s">
         <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>48</v>
+        <v>75</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -2637,6 +3024,9 @@
       <c r="F64">
         <v>5</v>
       </c>
+      <c r="G64">
+        <v>0</v>
+      </c>
       <c r="H64">
         <v>0</v>
       </c>
@@ -2644,24 +3034,24 @@
         <v>6</v>
       </c>
       <c r="J64">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K64" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="65" spans="1:11">
       <c r="A65" t="s">
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>63</v>
+        <v>76</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -2669,6 +3059,9 @@
       <c r="F65">
         <v>5</v>
       </c>
+      <c r="G65">
+        <v>0</v>
+      </c>
       <c r="H65">
         <v>0</v>
       </c>
@@ -2676,24 +3069,24 @@
         <v>6</v>
       </c>
       <c r="J65">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11">
       <c r="A66" t="s">
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>53</v>
+        <v>91</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -2701,6 +3094,9 @@
       <c r="F66">
         <v>5</v>
       </c>
+      <c r="G66">
+        <v>0</v>
+      </c>
       <c r="H66">
         <v>0</v>
       </c>
@@ -2711,21 +3107,21 @@
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11">
       <c r="A67" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>54</v>
+        <v>81</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -2733,6 +3129,9 @@
       <c r="F67">
         <v>5</v>
       </c>
+      <c r="G67">
+        <v>0</v>
+      </c>
       <c r="H67">
         <v>0</v>
       </c>
@@ -2743,21 +3142,21 @@
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11">
       <c r="A68" t="s">
         <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>55</v>
+        <v>82</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -2765,6 +3164,9 @@
       <c r="F68">
         <v>5</v>
       </c>
+      <c r="G68">
+        <v>0</v>
+      </c>
       <c r="H68">
         <v>0</v>
       </c>
@@ -2775,21 +3177,21 @@
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11">
       <c r="A69" t="s">
         <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>56</v>
+        <v>83</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -2797,6 +3199,9 @@
       <c r="F69">
         <v>5</v>
       </c>
+      <c r="G69">
+        <v>0</v>
+      </c>
       <c r="H69">
         <v>0</v>
       </c>
@@ -2807,21 +3212,21 @@
         <v>2</v>
       </c>
       <c r="K69" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11">
       <c r="A70" t="s">
         <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>84</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -2829,6 +3234,9 @@
       <c r="F70">
         <v>5</v>
       </c>
+      <c r="G70">
+        <v>0</v>
+      </c>
       <c r="H70">
         <v>0</v>
       </c>
@@ -2839,74 +3247,4312 @@
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="71" spans="1:11">
       <c r="A71" t="s">
         <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>58</v>
+        <v>85</v>
       </c>
       <c r="C71">
-        <v>8.4000000000000005E-2</v>
+        <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>65</v>
+        <v>138</v>
       </c>
       <c r="E71">
         <v>0</v>
       </c>
       <c r="F71">
+        <v>5</v>
+      </c>
+      <c r="G71">
+        <v>0</v>
+      </c>
+      <c r="H71">
+        <v>0</v>
+      </c>
+      <c r="I71">
+        <v>6</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="K71" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="72" spans="1:11">
+      <c r="A72" t="s">
+        <v>28</v>
+      </c>
+      <c r="B72" t="s">
+        <v>86</v>
+      </c>
+      <c r="C72">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="D72" t="s">
+        <v>138</v>
+      </c>
+      <c r="E72">
+        <v>0</v>
+      </c>
+      <c r="F72">
         <v>1</v>
       </c>
-      <c r="H71">
-        <v>0</v>
-      </c>
-      <c r="I71">
-        <v>1</v>
-      </c>
-      <c r="J71">
-        <v>1</v>
-      </c>
-      <c r="K71" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A72" t="s">
-        <v>29</v>
-      </c>
-      <c r="B72" t="s">
-        <v>36</v>
-      </c>
-      <c r="C72" t="s">
-        <v>64</v>
-      </c>
-      <c r="D72" t="s">
-        <v>66</v>
-      </c>
-      <c r="E72">
-        <v>13</v>
-      </c>
-      <c r="F72">
-        <v>9</v>
-      </c>
       <c r="G72">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I72">
         <v>1</v>
       </c>
       <c r="J72">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="K72" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="73" spans="1:11">
+      <c r="A73" t="s">
+        <v>28</v>
+      </c>
+      <c r="B73" t="s">
+        <v>92</v>
+      </c>
+      <c r="C73">
+        <v>3</v>
+      </c>
+      <c r="D73" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73">
+        <v>0</v>
+      </c>
+      <c r="F73">
+        <v>3</v>
+      </c>
+      <c r="G73">
+        <v>6</v>
+      </c>
+      <c r="H73">
+        <v>0</v>
+      </c>
+      <c r="I73">
+        <v>0</v>
+      </c>
+      <c r="J73">
+        <v>2</v>
+      </c>
+      <c r="K73" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="74" spans="1:11">
+      <c r="A74" t="s">
+        <v>28</v>
+      </c>
+      <c r="B74" t="s">
+        <v>93</v>
+      </c>
+      <c r="C74">
+        <v>3</v>
+      </c>
+      <c r="D74" t="s">
+        <v>138</v>
+      </c>
+      <c r="E74">
+        <v>0</v>
+      </c>
+      <c r="F74">
+        <v>3</v>
+      </c>
+      <c r="G74">
+        <v>6</v>
+      </c>
+      <c r="H74">
+        <v>0</v>
+      </c>
+      <c r="I74">
+        <v>0</v>
+      </c>
+      <c r="J74">
+        <v>2</v>
+      </c>
+      <c r="K74" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="75" spans="1:11">
+      <c r="A75" t="s">
+        <v>28</v>
+      </c>
+      <c r="B75" t="s">
+        <v>94</v>
+      </c>
+      <c r="C75">
+        <v>3</v>
+      </c>
+      <c r="D75" t="s">
+        <v>138</v>
+      </c>
+      <c r="E75">
+        <v>0</v>
+      </c>
+      <c r="F75">
+        <v>3</v>
+      </c>
+      <c r="G75">
+        <v>6</v>
+      </c>
+      <c r="H75">
+        <v>0</v>
+      </c>
+      <c r="I75">
+        <v>0</v>
+      </c>
+      <c r="J75">
+        <v>2</v>
+      </c>
+      <c r="K75" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="76" spans="1:11">
+      <c r="A76" t="s">
+        <v>29</v>
+      </c>
+      <c r="B76" t="s">
+        <v>75</v>
+      </c>
+      <c r="C76">
+        <v>3</v>
+      </c>
+      <c r="D76" t="s">
+        <v>138</v>
+      </c>
+      <c r="E76">
+        <v>0</v>
+      </c>
+      <c r="F76">
+        <v>5</v>
+      </c>
+      <c r="G76">
+        <v>0</v>
+      </c>
+      <c r="H76">
+        <v>0</v>
+      </c>
+      <c r="I76">
+        <v>9</v>
+      </c>
+      <c r="J76">
+        <v>3</v>
+      </c>
+      <c r="K76" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="77" spans="1:11">
+      <c r="A77" t="s">
+        <v>29</v>
+      </c>
+      <c r="B77" t="s">
+        <v>76</v>
+      </c>
+      <c r="C77">
+        <v>3</v>
+      </c>
+      <c r="D77" t="s">
+        <v>138</v>
+      </c>
+      <c r="E77">
+        <v>0</v>
+      </c>
+      <c r="F77">
+        <v>5</v>
+      </c>
+      <c r="G77">
+        <v>0</v>
+      </c>
+      <c r="H77">
+        <v>0</v>
+      </c>
+      <c r="I77">
+        <v>9</v>
+      </c>
+      <c r="J77">
+        <v>3</v>
+      </c>
+      <c r="K77" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="78" spans="1:11">
+      <c r="A78" t="s">
+        <v>29</v>
+      </c>
+      <c r="B78" t="s">
+        <v>91</v>
+      </c>
+      <c r="C78">
+        <v>3</v>
+      </c>
+      <c r="D78" t="s">
+        <v>138</v>
+      </c>
+      <c r="E78">
+        <v>0</v>
+      </c>
+      <c r="F78">
+        <v>5</v>
+      </c>
+      <c r="G78">
+        <v>0</v>
+      </c>
+      <c r="H78">
+        <v>0</v>
+      </c>
+      <c r="I78">
+        <v>9</v>
+      </c>
+      <c r="J78">
+        <v>3</v>
+      </c>
+      <c r="K78" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="79" spans="1:11">
+      <c r="A79" t="s">
+        <v>29</v>
+      </c>
+      <c r="B79" t="s">
+        <v>81</v>
+      </c>
+      <c r="C79">
+        <v>3</v>
+      </c>
+      <c r="D79" t="s">
+        <v>138</v>
+      </c>
+      <c r="E79">
+        <v>0</v>
+      </c>
+      <c r="F79">
+        <v>5</v>
+      </c>
+      <c r="G79">
+        <v>0</v>
+      </c>
+      <c r="H79">
+        <v>0</v>
+      </c>
+      <c r="I79">
+        <v>9</v>
+      </c>
+      <c r="J79">
+        <v>3</v>
+      </c>
+      <c r="K79" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="80" spans="1:11">
+      <c r="A80" t="s">
+        <v>30</v>
+      </c>
+      <c r="B80" t="s">
+        <v>95</v>
+      </c>
+      <c r="C80">
+        <v>3</v>
+      </c>
+      <c r="D80" t="s">
+        <v>139</v>
+      </c>
+      <c r="E80">
+        <v>0</v>
+      </c>
+      <c r="F80">
+        <v>3</v>
+      </c>
+      <c r="G80">
+        <v>6</v>
+      </c>
+      <c r="H80">
+        <v>0</v>
+      </c>
+      <c r="I80">
+        <v>0</v>
+      </c>
+      <c r="J80">
+        <v>2</v>
+      </c>
+      <c r="K80" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="81" spans="1:11">
+      <c r="A81" t="s">
+        <v>30</v>
+      </c>
+      <c r="B81" t="s">
+        <v>96</v>
+      </c>
+      <c r="C81">
+        <v>3</v>
+      </c>
+      <c r="D81" t="s">
+        <v>139</v>
+      </c>
+      <c r="E81">
+        <v>0</v>
+      </c>
+      <c r="F81">
+        <v>3</v>
+      </c>
+      <c r="G81">
+        <v>6</v>
+      </c>
+      <c r="H81">
+        <v>0</v>
+      </c>
+      <c r="I81">
+        <v>0</v>
+      </c>
+      <c r="J81">
+        <v>2</v>
+      </c>
+      <c r="K81" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="82" spans="1:11">
+      <c r="A82" t="s">
+        <v>30</v>
+      </c>
+      <c r="B82" t="s">
+        <v>97</v>
+      </c>
+      <c r="C82">
+        <v>3</v>
+      </c>
+      <c r="D82" t="s">
+        <v>139</v>
+      </c>
+      <c r="E82">
+        <v>0</v>
+      </c>
+      <c r="F82">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>6</v>
+      </c>
+      <c r="H82">
+        <v>0</v>
+      </c>
+      <c r="I82">
+        <v>6</v>
+      </c>
+      <c r="J82">
+        <v>2</v>
+      </c>
+      <c r="K82" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="83" spans="1:11">
+      <c r="A83" t="s">
+        <v>30</v>
+      </c>
+      <c r="B83" t="s">
+        <v>87</v>
+      </c>
+      <c r="C83">
+        <v>3</v>
+      </c>
+      <c r="D83" t="s">
+        <v>138</v>
+      </c>
+      <c r="E83">
+        <v>0</v>
+      </c>
+      <c r="F83">
+        <v>5</v>
+      </c>
+      <c r="G83">
+        <v>0</v>
+      </c>
+      <c r="H83">
+        <v>0</v>
+      </c>
+      <c r="I83">
+        <v>6</v>
+      </c>
+      <c r="J83">
+        <v>3</v>
+      </c>
+      <c r="K83" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="84" spans="1:11">
+      <c r="A84" t="s">
+        <v>30</v>
+      </c>
+      <c r="B84" t="s">
+        <v>88</v>
+      </c>
+      <c r="C84">
+        <v>3</v>
+      </c>
+      <c r="D84" t="s">
+        <v>138</v>
+      </c>
+      <c r="E84">
+        <v>0</v>
+      </c>
+      <c r="F84">
+        <v>5</v>
+      </c>
+      <c r="G84">
+        <v>0</v>
+      </c>
+      <c r="H84">
+        <v>0</v>
+      </c>
+      <c r="I84">
+        <v>6</v>
+      </c>
+      <c r="J84">
+        <v>3</v>
+      </c>
+      <c r="K84" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11">
+      <c r="A85" t="s">
+        <v>30</v>
+      </c>
+      <c r="B85" t="s">
+        <v>89</v>
+      </c>
+      <c r="C85">
+        <v>3</v>
+      </c>
+      <c r="D85" t="s">
+        <v>138</v>
+      </c>
+      <c r="E85">
+        <v>0</v>
+      </c>
+      <c r="F85">
+        <v>5</v>
+      </c>
+      <c r="G85">
+        <v>0</v>
+      </c>
+      <c r="H85">
+        <v>0</v>
+      </c>
+      <c r="I85">
+        <v>6</v>
+      </c>
+      <c r="J85">
+        <v>3</v>
+      </c>
+      <c r="K85" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11">
+      <c r="A86" t="s">
+        <v>31</v>
+      </c>
+      <c r="B86" t="s">
+        <v>82</v>
+      </c>
+      <c r="C86">
+        <v>3</v>
+      </c>
+      <c r="D86" t="s">
+        <v>138</v>
+      </c>
+      <c r="E86">
+        <v>0</v>
+      </c>
+      <c r="F86">
+        <v>5</v>
+      </c>
+      <c r="G86">
+        <v>0</v>
+      </c>
+      <c r="H86">
+        <v>0</v>
+      </c>
+      <c r="I86">
+        <v>9</v>
+      </c>
+      <c r="J86">
+        <v>3</v>
+      </c>
+      <c r="K86" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11">
+      <c r="A87" t="s">
+        <v>31</v>
+      </c>
+      <c r="B87" t="s">
+        <v>83</v>
+      </c>
+      <c r="C87">
+        <v>3</v>
+      </c>
+      <c r="D87" t="s">
+        <v>138</v>
+      </c>
+      <c r="E87">
+        <v>0</v>
+      </c>
+      <c r="F87">
+        <v>5</v>
+      </c>
+      <c r="G87">
+        <v>0</v>
+      </c>
+      <c r="H87">
+        <v>0</v>
+      </c>
+      <c r="I87">
+        <v>9</v>
+      </c>
+      <c r="J87">
+        <v>3</v>
+      </c>
+      <c r="K87" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11">
+      <c r="A88" t="s">
+        <v>31</v>
+      </c>
+      <c r="B88" t="s">
+        <v>84</v>
+      </c>
+      <c r="C88">
+        <v>3</v>
+      </c>
+      <c r="D88" t="s">
+        <v>138</v>
+      </c>
+      <c r="E88">
+        <v>0</v>
+      </c>
+      <c r="F88">
+        <v>5</v>
+      </c>
+      <c r="G88">
+        <v>0</v>
+      </c>
+      <c r="H88">
+        <v>0</v>
+      </c>
+      <c r="I88">
+        <v>9</v>
+      </c>
+      <c r="J88">
+        <v>3</v>
+      </c>
+      <c r="K88" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11">
+      <c r="A89" t="s">
+        <v>31</v>
+      </c>
+      <c r="B89" t="s">
+        <v>85</v>
+      </c>
+      <c r="C89">
+        <v>3</v>
+      </c>
+      <c r="D89" t="s">
+        <v>138</v>
+      </c>
+      <c r="E89">
+        <v>0</v>
+      </c>
+      <c r="F89">
+        <v>5</v>
+      </c>
+      <c r="G89">
+        <v>0</v>
+      </c>
+      <c r="H89">
+        <v>0</v>
+      </c>
+      <c r="I89">
+        <v>9</v>
+      </c>
+      <c r="J89">
+        <v>3</v>
+      </c>
+      <c r="K89" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11">
+      <c r="A90" t="s">
+        <v>31</v>
+      </c>
+      <c r="B90" t="s">
+        <v>86</v>
+      </c>
+      <c r="C90">
+        <v>0.421</v>
+      </c>
+      <c r="D90" t="s">
+        <v>138</v>
+      </c>
+      <c r="E90">
+        <v>0</v>
+      </c>
+      <c r="F90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>0</v>
+      </c>
+      <c r="H90">
+        <v>0</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="K90" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11">
+      <c r="A91" t="s">
+        <v>30</v>
+      </c>
+      <c r="B91" t="s">
+        <v>74</v>
+      </c>
+      <c r="C91">
+        <v>3</v>
+      </c>
+      <c r="D91" t="s">
+        <v>138</v>
+      </c>
+      <c r="E91">
+        <v>0</v>
+      </c>
+      <c r="F91">
+        <v>5</v>
+      </c>
+      <c r="G91">
+        <v>0</v>
+      </c>
+      <c r="H91">
+        <v>0</v>
+      </c>
+      <c r="I91">
+        <v>9</v>
+      </c>
+      <c r="J91">
+        <v>3</v>
+      </c>
+      <c r="K91" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11">
+      <c r="A92" t="s">
+        <v>30</v>
+      </c>
+      <c r="B92" t="s">
+        <v>77</v>
+      </c>
+      <c r="C92">
+        <v>3</v>
+      </c>
+      <c r="D92" t="s">
+        <v>138</v>
+      </c>
+      <c r="E92">
+        <v>0</v>
+      </c>
+      <c r="F92">
+        <v>5</v>
+      </c>
+      <c r="G92">
+        <v>0</v>
+      </c>
+      <c r="H92">
+        <v>0</v>
+      </c>
+      <c r="I92">
+        <v>9</v>
+      </c>
+      <c r="J92">
+        <v>3</v>
+      </c>
+      <c r="K92" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11">
+      <c r="A93" t="s">
+        <v>32</v>
+      </c>
+      <c r="B93" t="s">
+        <v>78</v>
+      </c>
+      <c r="C93">
+        <v>3</v>
+      </c>
+      <c r="D93" t="s">
+        <v>138</v>
+      </c>
+      <c r="E93">
+        <v>0</v>
+      </c>
+      <c r="F93">
+        <v>5</v>
+      </c>
+      <c r="G93">
+        <v>0</v>
+      </c>
+      <c r="H93">
+        <v>0</v>
+      </c>
+      <c r="I93">
+        <v>9</v>
+      </c>
+      <c r="J93">
+        <v>3</v>
+      </c>
+      <c r="K93" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11">
+      <c r="A94" t="s">
+        <v>30</v>
+      </c>
+      <c r="B94" t="s">
+        <v>79</v>
+      </c>
+      <c r="C94">
+        <v>3</v>
+      </c>
+      <c r="D94" t="s">
+        <v>138</v>
+      </c>
+      <c r="E94">
+        <v>0</v>
+      </c>
+      <c r="F94">
+        <v>5</v>
+      </c>
+      <c r="G94">
+        <v>0</v>
+      </c>
+      <c r="H94">
+        <v>0</v>
+      </c>
+      <c r="I94">
+        <v>9</v>
+      </c>
+      <c r="J94">
+        <v>3</v>
+      </c>
+      <c r="K94" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11">
+      <c r="A95" t="s">
+        <v>30</v>
+      </c>
+      <c r="B95" t="s">
+        <v>80</v>
+      </c>
+      <c r="C95">
+        <v>0.08400000000000001</v>
+      </c>
+      <c r="D95" t="s">
+        <v>138</v>
+      </c>
+      <c r="E95">
+        <v>0</v>
+      </c>
+      <c r="F95">
+        <v>1</v>
+      </c>
+      <c r="G95">
+        <v>0</v>
+      </c>
+      <c r="H95">
+        <v>0</v>
+      </c>
+      <c r="I95">
+        <v>2</v>
+      </c>
+      <c r="J95">
+        <v>1</v>
+      </c>
+      <c r="K95" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11">
+      <c r="A96" t="s">
+        <v>33</v>
+      </c>
+      <c r="B96" t="s">
+        <v>90</v>
+      </c>
+      <c r="C96">
+        <v>3</v>
+      </c>
+      <c r="D96" t="s">
+        <v>138</v>
+      </c>
+      <c r="E96">
+        <v>0</v>
+      </c>
+      <c r="F96">
+        <v>5</v>
+      </c>
+      <c r="G96">
+        <v>0</v>
+      </c>
+      <c r="H96">
+        <v>0</v>
+      </c>
+      <c r="I96">
+        <v>6</v>
+      </c>
+      <c r="J96">
+        <v>3</v>
+      </c>
+      <c r="K96" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11">
+      <c r="A97" t="s">
+        <v>33</v>
+      </c>
+      <c r="B97" t="s">
+        <v>92</v>
+      </c>
+      <c r="C97">
+        <v>3</v>
+      </c>
+      <c r="D97" t="s">
+        <v>138</v>
+      </c>
+      <c r="E97">
+        <v>0</v>
+      </c>
+      <c r="F97">
+        <v>5</v>
+      </c>
+      <c r="G97">
+        <v>0</v>
+      </c>
+      <c r="H97">
+        <v>0</v>
+      </c>
+      <c r="I97">
+        <v>6</v>
+      </c>
+      <c r="J97">
+        <v>3</v>
+      </c>
+      <c r="K97" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11">
+      <c r="A98" t="s">
+        <v>33</v>
+      </c>
+      <c r="B98" t="s">
+        <v>93</v>
+      </c>
+      <c r="C98">
+        <v>3</v>
+      </c>
+      <c r="D98" t="s">
+        <v>138</v>
+      </c>
+      <c r="E98">
+        <v>0</v>
+      </c>
+      <c r="F98">
+        <v>5</v>
+      </c>
+      <c r="G98">
+        <v>0</v>
+      </c>
+      <c r="H98">
+        <v>0</v>
+      </c>
+      <c r="I98">
+        <v>6</v>
+      </c>
+      <c r="J98">
+        <v>3</v>
+      </c>
+      <c r="K98" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11">
+      <c r="A99" t="s">
+        <v>33</v>
+      </c>
+      <c r="B99" t="s">
+        <v>94</v>
+      </c>
+      <c r="C99">
+        <v>3</v>
+      </c>
+      <c r="D99" t="s">
+        <v>138</v>
+      </c>
+      <c r="E99">
+        <v>0</v>
+      </c>
+      <c r="F99">
+        <v>5</v>
+      </c>
+      <c r="G99">
+        <v>0</v>
+      </c>
+      <c r="H99">
+        <v>0</v>
+      </c>
+      <c r="I99">
+        <v>6</v>
+      </c>
+      <c r="J99">
+        <v>3</v>
+      </c>
+      <c r="K99" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11">
+      <c r="A100" t="s">
+        <v>34</v>
+      </c>
+      <c r="B100" t="s">
+        <v>65</v>
+      </c>
+      <c r="C100">
+        <v>3</v>
+      </c>
+      <c r="D100" t="s">
+        <v>138</v>
+      </c>
+      <c r="E100">
+        <v>0</v>
+      </c>
+      <c r="F100">
+        <v>5</v>
+      </c>
+      <c r="G100">
+        <v>0</v>
+      </c>
+      <c r="H100">
+        <v>0</v>
+      </c>
+      <c r="I100">
+        <v>9</v>
+      </c>
+      <c r="J100">
+        <v>3</v>
+      </c>
+      <c r="K100" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11">
+      <c r="A101" t="s">
+        <v>34</v>
+      </c>
+      <c r="B101" t="s">
+        <v>66</v>
+      </c>
+      <c r="C101">
+        <v>3</v>
+      </c>
+      <c r="D101" t="s">
+        <v>138</v>
+      </c>
+      <c r="E101">
+        <v>0</v>
+      </c>
+      <c r="F101">
+        <v>5</v>
+      </c>
+      <c r="G101">
+        <v>0</v>
+      </c>
+      <c r="H101">
+        <v>0</v>
+      </c>
+      <c r="I101">
+        <v>9</v>
+      </c>
+      <c r="J101">
+        <v>3</v>
+      </c>
+      <c r="K101" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11">
+      <c r="A102" t="s">
+        <v>34</v>
+      </c>
+      <c r="B102" t="s">
+        <v>67</v>
+      </c>
+      <c r="C102">
+        <v>3</v>
+      </c>
+      <c r="D102" t="s">
+        <v>138</v>
+      </c>
+      <c r="E102">
+        <v>0</v>
+      </c>
+      <c r="F102">
+        <v>5</v>
+      </c>
+      <c r="G102">
+        <v>0</v>
+      </c>
+      <c r="H102">
+        <v>0</v>
+      </c>
+      <c r="I102">
+        <v>9</v>
+      </c>
+      <c r="J102">
+        <v>3</v>
+      </c>
+      <c r="K102" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11">
+      <c r="A103" t="s">
+        <v>34</v>
+      </c>
+      <c r="B103" t="s">
         <v>68</v>
+      </c>
+      <c r="C103">
+        <v>3</v>
+      </c>
+      <c r="D103" t="s">
+        <v>138</v>
+      </c>
+      <c r="E103">
+        <v>0</v>
+      </c>
+      <c r="F103">
+        <v>5</v>
+      </c>
+      <c r="G103">
+        <v>0</v>
+      </c>
+      <c r="H103">
+        <v>0</v>
+      </c>
+      <c r="I103">
+        <v>9</v>
+      </c>
+      <c r="J103">
+        <v>3</v>
+      </c>
+      <c r="K103" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11">
+      <c r="A104" t="s">
+        <v>35</v>
+      </c>
+      <c r="B104" t="s">
+        <v>98</v>
+      </c>
+      <c r="C104">
+        <v>3</v>
+      </c>
+      <c r="D104" t="s">
+        <v>140</v>
+      </c>
+      <c r="E104">
+        <v>0</v>
+      </c>
+      <c r="F104">
+        <v>3</v>
+      </c>
+      <c r="G104">
+        <v>6</v>
+      </c>
+      <c r="H104">
+        <v>0</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>2</v>
+      </c>
+      <c r="K104" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11">
+      <c r="A105" t="s">
+        <v>35</v>
+      </c>
+      <c r="B105" t="s">
+        <v>99</v>
+      </c>
+      <c r="C105">
+        <v>3</v>
+      </c>
+      <c r="D105" t="s">
+        <v>140</v>
+      </c>
+      <c r="E105">
+        <v>0</v>
+      </c>
+      <c r="F105">
+        <v>3</v>
+      </c>
+      <c r="G105">
+        <v>6</v>
+      </c>
+      <c r="H105">
+        <v>0</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>2</v>
+      </c>
+      <c r="K105" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11">
+      <c r="A106" t="s">
+        <v>35</v>
+      </c>
+      <c r="B106" t="s">
+        <v>100</v>
+      </c>
+      <c r="C106">
+        <v>3</v>
+      </c>
+      <c r="D106" t="s">
+        <v>140</v>
+      </c>
+      <c r="E106">
+        <v>0</v>
+      </c>
+      <c r="F106">
+        <v>3</v>
+      </c>
+      <c r="G106">
+        <v>6</v>
+      </c>
+      <c r="H106">
+        <v>0</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>2</v>
+      </c>
+      <c r="K106" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11">
+      <c r="A107" t="s">
+        <v>35</v>
+      </c>
+      <c r="B107" t="s">
+        <v>101</v>
+      </c>
+      <c r="C107">
+        <v>3</v>
+      </c>
+      <c r="D107" t="s">
+        <v>139</v>
+      </c>
+      <c r="E107">
+        <v>0</v>
+      </c>
+      <c r="F107">
+        <v>3</v>
+      </c>
+      <c r="G107">
+        <v>6</v>
+      </c>
+      <c r="H107">
+        <v>0</v>
+      </c>
+      <c r="I107">
+        <v>0</v>
+      </c>
+      <c r="J107">
+        <v>2</v>
+      </c>
+      <c r="K107" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11">
+      <c r="A108" t="s">
+        <v>35</v>
+      </c>
+      <c r="B108" t="s">
+        <v>102</v>
+      </c>
+      <c r="C108">
+        <v>3</v>
+      </c>
+      <c r="D108" t="s">
+        <v>139</v>
+      </c>
+      <c r="E108">
+        <v>0</v>
+      </c>
+      <c r="F108">
+        <v>3</v>
+      </c>
+      <c r="G108">
+        <v>6</v>
+      </c>
+      <c r="H108">
+        <v>0</v>
+      </c>
+      <c r="I108">
+        <v>0</v>
+      </c>
+      <c r="J108">
+        <v>2</v>
+      </c>
+      <c r="K108" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11">
+      <c r="A109" t="s">
+        <v>35</v>
+      </c>
+      <c r="B109" t="s">
+        <v>103</v>
+      </c>
+      <c r="C109">
+        <v>3</v>
+      </c>
+      <c r="D109" t="s">
+        <v>139</v>
+      </c>
+      <c r="E109">
+        <v>0</v>
+      </c>
+      <c r="F109">
+        <v>3</v>
+      </c>
+      <c r="G109">
+        <v>6</v>
+      </c>
+      <c r="H109">
+        <v>0</v>
+      </c>
+      <c r="I109">
+        <v>0</v>
+      </c>
+      <c r="J109">
+        <v>2</v>
+      </c>
+      <c r="K109" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11">
+      <c r="A110" t="s">
+        <v>36</v>
+      </c>
+      <c r="B110" t="s">
+        <v>104</v>
+      </c>
+      <c r="C110">
+        <v>3</v>
+      </c>
+      <c r="D110" t="s">
+        <v>141</v>
+      </c>
+      <c r="E110">
+        <v>0</v>
+      </c>
+      <c r="F110">
+        <v>3</v>
+      </c>
+      <c r="G110">
+        <v>6</v>
+      </c>
+      <c r="H110">
+        <v>0</v>
+      </c>
+      <c r="I110">
+        <v>0</v>
+      </c>
+      <c r="J110">
+        <v>2</v>
+      </c>
+      <c r="K110" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11">
+      <c r="A111" t="s">
+        <v>36</v>
+      </c>
+      <c r="B111" t="s">
+        <v>105</v>
+      </c>
+      <c r="C111">
+        <v>3</v>
+      </c>
+      <c r="D111" t="s">
+        <v>141</v>
+      </c>
+      <c r="E111">
+        <v>0</v>
+      </c>
+      <c r="F111">
+        <v>3</v>
+      </c>
+      <c r="G111">
+        <v>6</v>
+      </c>
+      <c r="H111">
+        <v>0</v>
+      </c>
+      <c r="I111">
+        <v>0</v>
+      </c>
+      <c r="J111">
+        <v>2</v>
+      </c>
+      <c r="K111" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11">
+      <c r="A112" t="s">
+        <v>37</v>
+      </c>
+      <c r="B112" t="s">
+        <v>104</v>
+      </c>
+      <c r="C112">
+        <v>3</v>
+      </c>
+      <c r="D112" t="s">
+        <v>141</v>
+      </c>
+      <c r="E112">
+        <v>9</v>
+      </c>
+      <c r="F112">
+        <v>0</v>
+      </c>
+      <c r="G112">
+        <v>0</v>
+      </c>
+      <c r="H112">
+        <v>3</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>2</v>
+      </c>
+      <c r="K112" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11">
+      <c r="A113" t="s">
+        <v>37</v>
+      </c>
+      <c r="B113" t="s">
+        <v>105</v>
+      </c>
+      <c r="C113">
+        <v>3</v>
+      </c>
+      <c r="D113" t="s">
+        <v>141</v>
+      </c>
+      <c r="E113">
+        <v>9</v>
+      </c>
+      <c r="F113">
+        <v>0</v>
+      </c>
+      <c r="G113">
+        <v>0</v>
+      </c>
+      <c r="H113">
+        <v>3</v>
+      </c>
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>2</v>
+      </c>
+      <c r="K113" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11">
+      <c r="A114" t="s">
+        <v>37</v>
+      </c>
+      <c r="B114" t="s">
+        <v>69</v>
+      </c>
+      <c r="C114">
+        <v>3</v>
+      </c>
+      <c r="D114" t="s">
+        <v>139</v>
+      </c>
+      <c r="E114">
+        <v>0</v>
+      </c>
+      <c r="F114">
+        <v>5</v>
+      </c>
+      <c r="G114">
+        <v>0</v>
+      </c>
+      <c r="H114">
+        <v>0</v>
+      </c>
+      <c r="I114">
+        <v>9</v>
+      </c>
+      <c r="J114">
+        <v>3</v>
+      </c>
+      <c r="K114" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11">
+      <c r="A115" t="s">
+        <v>37</v>
+      </c>
+      <c r="B115" t="s">
+        <v>70</v>
+      </c>
+      <c r="C115">
+        <v>3</v>
+      </c>
+      <c r="D115" t="s">
+        <v>139</v>
+      </c>
+      <c r="E115">
+        <v>0</v>
+      </c>
+      <c r="F115">
+        <v>5</v>
+      </c>
+      <c r="G115">
+        <v>0</v>
+      </c>
+      <c r="H115">
+        <v>0</v>
+      </c>
+      <c r="I115">
+        <v>9</v>
+      </c>
+      <c r="J115">
+        <v>3</v>
+      </c>
+      <c r="K115" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11">
+      <c r="A116" t="s">
+        <v>37</v>
+      </c>
+      <c r="B116" t="s">
+        <v>71</v>
+      </c>
+      <c r="C116">
+        <v>3</v>
+      </c>
+      <c r="D116" t="s">
+        <v>139</v>
+      </c>
+      <c r="E116">
+        <v>0</v>
+      </c>
+      <c r="F116">
+        <v>5</v>
+      </c>
+      <c r="G116">
+        <v>0</v>
+      </c>
+      <c r="H116">
+        <v>0</v>
+      </c>
+      <c r="I116">
+        <v>9</v>
+      </c>
+      <c r="J116">
+        <v>3</v>
+      </c>
+      <c r="K116" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11">
+      <c r="A117" t="s">
+        <v>37</v>
+      </c>
+      <c r="B117" t="s">
+        <v>72</v>
+      </c>
+      <c r="C117">
+        <v>3</v>
+      </c>
+      <c r="D117" t="s">
+        <v>139</v>
+      </c>
+      <c r="E117">
+        <v>0</v>
+      </c>
+      <c r="F117">
+        <v>5</v>
+      </c>
+      <c r="G117">
+        <v>0</v>
+      </c>
+      <c r="H117">
+        <v>0</v>
+      </c>
+      <c r="I117">
+        <v>9</v>
+      </c>
+      <c r="J117">
+        <v>3</v>
+      </c>
+      <c r="K117" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11">
+      <c r="A118" t="s">
+        <v>37</v>
+      </c>
+      <c r="B118" t="s">
+        <v>73</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="D118" t="s">
+        <v>139</v>
+      </c>
+      <c r="E118">
+        <v>0</v>
+      </c>
+      <c r="F118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>0</v>
+      </c>
+      <c r="H118">
+        <v>0</v>
+      </c>
+      <c r="I118">
+        <v>3</v>
+      </c>
+      <c r="J118">
+        <v>1</v>
+      </c>
+      <c r="K118" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11">
+      <c r="A119" t="s">
+        <v>37</v>
+      </c>
+      <c r="B119" t="s">
+        <v>106</v>
+      </c>
+      <c r="C119">
+        <v>3</v>
+      </c>
+      <c r="D119" t="s">
+        <v>139</v>
+      </c>
+      <c r="E119">
+        <v>0</v>
+      </c>
+      <c r="F119">
+        <v>3</v>
+      </c>
+      <c r="G119">
+        <v>6</v>
+      </c>
+      <c r="H119">
+        <v>0</v>
+      </c>
+      <c r="I119">
+        <v>0</v>
+      </c>
+      <c r="J119">
+        <v>2</v>
+      </c>
+      <c r="K119" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11">
+      <c r="A120" t="s">
+        <v>37</v>
+      </c>
+      <c r="B120" t="s">
+        <v>107</v>
+      </c>
+      <c r="C120">
+        <v>3</v>
+      </c>
+      <c r="D120" t="s">
+        <v>139</v>
+      </c>
+      <c r="E120">
+        <v>0</v>
+      </c>
+      <c r="F120">
+        <v>3</v>
+      </c>
+      <c r="G120">
+        <v>6</v>
+      </c>
+      <c r="H120">
+        <v>0</v>
+      </c>
+      <c r="I120">
+        <v>0</v>
+      </c>
+      <c r="J120">
+        <v>2</v>
+      </c>
+      <c r="K120" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11">
+      <c r="A121" t="s">
+        <v>38</v>
+      </c>
+      <c r="B121" t="s">
+        <v>108</v>
+      </c>
+      <c r="C121">
+        <v>3</v>
+      </c>
+      <c r="D121" t="s">
+        <v>140</v>
+      </c>
+      <c r="E121">
+        <v>0</v>
+      </c>
+      <c r="F121">
+        <v>3</v>
+      </c>
+      <c r="G121">
+        <v>6</v>
+      </c>
+      <c r="H121">
+        <v>0</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11">
+      <c r="A122" t="s">
+        <v>38</v>
+      </c>
+      <c r="B122" t="s">
+        <v>109</v>
+      </c>
+      <c r="C122">
+        <v>3</v>
+      </c>
+      <c r="D122" t="s">
+        <v>140</v>
+      </c>
+      <c r="E122">
+        <v>0</v>
+      </c>
+      <c r="F122">
+        <v>3</v>
+      </c>
+      <c r="G122">
+        <v>6</v>
+      </c>
+      <c r="H122">
+        <v>0</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11">
+      <c r="A123" t="s">
+        <v>38</v>
+      </c>
+      <c r="B123" t="s">
+        <v>110</v>
+      </c>
+      <c r="C123">
+        <v>3</v>
+      </c>
+      <c r="D123" t="s">
+        <v>140</v>
+      </c>
+      <c r="E123">
+        <v>0</v>
+      </c>
+      <c r="F123">
+        <v>3</v>
+      </c>
+      <c r="G123">
+        <v>6</v>
+      </c>
+      <c r="H123">
+        <v>0</v>
+      </c>
+      <c r="I123">
+        <v>0</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11">
+      <c r="A124" t="s">
+        <v>38</v>
+      </c>
+      <c r="B124" t="s">
+        <v>111</v>
+      </c>
+      <c r="C124">
+        <v>3</v>
+      </c>
+      <c r="D124" t="s">
+        <v>140</v>
+      </c>
+      <c r="E124">
+        <v>9</v>
+      </c>
+      <c r="F124">
+        <v>3</v>
+      </c>
+      <c r="G124">
+        <v>6</v>
+      </c>
+      <c r="H124">
+        <v>3</v>
+      </c>
+      <c r="I124">
+        <v>0</v>
+      </c>
+      <c r="J124">
+        <v>4</v>
+      </c>
+      <c r="K124" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11">
+      <c r="A125" t="s">
+        <v>38</v>
+      </c>
+      <c r="B125" t="s">
+        <v>112</v>
+      </c>
+      <c r="C125">
+        <v>3</v>
+      </c>
+      <c r="D125" t="s">
+        <v>140</v>
+      </c>
+      <c r="E125">
+        <v>9</v>
+      </c>
+      <c r="F125">
+        <v>3</v>
+      </c>
+      <c r="G125">
+        <v>6</v>
+      </c>
+      <c r="H125">
+        <v>3</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>4</v>
+      </c>
+      <c r="K125" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11">
+      <c r="A126" t="s">
+        <v>39</v>
+      </c>
+      <c r="B126" t="s">
+        <v>113</v>
+      </c>
+      <c r="C126">
+        <v>3</v>
+      </c>
+      <c r="D126" t="s">
+        <v>140</v>
+      </c>
+      <c r="E126">
+        <v>9</v>
+      </c>
+      <c r="F126">
+        <v>3</v>
+      </c>
+      <c r="G126">
+        <v>6</v>
+      </c>
+      <c r="H126">
+        <v>3</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>4</v>
+      </c>
+      <c r="K126" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11">
+      <c r="A127" t="s">
+        <v>39</v>
+      </c>
+      <c r="B127" t="s">
+        <v>114</v>
+      </c>
+      <c r="C127">
+        <v>3</v>
+      </c>
+      <c r="D127" t="s">
+        <v>140</v>
+      </c>
+      <c r="E127">
+        <v>9</v>
+      </c>
+      <c r="F127">
+        <v>3</v>
+      </c>
+      <c r="G127">
+        <v>6</v>
+      </c>
+      <c r="H127">
+        <v>3</v>
+      </c>
+      <c r="I127">
+        <v>0</v>
+      </c>
+      <c r="J127">
+        <v>4</v>
+      </c>
+      <c r="K127" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11">
+      <c r="A128" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" t="s">
+        <v>115</v>
+      </c>
+      <c r="C128">
+        <v>3</v>
+      </c>
+      <c r="D128" t="s">
+        <v>140</v>
+      </c>
+      <c r="E128">
+        <v>9</v>
+      </c>
+      <c r="F128">
+        <v>3</v>
+      </c>
+      <c r="G128">
+        <v>6</v>
+      </c>
+      <c r="H128">
+        <v>3</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>4</v>
+      </c>
+      <c r="K128" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11">
+      <c r="A129" t="s">
+        <v>40</v>
+      </c>
+      <c r="B129" t="s">
+        <v>116</v>
+      </c>
+      <c r="C129">
+        <v>3</v>
+      </c>
+      <c r="D129" t="s">
+        <v>140</v>
+      </c>
+      <c r="E129">
+        <v>9</v>
+      </c>
+      <c r="F129">
+        <v>3</v>
+      </c>
+      <c r="G129">
+        <v>6</v>
+      </c>
+      <c r="H129">
+        <v>3</v>
+      </c>
+      <c r="I129">
+        <v>0</v>
+      </c>
+      <c r="J129">
+        <v>4</v>
+      </c>
+      <c r="K129" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11">
+      <c r="A130" t="s">
+        <v>40</v>
+      </c>
+      <c r="B130" t="s">
+        <v>117</v>
+      </c>
+      <c r="C130">
+        <v>1</v>
+      </c>
+      <c r="D130" t="s">
+        <v>140</v>
+      </c>
+      <c r="E130">
+        <v>4</v>
+      </c>
+      <c r="F130">
+        <v>1</v>
+      </c>
+      <c r="G130">
+        <v>3</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>0</v>
+      </c>
+      <c r="J130">
+        <v>2</v>
+      </c>
+      <c r="K130" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11">
+      <c r="A131" t="s">
+        <v>41</v>
+      </c>
+      <c r="B131" t="s">
+        <v>87</v>
+      </c>
+      <c r="C131">
+        <v>3</v>
+      </c>
+      <c r="D131" t="s">
+        <v>138</v>
+      </c>
+      <c r="E131">
+        <v>0</v>
+      </c>
+      <c r="F131">
+        <v>5</v>
+      </c>
+      <c r="G131">
+        <v>0</v>
+      </c>
+      <c r="H131">
+        <v>0</v>
+      </c>
+      <c r="I131">
+        <v>9</v>
+      </c>
+      <c r="J131">
+        <v>3</v>
+      </c>
+      <c r="K131" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11">
+      <c r="A132" t="s">
+        <v>41</v>
+      </c>
+      <c r="B132" t="s">
+        <v>88</v>
+      </c>
+      <c r="C132">
+        <v>3</v>
+      </c>
+      <c r="D132" t="s">
+        <v>138</v>
+      </c>
+      <c r="E132">
+        <v>0</v>
+      </c>
+      <c r="F132">
+        <v>5</v>
+      </c>
+      <c r="G132">
+        <v>0</v>
+      </c>
+      <c r="H132">
+        <v>0</v>
+      </c>
+      <c r="I132">
+        <v>9</v>
+      </c>
+      <c r="J132">
+        <v>3</v>
+      </c>
+      <c r="K132" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11">
+      <c r="A133" t="s">
+        <v>41</v>
+      </c>
+      <c r="B133" t="s">
+        <v>89</v>
+      </c>
+      <c r="C133">
+        <v>3</v>
+      </c>
+      <c r="D133" t="s">
+        <v>138</v>
+      </c>
+      <c r="E133">
+        <v>0</v>
+      </c>
+      <c r="F133">
+        <v>5</v>
+      </c>
+      <c r="G133">
+        <v>0</v>
+      </c>
+      <c r="H133">
+        <v>0</v>
+      </c>
+      <c r="I133">
+        <v>9</v>
+      </c>
+      <c r="J133">
+        <v>3</v>
+      </c>
+      <c r="K133" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11">
+      <c r="A134" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134" t="s">
+        <v>90</v>
+      </c>
+      <c r="C134">
+        <v>3</v>
+      </c>
+      <c r="D134" t="s">
+        <v>138</v>
+      </c>
+      <c r="E134">
+        <v>0</v>
+      </c>
+      <c r="F134">
+        <v>5</v>
+      </c>
+      <c r="G134">
+        <v>0</v>
+      </c>
+      <c r="H134">
+        <v>0</v>
+      </c>
+      <c r="I134">
+        <v>9</v>
+      </c>
+      <c r="J134">
+        <v>3</v>
+      </c>
+      <c r="K134" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11">
+      <c r="A135" t="s">
+        <v>42</v>
+      </c>
+      <c r="B135" t="s">
+        <v>118</v>
+      </c>
+      <c r="C135">
+        <v>3</v>
+      </c>
+      <c r="D135" t="s">
+        <v>139</v>
+      </c>
+      <c r="E135">
+        <v>0</v>
+      </c>
+      <c r="F135">
+        <v>3</v>
+      </c>
+      <c r="G135">
+        <v>6</v>
+      </c>
+      <c r="H135">
+        <v>0</v>
+      </c>
+      <c r="I135">
+        <v>0</v>
+      </c>
+      <c r="J135">
+        <v>2</v>
+      </c>
+      <c r="K135" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11">
+      <c r="A136" t="s">
+        <v>42</v>
+      </c>
+      <c r="B136" t="s">
+        <v>119</v>
+      </c>
+      <c r="C136">
+        <v>3</v>
+      </c>
+      <c r="D136" t="s">
+        <v>139</v>
+      </c>
+      <c r="E136">
+        <v>0</v>
+      </c>
+      <c r="F136">
+        <v>3</v>
+      </c>
+      <c r="G136">
+        <v>6</v>
+      </c>
+      <c r="H136">
+        <v>0</v>
+      </c>
+      <c r="I136">
+        <v>0</v>
+      </c>
+      <c r="J136">
+        <v>2</v>
+      </c>
+      <c r="K136" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11">
+      <c r="A137" t="s">
+        <v>43</v>
+      </c>
+      <c r="B137" t="s">
+        <v>120</v>
+      </c>
+      <c r="C137">
+        <v>3</v>
+      </c>
+      <c r="D137" t="s">
+        <v>139</v>
+      </c>
+      <c r="E137">
+        <v>0</v>
+      </c>
+      <c r="F137">
+        <v>3</v>
+      </c>
+      <c r="G137">
+        <v>6</v>
+      </c>
+      <c r="H137">
+        <v>0</v>
+      </c>
+      <c r="I137">
+        <v>0</v>
+      </c>
+      <c r="J137">
+        <v>2</v>
+      </c>
+      <c r="K137" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11">
+      <c r="A138" t="s">
+        <v>43</v>
+      </c>
+      <c r="B138" t="s">
+        <v>121</v>
+      </c>
+      <c r="C138">
+        <v>3</v>
+      </c>
+      <c r="D138" t="s">
+        <v>139</v>
+      </c>
+      <c r="E138">
+        <v>0</v>
+      </c>
+      <c r="F138">
+        <v>3</v>
+      </c>
+      <c r="G138">
+        <v>6</v>
+      </c>
+      <c r="H138">
+        <v>0</v>
+      </c>
+      <c r="I138">
+        <v>0</v>
+      </c>
+      <c r="J138">
+        <v>2</v>
+      </c>
+      <c r="K138" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11">
+      <c r="A139" t="s">
+        <v>43</v>
+      </c>
+      <c r="B139" t="s">
+        <v>122</v>
+      </c>
+      <c r="C139">
+        <v>3</v>
+      </c>
+      <c r="D139" t="s">
+        <v>139</v>
+      </c>
+      <c r="E139">
+        <v>0</v>
+      </c>
+      <c r="F139">
+        <v>3</v>
+      </c>
+      <c r="G139">
+        <v>6</v>
+      </c>
+      <c r="H139">
+        <v>0</v>
+      </c>
+      <c r="I139">
+        <v>0</v>
+      </c>
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="K139" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11">
+      <c r="A140" t="s">
+        <v>44</v>
+      </c>
+      <c r="B140" t="s">
+        <v>92</v>
+      </c>
+      <c r="C140">
+        <v>3</v>
+      </c>
+      <c r="D140" t="s">
+        <v>138</v>
+      </c>
+      <c r="E140">
+        <v>0</v>
+      </c>
+      <c r="F140">
+        <v>5</v>
+      </c>
+      <c r="G140">
+        <v>0</v>
+      </c>
+      <c r="H140">
+        <v>0</v>
+      </c>
+      <c r="I140">
+        <v>9</v>
+      </c>
+      <c r="J140">
+        <v>3</v>
+      </c>
+      <c r="K140" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11">
+      <c r="A141" t="s">
+        <v>44</v>
+      </c>
+      <c r="B141" t="s">
+        <v>93</v>
+      </c>
+      <c r="C141">
+        <v>3</v>
+      </c>
+      <c r="D141" t="s">
+        <v>138</v>
+      </c>
+      <c r="E141">
+        <v>0</v>
+      </c>
+      <c r="F141">
+        <v>5</v>
+      </c>
+      <c r="G141">
+        <v>0</v>
+      </c>
+      <c r="H141">
+        <v>0</v>
+      </c>
+      <c r="I141">
+        <v>9</v>
+      </c>
+      <c r="J141">
+        <v>3</v>
+      </c>
+      <c r="K141" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11">
+      <c r="A142" t="s">
+        <v>44</v>
+      </c>
+      <c r="B142" t="s">
+        <v>94</v>
+      </c>
+      <c r="C142">
+        <v>3</v>
+      </c>
+      <c r="D142" t="s">
+        <v>138</v>
+      </c>
+      <c r="E142">
+        <v>0</v>
+      </c>
+      <c r="F142">
+        <v>5</v>
+      </c>
+      <c r="G142">
+        <v>0</v>
+      </c>
+      <c r="H142">
+        <v>0</v>
+      </c>
+      <c r="I142">
+        <v>9</v>
+      </c>
+      <c r="J142">
+        <v>3</v>
+      </c>
+      <c r="K142" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11">
+      <c r="A143" t="s">
+        <v>44</v>
+      </c>
+      <c r="B143" t="s">
+        <v>123</v>
+      </c>
+      <c r="C143">
+        <v>1.89</v>
+      </c>
+      <c r="D143" t="s">
+        <v>140</v>
+      </c>
+      <c r="E143">
+        <v>0</v>
+      </c>
+      <c r="F143">
+        <v>3</v>
+      </c>
+      <c r="G143">
+        <v>5</v>
+      </c>
+      <c r="H143">
+        <v>0</v>
+      </c>
+      <c r="I143">
+        <v>0</v>
+      </c>
+      <c r="J143">
+        <v>2</v>
+      </c>
+      <c r="K143" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11">
+      <c r="A144" t="s">
+        <v>45</v>
+      </c>
+      <c r="B144" t="s">
+        <v>124</v>
+      </c>
+      <c r="C144">
+        <v>3</v>
+      </c>
+      <c r="D144" t="s">
+        <v>139</v>
+      </c>
+      <c r="E144">
+        <v>0</v>
+      </c>
+      <c r="F144">
+        <v>3</v>
+      </c>
+      <c r="G144">
+        <v>6</v>
+      </c>
+      <c r="H144">
+        <v>0</v>
+      </c>
+      <c r="I144">
+        <v>0</v>
+      </c>
+      <c r="J144">
+        <v>2</v>
+      </c>
+      <c r="K144" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11">
+      <c r="A145" t="s">
+        <v>45</v>
+      </c>
+      <c r="B145" t="s">
+        <v>125</v>
+      </c>
+      <c r="C145">
+        <v>3</v>
+      </c>
+      <c r="D145" t="s">
+        <v>140</v>
+      </c>
+      <c r="E145">
+        <v>0</v>
+      </c>
+      <c r="F145">
+        <v>3</v>
+      </c>
+      <c r="G145">
+        <v>6</v>
+      </c>
+      <c r="H145">
+        <v>0</v>
+      </c>
+      <c r="I145">
+        <v>0</v>
+      </c>
+      <c r="J145">
+        <v>2</v>
+      </c>
+      <c r="K145" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11">
+      <c r="A146" t="s">
+        <v>45</v>
+      </c>
+      <c r="B146" t="s">
+        <v>126</v>
+      </c>
+      <c r="C146">
+        <v>3</v>
+      </c>
+      <c r="D146" t="s">
+        <v>139</v>
+      </c>
+      <c r="E146">
+        <v>0</v>
+      </c>
+      <c r="F146">
+        <v>3</v>
+      </c>
+      <c r="G146">
+        <v>6</v>
+      </c>
+      <c r="H146">
+        <v>0</v>
+      </c>
+      <c r="I146">
+        <v>0</v>
+      </c>
+      <c r="J146">
+        <v>2</v>
+      </c>
+      <c r="K146" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11">
+      <c r="A147" t="s">
+        <v>46</v>
+      </c>
+      <c r="B147" t="s">
+        <v>95</v>
+      </c>
+      <c r="C147">
+        <v>3</v>
+      </c>
+      <c r="D147" t="s">
+        <v>139</v>
+      </c>
+      <c r="E147">
+        <v>0</v>
+      </c>
+      <c r="F147">
+        <v>5</v>
+      </c>
+      <c r="G147">
+        <v>0</v>
+      </c>
+      <c r="H147">
+        <v>0</v>
+      </c>
+      <c r="I147">
+        <v>6</v>
+      </c>
+      <c r="J147">
+        <v>3</v>
+      </c>
+      <c r="K147" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11">
+      <c r="A148" t="s">
+        <v>46</v>
+      </c>
+      <c r="B148" t="s">
+        <v>96</v>
+      </c>
+      <c r="C148">
+        <v>3</v>
+      </c>
+      <c r="D148" t="s">
+        <v>139</v>
+      </c>
+      <c r="E148">
+        <v>0</v>
+      </c>
+      <c r="F148">
+        <v>5</v>
+      </c>
+      <c r="G148">
+        <v>0</v>
+      </c>
+      <c r="H148">
+        <v>0</v>
+      </c>
+      <c r="I148">
+        <v>6</v>
+      </c>
+      <c r="J148">
+        <v>3</v>
+      </c>
+      <c r="K148" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11">
+      <c r="A149" t="s">
+        <v>46</v>
+      </c>
+      <c r="B149" t="s">
+        <v>97</v>
+      </c>
+      <c r="C149">
+        <v>3</v>
+      </c>
+      <c r="D149" t="s">
+        <v>139</v>
+      </c>
+      <c r="E149">
+        <v>0</v>
+      </c>
+      <c r="F149">
+        <v>5</v>
+      </c>
+      <c r="G149">
+        <v>0</v>
+      </c>
+      <c r="H149">
+        <v>0</v>
+      </c>
+      <c r="I149">
+        <v>6</v>
+      </c>
+      <c r="J149">
+        <v>3</v>
+      </c>
+      <c r="K149" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11">
+      <c r="A150" t="s">
+        <v>47</v>
+      </c>
+      <c r="B150" t="s">
+        <v>101</v>
+      </c>
+      <c r="C150">
+        <v>3</v>
+      </c>
+      <c r="D150" t="s">
+        <v>139</v>
+      </c>
+      <c r="E150">
+        <v>0</v>
+      </c>
+      <c r="F150">
+        <v>5</v>
+      </c>
+      <c r="G150">
+        <v>0</v>
+      </c>
+      <c r="H150">
+        <v>0</v>
+      </c>
+      <c r="I150">
+        <v>6</v>
+      </c>
+      <c r="J150">
+        <v>3</v>
+      </c>
+      <c r="K150" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11">
+      <c r="A151" t="s">
+        <v>47</v>
+      </c>
+      <c r="B151" t="s">
+        <v>103</v>
+      </c>
+      <c r="C151">
+        <v>3</v>
+      </c>
+      <c r="D151" t="s">
+        <v>139</v>
+      </c>
+      <c r="E151">
+        <v>0</v>
+      </c>
+      <c r="F151">
+        <v>5</v>
+      </c>
+      <c r="G151">
+        <v>0</v>
+      </c>
+      <c r="H151">
+        <v>0</v>
+      </c>
+      <c r="I151">
+        <v>6</v>
+      </c>
+      <c r="J151">
+        <v>3</v>
+      </c>
+      <c r="K151" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11">
+      <c r="A152" t="s">
+        <v>47</v>
+      </c>
+      <c r="B152" t="s">
+        <v>102</v>
+      </c>
+      <c r="C152">
+        <v>3</v>
+      </c>
+      <c r="D152" t="s">
+        <v>139</v>
+      </c>
+      <c r="E152">
+        <v>0</v>
+      </c>
+      <c r="F152">
+        <v>5</v>
+      </c>
+      <c r="G152">
+        <v>0</v>
+      </c>
+      <c r="H152">
+        <v>0</v>
+      </c>
+      <c r="I152">
+        <v>6</v>
+      </c>
+      <c r="J152">
+        <v>3</v>
+      </c>
+      <c r="K152" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11">
+      <c r="A153" t="s">
+        <v>47</v>
+      </c>
+      <c r="B153" t="s">
+        <v>98</v>
+      </c>
+      <c r="C153">
+        <v>3</v>
+      </c>
+      <c r="D153" t="s">
+        <v>140</v>
+      </c>
+      <c r="E153">
+        <v>0</v>
+      </c>
+      <c r="F153">
+        <v>5</v>
+      </c>
+      <c r="G153">
+        <v>0</v>
+      </c>
+      <c r="H153">
+        <v>0</v>
+      </c>
+      <c r="I153">
+        <v>6</v>
+      </c>
+      <c r="J153">
+        <v>3</v>
+      </c>
+      <c r="K153" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11">
+      <c r="A154" t="s">
+        <v>48</v>
+      </c>
+      <c r="B154" t="s">
+        <v>106</v>
+      </c>
+      <c r="C154">
+        <v>3</v>
+      </c>
+      <c r="D154" t="s">
+        <v>139</v>
+      </c>
+      <c r="E154">
+        <v>0</v>
+      </c>
+      <c r="F154">
+        <v>5</v>
+      </c>
+      <c r="G154">
+        <v>0</v>
+      </c>
+      <c r="H154">
+        <v>0</v>
+      </c>
+      <c r="I154">
+        <v>6</v>
+      </c>
+      <c r="J154">
+        <v>3</v>
+      </c>
+      <c r="K154" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11">
+      <c r="A155" t="s">
+        <v>48</v>
+      </c>
+      <c r="B155" t="s">
+        <v>107</v>
+      </c>
+      <c r="C155">
+        <v>3</v>
+      </c>
+      <c r="D155" t="s">
+        <v>139</v>
+      </c>
+      <c r="E155">
+        <v>0</v>
+      </c>
+      <c r="F155">
+        <v>5</v>
+      </c>
+      <c r="G155">
+        <v>0</v>
+      </c>
+      <c r="H155">
+        <v>0</v>
+      </c>
+      <c r="I155">
+        <v>6</v>
+      </c>
+      <c r="J155">
+        <v>3</v>
+      </c>
+      <c r="K155" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11">
+      <c r="A156" t="s">
+        <v>49</v>
+      </c>
+      <c r="B156" t="s">
+        <v>108</v>
+      </c>
+      <c r="C156">
+        <v>3</v>
+      </c>
+      <c r="D156" t="s">
+        <v>140</v>
+      </c>
+      <c r="E156">
+        <v>0</v>
+      </c>
+      <c r="F156">
+        <v>5</v>
+      </c>
+      <c r="G156">
+        <v>0</v>
+      </c>
+      <c r="H156">
+        <v>0</v>
+      </c>
+      <c r="I156">
+        <v>6</v>
+      </c>
+      <c r="J156">
+        <v>3</v>
+      </c>
+      <c r="K156" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11">
+      <c r="A157" t="s">
+        <v>49</v>
+      </c>
+      <c r="B157" t="s">
+        <v>109</v>
+      </c>
+      <c r="C157">
+        <v>3</v>
+      </c>
+      <c r="D157" t="s">
+        <v>140</v>
+      </c>
+      <c r="E157">
+        <v>0</v>
+      </c>
+      <c r="F157">
+        <v>5</v>
+      </c>
+      <c r="G157">
+        <v>0</v>
+      </c>
+      <c r="H157">
+        <v>0</v>
+      </c>
+      <c r="I157">
+        <v>6</v>
+      </c>
+      <c r="J157">
+        <v>3</v>
+      </c>
+      <c r="K157" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11">
+      <c r="A158" t="s">
+        <v>49</v>
+      </c>
+      <c r="B158" t="s">
+        <v>110</v>
+      </c>
+      <c r="C158">
+        <v>2.897</v>
+      </c>
+      <c r="D158" t="s">
+        <v>140</v>
+      </c>
+      <c r="E158">
+        <v>0</v>
+      </c>
+      <c r="F158">
+        <v>3</v>
+      </c>
+      <c r="G158">
+        <v>0</v>
+      </c>
+      <c r="H158">
+        <v>0</v>
+      </c>
+      <c r="I158">
+        <v>4</v>
+      </c>
+      <c r="J158">
+        <v>2</v>
+      </c>
+      <c r="K158" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11">
+      <c r="A159" t="s">
+        <v>50</v>
+      </c>
+      <c r="B159" t="s">
+        <v>99</v>
+      </c>
+      <c r="C159">
+        <v>3</v>
+      </c>
+      <c r="D159" t="s">
+        <v>140</v>
+      </c>
+      <c r="E159">
+        <v>0</v>
+      </c>
+      <c r="F159">
+        <v>5</v>
+      </c>
+      <c r="G159">
+        <v>0</v>
+      </c>
+      <c r="H159">
+        <v>0</v>
+      </c>
+      <c r="I159">
+        <v>6</v>
+      </c>
+      <c r="J159">
+        <v>3</v>
+      </c>
+      <c r="K159" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11">
+      <c r="A160" t="s">
+        <v>50</v>
+      </c>
+      <c r="B160" t="s">
+        <v>100</v>
+      </c>
+      <c r="C160">
+        <v>3</v>
+      </c>
+      <c r="D160" t="s">
+        <v>140</v>
+      </c>
+      <c r="E160">
+        <v>0</v>
+      </c>
+      <c r="F160">
+        <v>5</v>
+      </c>
+      <c r="G160">
+        <v>0</v>
+      </c>
+      <c r="H160">
+        <v>0</v>
+      </c>
+      <c r="I160">
+        <v>6</v>
+      </c>
+      <c r="J160">
+        <v>3</v>
+      </c>
+      <c r="K160" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11">
+      <c r="A161" t="s">
+        <v>51</v>
+      </c>
+      <c r="B161" t="s">
+        <v>118</v>
+      </c>
+      <c r="C161">
+        <v>3</v>
+      </c>
+      <c r="D161" t="s">
+        <v>139</v>
+      </c>
+      <c r="E161">
+        <v>0</v>
+      </c>
+      <c r="F161">
+        <v>5</v>
+      </c>
+      <c r="G161">
+        <v>0</v>
+      </c>
+      <c r="H161">
+        <v>0</v>
+      </c>
+      <c r="I161">
+        <v>6</v>
+      </c>
+      <c r="J161">
+        <v>3</v>
+      </c>
+      <c r="K161" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11">
+      <c r="A162" t="s">
+        <v>51</v>
+      </c>
+      <c r="B162" t="s">
+        <v>119</v>
+      </c>
+      <c r="C162">
+        <v>3</v>
+      </c>
+      <c r="D162" t="s">
+        <v>139</v>
+      </c>
+      <c r="E162">
+        <v>0</v>
+      </c>
+      <c r="F162">
+        <v>5</v>
+      </c>
+      <c r="G162">
+        <v>0</v>
+      </c>
+      <c r="H162">
+        <v>0</v>
+      </c>
+      <c r="I162">
+        <v>6</v>
+      </c>
+      <c r="J162">
+        <v>3</v>
+      </c>
+      <c r="K162" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11">
+      <c r="A163" t="s">
+        <v>51</v>
+      </c>
+      <c r="B163" t="s">
+        <v>120</v>
+      </c>
+      <c r="C163">
+        <v>3</v>
+      </c>
+      <c r="D163" t="s">
+        <v>139</v>
+      </c>
+      <c r="E163">
+        <v>0</v>
+      </c>
+      <c r="F163">
+        <v>5</v>
+      </c>
+      <c r="G163">
+        <v>0</v>
+      </c>
+      <c r="H163">
+        <v>0</v>
+      </c>
+      <c r="I163">
+        <v>6</v>
+      </c>
+      <c r="J163">
+        <v>3</v>
+      </c>
+      <c r="K163" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11">
+      <c r="A164" t="s">
+        <v>51</v>
+      </c>
+      <c r="B164" t="s">
+        <v>118</v>
+      </c>
+      <c r="C164">
+        <v>3</v>
+      </c>
+      <c r="D164" t="s">
+        <v>139</v>
+      </c>
+      <c r="E164">
+        <v>0</v>
+      </c>
+      <c r="F164">
+        <v>5</v>
+      </c>
+      <c r="G164">
+        <v>0</v>
+      </c>
+      <c r="H164">
+        <v>0</v>
+      </c>
+      <c r="I164">
+        <v>9</v>
+      </c>
+      <c r="J164">
+        <v>4</v>
+      </c>
+      <c r="K164" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11">
+      <c r="A165" t="s">
+        <v>51</v>
+      </c>
+      <c r="B165" t="s">
+        <v>119</v>
+      </c>
+      <c r="C165">
+        <v>3</v>
+      </c>
+      <c r="D165" t="s">
+        <v>139</v>
+      </c>
+      <c r="E165">
+        <v>0</v>
+      </c>
+      <c r="F165">
+        <v>5</v>
+      </c>
+      <c r="G165">
+        <v>0</v>
+      </c>
+      <c r="H165">
+        <v>0</v>
+      </c>
+      <c r="I165">
+        <v>9</v>
+      </c>
+      <c r="J165">
+        <v>4</v>
+      </c>
+      <c r="K165" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11">
+      <c r="A166" t="s">
+        <v>51</v>
+      </c>
+      <c r="B166" t="s">
+        <v>120</v>
+      </c>
+      <c r="C166">
+        <v>3</v>
+      </c>
+      <c r="D166" t="s">
+        <v>139</v>
+      </c>
+      <c r="E166">
+        <v>0</v>
+      </c>
+      <c r="F166">
+        <v>5</v>
+      </c>
+      <c r="G166">
+        <v>0</v>
+      </c>
+      <c r="H166">
+        <v>0</v>
+      </c>
+      <c r="I166">
+        <v>9</v>
+      </c>
+      <c r="J166">
+        <v>4</v>
+      </c>
+      <c r="K166" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11">
+      <c r="A167" t="s">
+        <v>51</v>
+      </c>
+      <c r="B167" t="s">
+        <v>96</v>
+      </c>
+      <c r="C167">
+        <v>3</v>
+      </c>
+      <c r="D167" t="s">
+        <v>139</v>
+      </c>
+      <c r="E167">
+        <v>0</v>
+      </c>
+      <c r="F167">
+        <v>5</v>
+      </c>
+      <c r="G167">
+        <v>0</v>
+      </c>
+      <c r="H167">
+        <v>0</v>
+      </c>
+      <c r="I167">
+        <v>9</v>
+      </c>
+      <c r="J167">
+        <v>4</v>
+      </c>
+      <c r="K167" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11">
+      <c r="A168" t="s">
+        <v>51</v>
+      </c>
+      <c r="B168" t="s">
+        <v>97</v>
+      </c>
+      <c r="C168">
+        <v>3</v>
+      </c>
+      <c r="D168" t="s">
+        <v>139</v>
+      </c>
+      <c r="E168">
+        <v>0</v>
+      </c>
+      <c r="F168">
+        <v>5</v>
+      </c>
+      <c r="G168">
+        <v>0</v>
+      </c>
+      <c r="H168">
+        <v>0</v>
+      </c>
+      <c r="I168">
+        <v>9</v>
+      </c>
+      <c r="J168">
+        <v>4</v>
+      </c>
+      <c r="K168" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11">
+      <c r="A169" t="s">
+        <v>52</v>
+      </c>
+      <c r="B169" t="s">
+        <v>127</v>
+      </c>
+      <c r="C169">
+        <v>3</v>
+      </c>
+      <c r="D169" t="s">
+        <v>138</v>
+      </c>
+      <c r="E169">
+        <v>0</v>
+      </c>
+      <c r="F169">
+        <v>3</v>
+      </c>
+      <c r="G169">
+        <v>6</v>
+      </c>
+      <c r="H169">
+        <v>0</v>
+      </c>
+      <c r="I169">
+        <v>0</v>
+      </c>
+      <c r="J169">
+        <v>2</v>
+      </c>
+      <c r="K169" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11">
+      <c r="A170" t="s">
+        <v>52</v>
+      </c>
+      <c r="B170" t="s">
+        <v>128</v>
+      </c>
+      <c r="C170">
+        <v>3</v>
+      </c>
+      <c r="D170" t="s">
+        <v>138</v>
+      </c>
+      <c r="E170">
+        <v>0</v>
+      </c>
+      <c r="F170">
+        <v>3</v>
+      </c>
+      <c r="G170">
+        <v>6</v>
+      </c>
+      <c r="H170">
+        <v>0</v>
+      </c>
+      <c r="I170">
+        <v>0</v>
+      </c>
+      <c r="J170">
+        <v>2</v>
+      </c>
+      <c r="K170" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11">
+      <c r="A171" t="s">
+        <v>52</v>
+      </c>
+      <c r="B171" t="s">
+        <v>129</v>
+      </c>
+      <c r="C171">
+        <v>3</v>
+      </c>
+      <c r="D171" t="s">
+        <v>138</v>
+      </c>
+      <c r="E171">
+        <v>0</v>
+      </c>
+      <c r="F171">
+        <v>3</v>
+      </c>
+      <c r="G171">
+        <v>6</v>
+      </c>
+      <c r="H171">
+        <v>0</v>
+      </c>
+      <c r="I171">
+        <v>0</v>
+      </c>
+      <c r="J171">
+        <v>2</v>
+      </c>
+      <c r="K171" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11">
+      <c r="A172" t="s">
+        <v>52</v>
+      </c>
+      <c r="B172" t="s">
+        <v>98</v>
+      </c>
+      <c r="C172">
+        <v>3</v>
+      </c>
+      <c r="D172" t="s">
+        <v>140</v>
+      </c>
+      <c r="E172">
+        <v>0</v>
+      </c>
+      <c r="F172">
+        <v>5</v>
+      </c>
+      <c r="G172">
+        <v>0</v>
+      </c>
+      <c r="H172">
+        <v>0</v>
+      </c>
+      <c r="I172">
+        <v>9</v>
+      </c>
+      <c r="J172">
+        <v>4</v>
+      </c>
+      <c r="K172" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11">
+      <c r="A173" t="s">
+        <v>52</v>
+      </c>
+      <c r="B173" t="s">
+        <v>99</v>
+      </c>
+      <c r="C173">
+        <v>3</v>
+      </c>
+      <c r="D173" t="s">
+        <v>140</v>
+      </c>
+      <c r="E173">
+        <v>0</v>
+      </c>
+      <c r="F173">
+        <v>5</v>
+      </c>
+      <c r="G173">
+        <v>0</v>
+      </c>
+      <c r="H173">
+        <v>0</v>
+      </c>
+      <c r="I173">
+        <v>9</v>
+      </c>
+      <c r="J173">
+        <v>4</v>
+      </c>
+      <c r="K173" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11">
+      <c r="A174" t="s">
+        <v>52</v>
+      </c>
+      <c r="B174" t="s">
+        <v>100</v>
+      </c>
+      <c r="C174">
+        <v>3</v>
+      </c>
+      <c r="D174" t="s">
+        <v>140</v>
+      </c>
+      <c r="E174">
+        <v>0</v>
+      </c>
+      <c r="F174">
+        <v>5</v>
+      </c>
+      <c r="G174">
+        <v>0</v>
+      </c>
+      <c r="H174">
+        <v>0</v>
+      </c>
+      <c r="I174">
+        <v>9</v>
+      </c>
+      <c r="J174">
+        <v>4</v>
+      </c>
+      <c r="K174" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11">
+      <c r="A175" t="s">
+        <v>53</v>
+      </c>
+      <c r="B175" t="s">
+        <v>121</v>
+      </c>
+      <c r="C175">
+        <v>3</v>
+      </c>
+      <c r="D175" t="s">
+        <v>139</v>
+      </c>
+      <c r="E175">
+        <v>0</v>
+      </c>
+      <c r="F175">
+        <v>5</v>
+      </c>
+      <c r="G175">
+        <v>0</v>
+      </c>
+      <c r="H175">
+        <v>0</v>
+      </c>
+      <c r="I175">
+        <v>6</v>
+      </c>
+      <c r="J175">
+        <v>3</v>
+      </c>
+      <c r="K175" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11">
+      <c r="A176" t="s">
+        <v>53</v>
+      </c>
+      <c r="B176" t="s">
+        <v>122</v>
+      </c>
+      <c r="C176">
+        <v>3</v>
+      </c>
+      <c r="D176" t="s">
+        <v>139</v>
+      </c>
+      <c r="E176">
+        <v>0</v>
+      </c>
+      <c r="F176">
+        <v>5</v>
+      </c>
+      <c r="G176">
+        <v>0</v>
+      </c>
+      <c r="H176">
+        <v>0</v>
+      </c>
+      <c r="I176">
+        <v>6</v>
+      </c>
+      <c r="J176">
+        <v>3</v>
+      </c>
+      <c r="K176" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11">
+      <c r="A177" t="s">
+        <v>53</v>
+      </c>
+      <c r="B177" t="s">
+        <v>124</v>
+      </c>
+      <c r="C177">
+        <v>3</v>
+      </c>
+      <c r="D177" t="s">
+        <v>139</v>
+      </c>
+      <c r="E177">
+        <v>0</v>
+      </c>
+      <c r="F177">
+        <v>5</v>
+      </c>
+      <c r="G177">
+        <v>0</v>
+      </c>
+      <c r="H177">
+        <v>0</v>
+      </c>
+      <c r="I177">
+        <v>6</v>
+      </c>
+      <c r="J177">
+        <v>3</v>
+      </c>
+      <c r="K177" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11">
+      <c r="A178" t="s">
+        <v>53</v>
+      </c>
+      <c r="B178" t="s">
+        <v>121</v>
+      </c>
+      <c r="C178">
+        <v>3</v>
+      </c>
+      <c r="D178" t="s">
+        <v>139</v>
+      </c>
+      <c r="E178">
+        <v>0</v>
+      </c>
+      <c r="F178">
+        <v>5</v>
+      </c>
+      <c r="G178">
+        <v>0</v>
+      </c>
+      <c r="H178">
+        <v>0</v>
+      </c>
+      <c r="I178">
+        <v>9</v>
+      </c>
+      <c r="J178">
+        <v>4</v>
+      </c>
+      <c r="K178" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11">
+      <c r="A179" t="s">
+        <v>53</v>
+      </c>
+      <c r="B179" t="s">
+        <v>122</v>
+      </c>
+      <c r="C179">
+        <v>3</v>
+      </c>
+      <c r="D179" t="s">
+        <v>139</v>
+      </c>
+      <c r="E179">
+        <v>0</v>
+      </c>
+      <c r="F179">
+        <v>5</v>
+      </c>
+      <c r="G179">
+        <v>0</v>
+      </c>
+      <c r="H179">
+        <v>0</v>
+      </c>
+      <c r="I179">
+        <v>9</v>
+      </c>
+      <c r="J179">
+        <v>4</v>
+      </c>
+      <c r="K179" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11">
+      <c r="A180" t="s">
+        <v>53</v>
+      </c>
+      <c r="B180" t="s">
+        <v>124</v>
+      </c>
+      <c r="C180">
+        <v>3</v>
+      </c>
+      <c r="D180" t="s">
+        <v>139</v>
+      </c>
+      <c r="E180">
+        <v>0</v>
+      </c>
+      <c r="F180">
+        <v>5</v>
+      </c>
+      <c r="G180">
+        <v>0</v>
+      </c>
+      <c r="H180">
+        <v>0</v>
+      </c>
+      <c r="I180">
+        <v>9</v>
+      </c>
+      <c r="J180">
+        <v>4</v>
+      </c>
+      <c r="K180" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11">
+      <c r="A181" t="s">
+        <v>54</v>
+      </c>
+      <c r="B181" t="s">
+        <v>130</v>
+      </c>
+      <c r="C181">
+        <v>3</v>
+      </c>
+      <c r="D181" t="s">
+        <v>139</v>
+      </c>
+      <c r="E181">
+        <v>0</v>
+      </c>
+      <c r="F181">
+        <v>3</v>
+      </c>
+      <c r="G181">
+        <v>6</v>
+      </c>
+      <c r="H181">
+        <v>0</v>
+      </c>
+      <c r="I181">
+        <v>0</v>
+      </c>
+      <c r="J181">
+        <v>2</v>
+      </c>
+      <c r="K181" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11">
+      <c r="A182" t="s">
+        <v>54</v>
+      </c>
+      <c r="B182" t="s">
+        <v>131</v>
+      </c>
+      <c r="C182">
+        <v>3</v>
+      </c>
+      <c r="D182" t="s">
+        <v>139</v>
+      </c>
+      <c r="E182">
+        <v>0</v>
+      </c>
+      <c r="F182">
+        <v>3</v>
+      </c>
+      <c r="G182">
+        <v>6</v>
+      </c>
+      <c r="H182">
+        <v>0</v>
+      </c>
+      <c r="I182">
+        <v>0</v>
+      </c>
+      <c r="J182">
+        <v>2</v>
+      </c>
+      <c r="K182" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11">
+      <c r="A183" t="s">
+        <v>54</v>
+      </c>
+      <c r="B183" t="s">
+        <v>132</v>
+      </c>
+      <c r="C183">
+        <v>3</v>
+      </c>
+      <c r="D183" t="s">
+        <v>139</v>
+      </c>
+      <c r="E183">
+        <v>0</v>
+      </c>
+      <c r="F183">
+        <v>3</v>
+      </c>
+      <c r="G183">
+        <v>6</v>
+      </c>
+      <c r="H183">
+        <v>0</v>
+      </c>
+      <c r="I183">
+        <v>0</v>
+      </c>
+      <c r="J183">
+        <v>2</v>
+      </c>
+      <c r="K183" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11">
+      <c r="A184" t="s">
+        <v>54</v>
+      </c>
+      <c r="B184" t="s">
+        <v>133</v>
+      </c>
+      <c r="C184">
+        <v>1.5</v>
+      </c>
+      <c r="D184" t="s">
+        <v>139</v>
+      </c>
+      <c r="E184">
+        <v>0</v>
+      </c>
+      <c r="F184">
+        <v>2</v>
+      </c>
+      <c r="G184">
+        <v>3</v>
+      </c>
+      <c r="H184">
+        <v>0</v>
+      </c>
+      <c r="I184">
+        <v>0</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11">
+      <c r="A185" t="s">
+        <v>54</v>
+      </c>
+      <c r="B185" t="s">
+        <v>134</v>
+      </c>
+      <c r="C185">
+        <v>1</v>
+      </c>
+      <c r="D185" t="s">
+        <v>138</v>
+      </c>
+      <c r="E185">
+        <v>0</v>
+      </c>
+      <c r="F185">
+        <v>1</v>
+      </c>
+      <c r="G185">
+        <v>2</v>
+      </c>
+      <c r="H185">
+        <v>0</v>
+      </c>
+      <c r="I185">
+        <v>0</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11">
+      <c r="A186" t="s">
+        <v>55</v>
+      </c>
+      <c r="B186" t="s">
+        <v>125</v>
+      </c>
+      <c r="C186">
+        <v>3</v>
+      </c>
+      <c r="D186" t="s">
+        <v>139</v>
+      </c>
+      <c r="E186">
+        <v>0</v>
+      </c>
+      <c r="F186">
+        <v>5</v>
+      </c>
+      <c r="G186">
+        <v>6</v>
+      </c>
+      <c r="H186">
+        <v>0</v>
+      </c>
+      <c r="I186">
+        <v>0</v>
+      </c>
+      <c r="J186">
+        <v>3</v>
+      </c>
+      <c r="K186" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11">
+      <c r="A187" t="s">
+        <v>55</v>
+      </c>
+      <c r="B187" t="s">
+        <v>126</v>
+      </c>
+      <c r="C187">
+        <v>1.5</v>
+      </c>
+      <c r="D187" t="s">
+        <v>139</v>
+      </c>
+      <c r="E187">
+        <v>0</v>
+      </c>
+      <c r="F187">
+        <v>3</v>
+      </c>
+      <c r="G187">
+        <v>0</v>
+      </c>
+      <c r="H187">
+        <v>0</v>
+      </c>
+      <c r="I187">
+        <v>4</v>
+      </c>
+      <c r="J187">
+        <v>2</v>
+      </c>
+      <c r="K187" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11">
+      <c r="A188" t="s">
+        <v>55</v>
+      </c>
+      <c r="B188" t="s">
+        <v>125</v>
+      </c>
+      <c r="C188">
+        <v>3</v>
+      </c>
+      <c r="D188" t="s">
+        <v>139</v>
+      </c>
+      <c r="E188">
+        <v>0</v>
+      </c>
+      <c r="F188">
+        <v>5</v>
+      </c>
+      <c r="G188">
+        <v>0</v>
+      </c>
+      <c r="H188">
+        <v>0</v>
+      </c>
+      <c r="I188">
+        <v>9</v>
+      </c>
+      <c r="J188">
+        <v>4</v>
+      </c>
+      <c r="K188" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11">
+      <c r="A189" t="s">
+        <v>55</v>
+      </c>
+      <c r="B189" t="s">
+        <v>126</v>
+      </c>
+      <c r="C189">
+        <v>1.5</v>
+      </c>
+      <c r="D189" t="s">
+        <v>139</v>
+      </c>
+      <c r="E189">
+        <v>0</v>
+      </c>
+      <c r="F189">
+        <v>3</v>
+      </c>
+      <c r="G189">
+        <v>0</v>
+      </c>
+      <c r="H189">
+        <v>0</v>
+      </c>
+      <c r="I189">
+        <v>6</v>
+      </c>
+      <c r="J189">
+        <v>2</v>
+      </c>
+      <c r="K189" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11">
+      <c r="A190" t="s">
+        <v>56</v>
+      </c>
+      <c r="B190" t="s">
+        <v>135</v>
+      </c>
+      <c r="C190">
+        <v>3</v>
+      </c>
+      <c r="D190" t="s">
+        <v>140</v>
+      </c>
+      <c r="E190">
+        <v>0</v>
+      </c>
+      <c r="F190">
+        <v>3</v>
+      </c>
+      <c r="G190">
+        <v>6</v>
+      </c>
+      <c r="H190">
+        <v>0</v>
+      </c>
+      <c r="I190">
+        <v>0</v>
+      </c>
+      <c r="J190">
+        <v>2</v>
+      </c>
+      <c r="K190" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11">
+      <c r="A191" t="s">
+        <v>56</v>
+      </c>
+      <c r="B191" t="s">
+        <v>136</v>
+      </c>
+      <c r="C191">
+        <v>3</v>
+      </c>
+      <c r="D191" t="s">
+        <v>140</v>
+      </c>
+      <c r="E191">
+        <v>0</v>
+      </c>
+      <c r="F191">
+        <v>3</v>
+      </c>
+      <c r="G191">
+        <v>6</v>
+      </c>
+      <c r="H191">
+        <v>0</v>
+      </c>
+      <c r="I191">
+        <v>0</v>
+      </c>
+      <c r="J191">
+        <v>2</v>
+      </c>
+      <c r="K191" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11">
+      <c r="A192" t="s">
+        <v>57</v>
+      </c>
+      <c r="B192" t="s">
+        <v>123</v>
+      </c>
+      <c r="C192">
+        <v>4</v>
+      </c>
+      <c r="D192" t="s">
+        <v>140</v>
+      </c>
+      <c r="E192">
+        <v>0</v>
+      </c>
+      <c r="F192">
+        <v>4</v>
+      </c>
+      <c r="G192">
+        <v>0</v>
+      </c>
+      <c r="H192">
+        <v>0</v>
+      </c>
+      <c r="I192">
+        <v>5</v>
+      </c>
+      <c r="J192">
+        <v>2</v>
+      </c>
+      <c r="K192" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11">
+      <c r="A193" t="s">
+        <v>57</v>
+      </c>
+      <c r="B193" t="s">
+        <v>123</v>
+      </c>
+      <c r="C193" t="s">
+        <v>137</v>
+      </c>
+      <c r="D193" t="s">
+        <v>140</v>
+      </c>
+      <c r="E193">
+        <v>0</v>
+      </c>
+      <c r="F193">
+        <v>4</v>
+      </c>
+      <c r="G193">
+        <v>0</v>
+      </c>
+      <c r="H193">
+        <v>0</v>
+      </c>
+      <c r="I193">
+        <v>8</v>
+      </c>
+      <c r="J193">
+        <v>3</v>
+      </c>
+      <c r="K193" t="s">
+        <v>142</v>
       </c>
     </row>
   </sheetData>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="780" uniqueCount="143">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="227">
   <si>
     <t>Date</t>
   </si>
@@ -190,6 +190,57 @@
     <t>2021-11-16</t>
   </si>
   <si>
+    <t>2021-11-18</t>
+  </si>
+  <si>
+    <t>2021-11-20</t>
+  </si>
+  <si>
+    <t>2021-11-27</t>
+  </si>
+  <si>
+    <t>2021-11-29</t>
+  </si>
+  <si>
+    <t>2021-12-01</t>
+  </si>
+  <si>
+    <t>2021-12-02</t>
+  </si>
+  <si>
+    <t>2021-12-06</t>
+  </si>
+  <si>
+    <t>2021-12-08</t>
+  </si>
+  <si>
+    <t>2021-12-09</t>
+  </si>
+  <si>
+    <t>2021-12-14</t>
+  </si>
+  <si>
+    <t>2021-12-16</t>
+  </si>
+  <si>
+    <t>2021-12-18</t>
+  </si>
+  <si>
+    <t>2021-12-20</t>
+  </si>
+  <si>
+    <t>2021-12-21</t>
+  </si>
+  <si>
+    <t>2022-01-10</t>
+  </si>
+  <si>
+    <t>2022-01-11</t>
+  </si>
+  <si>
+    <t>2022-01-13</t>
+  </si>
+  <si>
     <t>DG27001</t>
   </si>
   <si>
@@ -247,6 +298,9 @@
     <t>DG22002</t>
   </si>
   <si>
+    <t>DG22003</t>
+  </si>
+  <si>
     <t>DG34002</t>
   </si>
   <si>
@@ -289,9 +343,6 @@
     <t>DG32004</t>
   </si>
   <si>
-    <t>DG22003</t>
-  </si>
-  <si>
     <t>DG32005</t>
   </si>
   <si>
@@ -427,7 +478,205 @@
     <t>DG39002</t>
   </si>
   <si>
-    <t>4</t>
+    <t>DG23001</t>
+  </si>
+  <si>
+    <t>DG23002</t>
+  </si>
+  <si>
+    <t>DG23003</t>
+  </si>
+  <si>
+    <t>DG23004</t>
+  </si>
+  <si>
+    <t>DG23005</t>
+  </si>
+  <si>
+    <t>DG23006</t>
+  </si>
+  <si>
+    <t>DG23007</t>
+  </si>
+  <si>
+    <t>DG26009</t>
+  </si>
+  <si>
+    <t>DG26008</t>
+  </si>
+  <si>
+    <t>DG26007</t>
+  </si>
+  <si>
+    <t>DG26006</t>
+  </si>
+  <si>
+    <t>DG28001</t>
+  </si>
+  <si>
+    <t>DG28002</t>
+  </si>
+  <si>
+    <t>DG28003</t>
+  </si>
+  <si>
+    <t>DG28004</t>
+  </si>
+  <si>
+    <t>DG28005</t>
+  </si>
+  <si>
+    <t>DG28006</t>
+  </si>
+  <si>
+    <t>DG26003</t>
+  </si>
+  <si>
+    <t>DG26004</t>
+  </si>
+  <si>
+    <t>DG26005</t>
+  </si>
+  <si>
+    <t>DG21001</t>
+  </si>
+  <si>
+    <t>DG21002</t>
+  </si>
+  <si>
+    <t>DG21003</t>
+  </si>
+  <si>
+    <t>DG26001</t>
+  </si>
+  <si>
+    <t>DG26002</t>
+  </si>
+  <si>
+    <t>DG30001</t>
+  </si>
+  <si>
+    <t>DG30002</t>
+  </si>
+  <si>
+    <t>DG30003</t>
+  </si>
+  <si>
+    <t>DG30004</t>
+  </si>
+  <si>
+    <t>DG28007</t>
+  </si>
+  <si>
+    <t>DG30005</t>
+  </si>
+  <si>
+    <t>DG30006</t>
+  </si>
+  <si>
+    <t>DG30007</t>
+  </si>
+  <si>
+    <t>N14</t>
+  </si>
+  <si>
+    <t>1.300</t>
+  </si>
+  <si>
+    <t>3.024</t>
+  </si>
+  <si>
+    <t>3.026</t>
+  </si>
+  <si>
+    <t>3.002</t>
+  </si>
+  <si>
+    <t>3.004</t>
+  </si>
+  <si>
+    <t>3.055</t>
+  </si>
+  <si>
+    <t>3.127</t>
+  </si>
+  <si>
+    <t>3.099</t>
+  </si>
+  <si>
+    <t>3.005</t>
+  </si>
+  <si>
+    <t>0.143</t>
+  </si>
+  <si>
+    <t>2.997</t>
+  </si>
+  <si>
+    <t>2.996</t>
+  </si>
+  <si>
+    <t>3.016</t>
+  </si>
+  <si>
+    <t>3.027</t>
+  </si>
+  <si>
+    <t>3.015</t>
+  </si>
+  <si>
+    <t>2.984</t>
+  </si>
+  <si>
+    <t>2.978</t>
+  </si>
+  <si>
+    <t>2.078</t>
+  </si>
+  <si>
+    <t>2.974</t>
+  </si>
+  <si>
+    <t>0.844</t>
+  </si>
+  <si>
+    <t>3.013</t>
+  </si>
+  <si>
+    <t>3.054</t>
+  </si>
+  <si>
+    <t>3.141</t>
+  </si>
+  <si>
+    <t>3.136</t>
+  </si>
+  <si>
+    <t>2.697</t>
+  </si>
+  <si>
+    <t>2.994</t>
+  </si>
+  <si>
+    <t>2.992</t>
+  </si>
+  <si>
+    <t>3.036</t>
+  </si>
+  <si>
+    <t>3.010</t>
+  </si>
+  <si>
+    <t>3.041</t>
+  </si>
+  <si>
+    <t>3.003</t>
+  </si>
+  <si>
+    <t>3.039</t>
+  </si>
+  <si>
+    <t>3.001</t>
   </si>
   <si>
     <t>N41</t>
@@ -440,6 +689,9 @@
   </si>
   <si>
     <t>97F1692</t>
+  </si>
+  <si>
+    <t>MN1</t>
   </si>
   <si>
     <t>2021/22</t>
@@ -800,7 +1052,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K193"/>
+  <dimension ref="A1:K298"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -843,13 +1095,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -870,7 +1122,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -878,13 +1130,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -905,7 +1157,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -913,13 +1165,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -940,7 +1192,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -948,13 +1200,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C5">
         <v>4.634</v>
       </c>
       <c r="D5" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -975,7 +1227,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -983,13 +1235,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1010,7 +1262,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1018,13 +1270,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1045,7 +1297,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1053,13 +1305,13 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1080,7 +1332,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1088,13 +1340,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1115,7 +1367,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1123,13 +1375,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1150,7 +1402,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1158,13 +1410,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1185,7 +1437,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1193,13 +1445,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C12">
         <v>4.634</v>
       </c>
       <c r="D12" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1220,7 +1472,7 @@
         <v>4</v>
       </c>
       <c r="K12" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1228,13 +1480,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1255,7 +1507,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1263,13 +1515,13 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1290,7 +1542,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1298,13 +1550,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1325,7 +1577,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1333,13 +1585,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1360,7 +1612,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1368,13 +1620,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1395,7 +1647,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1403,13 +1655,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1430,7 +1682,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1438,13 +1690,13 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1465,7 +1717,7 @@
         <v>2</v>
       </c>
       <c r="K19" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1473,13 +1725,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1500,7 +1752,7 @@
         <v>2</v>
       </c>
       <c r="K20" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1508,13 +1760,13 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1535,7 +1787,7 @@
         <v>2</v>
       </c>
       <c r="K21" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1543,13 +1795,13 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1570,7 +1822,7 @@
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1578,13 +1830,13 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1605,7 +1857,7 @@
         <v>2</v>
       </c>
       <c r="K23" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1613,13 +1865,13 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C24">
         <v>0.452</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1640,7 +1892,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1648,13 +1900,13 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1675,7 +1927,7 @@
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1683,13 +1935,13 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1710,7 +1962,7 @@
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1718,13 +1970,13 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1745,7 +1997,7 @@
         <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -1753,13 +2005,13 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>76</v>
+        <v>94</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -1780,7 +2032,7 @@
         <v>2</v>
       </c>
       <c r="K28" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -1788,13 +2040,13 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -1815,7 +2067,7 @@
         <v>2</v>
       </c>
       <c r="K29" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -1823,13 +2075,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -1850,7 +2102,7 @@
         <v>2</v>
       </c>
       <c r="K30" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -1858,13 +2110,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -1885,7 +2137,7 @@
         <v>2</v>
       </c>
       <c r="K31" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -1893,13 +2145,13 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C32">
         <v>0.08400000000000001</v>
       </c>
       <c r="D32" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -1920,7 +2172,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -1928,13 +2180,13 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -1955,7 +2207,7 @@
         <v>2</v>
       </c>
       <c r="K33" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -1963,13 +2215,13 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -1990,7 +2242,7 @@
         <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -1998,13 +2250,13 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2025,7 +2277,7 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2033,13 +2285,13 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2060,7 +2312,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2068,13 +2320,13 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2095,7 +2347,7 @@
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2103,13 +2355,13 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C38">
         <v>0.452</v>
       </c>
       <c r="D38" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2130,7 +2382,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2138,13 +2390,13 @@
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2165,7 +2417,7 @@
         <v>3</v>
       </c>
       <c r="K39" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2173,13 +2425,13 @@
         <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>59</v>
+        <v>76</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2200,7 +2452,7 @@
         <v>3</v>
       </c>
       <c r="K40" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2208,13 +2460,13 @@
         <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>60</v>
+        <v>77</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2235,7 +2487,7 @@
         <v>3</v>
       </c>
       <c r="K41" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2243,13 +2495,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2270,7 +2522,7 @@
         <v>3</v>
       </c>
       <c r="K42" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2278,13 +2530,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2305,7 +2557,7 @@
         <v>3</v>
       </c>
       <c r="K43" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2313,13 +2565,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2337,7 +2589,7 @@
         <v>6</v>
       </c>
       <c r="K44" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2345,13 +2597,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2372,7 +2624,7 @@
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2380,13 +2632,13 @@
         <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2407,7 +2659,7 @@
         <v>3</v>
       </c>
       <c r="K46" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2415,13 +2667,13 @@
         <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2442,7 +2694,7 @@
         <v>3</v>
       </c>
       <c r="K47" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2450,13 +2702,13 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2477,7 +2729,7 @@
         <v>3</v>
       </c>
       <c r="K48" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2485,13 +2737,13 @@
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2512,7 +2764,7 @@
         <v>3</v>
       </c>
       <c r="K49" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2520,13 +2772,13 @@
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C50">
         <v>0.845</v>
       </c>
       <c r="D50" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2547,7 +2799,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2555,13 +2807,13 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2582,7 +2834,7 @@
         <v>3</v>
       </c>
       <c r="K51" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2590,13 +2842,13 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2617,7 +2869,7 @@
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2625,13 +2877,13 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2652,7 +2904,7 @@
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2660,13 +2912,13 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2687,7 +2939,7 @@
         <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2695,13 +2947,13 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C55">
         <v>0.08400000000000001</v>
       </c>
       <c r="D55" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2722,7 +2974,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2730,13 +2982,13 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -2757,7 +3009,7 @@
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -2765,13 +3017,13 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -2792,7 +3044,7 @@
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -2800,13 +3052,13 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -2827,7 +3079,7 @@
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -2835,13 +3087,13 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -2862,7 +3114,7 @@
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -2870,13 +3122,13 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>62</v>
+        <v>79</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -2897,7 +3149,7 @@
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -2905,13 +3157,13 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -2932,7 +3184,7 @@
         <v>3</v>
       </c>
       <c r="K61" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -2940,13 +3192,13 @@
         <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>64</v>
+        <v>81</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -2967,7 +3219,7 @@
         <v>3</v>
       </c>
       <c r="K62" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -2975,13 +3227,13 @@
         <v>26</v>
       </c>
       <c r="B63" t="s">
-        <v>61</v>
+        <v>78</v>
       </c>
       <c r="C63">
         <v>4.634</v>
       </c>
       <c r="D63" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3002,7 +3254,7 @@
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3010,13 +3262,13 @@
         <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3037,7 +3289,7 @@
         <v>2</v>
       </c>
       <c r="K64" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3045,13 +3297,13 @@
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -3072,7 +3324,7 @@
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3080,13 +3332,13 @@
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -3107,7 +3359,7 @@
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3115,13 +3367,13 @@
         <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -3142,7 +3394,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3150,13 +3402,13 @@
         <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -3177,7 +3429,7 @@
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3185,13 +3437,13 @@
         <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3212,7 +3464,7 @@
         <v>2</v>
       </c>
       <c r="K69" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3220,13 +3472,13 @@
         <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3247,7 +3499,7 @@
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3255,13 +3507,13 @@
         <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3282,7 +3534,7 @@
         <v>2</v>
       </c>
       <c r="K71" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3290,13 +3542,13 @@
         <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C72">
         <v>0.08400000000000001</v>
       </c>
       <c r="D72" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3317,7 +3569,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3325,13 +3577,13 @@
         <v>28</v>
       </c>
       <c r="B73" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3352,7 +3604,7 @@
         <v>2</v>
       </c>
       <c r="K73" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3360,13 +3612,13 @@
         <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3387,7 +3639,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3395,13 +3647,13 @@
         <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3422,7 +3674,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3430,13 +3682,13 @@
         <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>75</v>
+        <v>92</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3457,7 +3709,7 @@
         <v>3</v>
       </c>
       <c r="K76" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3465,13 +3717,13 @@
         <v>29</v>
       </c>
       <c r="B77" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3492,7 +3744,7 @@
         <v>3</v>
       </c>
       <c r="K77" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3500,13 +3752,13 @@
         <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C78">
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3527,7 +3779,7 @@
         <v>3</v>
       </c>
       <c r="K78" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3535,13 +3787,13 @@
         <v>29</v>
       </c>
       <c r="B79" t="s">
-        <v>81</v>
+        <v>99</v>
       </c>
       <c r="C79">
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3562,7 +3814,7 @@
         <v>3</v>
       </c>
       <c r="K79" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3570,13 +3822,13 @@
         <v>30</v>
       </c>
       <c r="B80" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3597,7 +3849,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3605,13 +3857,13 @@
         <v>30</v>
       </c>
       <c r="B81" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C81">
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -3632,7 +3884,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3640,13 +3892,13 @@
         <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C82">
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3667,7 +3919,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3675,13 +3927,13 @@
         <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3702,7 +3954,7 @@
         <v>3</v>
       </c>
       <c r="K83" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3710,13 +3962,13 @@
         <v>30</v>
       </c>
       <c r="B84" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3737,7 +3989,7 @@
         <v>3</v>
       </c>
       <c r="K84" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3745,13 +3997,13 @@
         <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C85">
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -3772,7 +4024,7 @@
         <v>3</v>
       </c>
       <c r="K85" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -3780,13 +4032,13 @@
         <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>82</v>
+        <v>100</v>
       </c>
       <c r="C86">
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -3807,7 +4059,7 @@
         <v>3</v>
       </c>
       <c r="K86" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -3815,13 +4067,13 @@
         <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>83</v>
+        <v>101</v>
       </c>
       <c r="C87">
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -3842,7 +4094,7 @@
         <v>3</v>
       </c>
       <c r="K87" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -3850,13 +4102,13 @@
         <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="C88">
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -3877,7 +4129,7 @@
         <v>3</v>
       </c>
       <c r="K88" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -3885,13 +4137,13 @@
         <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -3912,7 +4164,7 @@
         <v>3</v>
       </c>
       <c r="K89" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -3920,13 +4172,13 @@
         <v>31</v>
       </c>
       <c r="B90" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="C90">
         <v>0.421</v>
       </c>
       <c r="D90" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -3947,7 +4199,7 @@
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -3955,13 +4207,13 @@
         <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>74</v>
+        <v>91</v>
       </c>
       <c r="C91">
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -3982,7 +4234,7 @@
         <v>3</v>
       </c>
       <c r="K91" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -3990,13 +4242,13 @@
         <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="C92">
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -4017,7 +4269,7 @@
         <v>3</v>
       </c>
       <c r="K92" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4025,13 +4277,13 @@
         <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>78</v>
+        <v>96</v>
       </c>
       <c r="C93">
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -4052,7 +4304,7 @@
         <v>3</v>
       </c>
       <c r="K93" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -4060,13 +4312,13 @@
         <v>30</v>
       </c>
       <c r="B94" t="s">
-        <v>79</v>
+        <v>97</v>
       </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -4087,7 +4339,7 @@
         <v>3</v>
       </c>
       <c r="K94" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -4095,13 +4347,13 @@
         <v>30</v>
       </c>
       <c r="B95" t="s">
-        <v>80</v>
+        <v>98</v>
       </c>
       <c r="C95">
         <v>0.08400000000000001</v>
       </c>
       <c r="D95" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -4122,7 +4374,7 @@
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -4130,13 +4382,13 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C96">
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -4157,7 +4409,7 @@
         <v>3</v>
       </c>
       <c r="K96" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4165,13 +4417,13 @@
         <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C97">
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -4192,7 +4444,7 @@
         <v>3</v>
       </c>
       <c r="K97" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -4200,13 +4452,13 @@
         <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C98">
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -4227,7 +4479,7 @@
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -4235,13 +4487,13 @@
         <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C99">
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4262,7 +4514,7 @@
         <v>3</v>
       </c>
       <c r="K99" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4270,13 +4522,13 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>65</v>
+        <v>82</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4297,7 +4549,7 @@
         <v>3</v>
       </c>
       <c r="K100" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4305,13 +4557,13 @@
         <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>66</v>
+        <v>83</v>
       </c>
       <c r="C101">
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4332,7 +4584,7 @@
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -4340,13 +4592,13 @@
         <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>67</v>
+        <v>84</v>
       </c>
       <c r="C102">
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4367,7 +4619,7 @@
         <v>3</v>
       </c>
       <c r="K102" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -4375,13 +4627,13 @@
         <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C103">
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4402,7 +4654,7 @@
         <v>3</v>
       </c>
       <c r="K103" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4410,13 +4662,13 @@
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C104">
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4437,7 +4689,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4445,13 +4697,13 @@
         <v>35</v>
       </c>
       <c r="B105" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C105">
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4472,7 +4724,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -4480,13 +4732,13 @@
         <v>35</v>
       </c>
       <c r="B106" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -4507,7 +4759,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4515,13 +4767,13 @@
         <v>35</v>
       </c>
       <c r="B107" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C107">
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4542,7 +4794,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4550,13 +4802,13 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C108">
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4577,7 +4829,7 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4585,13 +4837,13 @@
         <v>35</v>
       </c>
       <c r="B109" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C109">
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4612,7 +4864,7 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -4620,13 +4872,13 @@
         <v>36</v>
       </c>
       <c r="B110" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C110">
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4647,7 +4899,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4655,13 +4907,13 @@
         <v>36</v>
       </c>
       <c r="B111" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C111">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -4682,7 +4934,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4690,13 +4942,13 @@
         <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="C112">
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="E112">
         <v>9</v>
@@ -4717,7 +4969,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4725,13 +4977,13 @@
         <v>37</v>
       </c>
       <c r="B113" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="C113">
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>141</v>
+        <v>224</v>
       </c>
       <c r="E113">
         <v>9</v>
@@ -4752,7 +5004,7 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -4760,13 +5012,13 @@
         <v>37</v>
       </c>
       <c r="B114" t="s">
-        <v>69</v>
+        <v>86</v>
       </c>
       <c r="C114">
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -4787,7 +5039,7 @@
         <v>3</v>
       </c>
       <c r="K114" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -4795,13 +5047,13 @@
         <v>37</v>
       </c>
       <c r="B115" t="s">
-        <v>70</v>
+        <v>87</v>
       </c>
       <c r="C115">
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -4822,7 +5074,7 @@
         <v>3</v>
       </c>
       <c r="K115" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -4830,13 +5082,13 @@
         <v>37</v>
       </c>
       <c r="B116" t="s">
-        <v>71</v>
+        <v>88</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -4857,7 +5109,7 @@
         <v>3</v>
       </c>
       <c r="K116" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -4865,13 +5117,13 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>72</v>
+        <v>89</v>
       </c>
       <c r="C117">
         <v>3</v>
       </c>
       <c r="D117" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -4892,7 +5144,7 @@
         <v>3</v>
       </c>
       <c r="K117" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -4900,13 +5152,13 @@
         <v>37</v>
       </c>
       <c r="B118" t="s">
-        <v>73</v>
+        <v>90</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -4927,7 +5179,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -4935,13 +5187,13 @@
         <v>37</v>
       </c>
       <c r="B119" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C119">
         <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -4962,7 +5214,7 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -4970,13 +5222,13 @@
         <v>37</v>
       </c>
       <c r="B120" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C120">
         <v>3</v>
       </c>
       <c r="D120" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -4997,7 +5249,7 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -5005,13 +5257,13 @@
         <v>38</v>
       </c>
       <c r="B121" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C121">
         <v>3</v>
       </c>
       <c r="D121" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -5032,7 +5284,7 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5040,13 +5292,13 @@
         <v>38</v>
       </c>
       <c r="B122" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C122">
         <v>3</v>
       </c>
       <c r="D122" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -5067,7 +5319,7 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -5075,13 +5327,13 @@
         <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C123">
         <v>3</v>
       </c>
       <c r="D123" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -5102,7 +5354,7 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -5110,13 +5362,13 @@
         <v>38</v>
       </c>
       <c r="B124" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="C124">
         <v>3</v>
       </c>
       <c r="D124" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E124">
         <v>9</v>
@@ -5137,7 +5389,7 @@
         <v>4</v>
       </c>
       <c r="K124" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -5145,13 +5397,13 @@
         <v>38</v>
       </c>
       <c r="B125" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="C125">
         <v>3</v>
       </c>
       <c r="D125" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E125">
         <v>9</v>
@@ -5172,7 +5424,7 @@
         <v>4</v>
       </c>
       <c r="K125" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5180,13 +5432,13 @@
         <v>39</v>
       </c>
       <c r="B126" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C126">
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E126">
         <v>9</v>
@@ -5207,7 +5459,7 @@
         <v>4</v>
       </c>
       <c r="K126" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5215,13 +5467,13 @@
         <v>39</v>
       </c>
       <c r="B127" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="C127">
         <v>3</v>
       </c>
       <c r="D127" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E127">
         <v>9</v>
@@ -5242,7 +5494,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5250,13 +5502,13 @@
         <v>40</v>
       </c>
       <c r="B128" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
       <c r="C128">
         <v>3</v>
       </c>
       <c r="D128" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E128">
         <v>9</v>
@@ -5277,7 +5529,7 @@
         <v>4</v>
       </c>
       <c r="K128" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -5285,13 +5537,13 @@
         <v>40</v>
       </c>
       <c r="B129" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="C129">
         <v>3</v>
       </c>
       <c r="D129" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E129">
         <v>9</v>
@@ -5312,7 +5564,7 @@
         <v>4</v>
       </c>
       <c r="K129" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5320,13 +5572,13 @@
         <v>40</v>
       </c>
       <c r="B130" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="C130">
         <v>1</v>
       </c>
       <c r="D130" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E130">
         <v>4</v>
@@ -5347,7 +5599,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -5355,13 +5607,13 @@
         <v>41</v>
       </c>
       <c r="B131" t="s">
-        <v>87</v>
+        <v>105</v>
       </c>
       <c r="C131">
         <v>3</v>
       </c>
       <c r="D131" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -5382,7 +5634,7 @@
         <v>3</v>
       </c>
       <c r="K131" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -5390,13 +5642,13 @@
         <v>41</v>
       </c>
       <c r="B132" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="C132">
         <v>3</v>
       </c>
       <c r="D132" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -5417,7 +5669,7 @@
         <v>3</v>
       </c>
       <c r="K132" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -5425,13 +5677,13 @@
         <v>41</v>
       </c>
       <c r="B133" t="s">
-        <v>89</v>
+        <v>107</v>
       </c>
       <c r="C133">
         <v>3</v>
       </c>
       <c r="D133" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -5452,7 +5704,7 @@
         <v>3</v>
       </c>
       <c r="K133" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5460,13 +5712,13 @@
         <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>90</v>
+        <v>108</v>
       </c>
       <c r="C134">
         <v>3</v>
       </c>
       <c r="D134" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -5487,7 +5739,7 @@
         <v>3</v>
       </c>
       <c r="K134" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -5495,13 +5747,13 @@
         <v>42</v>
       </c>
       <c r="B135" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C135">
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -5522,7 +5774,7 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -5530,13 +5782,13 @@
         <v>42</v>
       </c>
       <c r="B136" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C136">
         <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -5557,7 +5809,7 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -5565,13 +5817,13 @@
         <v>43</v>
       </c>
       <c r="B137" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C137">
         <v>3</v>
       </c>
       <c r="D137" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -5592,7 +5844,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -5600,13 +5852,13 @@
         <v>43</v>
       </c>
       <c r="B138" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C138">
         <v>3</v>
       </c>
       <c r="D138" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -5627,7 +5879,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5635,13 +5887,13 @@
         <v>43</v>
       </c>
       <c r="B139" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C139">
         <v>3</v>
       </c>
       <c r="D139" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -5662,7 +5914,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5670,13 +5922,13 @@
         <v>44</v>
       </c>
       <c r="B140" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
       <c r="C140">
         <v>3</v>
       </c>
       <c r="D140" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -5697,7 +5949,7 @@
         <v>3</v>
       </c>
       <c r="K140" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -5705,13 +5957,13 @@
         <v>44</v>
       </c>
       <c r="B141" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="C141">
         <v>3</v>
       </c>
       <c r="D141" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -5732,7 +5984,7 @@
         <v>3</v>
       </c>
       <c r="K141" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -5740,13 +5992,13 @@
         <v>44</v>
       </c>
       <c r="B142" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="C142">
         <v>3</v>
       </c>
       <c r="D142" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -5767,7 +6019,7 @@
         <v>3</v>
       </c>
       <c r="K142" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -5775,13 +6027,13 @@
         <v>44</v>
       </c>
       <c r="B143" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C143">
         <v>1.89</v>
       </c>
       <c r="D143" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -5802,7 +6054,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -5810,13 +6062,13 @@
         <v>45</v>
       </c>
       <c r="B144" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C144">
         <v>3</v>
       </c>
       <c r="D144" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -5837,7 +6089,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -5845,13 +6097,13 @@
         <v>45</v>
       </c>
       <c r="B145" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C145">
         <v>3</v>
       </c>
       <c r="D145" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -5872,7 +6124,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -5880,13 +6132,13 @@
         <v>45</v>
       </c>
       <c r="B146" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C146">
         <v>3</v>
       </c>
       <c r="D146" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -5907,7 +6159,7 @@
         <v>2</v>
       </c>
       <c r="K146" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -5915,13 +6167,13 @@
         <v>46</v>
       </c>
       <c r="B147" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
       <c r="C147">
         <v>3</v>
       </c>
       <c r="D147" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -5942,7 +6194,7 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -5950,13 +6202,13 @@
         <v>46</v>
       </c>
       <c r="B148" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C148">
         <v>3</v>
       </c>
       <c r="D148" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -5977,7 +6229,7 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -5985,13 +6237,13 @@
         <v>46</v>
       </c>
       <c r="B149" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C149">
         <v>3</v>
       </c>
       <c r="D149" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -6012,7 +6264,7 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -6020,13 +6272,13 @@
         <v>47</v>
       </c>
       <c r="B150" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="C150">
         <v>3</v>
       </c>
       <c r="D150" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -6047,7 +6299,7 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6055,13 +6307,13 @@
         <v>47</v>
       </c>
       <c r="B151" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
       <c r="C151">
         <v>3</v>
       </c>
       <c r="D151" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -6082,7 +6334,7 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -6090,13 +6342,13 @@
         <v>47</v>
       </c>
       <c r="B152" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C152">
         <v>3</v>
       </c>
       <c r="D152" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -6117,7 +6369,7 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -6125,13 +6377,13 @@
         <v>47</v>
       </c>
       <c r="B153" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C153">
         <v>3</v>
       </c>
       <c r="D153" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -6152,7 +6404,7 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -6160,13 +6412,13 @@
         <v>48</v>
       </c>
       <c r="B154" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="C154">
         <v>3</v>
       </c>
       <c r="D154" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -6187,7 +6439,7 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -6195,13 +6447,13 @@
         <v>48</v>
       </c>
       <c r="B155" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="C155">
         <v>3</v>
       </c>
       <c r="D155" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -6222,7 +6474,7 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6230,13 +6482,13 @@
         <v>49</v>
       </c>
       <c r="B156" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="C156">
         <v>3</v>
       </c>
       <c r="D156" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -6257,7 +6509,7 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -6265,13 +6517,13 @@
         <v>49</v>
       </c>
       <c r="B157" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
       <c r="C157">
         <v>3</v>
       </c>
       <c r="D157" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -6292,7 +6544,7 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6300,13 +6552,13 @@
         <v>49</v>
       </c>
       <c r="B158" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C158">
         <v>2.897</v>
       </c>
       <c r="D158" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -6327,7 +6579,7 @@
         <v>2</v>
       </c>
       <c r="K158" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6335,13 +6587,13 @@
         <v>50</v>
       </c>
       <c r="B159" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C159">
         <v>3</v>
       </c>
       <c r="D159" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -6362,7 +6614,7 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -6370,13 +6622,13 @@
         <v>50</v>
       </c>
       <c r="B160" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C160">
         <v>3</v>
       </c>
       <c r="D160" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -6397,7 +6649,7 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -6405,13 +6657,13 @@
         <v>51</v>
       </c>
       <c r="B161" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C161">
         <v>3</v>
       </c>
       <c r="D161" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -6432,7 +6684,7 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -6440,13 +6692,13 @@
         <v>51</v>
       </c>
       <c r="B162" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C162">
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -6467,7 +6719,7 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -6475,13 +6727,13 @@
         <v>51</v>
       </c>
       <c r="B163" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C163">
         <v>3</v>
       </c>
       <c r="D163" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -6502,7 +6754,7 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -6510,13 +6762,13 @@
         <v>51</v>
       </c>
       <c r="B164" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="C164">
         <v>3</v>
       </c>
       <c r="D164" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -6537,7 +6789,7 @@
         <v>4</v>
       </c>
       <c r="K164" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -6545,13 +6797,13 @@
         <v>51</v>
       </c>
       <c r="B165" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="C165">
         <v>3</v>
       </c>
       <c r="D165" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -6572,7 +6824,7 @@
         <v>4</v>
       </c>
       <c r="K165" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -6580,13 +6832,13 @@
         <v>51</v>
       </c>
       <c r="B166" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="C166">
         <v>3</v>
       </c>
       <c r="D166" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -6607,7 +6859,7 @@
         <v>4</v>
       </c>
       <c r="K166" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -6615,13 +6867,13 @@
         <v>51</v>
       </c>
       <c r="B167" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="C167">
         <v>3</v>
       </c>
       <c r="D167" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -6642,7 +6894,7 @@
         <v>4</v>
       </c>
       <c r="K167" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -6650,13 +6902,13 @@
         <v>51</v>
       </c>
       <c r="B168" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C168">
         <v>3</v>
       </c>
       <c r="D168" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -6677,7 +6929,7 @@
         <v>4</v>
       </c>
       <c r="K168" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6685,13 +6937,13 @@
         <v>52</v>
       </c>
       <c r="B169" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="C169">
         <v>3</v>
       </c>
       <c r="D169" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -6712,7 +6964,7 @@
         <v>2</v>
       </c>
       <c r="K169" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -6720,13 +6972,13 @@
         <v>52</v>
       </c>
       <c r="B170" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="C170">
         <v>3</v>
       </c>
       <c r="D170" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -6747,7 +6999,7 @@
         <v>2</v>
       </c>
       <c r="K170" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -6755,13 +7007,13 @@
         <v>52</v>
       </c>
       <c r="B171" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="C171">
         <v>3</v>
       </c>
       <c r="D171" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -6782,7 +7034,7 @@
         <v>2</v>
       </c>
       <c r="K171" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -6790,13 +7042,13 @@
         <v>52</v>
       </c>
       <c r="B172" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="C172">
         <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -6817,7 +7069,7 @@
         <v>4</v>
       </c>
       <c r="K172" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -6825,13 +7077,13 @@
         <v>52</v>
       </c>
       <c r="B173" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="C173">
         <v>3</v>
       </c>
       <c r="D173" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -6852,7 +7104,7 @@
         <v>4</v>
       </c>
       <c r="K173" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -6860,13 +7112,13 @@
         <v>52</v>
       </c>
       <c r="B174" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="C174">
         <v>3</v>
       </c>
       <c r="D174" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -6887,7 +7139,7 @@
         <v>4</v>
       </c>
       <c r="K174" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -6895,13 +7147,13 @@
         <v>53</v>
       </c>
       <c r="B175" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C175">
         <v>3</v>
       </c>
       <c r="D175" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -6922,7 +7174,7 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -6930,13 +7182,13 @@
         <v>53</v>
       </c>
       <c r="B176" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C176">
         <v>3</v>
       </c>
       <c r="D176" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -6957,7 +7209,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -6965,13 +7217,13 @@
         <v>53</v>
       </c>
       <c r="B177" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C177">
         <v>3</v>
       </c>
       <c r="D177" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -6992,7 +7244,7 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -7000,13 +7252,13 @@
         <v>53</v>
       </c>
       <c r="B178" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="C178">
         <v>3</v>
       </c>
       <c r="D178" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -7027,7 +7279,7 @@
         <v>4</v>
       </c>
       <c r="K178" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -7035,13 +7287,13 @@
         <v>53</v>
       </c>
       <c r="B179" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="C179">
         <v>3</v>
       </c>
       <c r="D179" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -7062,7 +7314,7 @@
         <v>4</v>
       </c>
       <c r="K179" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -7070,13 +7322,13 @@
         <v>53</v>
       </c>
       <c r="B180" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="C180">
         <v>3</v>
       </c>
       <c r="D180" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -7097,7 +7349,7 @@
         <v>4</v>
       </c>
       <c r="K180" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7105,13 +7357,13 @@
         <v>54</v>
       </c>
       <c r="B181" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
       <c r="C181">
         <v>3</v>
       </c>
       <c r="D181" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -7132,7 +7384,7 @@
         <v>2</v>
       </c>
       <c r="K181" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7140,13 +7392,13 @@
         <v>54</v>
       </c>
       <c r="B182" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="C182">
         <v>3</v>
       </c>
       <c r="D182" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -7167,7 +7419,7 @@
         <v>2</v>
       </c>
       <c r="K182" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -7175,13 +7427,13 @@
         <v>54</v>
       </c>
       <c r="B183" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
       <c r="C183">
         <v>3</v>
       </c>
       <c r="D183" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -7202,7 +7454,7 @@
         <v>2</v>
       </c>
       <c r="K183" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7210,13 +7462,13 @@
         <v>54</v>
       </c>
       <c r="B184" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="C184">
         <v>1.5</v>
       </c>
       <c r="D184" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -7237,7 +7489,7 @@
         <v>1</v>
       </c>
       <c r="K184" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7245,13 +7497,13 @@
         <v>54</v>
       </c>
       <c r="B185" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -7272,7 +7524,7 @@
         <v>1</v>
       </c>
       <c r="K185" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7280,13 +7532,13 @@
         <v>55</v>
       </c>
       <c r="B186" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C186">
         <v>3</v>
       </c>
       <c r="D186" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -7307,7 +7559,7 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -7315,13 +7567,13 @@
         <v>55</v>
       </c>
       <c r="B187" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C187">
         <v>1.5</v>
       </c>
       <c r="D187" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -7342,7 +7594,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7350,13 +7602,13 @@
         <v>55</v>
       </c>
       <c r="B188" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C188">
         <v>3</v>
       </c>
       <c r="D188" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -7377,7 +7629,7 @@
         <v>4</v>
       </c>
       <c r="K188" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7385,13 +7637,13 @@
         <v>55</v>
       </c>
       <c r="B189" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
       <c r="C189">
         <v>1.5</v>
       </c>
       <c r="D189" t="s">
-        <v>139</v>
+        <v>222</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -7412,7 +7664,7 @@
         <v>2</v>
       </c>
       <c r="K189" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7420,13 +7672,13 @@
         <v>56</v>
       </c>
       <c r="B190" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C190">
         <v>3</v>
       </c>
       <c r="D190" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -7447,7 +7699,7 @@
         <v>2</v>
       </c>
       <c r="K190" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7455,13 +7707,13 @@
         <v>56</v>
       </c>
       <c r="B191" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
       <c r="C191">
         <v>3</v>
       </c>
       <c r="D191" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -7482,7 +7734,7 @@
         <v>2</v>
       </c>
       <c r="K191" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -7490,13 +7742,13 @@
         <v>57</v>
       </c>
       <c r="B192" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="C192">
         <v>4</v>
       </c>
       <c r="D192" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -7517,7 +7769,7 @@
         <v>2</v>
       </c>
       <c r="K192" t="s">
-        <v>142</v>
+        <v>226</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -7525,13 +7777,13 @@
         <v>57</v>
       </c>
       <c r="B193" t="s">
-        <v>123</v>
-      </c>
-      <c r="C193" t="s">
-        <v>137</v>
+        <v>140</v>
+      </c>
+      <c r="C193">
+        <v>4</v>
       </c>
       <c r="D193" t="s">
-        <v>140</v>
+        <v>223</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -7552,7 +7804,3682 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>142</v>
+        <v>226</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11">
+      <c r="A194" t="s">
+        <v>57</v>
+      </c>
+      <c r="B194" t="s">
+        <v>121</v>
+      </c>
+      <c r="C194">
+        <v>3.001</v>
+      </c>
+      <c r="D194" t="s">
+        <v>187</v>
+      </c>
+      <c r="E194">
+        <v>0</v>
+      </c>
+      <c r="F194">
+        <v>5</v>
+      </c>
+      <c r="G194">
+        <v>0</v>
+      </c>
+      <c r="H194">
+        <v>0</v>
+      </c>
+      <c r="I194">
+        <v>6</v>
+      </c>
+      <c r="J194">
+        <v>3</v>
+      </c>
+      <c r="K194" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11">
+      <c r="A195" t="s">
+        <v>57</v>
+      </c>
+      <c r="B195" t="s">
+        <v>122</v>
+      </c>
+      <c r="C195">
+        <v>3.001</v>
+      </c>
+      <c r="D195" t="s">
+        <v>187</v>
+      </c>
+      <c r="E195">
+        <v>0</v>
+      </c>
+      <c r="F195">
+        <v>5</v>
+      </c>
+      <c r="G195">
+        <v>0</v>
+      </c>
+      <c r="H195">
+        <v>0</v>
+      </c>
+      <c r="I195">
+        <v>6</v>
+      </c>
+      <c r="J195">
+        <v>3</v>
+      </c>
+      <c r="K195" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11">
+      <c r="A196" t="s">
+        <v>57</v>
+      </c>
+      <c r="B196" t="s">
+        <v>134</v>
+      </c>
+      <c r="C196">
+        <v>1.3</v>
+      </c>
+      <c r="D196" t="s">
+        <v>187</v>
+      </c>
+      <c r="E196">
+        <v>0</v>
+      </c>
+      <c r="F196">
+        <v>2</v>
+      </c>
+      <c r="G196">
+        <v>0</v>
+      </c>
+      <c r="H196">
+        <v>0</v>
+      </c>
+      <c r="I196">
+        <v>3</v>
+      </c>
+      <c r="J196">
+        <v>1</v>
+      </c>
+      <c r="K196" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11">
+      <c r="A197" t="s">
+        <v>57</v>
+      </c>
+      <c r="B197" t="s">
+        <v>119</v>
+      </c>
+      <c r="C197">
+        <v>3.099</v>
+      </c>
+      <c r="D197" t="s">
+        <v>222</v>
+      </c>
+      <c r="E197">
+        <v>0</v>
+      </c>
+      <c r="F197">
+        <v>5</v>
+      </c>
+      <c r="G197">
+        <v>0</v>
+      </c>
+      <c r="H197">
+        <v>0</v>
+      </c>
+      <c r="I197">
+        <v>9</v>
+      </c>
+      <c r="J197">
+        <v>4</v>
+      </c>
+      <c r="K197" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11">
+      <c r="A198" t="s">
+        <v>57</v>
+      </c>
+      <c r="B198" t="s">
+        <v>120</v>
+      </c>
+      <c r="C198">
+        <v>3.093</v>
+      </c>
+      <c r="D198" t="s">
+        <v>222</v>
+      </c>
+      <c r="E198">
+        <v>0</v>
+      </c>
+      <c r="F198">
+        <v>5</v>
+      </c>
+      <c r="G198">
+        <v>0</v>
+      </c>
+      <c r="H198">
+        <v>0</v>
+      </c>
+      <c r="I198">
+        <v>9</v>
+      </c>
+      <c r="J198">
+        <v>4</v>
+      </c>
+      <c r="K198" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11">
+      <c r="A199" t="s">
+        <v>57</v>
+      </c>
+      <c r="B199" t="s">
+        <v>112</v>
+      </c>
+      <c r="C199">
+        <v>3.087</v>
+      </c>
+      <c r="D199" t="s">
+        <v>222</v>
+      </c>
+      <c r="E199">
+        <v>0</v>
+      </c>
+      <c r="F199">
+        <v>5</v>
+      </c>
+      <c r="G199">
+        <v>0</v>
+      </c>
+      <c r="H199">
+        <v>0</v>
+      </c>
+      <c r="I199">
+        <v>9</v>
+      </c>
+      <c r="J199">
+        <v>4</v>
+      </c>
+      <c r="K199" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11">
+      <c r="A200" t="s">
+        <v>58</v>
+      </c>
+      <c r="B200" t="s">
+        <v>123</v>
+      </c>
+      <c r="C200">
+        <v>3.055</v>
+      </c>
+      <c r="D200" t="s">
+        <v>222</v>
+      </c>
+      <c r="E200">
+        <v>0</v>
+      </c>
+      <c r="F200">
+        <v>0</v>
+      </c>
+      <c r="G200">
+        <v>0</v>
+      </c>
+      <c r="H200">
+        <v>0</v>
+      </c>
+      <c r="I200">
+        <v>9</v>
+      </c>
+      <c r="J200">
+        <v>2</v>
+      </c>
+      <c r="K200" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11">
+      <c r="A201" t="s">
+        <v>58</v>
+      </c>
+      <c r="B201" t="s">
+        <v>124</v>
+      </c>
+      <c r="C201">
+        <v>3.127</v>
+      </c>
+      <c r="D201" t="s">
+        <v>222</v>
+      </c>
+      <c r="E201">
+        <v>0</v>
+      </c>
+      <c r="F201">
+        <v>0</v>
+      </c>
+      <c r="G201">
+        <v>0</v>
+      </c>
+      <c r="H201">
+        <v>0</v>
+      </c>
+      <c r="I201">
+        <v>9</v>
+      </c>
+      <c r="J201">
+        <v>3</v>
+      </c>
+      <c r="K201" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11">
+      <c r="A202" t="s">
+        <v>58</v>
+      </c>
+      <c r="B202" t="s">
+        <v>118</v>
+      </c>
+      <c r="C202">
+        <v>3.089</v>
+      </c>
+      <c r="D202" t="s">
+        <v>222</v>
+      </c>
+      <c r="E202">
+        <v>0</v>
+      </c>
+      <c r="F202">
+        <v>0</v>
+      </c>
+      <c r="G202">
+        <v>0</v>
+      </c>
+      <c r="H202">
+        <v>0</v>
+      </c>
+      <c r="I202">
+        <v>9</v>
+      </c>
+      <c r="J202">
+        <v>3</v>
+      </c>
+      <c r="K202" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11">
+      <c r="A203" t="s">
+        <v>59</v>
+      </c>
+      <c r="B203" t="s">
+        <v>128</v>
+      </c>
+      <c r="C203">
+        <v>3.002</v>
+      </c>
+      <c r="D203" t="s">
+        <v>187</v>
+      </c>
+      <c r="E203">
+        <v>0</v>
+      </c>
+      <c r="F203">
+        <v>0</v>
+      </c>
+      <c r="G203">
+        <v>0</v>
+      </c>
+      <c r="H203">
+        <v>0</v>
+      </c>
+      <c r="I203">
+        <v>9</v>
+      </c>
+      <c r="J203">
+        <v>3</v>
+      </c>
+      <c r="K203" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11">
+      <c r="A204" t="s">
+        <v>59</v>
+      </c>
+      <c r="B204" t="s">
+        <v>129</v>
+      </c>
+      <c r="C204">
+        <v>3.004</v>
+      </c>
+      <c r="D204" t="s">
+        <v>187</v>
+      </c>
+      <c r="E204">
+        <v>0</v>
+      </c>
+      <c r="F204">
+        <v>0</v>
+      </c>
+      <c r="G204">
+        <v>0</v>
+      </c>
+      <c r="H204">
+        <v>0</v>
+      </c>
+      <c r="I204">
+        <v>9</v>
+      </c>
+      <c r="J204">
+        <v>3</v>
+      </c>
+      <c r="K204" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11">
+      <c r="A205" t="s">
+        <v>59</v>
+      </c>
+      <c r="B205" t="s">
+        <v>154</v>
+      </c>
+      <c r="C205">
+        <v>3.038</v>
+      </c>
+      <c r="D205" t="s">
+        <v>225</v>
+      </c>
+      <c r="E205">
+        <v>0</v>
+      </c>
+      <c r="F205">
+        <v>0</v>
+      </c>
+      <c r="G205">
+        <v>6</v>
+      </c>
+      <c r="H205">
+        <v>0</v>
+      </c>
+      <c r="I205">
+        <v>0</v>
+      </c>
+      <c r="J205">
+        <v>2</v>
+      </c>
+      <c r="K205" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11">
+      <c r="A206" t="s">
+        <v>59</v>
+      </c>
+      <c r="B206" t="s">
+        <v>155</v>
+      </c>
+      <c r="C206">
+        <v>3.025</v>
+      </c>
+      <c r="D206" t="s">
+        <v>225</v>
+      </c>
+      <c r="E206">
+        <v>0</v>
+      </c>
+      <c r="F206">
+        <v>0</v>
+      </c>
+      <c r="G206">
+        <v>6</v>
+      </c>
+      <c r="H206">
+        <v>0</v>
+      </c>
+      <c r="I206">
+        <v>0</v>
+      </c>
+      <c r="J206">
+        <v>3</v>
+      </c>
+      <c r="K206" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11">
+      <c r="A207" t="s">
+        <v>59</v>
+      </c>
+      <c r="B207" t="s">
+        <v>156</v>
+      </c>
+      <c r="C207">
+        <v>3.03</v>
+      </c>
+      <c r="D207" t="s">
+        <v>225</v>
+      </c>
+      <c r="E207">
+        <v>0</v>
+      </c>
+      <c r="F207">
+        <v>0</v>
+      </c>
+      <c r="G207">
+        <v>6</v>
+      </c>
+      <c r="H207">
+        <v>0</v>
+      </c>
+      <c r="I207">
+        <v>0</v>
+      </c>
+      <c r="J207">
+        <v>3</v>
+      </c>
+      <c r="K207" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11">
+      <c r="A208" t="s">
+        <v>60</v>
+      </c>
+      <c r="B208" t="s">
+        <v>125</v>
+      </c>
+      <c r="C208">
+        <v>3.136</v>
+      </c>
+      <c r="D208" t="s">
+        <v>221</v>
+      </c>
+      <c r="E208">
+        <v>0</v>
+      </c>
+      <c r="F208">
+        <v>0</v>
+      </c>
+      <c r="G208">
+        <v>0</v>
+      </c>
+      <c r="H208">
+        <v>0</v>
+      </c>
+      <c r="I208">
+        <v>9</v>
+      </c>
+      <c r="J208">
+        <v>3</v>
+      </c>
+      <c r="K208" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11">
+      <c r="A209" t="s">
+        <v>60</v>
+      </c>
+      <c r="B209" t="s">
+        <v>126</v>
+      </c>
+      <c r="C209">
+        <v>3.141</v>
+      </c>
+      <c r="D209" t="s">
+        <v>221</v>
+      </c>
+      <c r="E209">
+        <v>0</v>
+      </c>
+      <c r="F209">
+        <v>0</v>
+      </c>
+      <c r="G209">
+        <v>0</v>
+      </c>
+      <c r="H209">
+        <v>0</v>
+      </c>
+      <c r="I209">
+        <v>9</v>
+      </c>
+      <c r="J209">
+        <v>3</v>
+      </c>
+      <c r="K209" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11">
+      <c r="A210" t="s">
+        <v>60</v>
+      </c>
+      <c r="B210" t="s">
+        <v>127</v>
+      </c>
+      <c r="C210">
+        <v>2.697</v>
+      </c>
+      <c r="D210" t="s">
+        <v>221</v>
+      </c>
+      <c r="E210">
+        <v>0</v>
+      </c>
+      <c r="F210">
+        <v>0</v>
+      </c>
+      <c r="G210">
+        <v>0</v>
+      </c>
+      <c r="H210">
+        <v>0</v>
+      </c>
+      <c r="I210">
+        <v>6</v>
+      </c>
+      <c r="J210">
+        <v>2</v>
+      </c>
+      <c r="K210" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11">
+      <c r="A211" t="s">
+        <v>60</v>
+      </c>
+      <c r="B211" t="s">
+        <v>132</v>
+      </c>
+      <c r="C211">
+        <v>3.004</v>
+      </c>
+      <c r="D211" t="s">
+        <v>221</v>
+      </c>
+      <c r="E211">
+        <v>0</v>
+      </c>
+      <c r="F211">
+        <v>0</v>
+      </c>
+      <c r="G211">
+        <v>0</v>
+      </c>
+      <c r="H211">
+        <v>0</v>
+      </c>
+      <c r="I211">
+        <v>6</v>
+      </c>
+      <c r="J211">
+        <v>2</v>
+      </c>
+      <c r="K211" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11">
+      <c r="A212" t="s">
+        <v>60</v>
+      </c>
+      <c r="B212" t="s">
+        <v>133</v>
+      </c>
+      <c r="C212">
+        <v>3.005</v>
+      </c>
+      <c r="D212" t="s">
+        <v>187</v>
+      </c>
+      <c r="E212">
+        <v>0</v>
+      </c>
+      <c r="F212">
+        <v>0</v>
+      </c>
+      <c r="G212">
+        <v>0</v>
+      </c>
+      <c r="H212">
+        <v>0</v>
+      </c>
+      <c r="I212">
+        <v>6</v>
+      </c>
+      <c r="J212">
+        <v>2</v>
+      </c>
+      <c r="K212" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11">
+      <c r="A213" t="s">
+        <v>61</v>
+      </c>
+      <c r="B213" t="s">
+        <v>121</v>
+      </c>
+      <c r="C213">
+        <v>3.001</v>
+      </c>
+      <c r="D213" t="s">
+        <v>187</v>
+      </c>
+      <c r="E213">
+        <v>0</v>
+      </c>
+      <c r="F213">
+        <v>0</v>
+      </c>
+      <c r="G213">
+        <v>0</v>
+      </c>
+      <c r="H213">
+        <v>0</v>
+      </c>
+      <c r="I213">
+        <v>9</v>
+      </c>
+      <c r="J213">
+        <v>3</v>
+      </c>
+      <c r="K213" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11">
+      <c r="A214" t="s">
+        <v>61</v>
+      </c>
+      <c r="B214" t="s">
+        <v>122</v>
+      </c>
+      <c r="C214">
+        <v>3.001</v>
+      </c>
+      <c r="D214" t="s">
+        <v>187</v>
+      </c>
+      <c r="E214">
+        <v>0</v>
+      </c>
+      <c r="F214">
+        <v>0</v>
+      </c>
+      <c r="G214">
+        <v>0</v>
+      </c>
+      <c r="H214">
+        <v>0</v>
+      </c>
+      <c r="I214">
+        <v>9</v>
+      </c>
+      <c r="J214">
+        <v>3</v>
+      </c>
+      <c r="K214" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11">
+      <c r="A215" t="s">
+        <v>61</v>
+      </c>
+      <c r="B215" t="s">
+        <v>134</v>
+      </c>
+      <c r="C215">
+        <v>1.3</v>
+      </c>
+      <c r="D215" t="s">
+        <v>187</v>
+      </c>
+      <c r="E215">
+        <v>0</v>
+      </c>
+      <c r="F215">
+        <v>0</v>
+      </c>
+      <c r="G215">
+        <v>0</v>
+      </c>
+      <c r="H215">
+        <v>0</v>
+      </c>
+      <c r="I215">
+        <v>4</v>
+      </c>
+      <c r="J215">
+        <v>2</v>
+      </c>
+      <c r="K215" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11">
+      <c r="A216" t="s">
+        <v>61</v>
+      </c>
+      <c r="B216" t="s">
+        <v>157</v>
+      </c>
+      <c r="C216">
+        <v>3.03</v>
+      </c>
+      <c r="D216" t="s">
+        <v>225</v>
+      </c>
+      <c r="E216">
+        <v>0</v>
+      </c>
+      <c r="F216">
+        <v>0</v>
+      </c>
+      <c r="G216">
+        <v>6</v>
+      </c>
+      <c r="H216">
+        <v>0</v>
+      </c>
+      <c r="I216">
+        <v>0</v>
+      </c>
+      <c r="J216">
+        <v>2</v>
+      </c>
+      <c r="K216" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11">
+      <c r="A217" t="s">
+        <v>61</v>
+      </c>
+      <c r="B217" t="s">
+        <v>158</v>
+      </c>
+      <c r="C217">
+        <v>3.005</v>
+      </c>
+      <c r="D217" t="s">
+        <v>225</v>
+      </c>
+      <c r="E217">
+        <v>0</v>
+      </c>
+      <c r="F217">
+        <v>0</v>
+      </c>
+      <c r="G217">
+        <v>6</v>
+      </c>
+      <c r="H217">
+        <v>0</v>
+      </c>
+      <c r="I217">
+        <v>0</v>
+      </c>
+      <c r="J217">
+        <v>2</v>
+      </c>
+      <c r="K217" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11">
+      <c r="A218" t="s">
+        <v>61</v>
+      </c>
+      <c r="B218" t="s">
+        <v>159</v>
+      </c>
+      <c r="C218">
+        <v>3.011</v>
+      </c>
+      <c r="D218" t="s">
+        <v>225</v>
+      </c>
+      <c r="E218">
+        <v>0</v>
+      </c>
+      <c r="F218">
+        <v>0</v>
+      </c>
+      <c r="G218">
+        <v>6</v>
+      </c>
+      <c r="H218">
+        <v>0</v>
+      </c>
+      <c r="I218">
+        <v>0</v>
+      </c>
+      <c r="J218">
+        <v>2</v>
+      </c>
+      <c r="K218" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11">
+      <c r="A219" t="s">
+        <v>61</v>
+      </c>
+      <c r="B219" t="s">
+        <v>160</v>
+      </c>
+      <c r="C219">
+        <v>1.011</v>
+      </c>
+      <c r="D219" t="s">
+        <v>225</v>
+      </c>
+      <c r="E219">
+        <v>0</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>2</v>
+      </c>
+      <c r="H219">
+        <v>0</v>
+      </c>
+      <c r="I219">
+        <v>0</v>
+      </c>
+      <c r="J219">
+        <v>1</v>
+      </c>
+      <c r="K219" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11">
+      <c r="A220" t="s">
+        <v>62</v>
+      </c>
+      <c r="B220" t="s">
+        <v>121</v>
+      </c>
+      <c r="C220">
+        <v>3.001</v>
+      </c>
+      <c r="D220" t="s">
+        <v>187</v>
+      </c>
+      <c r="E220">
+        <v>0</v>
+      </c>
+      <c r="F220">
+        <v>5</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+      <c r="H220">
+        <v>0</v>
+      </c>
+      <c r="I220">
+        <v>0</v>
+      </c>
+      <c r="J220">
+        <v>2</v>
+      </c>
+      <c r="K220" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11">
+      <c r="A221" t="s">
+        <v>62</v>
+      </c>
+      <c r="B221" t="s">
+        <v>122</v>
+      </c>
+      <c r="C221" t="s">
+        <v>187</v>
+      </c>
+      <c r="D221" t="s">
+        <v>220</v>
+      </c>
+      <c r="E221">
+        <v>0</v>
+      </c>
+      <c r="F221">
+        <v>5</v>
+      </c>
+      <c r="G221">
+        <v>0</v>
+      </c>
+      <c r="H221">
+        <v>0</v>
+      </c>
+      <c r="I221">
+        <v>0</v>
+      </c>
+      <c r="J221">
+        <v>2</v>
+      </c>
+      <c r="K221" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11">
+      <c r="A222" t="s">
+        <v>62</v>
+      </c>
+      <c r="B222" t="s">
+        <v>134</v>
+      </c>
+      <c r="C222" t="s">
+        <v>188</v>
+      </c>
+      <c r="D222" t="s">
+        <v>187</v>
+      </c>
+      <c r="E222">
+        <v>0</v>
+      </c>
+      <c r="F222">
+        <v>2</v>
+      </c>
+      <c r="G222">
+        <v>0</v>
+      </c>
+      <c r="H222">
+        <v>0</v>
+      </c>
+      <c r="I222">
+        <v>0</v>
+      </c>
+      <c r="J222">
+        <v>1</v>
+      </c>
+      <c r="K222" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11">
+      <c r="A223" t="s">
+        <v>63</v>
+      </c>
+      <c r="B223" t="s">
+        <v>152</v>
+      </c>
+      <c r="C223" t="s">
+        <v>189</v>
+      </c>
+      <c r="D223" t="s">
+        <v>223</v>
+      </c>
+      <c r="E223">
+        <v>0</v>
+      </c>
+      <c r="F223">
+        <v>5</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>0</v>
+      </c>
+      <c r="I223">
+        <v>6</v>
+      </c>
+      <c r="J223">
+        <v>3</v>
+      </c>
+      <c r="K223" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11">
+      <c r="A224" t="s">
+        <v>63</v>
+      </c>
+      <c r="B224" t="s">
+        <v>153</v>
+      </c>
+      <c r="C224" t="s">
+        <v>190</v>
+      </c>
+      <c r="D224" t="s">
+        <v>223</v>
+      </c>
+      <c r="E224">
+        <v>0</v>
+      </c>
+      <c r="F224">
+        <v>5</v>
+      </c>
+      <c r="G224">
+        <v>0</v>
+      </c>
+      <c r="H224">
+        <v>0</v>
+      </c>
+      <c r="I224">
+        <v>6</v>
+      </c>
+      <c r="J224">
+        <v>3</v>
+      </c>
+      <c r="K224" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11">
+      <c r="A225" t="s">
+        <v>63</v>
+      </c>
+      <c r="B225" t="s">
+        <v>152</v>
+      </c>
+      <c r="C225" t="s">
+        <v>189</v>
+      </c>
+      <c r="D225" t="s">
+        <v>223</v>
+      </c>
+      <c r="E225">
+        <v>0</v>
+      </c>
+      <c r="F225">
+        <v>5</v>
+      </c>
+      <c r="G225">
+        <v>0</v>
+      </c>
+      <c r="H225">
+        <v>0</v>
+      </c>
+      <c r="I225">
+        <v>9</v>
+      </c>
+      <c r="J225">
+        <v>4</v>
+      </c>
+      <c r="K225" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11">
+      <c r="A226" t="s">
+        <v>63</v>
+      </c>
+      <c r="B226" t="s">
+        <v>153</v>
+      </c>
+      <c r="C226" t="s">
+        <v>190</v>
+      </c>
+      <c r="D226" t="s">
+        <v>223</v>
+      </c>
+      <c r="E226">
+        <v>0</v>
+      </c>
+      <c r="F226">
+        <v>5</v>
+      </c>
+      <c r="G226">
+        <v>0</v>
+      </c>
+      <c r="H226">
+        <v>0</v>
+      </c>
+      <c r="I226">
+        <v>9</v>
+      </c>
+      <c r="J226">
+        <v>4</v>
+      </c>
+      <c r="K226" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11">
+      <c r="A227" t="s">
+        <v>63</v>
+      </c>
+      <c r="B227" t="s">
+        <v>128</v>
+      </c>
+      <c r="C227" t="s">
+        <v>191</v>
+      </c>
+      <c r="D227" t="s">
+        <v>187</v>
+      </c>
+      <c r="E227">
+        <v>0</v>
+      </c>
+      <c r="F227">
+        <v>5</v>
+      </c>
+      <c r="G227">
+        <v>0</v>
+      </c>
+      <c r="H227">
+        <v>0</v>
+      </c>
+      <c r="I227">
+        <v>0</v>
+      </c>
+      <c r="J227">
+        <v>2</v>
+      </c>
+      <c r="K227" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11">
+      <c r="A228" t="s">
+        <v>63</v>
+      </c>
+      <c r="B228" t="s">
+        <v>129</v>
+      </c>
+      <c r="C228" t="s">
+        <v>192</v>
+      </c>
+      <c r="D228" t="s">
+        <v>187</v>
+      </c>
+      <c r="E228">
+        <v>0</v>
+      </c>
+      <c r="F228">
+        <v>5</v>
+      </c>
+      <c r="G228">
+        <v>0</v>
+      </c>
+      <c r="H228">
+        <v>0</v>
+      </c>
+      <c r="I228">
+        <v>0</v>
+      </c>
+      <c r="J228">
+        <v>2</v>
+      </c>
+      <c r="K228" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11">
+      <c r="A229" t="s">
+        <v>63</v>
+      </c>
+      <c r="B229" t="s">
+        <v>128</v>
+      </c>
+      <c r="C229" t="s">
+        <v>191</v>
+      </c>
+      <c r="D229" t="s">
+        <v>187</v>
+      </c>
+      <c r="E229">
+        <v>0</v>
+      </c>
+      <c r="F229">
+        <v>5</v>
+      </c>
+      <c r="G229">
+        <v>0</v>
+      </c>
+      <c r="H229">
+        <v>0</v>
+      </c>
+      <c r="I229">
+        <v>9</v>
+      </c>
+      <c r="J229">
+        <v>4</v>
+      </c>
+      <c r="K229" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11">
+      <c r="A230" t="s">
+        <v>63</v>
+      </c>
+      <c r="B230" t="s">
+        <v>129</v>
+      </c>
+      <c r="C230" t="s">
+        <v>192</v>
+      </c>
+      <c r="D230" t="s">
+        <v>187</v>
+      </c>
+      <c r="E230">
+        <v>0</v>
+      </c>
+      <c r="F230">
+        <v>5</v>
+      </c>
+      <c r="G230">
+        <v>0</v>
+      </c>
+      <c r="H230">
+        <v>0</v>
+      </c>
+      <c r="I230">
+        <v>9</v>
+      </c>
+      <c r="J230">
+        <v>4</v>
+      </c>
+      <c r="K230" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11">
+      <c r="A231" t="s">
+        <v>64</v>
+      </c>
+      <c r="B231" t="s">
+        <v>123</v>
+      </c>
+      <c r="C231" t="s">
+        <v>193</v>
+      </c>
+      <c r="D231" t="s">
+        <v>222</v>
+      </c>
+      <c r="E231">
+        <v>0</v>
+      </c>
+      <c r="F231">
+        <v>5</v>
+      </c>
+      <c r="G231">
+        <v>0</v>
+      </c>
+      <c r="H231">
+        <v>0</v>
+      </c>
+      <c r="I231">
+        <v>0</v>
+      </c>
+      <c r="J231">
+        <v>2</v>
+      </c>
+      <c r="K231" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11">
+      <c r="A232" t="s">
+        <v>64</v>
+      </c>
+      <c r="B232" t="s">
+        <v>124</v>
+      </c>
+      <c r="C232" t="s">
+        <v>194</v>
+      </c>
+      <c r="D232" t="s">
+        <v>222</v>
+      </c>
+      <c r="E232">
+        <v>0</v>
+      </c>
+      <c r="F232">
+        <v>5</v>
+      </c>
+      <c r="G232">
+        <v>0</v>
+      </c>
+      <c r="H232">
+        <v>0</v>
+      </c>
+      <c r="I232">
+        <v>0</v>
+      </c>
+      <c r="J232">
+        <v>2</v>
+      </c>
+      <c r="K232" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11">
+      <c r="A233" t="s">
+        <v>64</v>
+      </c>
+      <c r="B233" t="s">
+        <v>118</v>
+      </c>
+      <c r="C233" t="s">
+        <v>195</v>
+      </c>
+      <c r="D233" t="s">
+        <v>222</v>
+      </c>
+      <c r="E233">
+        <v>0</v>
+      </c>
+      <c r="F233">
+        <v>5</v>
+      </c>
+      <c r="G233">
+        <v>0</v>
+      </c>
+      <c r="H233">
+        <v>0</v>
+      </c>
+      <c r="I233">
+        <v>0</v>
+      </c>
+      <c r="J233">
+        <v>2</v>
+      </c>
+      <c r="K233" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11">
+      <c r="A234" t="s">
+        <v>64</v>
+      </c>
+      <c r="B234" t="s">
+        <v>130</v>
+      </c>
+      <c r="C234" t="s">
+        <v>192</v>
+      </c>
+      <c r="D234" t="s">
+        <v>187</v>
+      </c>
+      <c r="E234">
+        <v>0</v>
+      </c>
+      <c r="F234">
+        <v>5</v>
+      </c>
+      <c r="G234">
+        <v>0</v>
+      </c>
+      <c r="H234">
+        <v>0</v>
+      </c>
+      <c r="I234">
+        <v>6</v>
+      </c>
+      <c r="J234">
+        <v>3</v>
+      </c>
+      <c r="K234" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11">
+      <c r="A235" t="s">
+        <v>64</v>
+      </c>
+      <c r="B235" t="s">
+        <v>131</v>
+      </c>
+      <c r="C235" t="s">
+        <v>196</v>
+      </c>
+      <c r="D235" t="s">
+        <v>187</v>
+      </c>
+      <c r="E235">
+        <v>0</v>
+      </c>
+      <c r="F235">
+        <v>5</v>
+      </c>
+      <c r="G235">
+        <v>0</v>
+      </c>
+      <c r="H235">
+        <v>0</v>
+      </c>
+      <c r="I235">
+        <v>6</v>
+      </c>
+      <c r="J235">
+        <v>3</v>
+      </c>
+      <c r="K235" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11">
+      <c r="A236" t="s">
+        <v>64</v>
+      </c>
+      <c r="B236" t="s">
+        <v>130</v>
+      </c>
+      <c r="C236" t="s">
+        <v>196</v>
+      </c>
+      <c r="D236" t="s">
+        <v>187</v>
+      </c>
+      <c r="E236">
+        <v>0</v>
+      </c>
+      <c r="F236">
+        <v>5</v>
+      </c>
+      <c r="G236">
+        <v>0</v>
+      </c>
+      <c r="H236">
+        <v>0</v>
+      </c>
+      <c r="I236">
+        <v>9</v>
+      </c>
+      <c r="J236">
+        <v>4</v>
+      </c>
+      <c r="K236" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11">
+      <c r="A237" t="s">
+        <v>64</v>
+      </c>
+      <c r="B237" t="s">
+        <v>131</v>
+      </c>
+      <c r="C237" t="s">
+        <v>196</v>
+      </c>
+      <c r="D237" t="s">
+        <v>187</v>
+      </c>
+      <c r="E237">
+        <v>0</v>
+      </c>
+      <c r="F237">
+        <v>5</v>
+      </c>
+      <c r="G237">
+        <v>0</v>
+      </c>
+      <c r="H237">
+        <v>0</v>
+      </c>
+      <c r="I237">
+        <v>9</v>
+      </c>
+      <c r="J237">
+        <v>4</v>
+      </c>
+      <c r="K237" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11">
+      <c r="A238" t="s">
+        <v>65</v>
+      </c>
+      <c r="B238" t="s">
+        <v>161</v>
+      </c>
+      <c r="C238" t="s">
+        <v>197</v>
+      </c>
+      <c r="D238" t="s">
+        <v>222</v>
+      </c>
+      <c r="E238">
+        <v>0</v>
+      </c>
+      <c r="F238">
+        <v>1</v>
+      </c>
+      <c r="G238">
+        <v>1</v>
+      </c>
+      <c r="H238">
+        <v>0</v>
+      </c>
+      <c r="I238">
+        <v>0</v>
+      </c>
+      <c r="J238">
+        <v>1</v>
+      </c>
+      <c r="K238" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11">
+      <c r="A239" t="s">
+        <v>65</v>
+      </c>
+      <c r="B239" t="s">
+        <v>162</v>
+      </c>
+      <c r="C239" t="s">
+        <v>198</v>
+      </c>
+      <c r="D239" t="s">
+        <v>222</v>
+      </c>
+      <c r="E239">
+        <v>0</v>
+      </c>
+      <c r="F239">
+        <v>3</v>
+      </c>
+      <c r="G239">
+        <v>6</v>
+      </c>
+      <c r="H239">
+        <v>0</v>
+      </c>
+      <c r="I239">
+        <v>0</v>
+      </c>
+      <c r="J239">
+        <v>2</v>
+      </c>
+      <c r="K239" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11">
+      <c r="A240" t="s">
+        <v>65</v>
+      </c>
+      <c r="B240" t="s">
+        <v>163</v>
+      </c>
+      <c r="C240" t="s">
+        <v>199</v>
+      </c>
+      <c r="D240" t="s">
+        <v>222</v>
+      </c>
+      <c r="E240">
+        <v>0</v>
+      </c>
+      <c r="F240">
+        <v>3</v>
+      </c>
+      <c r="G240">
+        <v>6</v>
+      </c>
+      <c r="H240">
+        <v>0</v>
+      </c>
+      <c r="I240">
+        <v>0</v>
+      </c>
+      <c r="J240">
+        <v>2</v>
+      </c>
+      <c r="K240" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11">
+      <c r="A241" t="s">
+        <v>65</v>
+      </c>
+      <c r="B241" t="s">
+        <v>164</v>
+      </c>
+      <c r="C241" t="s">
+        <v>199</v>
+      </c>
+      <c r="D241" t="s">
+        <v>222</v>
+      </c>
+      <c r="E241">
+        <v>0</v>
+      </c>
+      <c r="F241">
+        <v>3</v>
+      </c>
+      <c r="G241">
+        <v>6</v>
+      </c>
+      <c r="H241">
+        <v>0</v>
+      </c>
+      <c r="I241">
+        <v>0</v>
+      </c>
+      <c r="J241">
+        <v>2</v>
+      </c>
+      <c r="K241" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11">
+      <c r="A242" t="s">
+        <v>65</v>
+      </c>
+      <c r="B242" t="s">
+        <v>165</v>
+      </c>
+      <c r="C242" t="s">
+        <v>200</v>
+      </c>
+      <c r="D242" t="s">
+        <v>225</v>
+      </c>
+      <c r="E242">
+        <v>0</v>
+      </c>
+      <c r="F242">
+        <v>3</v>
+      </c>
+      <c r="G242">
+        <v>6</v>
+      </c>
+      <c r="H242">
+        <v>0</v>
+      </c>
+      <c r="I242">
+        <v>0</v>
+      </c>
+      <c r="J242">
+        <v>2</v>
+      </c>
+      <c r="K242" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11">
+      <c r="A243" t="s">
+        <v>65</v>
+      </c>
+      <c r="B243" t="s">
+        <v>166</v>
+      </c>
+      <c r="C243" t="s">
+        <v>201</v>
+      </c>
+      <c r="D243" t="s">
+        <v>225</v>
+      </c>
+      <c r="E243">
+        <v>0</v>
+      </c>
+      <c r="F243">
+        <v>3</v>
+      </c>
+      <c r="G243">
+        <v>6</v>
+      </c>
+      <c r="H243">
+        <v>0</v>
+      </c>
+      <c r="I243">
+        <v>0</v>
+      </c>
+      <c r="J243">
+        <v>2</v>
+      </c>
+      <c r="K243" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11">
+      <c r="A244" t="s">
+        <v>65</v>
+      </c>
+      <c r="B244" t="s">
+        <v>167</v>
+      </c>
+      <c r="C244" t="s">
+        <v>189</v>
+      </c>
+      <c r="D244" t="s">
+        <v>225</v>
+      </c>
+      <c r="E244">
+        <v>0</v>
+      </c>
+      <c r="F244">
+        <v>3</v>
+      </c>
+      <c r="G244">
+        <v>6</v>
+      </c>
+      <c r="H244">
+        <v>0</v>
+      </c>
+      <c r="I244">
+        <v>0</v>
+      </c>
+      <c r="J244">
+        <v>2</v>
+      </c>
+      <c r="K244" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11">
+      <c r="A245" t="s">
+        <v>66</v>
+      </c>
+      <c r="B245" t="s">
+        <v>132</v>
+      </c>
+      <c r="C245" t="s">
+        <v>192</v>
+      </c>
+      <c r="D245" t="s">
+        <v>187</v>
+      </c>
+      <c r="E245">
+        <v>0</v>
+      </c>
+      <c r="F245">
+        <v>5</v>
+      </c>
+      <c r="G245">
+        <v>0</v>
+      </c>
+      <c r="H245">
+        <v>0</v>
+      </c>
+      <c r="I245">
+        <v>9</v>
+      </c>
+      <c r="J245">
+        <v>4</v>
+      </c>
+      <c r="K245" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11">
+      <c r="A246" t="s">
+        <v>66</v>
+      </c>
+      <c r="B246" t="s">
+        <v>133</v>
+      </c>
+      <c r="C246" t="s">
+        <v>196</v>
+      </c>
+      <c r="D246" t="s">
+        <v>187</v>
+      </c>
+      <c r="E246">
+        <v>0</v>
+      </c>
+      <c r="F246">
+        <v>5</v>
+      </c>
+      <c r="G246">
+        <v>0</v>
+      </c>
+      <c r="H246">
+        <v>0</v>
+      </c>
+      <c r="I246">
+        <v>9</v>
+      </c>
+      <c r="J246">
+        <v>4</v>
+      </c>
+      <c r="K246" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11">
+      <c r="A247" t="s">
+        <v>66</v>
+      </c>
+      <c r="B247" t="s">
+        <v>147</v>
+      </c>
+      <c r="C247" t="s">
+        <v>200</v>
+      </c>
+      <c r="D247" t="s">
+        <v>225</v>
+      </c>
+      <c r="E247">
+        <v>0</v>
+      </c>
+      <c r="F247">
+        <v>5</v>
+      </c>
+      <c r="G247">
+        <v>0</v>
+      </c>
+      <c r="H247">
+        <v>0</v>
+      </c>
+      <c r="I247">
+        <v>6</v>
+      </c>
+      <c r="J247">
+        <v>3</v>
+      </c>
+      <c r="K247" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11">
+      <c r="A248" t="s">
+        <v>66</v>
+      </c>
+      <c r="B248" t="s">
+        <v>148</v>
+      </c>
+      <c r="C248" t="s">
+        <v>202</v>
+      </c>
+      <c r="D248" t="s">
+        <v>225</v>
+      </c>
+      <c r="E248">
+        <v>0</v>
+      </c>
+      <c r="F248">
+        <v>5</v>
+      </c>
+      <c r="G248">
+        <v>0</v>
+      </c>
+      <c r="H248">
+        <v>0</v>
+      </c>
+      <c r="I248">
+        <v>9</v>
+      </c>
+      <c r="J248">
+        <v>4</v>
+      </c>
+      <c r="K248" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11">
+      <c r="A249" t="s">
+        <v>66</v>
+      </c>
+      <c r="B249" t="s">
+        <v>147</v>
+      </c>
+      <c r="C249" t="s">
+        <v>200</v>
+      </c>
+      <c r="D249" t="s">
+        <v>225</v>
+      </c>
+      <c r="E249">
+        <v>0</v>
+      </c>
+      <c r="F249">
+        <v>5</v>
+      </c>
+      <c r="G249">
+        <v>0</v>
+      </c>
+      <c r="H249">
+        <v>0</v>
+      </c>
+      <c r="I249">
+        <v>9</v>
+      </c>
+      <c r="J249">
+        <v>4</v>
+      </c>
+      <c r="K249" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11">
+      <c r="A250" t="s">
+        <v>66</v>
+      </c>
+      <c r="B250" t="s">
+        <v>148</v>
+      </c>
+      <c r="C250" t="s">
+        <v>202</v>
+      </c>
+      <c r="D250" t="s">
+        <v>225</v>
+      </c>
+      <c r="E250">
+        <v>0</v>
+      </c>
+      <c r="F250">
+        <v>5</v>
+      </c>
+      <c r="G250">
+        <v>0</v>
+      </c>
+      <c r="H250">
+        <v>0</v>
+      </c>
+      <c r="I250">
+        <v>6</v>
+      </c>
+      <c r="J250">
+        <v>3</v>
+      </c>
+      <c r="K250" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11">
+      <c r="A251" t="s">
+        <v>67</v>
+      </c>
+      <c r="B251" t="s">
+        <v>144</v>
+      </c>
+      <c r="C251" t="s">
+        <v>203</v>
+      </c>
+      <c r="D251" t="s">
+        <v>221</v>
+      </c>
+      <c r="E251">
+        <v>0</v>
+      </c>
+      <c r="F251">
+        <v>5</v>
+      </c>
+      <c r="G251">
+        <v>0</v>
+      </c>
+      <c r="H251">
+        <v>0</v>
+      </c>
+      <c r="I251">
+        <v>6</v>
+      </c>
+      <c r="J251">
+        <v>3</v>
+      </c>
+      <c r="K251" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11">
+      <c r="A252" t="s">
+        <v>67</v>
+      </c>
+      <c r="B252" t="s">
+        <v>145</v>
+      </c>
+      <c r="C252" t="s">
+        <v>204</v>
+      </c>
+      <c r="D252" t="s">
+        <v>221</v>
+      </c>
+      <c r="E252">
+        <v>0</v>
+      </c>
+      <c r="F252">
+        <v>5</v>
+      </c>
+      <c r="G252">
+        <v>0</v>
+      </c>
+      <c r="H252">
+        <v>0</v>
+      </c>
+      <c r="I252">
+        <v>6</v>
+      </c>
+      <c r="J252">
+        <v>3</v>
+      </c>
+      <c r="K252" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11">
+      <c r="A253" t="s">
+        <v>67</v>
+      </c>
+      <c r="B253" t="s">
+        <v>149</v>
+      </c>
+      <c r="C253" t="s">
+        <v>200</v>
+      </c>
+      <c r="D253" t="s">
+        <v>225</v>
+      </c>
+      <c r="E253">
+        <v>0</v>
+      </c>
+      <c r="F253">
+        <v>5</v>
+      </c>
+      <c r="G253">
+        <v>0</v>
+      </c>
+      <c r="H253">
+        <v>0</v>
+      </c>
+      <c r="I253">
+        <v>6</v>
+      </c>
+      <c r="J253">
+        <v>3</v>
+      </c>
+      <c r="K253" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11">
+      <c r="A254" t="s">
+        <v>67</v>
+      </c>
+      <c r="B254" t="s">
+        <v>150</v>
+      </c>
+      <c r="C254" t="s">
+        <v>205</v>
+      </c>
+      <c r="D254" t="s">
+        <v>225</v>
+      </c>
+      <c r="E254">
+        <v>0</v>
+      </c>
+      <c r="F254">
+        <v>2</v>
+      </c>
+      <c r="G254">
+        <v>0</v>
+      </c>
+      <c r="H254">
+        <v>0</v>
+      </c>
+      <c r="I254">
+        <v>5</v>
+      </c>
+      <c r="J254">
+        <v>2</v>
+      </c>
+      <c r="K254" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11">
+      <c r="A255" t="s">
+        <v>67</v>
+      </c>
+      <c r="B255" t="s">
+        <v>144</v>
+      </c>
+      <c r="C255" t="s">
+        <v>203</v>
+      </c>
+      <c r="D255" t="s">
+        <v>221</v>
+      </c>
+      <c r="E255">
+        <v>0</v>
+      </c>
+      <c r="F255">
+        <v>5</v>
+      </c>
+      <c r="G255">
+        <v>0</v>
+      </c>
+      <c r="H255">
+        <v>0</v>
+      </c>
+      <c r="I255">
+        <v>9</v>
+      </c>
+      <c r="J255">
+        <v>4</v>
+      </c>
+      <c r="K255" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11">
+      <c r="A256" t="s">
+        <v>67</v>
+      </c>
+      <c r="B256" t="s">
+        <v>145</v>
+      </c>
+      <c r="C256" t="s">
+        <v>204</v>
+      </c>
+      <c r="D256" t="s">
+        <v>221</v>
+      </c>
+      <c r="E256">
+        <v>0</v>
+      </c>
+      <c r="F256">
+        <v>5</v>
+      </c>
+      <c r="G256">
+        <v>0</v>
+      </c>
+      <c r="H256">
+        <v>0</v>
+      </c>
+      <c r="I256">
+        <v>9</v>
+      </c>
+      <c r="J256">
+        <v>4</v>
+      </c>
+      <c r="K256" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11">
+      <c r="A257" t="s">
+        <v>67</v>
+      </c>
+      <c r="B257" t="s">
+        <v>149</v>
+      </c>
+      <c r="C257" t="s">
+        <v>200</v>
+      </c>
+      <c r="D257" t="s">
+        <v>225</v>
+      </c>
+      <c r="E257">
+        <v>0</v>
+      </c>
+      <c r="F257">
+        <v>5</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>0</v>
+      </c>
+      <c r="I257">
+        <v>9</v>
+      </c>
+      <c r="J257">
+        <v>4</v>
+      </c>
+      <c r="K257" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11">
+      <c r="A258" t="s">
+        <v>67</v>
+      </c>
+      <c r="B258" t="s">
+        <v>150</v>
+      </c>
+      <c r="C258" t="s">
+        <v>205</v>
+      </c>
+      <c r="D258" t="s">
+        <v>225</v>
+      </c>
+      <c r="E258">
+        <v>0</v>
+      </c>
+      <c r="F258">
+        <v>2</v>
+      </c>
+      <c r="G258">
+        <v>0</v>
+      </c>
+      <c r="H258">
+        <v>0</v>
+      </c>
+      <c r="I258">
+        <v>4</v>
+      </c>
+      <c r="J258">
+        <v>2</v>
+      </c>
+      <c r="K258" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11">
+      <c r="A259" t="s">
+        <v>68</v>
+      </c>
+      <c r="B259" t="s">
+        <v>146</v>
+      </c>
+      <c r="C259" t="s">
+        <v>206</v>
+      </c>
+      <c r="D259" t="s">
+        <v>221</v>
+      </c>
+      <c r="E259">
+        <v>0</v>
+      </c>
+      <c r="F259">
+        <v>5</v>
+      </c>
+      <c r="G259">
+        <v>0</v>
+      </c>
+      <c r="H259">
+        <v>0</v>
+      </c>
+      <c r="I259">
+        <v>6</v>
+      </c>
+      <c r="J259">
+        <v>3</v>
+      </c>
+      <c r="K259" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11">
+      <c r="A260" t="s">
+        <v>68</v>
+      </c>
+      <c r="B260" t="s">
+        <v>151</v>
+      </c>
+      <c r="C260" t="s">
+        <v>207</v>
+      </c>
+      <c r="D260" t="s">
+        <v>221</v>
+      </c>
+      <c r="E260">
+        <v>0</v>
+      </c>
+      <c r="F260">
+        <v>1</v>
+      </c>
+      <c r="G260">
+        <v>0</v>
+      </c>
+      <c r="H260">
+        <v>0</v>
+      </c>
+      <c r="I260">
+        <v>2</v>
+      </c>
+      <c r="J260">
+        <v>1</v>
+      </c>
+      <c r="K260" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11">
+      <c r="A261" t="s">
+        <v>68</v>
+      </c>
+      <c r="B261" t="s">
+        <v>146</v>
+      </c>
+      <c r="C261" t="s">
+        <v>206</v>
+      </c>
+      <c r="D261" t="s">
+        <v>221</v>
+      </c>
+      <c r="E261">
+        <v>0</v>
+      </c>
+      <c r="F261">
+        <v>5</v>
+      </c>
+      <c r="G261">
+        <v>0</v>
+      </c>
+      <c r="H261">
+        <v>0</v>
+      </c>
+      <c r="I261">
+        <v>9</v>
+      </c>
+      <c r="J261">
+        <v>4</v>
+      </c>
+      <c r="K261" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11">
+      <c r="A262" t="s">
+        <v>68</v>
+      </c>
+      <c r="B262" t="s">
+        <v>151</v>
+      </c>
+      <c r="C262" t="s">
+        <v>207</v>
+      </c>
+      <c r="D262" t="s">
+        <v>221</v>
+      </c>
+      <c r="E262">
+        <v>0</v>
+      </c>
+      <c r="F262">
+        <v>1</v>
+      </c>
+      <c r="G262">
+        <v>0</v>
+      </c>
+      <c r="H262">
+        <v>0</v>
+      </c>
+      <c r="I262">
+        <v>3</v>
+      </c>
+      <c r="J262">
+        <v>1</v>
+      </c>
+      <c r="K262" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11">
+      <c r="A263" t="s">
+        <v>68</v>
+      </c>
+      <c r="B263" t="s">
+        <v>168</v>
+      </c>
+      <c r="C263" t="s">
+        <v>201</v>
+      </c>
+      <c r="D263" t="s">
+        <v>225</v>
+      </c>
+      <c r="E263">
+        <v>0</v>
+      </c>
+      <c r="F263">
+        <v>3</v>
+      </c>
+      <c r="G263">
+        <v>6</v>
+      </c>
+      <c r="H263">
+        <v>0</v>
+      </c>
+      <c r="I263">
+        <v>0</v>
+      </c>
+      <c r="J263">
+        <v>2</v>
+      </c>
+      <c r="K263" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11">
+      <c r="A264" t="s">
+        <v>68</v>
+      </c>
+      <c r="B264" t="s">
+        <v>169</v>
+      </c>
+      <c r="C264" t="s">
+        <v>201</v>
+      </c>
+      <c r="D264" t="s">
+        <v>225</v>
+      </c>
+      <c r="E264">
+        <v>0</v>
+      </c>
+      <c r="F264">
+        <v>3</v>
+      </c>
+      <c r="G264">
+        <v>6</v>
+      </c>
+      <c r="H264">
+        <v>0</v>
+      </c>
+      <c r="I264">
+        <v>0</v>
+      </c>
+      <c r="J264">
+        <v>2</v>
+      </c>
+      <c r="K264" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11">
+      <c r="A265" t="s">
+        <v>68</v>
+      </c>
+      <c r="B265" t="s">
+        <v>170</v>
+      </c>
+      <c r="C265" t="s">
+        <v>208</v>
+      </c>
+      <c r="D265" t="s">
+        <v>225</v>
+      </c>
+      <c r="E265">
+        <v>0</v>
+      </c>
+      <c r="F265">
+        <v>3</v>
+      </c>
+      <c r="G265">
+        <v>6</v>
+      </c>
+      <c r="H265">
+        <v>0</v>
+      </c>
+      <c r="I265">
+        <v>0</v>
+      </c>
+      <c r="J265">
+        <v>2</v>
+      </c>
+      <c r="K265" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11">
+      <c r="A266" t="s">
+        <v>69</v>
+      </c>
+      <c r="B266" t="s">
+        <v>171</v>
+      </c>
+      <c r="C266" t="s">
+        <v>199</v>
+      </c>
+      <c r="D266" t="s">
+        <v>222</v>
+      </c>
+      <c r="E266">
+        <v>0</v>
+      </c>
+      <c r="F266">
+        <v>3</v>
+      </c>
+      <c r="G266">
+        <v>6</v>
+      </c>
+      <c r="H266">
+        <v>0</v>
+      </c>
+      <c r="I266">
+        <v>0</v>
+      </c>
+      <c r="J266">
+        <v>2</v>
+      </c>
+      <c r="K266" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11">
+      <c r="A267" t="s">
+        <v>69</v>
+      </c>
+      <c r="B267" t="s">
+        <v>172</v>
+      </c>
+      <c r="C267" t="s">
+        <v>198</v>
+      </c>
+      <c r="D267" t="s">
+        <v>222</v>
+      </c>
+      <c r="E267">
+        <v>0</v>
+      </c>
+      <c r="F267">
+        <v>3</v>
+      </c>
+      <c r="G267">
+        <v>6</v>
+      </c>
+      <c r="H267">
+        <v>0</v>
+      </c>
+      <c r="I267">
+        <v>0</v>
+      </c>
+      <c r="J267">
+        <v>2</v>
+      </c>
+      <c r="K267" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11">
+      <c r="A268" t="s">
+        <v>69</v>
+      </c>
+      <c r="B268" t="s">
+        <v>173</v>
+      </c>
+      <c r="C268" t="s">
+        <v>199</v>
+      </c>
+      <c r="D268" t="s">
+        <v>222</v>
+      </c>
+      <c r="E268">
+        <v>0</v>
+      </c>
+      <c r="F268">
+        <v>3</v>
+      </c>
+      <c r="G268">
+        <v>6</v>
+      </c>
+      <c r="H268">
+        <v>0</v>
+      </c>
+      <c r="I268">
+        <v>0</v>
+      </c>
+      <c r="J268">
+        <v>2</v>
+      </c>
+      <c r="K268" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11">
+      <c r="A269" t="s">
+        <v>69</v>
+      </c>
+      <c r="B269" t="s">
+        <v>174</v>
+      </c>
+      <c r="C269" t="s">
+        <v>209</v>
+      </c>
+      <c r="D269" t="s">
+        <v>225</v>
+      </c>
+      <c r="E269">
+        <v>0</v>
+      </c>
+      <c r="F269">
+        <v>3</v>
+      </c>
+      <c r="G269">
+        <v>6</v>
+      </c>
+      <c r="H269">
+        <v>0</v>
+      </c>
+      <c r="I269">
+        <v>0</v>
+      </c>
+      <c r="J269">
+        <v>2</v>
+      </c>
+      <c r="K269" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11">
+      <c r="A270" t="s">
+        <v>69</v>
+      </c>
+      <c r="B270" t="s">
+        <v>175</v>
+      </c>
+      <c r="C270" t="s">
+        <v>193</v>
+      </c>
+      <c r="D270" t="s">
+        <v>225</v>
+      </c>
+      <c r="E270">
+        <v>0</v>
+      </c>
+      <c r="F270">
+        <v>3</v>
+      </c>
+      <c r="G270">
+        <v>6</v>
+      </c>
+      <c r="H270">
+        <v>0</v>
+      </c>
+      <c r="I270">
+        <v>0</v>
+      </c>
+      <c r="J270">
+        <v>2</v>
+      </c>
+      <c r="K270" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11">
+      <c r="A271" t="s">
+        <v>69</v>
+      </c>
+      <c r="B271" t="s">
+        <v>176</v>
+      </c>
+      <c r="C271" t="s">
+        <v>210</v>
+      </c>
+      <c r="D271" t="s">
+        <v>225</v>
+      </c>
+      <c r="E271">
+        <v>0</v>
+      </c>
+      <c r="F271">
+        <v>3</v>
+      </c>
+      <c r="G271">
+        <v>6</v>
+      </c>
+      <c r="H271">
+        <v>0</v>
+      </c>
+      <c r="I271">
+        <v>0</v>
+      </c>
+      <c r="J271">
+        <v>2</v>
+      </c>
+      <c r="K271" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11">
+      <c r="A272" t="s">
+        <v>69</v>
+      </c>
+      <c r="B272" t="s">
+        <v>125</v>
+      </c>
+      <c r="C272" t="s">
+        <v>211</v>
+      </c>
+      <c r="D272" t="s">
+        <v>221</v>
+      </c>
+      <c r="E272">
+        <v>0</v>
+      </c>
+      <c r="F272">
+        <v>5</v>
+      </c>
+      <c r="G272">
+        <v>0</v>
+      </c>
+      <c r="H272">
+        <v>0</v>
+      </c>
+      <c r="I272">
+        <v>0</v>
+      </c>
+      <c r="J272">
+        <v>2</v>
+      </c>
+      <c r="K272" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11">
+      <c r="A273" t="s">
+        <v>69</v>
+      </c>
+      <c r="B273" t="s">
+        <v>126</v>
+      </c>
+      <c r="C273" t="s">
+        <v>210</v>
+      </c>
+      <c r="D273" t="s">
+        <v>221</v>
+      </c>
+      <c r="E273">
+        <v>0</v>
+      </c>
+      <c r="F273">
+        <v>5</v>
+      </c>
+      <c r="G273">
+        <v>0</v>
+      </c>
+      <c r="H273">
+        <v>0</v>
+      </c>
+      <c r="I273">
+        <v>0</v>
+      </c>
+      <c r="J273">
+        <v>2</v>
+      </c>
+      <c r="K273" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11">
+      <c r="A274" t="s">
+        <v>69</v>
+      </c>
+      <c r="B274" t="s">
+        <v>127</v>
+      </c>
+      <c r="C274" t="s">
+        <v>212</v>
+      </c>
+      <c r="D274" t="s">
+        <v>221</v>
+      </c>
+      <c r="E274">
+        <v>0</v>
+      </c>
+      <c r="F274">
+        <v>3</v>
+      </c>
+      <c r="G274">
+        <v>0</v>
+      </c>
+      <c r="H274">
+        <v>0</v>
+      </c>
+      <c r="I274">
+        <v>0</v>
+      </c>
+      <c r="J274">
+        <v>1</v>
+      </c>
+      <c r="K274" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11">
+      <c r="A275" t="s">
+        <v>70</v>
+      </c>
+      <c r="B275" t="s">
+        <v>177</v>
+      </c>
+      <c r="C275" t="s">
+        <v>213</v>
+      </c>
+      <c r="D275" t="s">
+        <v>222</v>
+      </c>
+      <c r="E275">
+        <v>0</v>
+      </c>
+      <c r="F275">
+        <v>3</v>
+      </c>
+      <c r="G275">
+        <v>6</v>
+      </c>
+      <c r="H275">
+        <v>0</v>
+      </c>
+      <c r="I275">
+        <v>0</v>
+      </c>
+      <c r="J275">
+        <v>2</v>
+      </c>
+      <c r="K275" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11">
+      <c r="A276" t="s">
+        <v>70</v>
+      </c>
+      <c r="B276" t="s">
+        <v>178</v>
+      </c>
+      <c r="C276" t="s">
+        <v>214</v>
+      </c>
+      <c r="D276" t="s">
+        <v>222</v>
+      </c>
+      <c r="E276">
+        <v>0</v>
+      </c>
+      <c r="F276">
+        <v>3</v>
+      </c>
+      <c r="G276">
+        <v>0</v>
+      </c>
+      <c r="H276">
+        <v>0</v>
+      </c>
+      <c r="I276">
+        <v>0</v>
+      </c>
+      <c r="J276">
+        <v>1</v>
+      </c>
+      <c r="K276" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11">
+      <c r="A277" t="s">
+        <v>70</v>
+      </c>
+      <c r="B277" t="s">
+        <v>179</v>
+      </c>
+      <c r="C277" t="s">
+        <v>215</v>
+      </c>
+      <c r="D277" t="s">
+        <v>222</v>
+      </c>
+      <c r="E277">
+        <v>0</v>
+      </c>
+      <c r="F277">
+        <v>3</v>
+      </c>
+      <c r="G277">
+        <v>0</v>
+      </c>
+      <c r="H277">
+        <v>0</v>
+      </c>
+      <c r="I277">
+        <v>0</v>
+      </c>
+      <c r="J277">
+        <v>1</v>
+      </c>
+      <c r="K277" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11">
+      <c r="A278" t="s">
+        <v>70</v>
+      </c>
+      <c r="B278" t="s">
+        <v>180</v>
+      </c>
+      <c r="C278" t="s">
+        <v>216</v>
+      </c>
+      <c r="D278" t="s">
+        <v>222</v>
+      </c>
+      <c r="E278">
+        <v>0</v>
+      </c>
+      <c r="F278">
+        <v>3</v>
+      </c>
+      <c r="G278">
+        <v>0</v>
+      </c>
+      <c r="H278">
+        <v>0</v>
+      </c>
+      <c r="I278">
+        <v>0</v>
+      </c>
+      <c r="J278">
+        <v>1</v>
+      </c>
+      <c r="K278" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11">
+      <c r="A279" t="s">
+        <v>70</v>
+      </c>
+      <c r="B279" t="s">
+        <v>181</v>
+      </c>
+      <c r="C279" t="s">
+        <v>202</v>
+      </c>
+      <c r="D279" t="s">
+        <v>222</v>
+      </c>
+      <c r="E279">
+        <v>0</v>
+      </c>
+      <c r="F279">
+        <v>3</v>
+      </c>
+      <c r="G279">
+        <v>0</v>
+      </c>
+      <c r="H279">
+        <v>0</v>
+      </c>
+      <c r="I279">
+        <v>0</v>
+      </c>
+      <c r="J279">
+        <v>1</v>
+      </c>
+      <c r="K279" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11">
+      <c r="A280" t="s">
+        <v>70</v>
+      </c>
+      <c r="B280" t="s">
+        <v>181</v>
+      </c>
+      <c r="C280" t="s">
+        <v>202</v>
+      </c>
+      <c r="D280" t="s">
+        <v>222</v>
+      </c>
+      <c r="E280">
+        <v>0</v>
+      </c>
+      <c r="F280">
+        <v>3</v>
+      </c>
+      <c r="G280">
+        <v>0</v>
+      </c>
+      <c r="H280">
+        <v>0</v>
+      </c>
+      <c r="I280">
+        <v>0</v>
+      </c>
+      <c r="J280">
+        <v>1</v>
+      </c>
+      <c r="K280" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11">
+      <c r="A281" t="s">
+        <v>70</v>
+      </c>
+      <c r="B281" t="s">
+        <v>182</v>
+      </c>
+      <c r="C281" t="s">
+        <v>217</v>
+      </c>
+      <c r="D281" t="s">
+        <v>222</v>
+      </c>
+      <c r="E281">
+        <v>0</v>
+      </c>
+      <c r="F281">
+        <v>3</v>
+      </c>
+      <c r="G281">
+        <v>0</v>
+      </c>
+      <c r="H281">
+        <v>0</v>
+      </c>
+      <c r="I281">
+        <v>0</v>
+      </c>
+      <c r="J281">
+        <v>1</v>
+      </c>
+      <c r="K281" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11">
+      <c r="A282" t="s">
+        <v>71</v>
+      </c>
+      <c r="B282" t="s">
+        <v>183</v>
+      </c>
+      <c r="C282" t="s">
+        <v>218</v>
+      </c>
+      <c r="D282" t="s">
+        <v>225</v>
+      </c>
+      <c r="E282">
+        <v>0</v>
+      </c>
+      <c r="F282">
+        <v>3</v>
+      </c>
+      <c r="G282">
+        <v>0</v>
+      </c>
+      <c r="H282">
+        <v>0</v>
+      </c>
+      <c r="I282">
+        <v>0</v>
+      </c>
+      <c r="J282">
+        <v>1</v>
+      </c>
+      <c r="K282" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11">
+      <c r="A283" t="s">
+        <v>71</v>
+      </c>
+      <c r="B283" t="s">
+        <v>184</v>
+      </c>
+      <c r="C283" t="s">
+        <v>219</v>
+      </c>
+      <c r="D283" t="s">
+        <v>222</v>
+      </c>
+      <c r="E283">
+        <v>0</v>
+      </c>
+      <c r="F283">
+        <v>3</v>
+      </c>
+      <c r="G283">
+        <v>0</v>
+      </c>
+      <c r="H283">
+        <v>0</v>
+      </c>
+      <c r="I283">
+        <v>0</v>
+      </c>
+      <c r="J283">
+        <v>1</v>
+      </c>
+      <c r="K283" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11">
+      <c r="A284" t="s">
+        <v>71</v>
+      </c>
+      <c r="B284" t="s">
+        <v>185</v>
+      </c>
+      <c r="C284" t="s">
+        <v>220</v>
+      </c>
+      <c r="D284" t="s">
+        <v>222</v>
+      </c>
+      <c r="E284">
+        <v>0</v>
+      </c>
+      <c r="F284">
+        <v>3</v>
+      </c>
+      <c r="G284">
+        <v>0</v>
+      </c>
+      <c r="H284">
+        <v>0</v>
+      </c>
+      <c r="I284">
+        <v>0</v>
+      </c>
+      <c r="J284">
+        <v>1</v>
+      </c>
+      <c r="K284" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11">
+      <c r="A285" t="s">
+        <v>71</v>
+      </c>
+      <c r="B285" t="s">
+        <v>186</v>
+      </c>
+      <c r="C285" t="s">
+        <v>220</v>
+      </c>
+      <c r="D285" t="s">
+        <v>222</v>
+      </c>
+      <c r="E285">
+        <v>0</v>
+      </c>
+      <c r="F285">
+        <v>3</v>
+      </c>
+      <c r="G285">
+        <v>0</v>
+      </c>
+      <c r="H285">
+        <v>0</v>
+      </c>
+      <c r="I285">
+        <v>0</v>
+      </c>
+      <c r="J285">
+        <v>1</v>
+      </c>
+      <c r="K285" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11">
+      <c r="A286" t="s">
+        <v>72</v>
+      </c>
+      <c r="B286" t="s">
+        <v>177</v>
+      </c>
+      <c r="C286" t="s">
+        <v>213</v>
+      </c>
+      <c r="D286" t="s">
+        <v>222</v>
+      </c>
+      <c r="E286">
+        <v>0</v>
+      </c>
+      <c r="F286">
+        <v>5</v>
+      </c>
+      <c r="G286">
+        <v>6</v>
+      </c>
+      <c r="H286">
+        <v>0</v>
+      </c>
+      <c r="I286">
+        <v>6</v>
+      </c>
+      <c r="J286">
+        <v>5</v>
+      </c>
+      <c r="K286" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11">
+      <c r="A287" t="s">
+        <v>72</v>
+      </c>
+      <c r="B287" t="s">
+        <v>178</v>
+      </c>
+      <c r="C287" t="s">
+        <v>213</v>
+      </c>
+      <c r="D287" t="s">
+        <v>222</v>
+      </c>
+      <c r="E287">
+        <v>0</v>
+      </c>
+      <c r="F287">
+        <v>5</v>
+      </c>
+      <c r="G287">
+        <v>0</v>
+      </c>
+      <c r="H287">
+        <v>0</v>
+      </c>
+      <c r="I287">
+        <v>6</v>
+      </c>
+      <c r="J287">
+        <v>4</v>
+      </c>
+      <c r="K287" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11">
+      <c r="A288" t="s">
+        <v>72</v>
+      </c>
+      <c r="B288" t="s">
+        <v>171</v>
+      </c>
+      <c r="C288" t="s">
+        <v>199</v>
+      </c>
+      <c r="D288" t="s">
+        <v>222</v>
+      </c>
+      <c r="E288">
+        <v>0</v>
+      </c>
+      <c r="F288">
+        <v>5</v>
+      </c>
+      <c r="G288">
+        <v>0</v>
+      </c>
+      <c r="H288">
+        <v>0</v>
+      </c>
+      <c r="I288">
+        <v>6</v>
+      </c>
+      <c r="J288">
+        <v>4</v>
+      </c>
+      <c r="K288" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11">
+      <c r="A289" t="s">
+        <v>72</v>
+      </c>
+      <c r="B289" t="s">
+        <v>172</v>
+      </c>
+      <c r="C289" t="s">
+        <v>198</v>
+      </c>
+      <c r="D289" t="s">
+        <v>222</v>
+      </c>
+      <c r="E289">
+        <v>0</v>
+      </c>
+      <c r="F289">
+        <v>5</v>
+      </c>
+      <c r="G289">
+        <v>0</v>
+      </c>
+      <c r="H289">
+        <v>0</v>
+      </c>
+      <c r="I289">
+        <v>6</v>
+      </c>
+      <c r="J289">
+        <v>4</v>
+      </c>
+      <c r="K289" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11">
+      <c r="A290" t="s">
+        <v>72</v>
+      </c>
+      <c r="B290" t="s">
+        <v>179</v>
+      </c>
+      <c r="C290" t="s">
+        <v>215</v>
+      </c>
+      <c r="D290" t="s">
+        <v>222</v>
+      </c>
+      <c r="E290">
+        <v>0</v>
+      </c>
+      <c r="F290">
+        <v>0</v>
+      </c>
+      <c r="G290">
+        <v>6</v>
+      </c>
+      <c r="H290">
+        <v>0</v>
+      </c>
+      <c r="I290">
+        <v>0</v>
+      </c>
+      <c r="J290">
+        <v>2</v>
+      </c>
+      <c r="K290" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11">
+      <c r="A291" t="s">
+        <v>72</v>
+      </c>
+      <c r="B291" t="s">
+        <v>180</v>
+      </c>
+      <c r="C291" t="s">
+        <v>216</v>
+      </c>
+      <c r="D291" t="s">
+        <v>222</v>
+      </c>
+      <c r="E291">
+        <v>0</v>
+      </c>
+      <c r="F291">
+        <v>0</v>
+      </c>
+      <c r="G291">
+        <v>6</v>
+      </c>
+      <c r="H291">
+        <v>0</v>
+      </c>
+      <c r="I291">
+        <v>0</v>
+      </c>
+      <c r="J291">
+        <v>2</v>
+      </c>
+      <c r="K291" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11">
+      <c r="A292" t="s">
+        <v>72</v>
+      </c>
+      <c r="B292" t="s">
+        <v>181</v>
+      </c>
+      <c r="C292" t="s">
+        <v>202</v>
+      </c>
+      <c r="D292" t="s">
+        <v>222</v>
+      </c>
+      <c r="E292">
+        <v>0</v>
+      </c>
+      <c r="F292">
+        <v>0</v>
+      </c>
+      <c r="G292">
+        <v>6</v>
+      </c>
+      <c r="H292">
+        <v>0</v>
+      </c>
+      <c r="I292">
+        <v>0</v>
+      </c>
+      <c r="J292">
+        <v>2</v>
+      </c>
+      <c r="K292" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11">
+      <c r="A293" t="s">
+        <v>72</v>
+      </c>
+      <c r="B293" t="s">
+        <v>182</v>
+      </c>
+      <c r="C293" t="s">
+        <v>217</v>
+      </c>
+      <c r="D293" t="s">
+        <v>222</v>
+      </c>
+      <c r="E293">
+        <v>0</v>
+      </c>
+      <c r="F293">
+        <v>0</v>
+      </c>
+      <c r="G293">
+        <v>6</v>
+      </c>
+      <c r="H293">
+        <v>0</v>
+      </c>
+      <c r="I293">
+        <v>0</v>
+      </c>
+      <c r="J293">
+        <v>2</v>
+      </c>
+      <c r="K293" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11">
+      <c r="A294" t="s">
+        <v>73</v>
+      </c>
+      <c r="B294" t="s">
+        <v>173</v>
+      </c>
+      <c r="C294" t="s">
+        <v>199</v>
+      </c>
+      <c r="D294" t="s">
+        <v>222</v>
+      </c>
+      <c r="E294">
+        <v>0</v>
+      </c>
+      <c r="F294">
+        <v>5</v>
+      </c>
+      <c r="G294">
+        <v>0</v>
+      </c>
+      <c r="H294">
+        <v>0</v>
+      </c>
+      <c r="I294">
+        <v>6</v>
+      </c>
+      <c r="J294">
+        <v>2</v>
+      </c>
+      <c r="K294" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11">
+      <c r="A295" t="s">
+        <v>73</v>
+      </c>
+      <c r="B295" t="s">
+        <v>164</v>
+      </c>
+      <c r="C295" t="s">
+        <v>199</v>
+      </c>
+      <c r="D295" t="s">
+        <v>222</v>
+      </c>
+      <c r="E295">
+        <v>0</v>
+      </c>
+      <c r="F295">
+        <v>5</v>
+      </c>
+      <c r="G295">
+        <v>0</v>
+      </c>
+      <c r="H295">
+        <v>0</v>
+      </c>
+      <c r="I295">
+        <v>6</v>
+      </c>
+      <c r="J295">
+        <v>2</v>
+      </c>
+      <c r="K295" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11">
+      <c r="A296" t="s">
+        <v>73</v>
+      </c>
+      <c r="B296" t="s">
+        <v>173</v>
+      </c>
+      <c r="C296" t="s">
+        <v>199</v>
+      </c>
+      <c r="D296" t="s">
+        <v>222</v>
+      </c>
+      <c r="E296">
+        <v>0</v>
+      </c>
+      <c r="F296">
+        <v>5</v>
+      </c>
+      <c r="G296">
+        <v>0</v>
+      </c>
+      <c r="H296">
+        <v>0</v>
+      </c>
+      <c r="I296">
+        <v>9</v>
+      </c>
+      <c r="J296">
+        <v>4</v>
+      </c>
+      <c r="K296" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11">
+      <c r="A297" t="s">
+        <v>73</v>
+      </c>
+      <c r="B297" t="s">
+        <v>164</v>
+      </c>
+      <c r="C297" t="s">
+        <v>199</v>
+      </c>
+      <c r="D297" t="s">
+        <v>222</v>
+      </c>
+      <c r="E297">
+        <v>0</v>
+      </c>
+      <c r="F297">
+        <v>5</v>
+      </c>
+      <c r="G297">
+        <v>0</v>
+      </c>
+      <c r="H297">
+        <v>0</v>
+      </c>
+      <c r="I297">
+        <v>9</v>
+      </c>
+      <c r="J297">
+        <v>4</v>
+      </c>
+      <c r="K297" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11">
+      <c r="A298" t="s">
+        <v>74</v>
+      </c>
+      <c r="B298" t="s">
+        <v>163</v>
+      </c>
+      <c r="C298" t="s">
+        <v>199</v>
+      </c>
+      <c r="D298" t="s">
+        <v>222</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>5</v>
+      </c>
+      <c r="G298">
+        <v>0</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>6</v>
+      </c>
+      <c r="J298">
+        <v>2</v>
+      </c>
+      <c r="K298" t="s">
+        <v>226</v>
       </c>
     </row>
   </sheetData>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1277" uniqueCount="227">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1497" uniqueCount="250">
   <si>
     <t>Date</t>
   </si>
@@ -241,6 +241,27 @@
     <t>2022-01-13</t>
   </si>
   <si>
+    <t>2022-01-14</t>
+  </si>
+  <si>
+    <t>2022-01-15</t>
+  </si>
+  <si>
+    <t>2022-01-18</t>
+  </si>
+  <si>
+    <t>2022-01-19</t>
+  </si>
+  <si>
+    <t>2022-01-20</t>
+  </si>
+  <si>
+    <t>2022-01-22</t>
+  </si>
+  <si>
+    <t>2022-02-11</t>
+  </si>
+  <si>
     <t>DG27001</t>
   </si>
   <si>
@@ -577,6 +598,24 @@
     <t>DG30007</t>
   </si>
   <si>
+    <t>DG21004</t>
+  </si>
+  <si>
+    <t>DG21005</t>
+  </si>
+  <si>
+    <t>DG21006</t>
+  </si>
+  <si>
+    <t>DG21007</t>
+  </si>
+  <si>
+    <t>DG30008</t>
+  </si>
+  <si>
+    <t>DG28008</t>
+  </si>
+  <si>
     <t>N14</t>
   </si>
   <si>
@@ -677,6 +716,36 @@
   </si>
   <si>
     <t>3.001</t>
+  </si>
+  <si>
+    <t>3.120</t>
+  </si>
+  <si>
+    <t>3.064</t>
+  </si>
+  <si>
+    <t>0.114</t>
+  </si>
+  <si>
+    <t>0.715</t>
+  </si>
+  <si>
+    <t>3.030</t>
+  </si>
+  <si>
+    <t>3.011</t>
+  </si>
+  <si>
+    <t>1.011</t>
+  </si>
+  <si>
+    <t>3.038</t>
+  </si>
+  <si>
+    <t>3.025</t>
+  </si>
+  <si>
+    <t>2.025</t>
   </si>
   <si>
     <t>N41</t>
@@ -1052,7 +1121,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K298"/>
+  <dimension ref="A1:K342"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -1095,13 +1164,13 @@
         <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C2">
         <v>3</v>
       </c>
       <c r="D2" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -1122,7 +1191,7 @@
         <v>2</v>
       </c>
       <c r="K2" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1130,13 +1199,13 @@
         <v>11</v>
       </c>
       <c r="B3" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E3">
         <v>0</v>
@@ -1157,7 +1226,7 @@
         <v>2</v>
       </c>
       <c r="K3" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -1165,13 +1234,13 @@
         <v>11</v>
       </c>
       <c r="B4" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C4">
         <v>3</v>
       </c>
       <c r="D4" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E4">
         <v>0</v>
@@ -1192,7 +1261,7 @@
         <v>2</v>
       </c>
       <c r="K4" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -1200,13 +1269,13 @@
         <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C5">
         <v>4.634</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E5">
         <v>0</v>
@@ -1227,7 +1296,7 @@
         <v>3</v>
       </c>
       <c r="K5" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -1235,13 +1304,13 @@
         <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C6">
         <v>3</v>
       </c>
       <c r="D6" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E6">
         <v>0</v>
@@ -1262,7 +1331,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -1270,13 +1339,13 @@
         <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C7">
         <v>3</v>
       </c>
       <c r="D7" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E7">
         <v>0</v>
@@ -1297,7 +1366,7 @@
         <v>2</v>
       </c>
       <c r="K7" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -1305,13 +1374,13 @@
         <v>12</v>
       </c>
       <c r="B8" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C8">
         <v>3</v>
       </c>
       <c r="D8" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -1332,7 +1401,7 @@
         <v>2</v>
       </c>
       <c r="K8" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -1340,13 +1409,13 @@
         <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C9">
         <v>3</v>
       </c>
       <c r="D9" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -1367,7 +1436,7 @@
         <v>3</v>
       </c>
       <c r="K9" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -1375,13 +1444,13 @@
         <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C10">
         <v>3</v>
       </c>
       <c r="D10" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E10">
         <v>0</v>
@@ -1402,7 +1471,7 @@
         <v>3</v>
       </c>
       <c r="K10" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -1410,13 +1479,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C11">
         <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -1437,7 +1506,7 @@
         <v>3</v>
       </c>
       <c r="K11" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -1445,13 +1514,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C12">
         <v>4.634</v>
       </c>
       <c r="D12" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -1472,7 +1541,7 @@
         <v>4</v>
       </c>
       <c r="K12" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -1480,13 +1549,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C13">
         <v>3</v>
       </c>
       <c r="D13" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -1507,7 +1576,7 @@
         <v>3</v>
       </c>
       <c r="K13" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -1515,13 +1584,13 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C14">
         <v>3</v>
       </c>
       <c r="D14" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -1542,7 +1611,7 @@
         <v>3</v>
       </c>
       <c r="K14" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -1550,13 +1619,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C15">
         <v>3</v>
       </c>
       <c r="D15" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -1577,7 +1646,7 @@
         <v>3</v>
       </c>
       <c r="K15" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -1585,13 +1654,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C16">
         <v>3</v>
       </c>
       <c r="D16" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -1612,7 +1681,7 @@
         <v>2</v>
       </c>
       <c r="K16" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="17" spans="1:11">
@@ -1620,13 +1689,13 @@
         <v>15</v>
       </c>
       <c r="B17" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C17">
         <v>3</v>
       </c>
       <c r="D17" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -1647,7 +1716,7 @@
         <v>2</v>
       </c>
       <c r="K17" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="18" spans="1:11">
@@ -1655,13 +1724,13 @@
         <v>15</v>
       </c>
       <c r="B18" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C18">
         <v>3</v>
       </c>
       <c r="D18" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -1682,7 +1751,7 @@
         <v>2</v>
       </c>
       <c r="K18" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="19" spans="1:11">
@@ -1690,13 +1759,13 @@
         <v>15</v>
       </c>
       <c r="B19" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C19">
         <v>3</v>
       </c>
       <c r="D19" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -1717,7 +1786,7 @@
         <v>2</v>
       </c>
       <c r="K19" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:11">
@@ -1725,13 +1794,13 @@
         <v>16</v>
       </c>
       <c r="B20" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C20">
         <v>3</v>
       </c>
       <c r="D20" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -1752,7 +1821,7 @@
         <v>2</v>
       </c>
       <c r="K20" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="21" spans="1:11">
@@ -1760,13 +1829,13 @@
         <v>16</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>3</v>
       </c>
       <c r="D21" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -1787,7 +1856,7 @@
         <v>2</v>
       </c>
       <c r="K21" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="22" spans="1:11">
@@ -1795,13 +1864,13 @@
         <v>17</v>
       </c>
       <c r="B22" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C22">
         <v>3</v>
       </c>
       <c r="D22" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -1822,7 +1891,7 @@
         <v>2</v>
       </c>
       <c r="K22" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="23" spans="1:11">
@@ -1830,13 +1899,13 @@
         <v>17</v>
       </c>
       <c r="B23" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C23">
         <v>3</v>
       </c>
       <c r="D23" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -1857,7 +1926,7 @@
         <v>2</v>
       </c>
       <c r="K23" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="24" spans="1:11">
@@ -1865,13 +1934,13 @@
         <v>17</v>
       </c>
       <c r="B24" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C24">
         <v>0.452</v>
       </c>
       <c r="D24" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -1892,7 +1961,7 @@
         <v>1</v>
       </c>
       <c r="K24" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="25" spans="1:11">
@@ -1900,13 +1969,13 @@
         <v>17</v>
       </c>
       <c r="B25" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C25">
         <v>3</v>
       </c>
       <c r="D25" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E25">
         <v>0</v>
@@ -1927,7 +1996,7 @@
         <v>2</v>
       </c>
       <c r="K25" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="26" spans="1:11">
@@ -1935,13 +2004,13 @@
         <v>18</v>
       </c>
       <c r="B26" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C26">
         <v>3</v>
       </c>
       <c r="D26" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E26">
         <v>0</v>
@@ -1962,7 +2031,7 @@
         <v>2</v>
       </c>
       <c r="K26" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="27" spans="1:11">
@@ -1970,13 +2039,13 @@
         <v>18</v>
       </c>
       <c r="B27" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C27">
         <v>3</v>
       </c>
       <c r="D27" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E27">
         <v>0</v>
@@ -1997,7 +2066,7 @@
         <v>2</v>
       </c>
       <c r="K27" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="28" spans="1:11">
@@ -2005,13 +2074,13 @@
         <v>18</v>
       </c>
       <c r="B28" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C28">
         <v>3</v>
       </c>
       <c r="D28" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E28">
         <v>0</v>
@@ -2032,7 +2101,7 @@
         <v>2</v>
       </c>
       <c r="K28" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="29" spans="1:11">
@@ -2040,13 +2109,13 @@
         <v>19</v>
       </c>
       <c r="B29" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C29">
         <v>3</v>
       </c>
       <c r="D29" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -2067,7 +2136,7 @@
         <v>2</v>
       </c>
       <c r="K29" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="30" spans="1:11">
@@ -2075,13 +2144,13 @@
         <v>19</v>
       </c>
       <c r="B30" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C30">
         <v>3</v>
       </c>
       <c r="D30" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -2102,7 +2171,7 @@
         <v>2</v>
       </c>
       <c r="K30" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="31" spans="1:11">
@@ -2110,13 +2179,13 @@
         <v>19</v>
       </c>
       <c r="B31" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C31">
         <v>3</v>
       </c>
       <c r="D31" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E31">
         <v>0</v>
@@ -2137,7 +2206,7 @@
         <v>2</v>
       </c>
       <c r="K31" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="32" spans="1:11">
@@ -2145,13 +2214,13 @@
         <v>19</v>
       </c>
       <c r="B32" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C32">
         <v>0.08400000000000001</v>
       </c>
       <c r="D32" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E32">
         <v>0</v>
@@ -2172,7 +2241,7 @@
         <v>1</v>
       </c>
       <c r="K32" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="33" spans="1:11">
@@ -2180,13 +2249,13 @@
         <v>20</v>
       </c>
       <c r="B33" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C33">
         <v>3</v>
       </c>
       <c r="D33" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E33">
         <v>0</v>
@@ -2207,7 +2276,7 @@
         <v>2</v>
       </c>
       <c r="K33" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="34" spans="1:11">
@@ -2215,13 +2284,13 @@
         <v>20</v>
       </c>
       <c r="B34" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C34">
         <v>3</v>
       </c>
       <c r="D34" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E34">
         <v>0</v>
@@ -2242,7 +2311,7 @@
         <v>2</v>
       </c>
       <c r="K34" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="35" spans="1:11">
@@ -2250,13 +2319,13 @@
         <v>20</v>
       </c>
       <c r="B35" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C35">
         <v>3</v>
       </c>
       <c r="D35" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E35">
         <v>0</v>
@@ -2277,7 +2346,7 @@
         <v>2</v>
       </c>
       <c r="K35" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="36" spans="1:11">
@@ -2285,13 +2354,13 @@
         <v>21</v>
       </c>
       <c r="B36" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C36">
         <v>3</v>
       </c>
       <c r="D36" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E36">
         <v>0</v>
@@ -2312,7 +2381,7 @@
         <v>2</v>
       </c>
       <c r="K36" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="37" spans="1:11">
@@ -2320,13 +2389,13 @@
         <v>21</v>
       </c>
       <c r="B37" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C37">
         <v>3</v>
       </c>
       <c r="D37" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E37">
         <v>0</v>
@@ -2347,7 +2416,7 @@
         <v>2</v>
       </c>
       <c r="K37" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="38" spans="1:11">
@@ -2355,13 +2424,13 @@
         <v>21</v>
       </c>
       <c r="B38" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C38">
         <v>0.452</v>
       </c>
       <c r="D38" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E38">
         <v>0</v>
@@ -2382,7 +2451,7 @@
         <v>1</v>
       </c>
       <c r="K38" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="39" spans="1:11">
@@ -2390,13 +2459,13 @@
         <v>22</v>
       </c>
       <c r="B39" t="s">
-        <v>75</v>
+        <v>82</v>
       </c>
       <c r="C39">
         <v>3</v>
       </c>
       <c r="D39" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E39">
         <v>0</v>
@@ -2417,7 +2486,7 @@
         <v>3</v>
       </c>
       <c r="K39" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="40" spans="1:11">
@@ -2425,13 +2494,13 @@
         <v>22</v>
       </c>
       <c r="B40" t="s">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="C40">
         <v>3</v>
       </c>
       <c r="D40" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E40">
         <v>0</v>
@@ -2452,7 +2521,7 @@
         <v>3</v>
       </c>
       <c r="K40" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="41" spans="1:11">
@@ -2460,13 +2529,13 @@
         <v>22</v>
       </c>
       <c r="B41" t="s">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="C41">
         <v>3</v>
       </c>
       <c r="D41" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E41">
         <v>0</v>
@@ -2487,7 +2556,7 @@
         <v>3</v>
       </c>
       <c r="K41" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="42" spans="1:11">
@@ -2495,13 +2564,13 @@
         <v>23</v>
       </c>
       <c r="B42" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C42">
         <v>3</v>
       </c>
       <c r="D42" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E42">
         <v>0</v>
@@ -2522,7 +2591,7 @@
         <v>3</v>
       </c>
       <c r="K42" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="43" spans="1:11">
@@ -2530,13 +2599,13 @@
         <v>23</v>
       </c>
       <c r="B43" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C43">
         <v>3</v>
       </c>
       <c r="D43" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E43">
         <v>0</v>
@@ -2557,7 +2626,7 @@
         <v>3</v>
       </c>
       <c r="K43" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="44" spans="1:11">
@@ -2565,13 +2634,13 @@
         <v>23</v>
       </c>
       <c r="B44" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C44">
         <v>3</v>
       </c>
       <c r="D44" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E44">
         <v>0</v>
@@ -2589,7 +2658,7 @@
         <v>6</v>
       </c>
       <c r="K44" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="45" spans="1:11">
@@ -2597,13 +2666,13 @@
         <v>23</v>
       </c>
       <c r="B45" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C45">
         <v>3</v>
       </c>
       <c r="D45" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E45">
         <v>0</v>
@@ -2624,7 +2693,7 @@
         <v>3</v>
       </c>
       <c r="K45" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="46" spans="1:11">
@@ -2632,13 +2701,13 @@
         <v>24</v>
       </c>
       <c r="B46" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C46">
         <v>3</v>
       </c>
       <c r="D46" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E46">
         <v>0</v>
@@ -2659,7 +2728,7 @@
         <v>3</v>
       </c>
       <c r="K46" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="47" spans="1:11">
@@ -2667,13 +2736,13 @@
         <v>24</v>
       </c>
       <c r="B47" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C47">
         <v>3</v>
       </c>
       <c r="D47" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E47">
         <v>0</v>
@@ -2694,7 +2763,7 @@
         <v>3</v>
       </c>
       <c r="K47" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="48" spans="1:11">
@@ -2702,13 +2771,13 @@
         <v>24</v>
       </c>
       <c r="B48" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C48">
         <v>3</v>
       </c>
       <c r="D48" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E48">
         <v>0</v>
@@ -2729,7 +2798,7 @@
         <v>3</v>
       </c>
       <c r="K48" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="49" spans="1:11">
@@ -2737,13 +2806,13 @@
         <v>24</v>
       </c>
       <c r="B49" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C49">
         <v>3</v>
       </c>
       <c r="D49" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E49">
         <v>0</v>
@@ -2764,7 +2833,7 @@
         <v>3</v>
       </c>
       <c r="K49" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="50" spans="1:11">
@@ -2772,13 +2841,13 @@
         <v>24</v>
       </c>
       <c r="B50" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C50">
         <v>0.845</v>
       </c>
       <c r="D50" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E50">
         <v>0</v>
@@ -2799,7 +2868,7 @@
         <v>1</v>
       </c>
       <c r="K50" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="51" spans="1:11">
@@ -2807,13 +2876,13 @@
         <v>25</v>
       </c>
       <c r="B51" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C51">
         <v>3</v>
       </c>
       <c r="D51" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E51">
         <v>0</v>
@@ -2834,7 +2903,7 @@
         <v>3</v>
       </c>
       <c r="K51" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="52" spans="1:11">
@@ -2842,13 +2911,13 @@
         <v>25</v>
       </c>
       <c r="B52" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C52">
         <v>3</v>
       </c>
       <c r="D52" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E52">
         <v>0</v>
@@ -2869,7 +2938,7 @@
         <v>2</v>
       </c>
       <c r="K52" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="53" spans="1:11">
@@ -2877,13 +2946,13 @@
         <v>25</v>
       </c>
       <c r="B53" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C53">
         <v>3</v>
       </c>
       <c r="D53" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E53">
         <v>0</v>
@@ -2904,7 +2973,7 @@
         <v>2</v>
       </c>
       <c r="K53" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="54" spans="1:11">
@@ -2912,13 +2981,13 @@
         <v>25</v>
       </c>
       <c r="B54" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C54">
         <v>3</v>
       </c>
       <c r="D54" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E54">
         <v>0</v>
@@ -2939,7 +3008,7 @@
         <v>2</v>
       </c>
       <c r="K54" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="55" spans="1:11">
@@ -2947,13 +3016,13 @@
         <v>25</v>
       </c>
       <c r="B55" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C55">
         <v>0.08400000000000001</v>
       </c>
       <c r="D55" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E55">
         <v>0</v>
@@ -2974,7 +3043,7 @@
         <v>1</v>
       </c>
       <c r="K55" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="56" spans="1:11">
@@ -2982,13 +3051,13 @@
         <v>25</v>
       </c>
       <c r="B56" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C56">
         <v>3</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E56">
         <v>0</v>
@@ -3009,7 +3078,7 @@
         <v>2</v>
       </c>
       <c r="K56" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="57" spans="1:11">
@@ -3017,13 +3086,13 @@
         <v>25</v>
       </c>
       <c r="B57" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C57">
         <v>3</v>
       </c>
       <c r="D57" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E57">
         <v>0</v>
@@ -3044,7 +3113,7 @@
         <v>2</v>
       </c>
       <c r="K57" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="58" spans="1:11">
@@ -3052,13 +3121,13 @@
         <v>25</v>
       </c>
       <c r="B58" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C58">
         <v>3</v>
       </c>
       <c r="D58" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E58">
         <v>0</v>
@@ -3079,7 +3148,7 @@
         <v>2</v>
       </c>
       <c r="K58" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="59" spans="1:11">
@@ -3087,13 +3156,13 @@
         <v>25</v>
       </c>
       <c r="B59" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C59">
         <v>3</v>
       </c>
       <c r="D59" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E59">
         <v>0</v>
@@ -3114,7 +3183,7 @@
         <v>2</v>
       </c>
       <c r="K59" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="60" spans="1:11">
@@ -3122,13 +3191,13 @@
         <v>26</v>
       </c>
       <c r="B60" t="s">
-        <v>79</v>
+        <v>86</v>
       </c>
       <c r="C60">
         <v>3</v>
       </c>
       <c r="D60" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E60">
         <v>0</v>
@@ -3149,7 +3218,7 @@
         <v>3</v>
       </c>
       <c r="K60" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="61" spans="1:11">
@@ -3157,13 +3226,13 @@
         <v>26</v>
       </c>
       <c r="B61" t="s">
-        <v>80</v>
+        <v>87</v>
       </c>
       <c r="C61">
         <v>3</v>
       </c>
       <c r="D61" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E61">
         <v>0</v>
@@ -3184,7 +3253,7 @@
         <v>3</v>
       </c>
       <c r="K61" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="62" spans="1:11">
@@ -3192,13 +3261,13 @@
         <v>26</v>
       </c>
       <c r="B62" t="s">
-        <v>81</v>
+        <v>88</v>
       </c>
       <c r="C62">
         <v>3</v>
       </c>
       <c r="D62" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E62">
         <v>0</v>
@@ -3219,7 +3288,7 @@
         <v>3</v>
       </c>
       <c r="K62" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="63" spans="1:11">
@@ -3227,13 +3296,13 @@
         <v>26</v>
       </c>
       <c r="B63" t="s">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="C63">
         <v>4.634</v>
       </c>
       <c r="D63" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E63">
         <v>0</v>
@@ -3254,7 +3323,7 @@
         <v>4</v>
       </c>
       <c r="K63" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="64" spans="1:11">
@@ -3262,13 +3331,13 @@
         <v>27</v>
       </c>
       <c r="B64" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C64">
         <v>3</v>
       </c>
       <c r="D64" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E64">
         <v>0</v>
@@ -3289,7 +3358,7 @@
         <v>2</v>
       </c>
       <c r="K64" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="65" spans="1:11">
@@ -3297,13 +3366,13 @@
         <v>27</v>
       </c>
       <c r="B65" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C65">
         <v>3</v>
       </c>
       <c r="D65" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E65">
         <v>0</v>
@@ -3324,7 +3393,7 @@
         <v>3</v>
       </c>
       <c r="K65" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="66" spans="1:11">
@@ -3332,13 +3401,13 @@
         <v>27</v>
       </c>
       <c r="B66" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C66">
         <v>3</v>
       </c>
       <c r="D66" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E66">
         <v>0</v>
@@ -3359,7 +3428,7 @@
         <v>2</v>
       </c>
       <c r="K66" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="67" spans="1:11">
@@ -3367,13 +3436,13 @@
         <v>27</v>
       </c>
       <c r="B67" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C67">
         <v>3</v>
       </c>
       <c r="D67" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E67">
         <v>0</v>
@@ -3394,7 +3463,7 @@
         <v>2</v>
       </c>
       <c r="K67" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68" spans="1:11">
@@ -3402,13 +3471,13 @@
         <v>28</v>
       </c>
       <c r="B68" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C68">
         <v>3</v>
       </c>
       <c r="D68" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E68">
         <v>0</v>
@@ -3429,7 +3498,7 @@
         <v>2</v>
       </c>
       <c r="K68" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="69" spans="1:11">
@@ -3437,13 +3506,13 @@
         <v>28</v>
       </c>
       <c r="B69" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C69">
         <v>3</v>
       </c>
       <c r="D69" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E69">
         <v>0</v>
@@ -3464,7 +3533,7 @@
         <v>2</v>
       </c>
       <c r="K69" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="70" spans="1:11">
@@ -3472,13 +3541,13 @@
         <v>28</v>
       </c>
       <c r="B70" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C70">
         <v>3</v>
       </c>
       <c r="D70" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E70">
         <v>0</v>
@@ -3499,7 +3568,7 @@
         <v>2</v>
       </c>
       <c r="K70" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="71" spans="1:11">
@@ -3507,13 +3576,13 @@
         <v>28</v>
       </c>
       <c r="B71" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C71">
         <v>3</v>
       </c>
       <c r="D71" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E71">
         <v>0</v>
@@ -3534,7 +3603,7 @@
         <v>2</v>
       </c>
       <c r="K71" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="72" spans="1:11">
@@ -3542,13 +3611,13 @@
         <v>28</v>
       </c>
       <c r="B72" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C72">
         <v>0.08400000000000001</v>
       </c>
       <c r="D72" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E72">
         <v>0</v>
@@ -3569,7 +3638,7 @@
         <v>1</v>
       </c>
       <c r="K72" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="73" spans="1:11">
@@ -3577,13 +3646,13 @@
         <v>28</v>
       </c>
       <c r="B73" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C73">
         <v>3</v>
       </c>
       <c r="D73" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E73">
         <v>0</v>
@@ -3604,7 +3673,7 @@
         <v>2</v>
       </c>
       <c r="K73" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="74" spans="1:11">
@@ -3612,13 +3681,13 @@
         <v>28</v>
       </c>
       <c r="B74" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C74">
         <v>3</v>
       </c>
       <c r="D74" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E74">
         <v>0</v>
@@ -3639,7 +3708,7 @@
         <v>2</v>
       </c>
       <c r="K74" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="75" spans="1:11">
@@ -3647,13 +3716,13 @@
         <v>28</v>
       </c>
       <c r="B75" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C75">
         <v>3</v>
       </c>
       <c r="D75" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E75">
         <v>0</v>
@@ -3674,7 +3743,7 @@
         <v>2</v>
       </c>
       <c r="K75" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="76" spans="1:11">
@@ -3682,13 +3751,13 @@
         <v>29</v>
       </c>
       <c r="B76" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="C76">
         <v>3</v>
       </c>
       <c r="D76" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E76">
         <v>0</v>
@@ -3709,7 +3778,7 @@
         <v>3</v>
       </c>
       <c r="K76" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="77" spans="1:11">
@@ -3717,13 +3786,13 @@
         <v>29</v>
       </c>
       <c r="B77" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C77">
         <v>3</v>
       </c>
       <c r="D77" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E77">
         <v>0</v>
@@ -3744,7 +3813,7 @@
         <v>3</v>
       </c>
       <c r="K77" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="78" spans="1:11">
@@ -3752,13 +3821,13 @@
         <v>29</v>
       </c>
       <c r="B78" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="C78">
         <v>3</v>
       </c>
       <c r="D78" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E78">
         <v>0</v>
@@ -3779,7 +3848,7 @@
         <v>3</v>
       </c>
       <c r="K78" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="79" spans="1:11">
@@ -3787,13 +3856,13 @@
         <v>29</v>
       </c>
       <c r="B79" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="C79">
         <v>3</v>
       </c>
       <c r="D79" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E79">
         <v>0</v>
@@ -3814,7 +3883,7 @@
         <v>3</v>
       </c>
       <c r="K79" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="80" spans="1:11">
@@ -3822,13 +3891,13 @@
         <v>30</v>
       </c>
       <c r="B80" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C80">
         <v>3</v>
       </c>
       <c r="D80" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E80">
         <v>0</v>
@@ -3849,7 +3918,7 @@
         <v>2</v>
       </c>
       <c r="K80" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="81" spans="1:11">
@@ -3857,13 +3926,13 @@
         <v>30</v>
       </c>
       <c r="B81" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C81">
         <v>3</v>
       </c>
       <c r="D81" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E81">
         <v>0</v>
@@ -3884,7 +3953,7 @@
         <v>2</v>
       </c>
       <c r="K81" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="82" spans="1:11">
@@ -3892,13 +3961,13 @@
         <v>30</v>
       </c>
       <c r="B82" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C82">
         <v>3</v>
       </c>
       <c r="D82" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E82">
         <v>0</v>
@@ -3919,7 +3988,7 @@
         <v>2</v>
       </c>
       <c r="K82" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="83" spans="1:11">
@@ -3927,13 +3996,13 @@
         <v>30</v>
       </c>
       <c r="B83" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C83">
         <v>3</v>
       </c>
       <c r="D83" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E83">
         <v>0</v>
@@ -3954,7 +4023,7 @@
         <v>3</v>
       </c>
       <c r="K83" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="84" spans="1:11">
@@ -3962,13 +4031,13 @@
         <v>30</v>
       </c>
       <c r="B84" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C84">
         <v>3</v>
       </c>
       <c r="D84" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E84">
         <v>0</v>
@@ -3989,7 +4058,7 @@
         <v>3</v>
       </c>
       <c r="K84" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="85" spans="1:11">
@@ -3997,13 +4066,13 @@
         <v>30</v>
       </c>
       <c r="B85" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C85">
         <v>3</v>
       </c>
       <c r="D85" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E85">
         <v>0</v>
@@ -4024,7 +4093,7 @@
         <v>3</v>
       </c>
       <c r="K85" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="86" spans="1:11">
@@ -4032,13 +4101,13 @@
         <v>31</v>
       </c>
       <c r="B86" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="C86">
         <v>3</v>
       </c>
       <c r="D86" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E86">
         <v>0</v>
@@ -4059,7 +4128,7 @@
         <v>3</v>
       </c>
       <c r="K86" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="87" spans="1:11">
@@ -4067,13 +4136,13 @@
         <v>31</v>
       </c>
       <c r="B87" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="C87">
         <v>3</v>
       </c>
       <c r="D87" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E87">
         <v>0</v>
@@ -4094,7 +4163,7 @@
         <v>3</v>
       </c>
       <c r="K87" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="88" spans="1:11">
@@ -4102,13 +4171,13 @@
         <v>31</v>
       </c>
       <c r="B88" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="C88">
         <v>3</v>
       </c>
       <c r="D88" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E88">
         <v>0</v>
@@ -4129,7 +4198,7 @@
         <v>3</v>
       </c>
       <c r="K88" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="89" spans="1:11">
@@ -4137,13 +4206,13 @@
         <v>31</v>
       </c>
       <c r="B89" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="C89">
         <v>3</v>
       </c>
       <c r="D89" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E89">
         <v>0</v>
@@ -4164,7 +4233,7 @@
         <v>3</v>
       </c>
       <c r="K89" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="90" spans="1:11">
@@ -4172,13 +4241,13 @@
         <v>31</v>
       </c>
       <c r="B90" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="C90">
         <v>0.421</v>
       </c>
       <c r="D90" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E90">
         <v>0</v>
@@ -4199,7 +4268,7 @@
         <v>1</v>
       </c>
       <c r="K90" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="91" spans="1:11">
@@ -4207,13 +4276,13 @@
         <v>30</v>
       </c>
       <c r="B91" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
       <c r="C91">
         <v>3</v>
       </c>
       <c r="D91" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E91">
         <v>0</v>
@@ -4234,7 +4303,7 @@
         <v>3</v>
       </c>
       <c r="K91" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="92" spans="1:11">
@@ -4242,13 +4311,13 @@
         <v>30</v>
       </c>
       <c r="B92" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="C92">
         <v>3</v>
       </c>
       <c r="D92" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E92">
         <v>0</v>
@@ -4269,7 +4338,7 @@
         <v>3</v>
       </c>
       <c r="K92" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="93" spans="1:11">
@@ -4277,13 +4346,13 @@
         <v>32</v>
       </c>
       <c r="B93" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="C93">
         <v>3</v>
       </c>
       <c r="D93" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E93">
         <v>0</v>
@@ -4304,7 +4373,7 @@
         <v>3</v>
       </c>
       <c r="K93" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="94" spans="1:11">
@@ -4312,13 +4381,13 @@
         <v>30</v>
       </c>
       <c r="B94" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="C94">
         <v>3</v>
       </c>
       <c r="D94" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E94">
         <v>0</v>
@@ -4339,7 +4408,7 @@
         <v>3</v>
       </c>
       <c r="K94" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="95" spans="1:11">
@@ -4347,13 +4416,13 @@
         <v>30</v>
       </c>
       <c r="B95" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="C95">
         <v>0.08400000000000001</v>
       </c>
       <c r="D95" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E95">
         <v>0</v>
@@ -4374,7 +4443,7 @@
         <v>1</v>
       </c>
       <c r="K95" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="96" spans="1:11">
@@ -4382,13 +4451,13 @@
         <v>33</v>
       </c>
       <c r="B96" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C96">
         <v>3</v>
       </c>
       <c r="D96" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E96">
         <v>0</v>
@@ -4409,7 +4478,7 @@
         <v>3</v>
       </c>
       <c r="K96" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="97" spans="1:11">
@@ -4417,13 +4486,13 @@
         <v>33</v>
       </c>
       <c r="B97" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C97">
         <v>3</v>
       </c>
       <c r="D97" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E97">
         <v>0</v>
@@ -4444,7 +4513,7 @@
         <v>3</v>
       </c>
       <c r="K97" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="98" spans="1:11">
@@ -4452,13 +4521,13 @@
         <v>33</v>
       </c>
       <c r="B98" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C98">
         <v>3</v>
       </c>
       <c r="D98" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E98">
         <v>0</v>
@@ -4479,7 +4548,7 @@
         <v>3</v>
       </c>
       <c r="K98" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="99" spans="1:11">
@@ -4487,13 +4556,13 @@
         <v>33</v>
       </c>
       <c r="B99" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C99">
         <v>3</v>
       </c>
       <c r="D99" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E99">
         <v>0</v>
@@ -4514,7 +4583,7 @@
         <v>3</v>
       </c>
       <c r="K99" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="100" spans="1:11">
@@ -4522,13 +4591,13 @@
         <v>34</v>
       </c>
       <c r="B100" t="s">
-        <v>82</v>
+        <v>89</v>
       </c>
       <c r="C100">
         <v>3</v>
       </c>
       <c r="D100" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E100">
         <v>0</v>
@@ -4549,7 +4618,7 @@
         <v>3</v>
       </c>
       <c r="K100" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="101" spans="1:11">
@@ -4557,13 +4626,13 @@
         <v>34</v>
       </c>
       <c r="B101" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="C101">
         <v>3</v>
       </c>
       <c r="D101" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E101">
         <v>0</v>
@@ -4584,7 +4653,7 @@
         <v>3</v>
       </c>
       <c r="K101" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="102" spans="1:11">
@@ -4592,13 +4661,13 @@
         <v>34</v>
       </c>
       <c r="B102" t="s">
-        <v>84</v>
+        <v>91</v>
       </c>
       <c r="C102">
         <v>3</v>
       </c>
       <c r="D102" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E102">
         <v>0</v>
@@ -4619,7 +4688,7 @@
         <v>3</v>
       </c>
       <c r="K102" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="103" spans="1:11">
@@ -4627,13 +4696,13 @@
         <v>34</v>
       </c>
       <c r="B103" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="C103">
         <v>3</v>
       </c>
       <c r="D103" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E103">
         <v>0</v>
@@ -4654,7 +4723,7 @@
         <v>3</v>
       </c>
       <c r="K103" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="104" spans="1:11">
@@ -4662,13 +4731,13 @@
         <v>35</v>
       </c>
       <c r="B104" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C104">
         <v>3</v>
       </c>
       <c r="D104" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E104">
         <v>0</v>
@@ -4689,7 +4758,7 @@
         <v>2</v>
       </c>
       <c r="K104" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="105" spans="1:11">
@@ -4697,13 +4766,13 @@
         <v>35</v>
       </c>
       <c r="B105" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C105">
         <v>3</v>
       </c>
       <c r="D105" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E105">
         <v>0</v>
@@ -4724,7 +4793,7 @@
         <v>2</v>
       </c>
       <c r="K105" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="106" spans="1:11">
@@ -4732,13 +4801,13 @@
         <v>35</v>
       </c>
       <c r="B106" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C106">
         <v>3</v>
       </c>
       <c r="D106" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E106">
         <v>0</v>
@@ -4759,7 +4828,7 @@
         <v>2</v>
       </c>
       <c r="K106" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="107" spans="1:11">
@@ -4767,13 +4836,13 @@
         <v>35</v>
       </c>
       <c r="B107" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C107">
         <v>3</v>
       </c>
       <c r="D107" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E107">
         <v>0</v>
@@ -4794,7 +4863,7 @@
         <v>2</v>
       </c>
       <c r="K107" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="108" spans="1:11">
@@ -4802,13 +4871,13 @@
         <v>35</v>
       </c>
       <c r="B108" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C108">
         <v>3</v>
       </c>
       <c r="D108" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E108">
         <v>0</v>
@@ -4829,7 +4898,7 @@
         <v>2</v>
       </c>
       <c r="K108" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="109" spans="1:11">
@@ -4837,13 +4906,13 @@
         <v>35</v>
       </c>
       <c r="B109" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C109">
         <v>3</v>
       </c>
       <c r="D109" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E109">
         <v>0</v>
@@ -4864,7 +4933,7 @@
         <v>2</v>
       </c>
       <c r="K109" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="110" spans="1:11">
@@ -4872,13 +4941,13 @@
         <v>36</v>
       </c>
       <c r="B110" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C110">
         <v>3</v>
       </c>
       <c r="D110" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="E110">
         <v>0</v>
@@ -4899,7 +4968,7 @@
         <v>2</v>
       </c>
       <c r="K110" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="111" spans="1:11">
@@ -4907,13 +4976,13 @@
         <v>36</v>
       </c>
       <c r="B111" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C111">
         <v>3</v>
       </c>
       <c r="D111" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="E111">
         <v>0</v>
@@ -4934,7 +5003,7 @@
         <v>2</v>
       </c>
       <c r="K111" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="112" spans="1:11">
@@ -4942,13 +5011,13 @@
         <v>37</v>
       </c>
       <c r="B112" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C112">
         <v>3</v>
       </c>
       <c r="D112" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="E112">
         <v>9</v>
@@ -4969,7 +5038,7 @@
         <v>2</v>
       </c>
       <c r="K112" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="113" spans="1:11">
@@ -4977,13 +5046,13 @@
         <v>37</v>
       </c>
       <c r="B113" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C113">
         <v>3</v>
       </c>
       <c r="D113" t="s">
-        <v>224</v>
+        <v>247</v>
       </c>
       <c r="E113">
         <v>9</v>
@@ -5004,7 +5073,7 @@
         <v>2</v>
       </c>
       <c r="K113" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="114" spans="1:11">
@@ -5012,13 +5081,13 @@
         <v>37</v>
       </c>
       <c r="B114" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C114">
         <v>3</v>
       </c>
       <c r="D114" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E114">
         <v>0</v>
@@ -5039,7 +5108,7 @@
         <v>3</v>
       </c>
       <c r="K114" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="115" spans="1:11">
@@ -5047,13 +5116,13 @@
         <v>37</v>
       </c>
       <c r="B115" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="C115">
         <v>3</v>
       </c>
       <c r="D115" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E115">
         <v>0</v>
@@ -5074,7 +5143,7 @@
         <v>3</v>
       </c>
       <c r="K115" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="116" spans="1:11">
@@ -5082,13 +5151,13 @@
         <v>37</v>
       </c>
       <c r="B116" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C116">
         <v>3</v>
       </c>
       <c r="D116" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E116">
         <v>0</v>
@@ -5109,7 +5178,7 @@
         <v>3</v>
       </c>
       <c r="K116" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="117" spans="1:11">
@@ -5117,13 +5186,13 @@
         <v>37</v>
       </c>
       <c r="B117" t="s">
-        <v>89</v>
+        <v>96</v>
       </c>
       <c r="C117">
         <v>3</v>
       </c>
       <c r="D117" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E117">
         <v>0</v>
@@ -5144,7 +5213,7 @@
         <v>3</v>
       </c>
       <c r="K117" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="118" spans="1:11">
@@ -5152,13 +5221,13 @@
         <v>37</v>
       </c>
       <c r="B118" t="s">
-        <v>90</v>
+        <v>97</v>
       </c>
       <c r="C118">
         <v>1</v>
       </c>
       <c r="D118" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E118">
         <v>0</v>
@@ -5179,7 +5248,7 @@
         <v>1</v>
       </c>
       <c r="K118" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="119" spans="1:11">
@@ -5187,13 +5256,13 @@
         <v>37</v>
       </c>
       <c r="B119" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C119">
         <v>3</v>
       </c>
       <c r="D119" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E119">
         <v>0</v>
@@ -5214,7 +5283,7 @@
         <v>2</v>
       </c>
       <c r="K119" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="120" spans="1:11">
@@ -5222,13 +5291,13 @@
         <v>37</v>
       </c>
       <c r="B120" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C120">
         <v>3</v>
       </c>
       <c r="D120" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E120">
         <v>0</v>
@@ -5249,7 +5318,7 @@
         <v>2</v>
       </c>
       <c r="K120" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="121" spans="1:11">
@@ -5257,13 +5326,13 @@
         <v>38</v>
       </c>
       <c r="B121" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C121">
         <v>3</v>
       </c>
       <c r="D121" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E121">
         <v>0</v>
@@ -5284,7 +5353,7 @@
         <v>2</v>
       </c>
       <c r="K121" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="122" spans="1:11">
@@ -5292,13 +5361,13 @@
         <v>38</v>
       </c>
       <c r="B122" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C122">
         <v>3</v>
       </c>
       <c r="D122" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E122">
         <v>0</v>
@@ -5319,7 +5388,7 @@
         <v>2</v>
       </c>
       <c r="K122" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="123" spans="1:11">
@@ -5327,13 +5396,13 @@
         <v>38</v>
       </c>
       <c r="B123" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C123">
         <v>3</v>
       </c>
       <c r="D123" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E123">
         <v>0</v>
@@ -5354,7 +5423,7 @@
         <v>2</v>
       </c>
       <c r="K123" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="124" spans="1:11">
@@ -5362,13 +5431,13 @@
         <v>38</v>
       </c>
       <c r="B124" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C124">
         <v>3</v>
       </c>
       <c r="D124" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E124">
         <v>9</v>
@@ -5389,7 +5458,7 @@
         <v>4</v>
       </c>
       <c r="K124" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="125" spans="1:11">
@@ -5397,13 +5466,13 @@
         <v>38</v>
       </c>
       <c r="B125" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C125">
         <v>3</v>
       </c>
       <c r="D125" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E125">
         <v>9</v>
@@ -5424,7 +5493,7 @@
         <v>4</v>
       </c>
       <c r="K125" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="126" spans="1:11">
@@ -5432,13 +5501,13 @@
         <v>39</v>
       </c>
       <c r="B126" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C126">
         <v>3</v>
       </c>
       <c r="D126" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E126">
         <v>9</v>
@@ -5459,7 +5528,7 @@
         <v>4</v>
       </c>
       <c r="K126" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="127" spans="1:11">
@@ -5467,13 +5536,13 @@
         <v>39</v>
       </c>
       <c r="B127" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C127">
         <v>3</v>
       </c>
       <c r="D127" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E127">
         <v>9</v>
@@ -5494,7 +5563,7 @@
         <v>4</v>
       </c>
       <c r="K127" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="128" spans="1:11">
@@ -5502,13 +5571,13 @@
         <v>40</v>
       </c>
       <c r="B128" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C128">
         <v>3</v>
       </c>
       <c r="D128" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E128">
         <v>9</v>
@@ -5529,7 +5598,7 @@
         <v>4</v>
       </c>
       <c r="K128" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="129" spans="1:11">
@@ -5537,13 +5606,13 @@
         <v>40</v>
       </c>
       <c r="B129" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C129">
         <v>3</v>
       </c>
       <c r="D129" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E129">
         <v>9</v>
@@ -5564,7 +5633,7 @@
         <v>4</v>
       </c>
       <c r="K129" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="130" spans="1:11">
@@ -5572,13 +5641,13 @@
         <v>40</v>
       </c>
       <c r="B130" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C130">
         <v>1</v>
       </c>
       <c r="D130" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E130">
         <v>4</v>
@@ -5599,7 +5668,7 @@
         <v>2</v>
       </c>
       <c r="K130" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="131" spans="1:11">
@@ -5607,13 +5676,13 @@
         <v>41</v>
       </c>
       <c r="B131" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="C131">
         <v>3</v>
       </c>
       <c r="D131" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E131">
         <v>0</v>
@@ -5634,7 +5703,7 @@
         <v>3</v>
       </c>
       <c r="K131" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="132" spans="1:11">
@@ -5642,13 +5711,13 @@
         <v>41</v>
       </c>
       <c r="B132" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="C132">
         <v>3</v>
       </c>
       <c r="D132" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E132">
         <v>0</v>
@@ -5669,7 +5738,7 @@
         <v>3</v>
       </c>
       <c r="K132" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="133" spans="1:11">
@@ -5677,13 +5746,13 @@
         <v>41</v>
       </c>
       <c r="B133" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="C133">
         <v>3</v>
       </c>
       <c r="D133" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E133">
         <v>0</v>
@@ -5704,7 +5773,7 @@
         <v>3</v>
       </c>
       <c r="K133" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="134" spans="1:11">
@@ -5712,13 +5781,13 @@
         <v>41</v>
       </c>
       <c r="B134" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="C134">
         <v>3</v>
       </c>
       <c r="D134" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E134">
         <v>0</v>
@@ -5739,7 +5808,7 @@
         <v>3</v>
       </c>
       <c r="K134" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="135" spans="1:11">
@@ -5747,13 +5816,13 @@
         <v>42</v>
       </c>
       <c r="B135" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C135">
         <v>3</v>
       </c>
       <c r="D135" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E135">
         <v>0</v>
@@ -5774,7 +5843,7 @@
         <v>2</v>
       </c>
       <c r="K135" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="136" spans="1:11">
@@ -5782,13 +5851,13 @@
         <v>42</v>
       </c>
       <c r="B136" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C136">
         <v>3</v>
       </c>
       <c r="D136" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E136">
         <v>0</v>
@@ -5809,7 +5878,7 @@
         <v>2</v>
       </c>
       <c r="K136" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="137" spans="1:11">
@@ -5817,13 +5886,13 @@
         <v>43</v>
       </c>
       <c r="B137" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C137">
         <v>3</v>
       </c>
       <c r="D137" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E137">
         <v>0</v>
@@ -5844,7 +5913,7 @@
         <v>2</v>
       </c>
       <c r="K137" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="138" spans="1:11">
@@ -5852,13 +5921,13 @@
         <v>43</v>
       </c>
       <c r="B138" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C138">
         <v>3</v>
       </c>
       <c r="D138" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E138">
         <v>0</v>
@@ -5879,7 +5948,7 @@
         <v>2</v>
       </c>
       <c r="K138" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="139" spans="1:11">
@@ -5887,13 +5956,13 @@
         <v>43</v>
       </c>
       <c r="B139" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C139">
         <v>3</v>
       </c>
       <c r="D139" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E139">
         <v>0</v>
@@ -5914,7 +5983,7 @@
         <v>2</v>
       </c>
       <c r="K139" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="140" spans="1:11">
@@ -5922,13 +5991,13 @@
         <v>44</v>
       </c>
       <c r="B140" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="C140">
         <v>3</v>
       </c>
       <c r="D140" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E140">
         <v>0</v>
@@ -5949,7 +6018,7 @@
         <v>3</v>
       </c>
       <c r="K140" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="141" spans="1:11">
@@ -5957,13 +6026,13 @@
         <v>44</v>
       </c>
       <c r="B141" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="C141">
         <v>3</v>
       </c>
       <c r="D141" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E141">
         <v>0</v>
@@ -5984,7 +6053,7 @@
         <v>3</v>
       </c>
       <c r="K141" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="142" spans="1:11">
@@ -5992,13 +6061,13 @@
         <v>44</v>
       </c>
       <c r="B142" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="C142">
         <v>3</v>
       </c>
       <c r="D142" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E142">
         <v>0</v>
@@ -6019,7 +6088,7 @@
         <v>3</v>
       </c>
       <c r="K142" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="143" spans="1:11">
@@ -6027,13 +6096,13 @@
         <v>44</v>
       </c>
       <c r="B143" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C143">
         <v>1.89</v>
       </c>
       <c r="D143" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E143">
         <v>0</v>
@@ -6054,7 +6123,7 @@
         <v>2</v>
       </c>
       <c r="K143" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="144" spans="1:11">
@@ -6062,13 +6131,13 @@
         <v>45</v>
       </c>
       <c r="B144" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C144">
         <v>3</v>
       </c>
       <c r="D144" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E144">
         <v>0</v>
@@ -6089,7 +6158,7 @@
         <v>2</v>
       </c>
       <c r="K144" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="145" spans="1:11">
@@ -6097,13 +6166,13 @@
         <v>45</v>
       </c>
       <c r="B145" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C145">
         <v>3</v>
       </c>
       <c r="D145" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E145">
         <v>0</v>
@@ -6124,7 +6193,7 @@
         <v>2</v>
       </c>
       <c r="K145" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="146" spans="1:11">
@@ -6132,13 +6201,13 @@
         <v>45</v>
       </c>
       <c r="B146" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C146">
         <v>3</v>
       </c>
       <c r="D146" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E146">
         <v>0</v>
@@ -6159,7 +6228,7 @@
         <v>2</v>
       </c>
       <c r="K146" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="147" spans="1:11">
@@ -6167,13 +6236,13 @@
         <v>46</v>
       </c>
       <c r="B147" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C147">
         <v>3</v>
       </c>
       <c r="D147" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E147">
         <v>0</v>
@@ -6194,7 +6263,7 @@
         <v>3</v>
       </c>
       <c r="K147" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="148" spans="1:11">
@@ -6202,13 +6271,13 @@
         <v>46</v>
       </c>
       <c r="B148" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C148">
         <v>3</v>
       </c>
       <c r="D148" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E148">
         <v>0</v>
@@ -6229,7 +6298,7 @@
         <v>3</v>
       </c>
       <c r="K148" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="149" spans="1:11">
@@ -6237,13 +6306,13 @@
         <v>46</v>
       </c>
       <c r="B149" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C149">
         <v>3</v>
       </c>
       <c r="D149" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E149">
         <v>0</v>
@@ -6264,7 +6333,7 @@
         <v>3</v>
       </c>
       <c r="K149" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="150" spans="1:11">
@@ -6272,13 +6341,13 @@
         <v>47</v>
       </c>
       <c r="B150" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C150">
         <v>3</v>
       </c>
       <c r="D150" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E150">
         <v>0</v>
@@ -6299,7 +6368,7 @@
         <v>3</v>
       </c>
       <c r="K150" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="151" spans="1:11">
@@ -6307,13 +6376,13 @@
         <v>47</v>
       </c>
       <c r="B151" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C151">
         <v>3</v>
       </c>
       <c r="D151" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E151">
         <v>0</v>
@@ -6334,7 +6403,7 @@
         <v>3</v>
       </c>
       <c r="K151" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="152" spans="1:11">
@@ -6342,13 +6411,13 @@
         <v>47</v>
       </c>
       <c r="B152" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C152">
         <v>3</v>
       </c>
       <c r="D152" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E152">
         <v>0</v>
@@ -6369,7 +6438,7 @@
         <v>3</v>
       </c>
       <c r="K152" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="153" spans="1:11">
@@ -6377,13 +6446,13 @@
         <v>47</v>
       </c>
       <c r="B153" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C153">
         <v>3</v>
       </c>
       <c r="D153" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E153">
         <v>0</v>
@@ -6404,7 +6473,7 @@
         <v>3</v>
       </c>
       <c r="K153" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="154" spans="1:11">
@@ -6412,13 +6481,13 @@
         <v>48</v>
       </c>
       <c r="B154" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C154">
         <v>3</v>
       </c>
       <c r="D154" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E154">
         <v>0</v>
@@ -6439,7 +6508,7 @@
         <v>3</v>
       </c>
       <c r="K154" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="155" spans="1:11">
@@ -6447,13 +6516,13 @@
         <v>48</v>
       </c>
       <c r="B155" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C155">
         <v>3</v>
       </c>
       <c r="D155" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E155">
         <v>0</v>
@@ -6474,7 +6543,7 @@
         <v>3</v>
       </c>
       <c r="K155" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="156" spans="1:11">
@@ -6482,13 +6551,13 @@
         <v>49</v>
       </c>
       <c r="B156" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C156">
         <v>3</v>
       </c>
       <c r="D156" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E156">
         <v>0</v>
@@ -6509,7 +6578,7 @@
         <v>3</v>
       </c>
       <c r="K156" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="157" spans="1:11">
@@ -6517,13 +6586,13 @@
         <v>49</v>
       </c>
       <c r="B157" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C157">
         <v>3</v>
       </c>
       <c r="D157" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E157">
         <v>0</v>
@@ -6544,7 +6613,7 @@
         <v>3</v>
       </c>
       <c r="K157" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="158" spans="1:11">
@@ -6552,13 +6621,13 @@
         <v>49</v>
       </c>
       <c r="B158" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C158">
         <v>2.897</v>
       </c>
       <c r="D158" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E158">
         <v>0</v>
@@ -6579,7 +6648,7 @@
         <v>2</v>
       </c>
       <c r="K158" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="159" spans="1:11">
@@ -6587,13 +6656,13 @@
         <v>50</v>
       </c>
       <c r="B159" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C159">
         <v>3</v>
       </c>
       <c r="D159" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E159">
         <v>0</v>
@@ -6614,7 +6683,7 @@
         <v>3</v>
       </c>
       <c r="K159" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="160" spans="1:11">
@@ -6622,13 +6691,13 @@
         <v>50</v>
       </c>
       <c r="B160" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C160">
         <v>3</v>
       </c>
       <c r="D160" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E160">
         <v>0</v>
@@ -6649,7 +6718,7 @@
         <v>3</v>
       </c>
       <c r="K160" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="161" spans="1:11">
@@ -6657,13 +6726,13 @@
         <v>51</v>
       </c>
       <c r="B161" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C161">
         <v>3</v>
       </c>
       <c r="D161" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E161">
         <v>0</v>
@@ -6684,7 +6753,7 @@
         <v>3</v>
       </c>
       <c r="K161" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="162" spans="1:11">
@@ -6692,13 +6761,13 @@
         <v>51</v>
       </c>
       <c r="B162" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C162">
         <v>3</v>
       </c>
       <c r="D162" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E162">
         <v>0</v>
@@ -6719,7 +6788,7 @@
         <v>3</v>
       </c>
       <c r="K162" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="163" spans="1:11">
@@ -6727,13 +6796,13 @@
         <v>51</v>
       </c>
       <c r="B163" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C163">
         <v>3</v>
       </c>
       <c r="D163" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E163">
         <v>0</v>
@@ -6754,7 +6823,7 @@
         <v>3</v>
       </c>
       <c r="K163" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="164" spans="1:11">
@@ -6762,13 +6831,13 @@
         <v>51</v>
       </c>
       <c r="B164" t="s">
-        <v>135</v>
+        <v>142</v>
       </c>
       <c r="C164">
         <v>3</v>
       </c>
       <c r="D164" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E164">
         <v>0</v>
@@ -6789,7 +6858,7 @@
         <v>4</v>
       </c>
       <c r="K164" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="165" spans="1:11">
@@ -6797,13 +6866,13 @@
         <v>51</v>
       </c>
       <c r="B165" t="s">
-        <v>136</v>
+        <v>143</v>
       </c>
       <c r="C165">
         <v>3</v>
       </c>
       <c r="D165" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E165">
         <v>0</v>
@@ -6824,7 +6893,7 @@
         <v>4</v>
       </c>
       <c r="K165" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="166" spans="1:11">
@@ -6832,13 +6901,13 @@
         <v>51</v>
       </c>
       <c r="B166" t="s">
-        <v>137</v>
+        <v>144</v>
       </c>
       <c r="C166">
         <v>3</v>
       </c>
       <c r="D166" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E166">
         <v>0</v>
@@ -6859,7 +6928,7 @@
         <v>4</v>
       </c>
       <c r="K166" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="167" spans="1:11">
@@ -6867,13 +6936,13 @@
         <v>51</v>
       </c>
       <c r="B167" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="C167">
         <v>3</v>
       </c>
       <c r="D167" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E167">
         <v>0</v>
@@ -6894,7 +6963,7 @@
         <v>4</v>
       </c>
       <c r="K167" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="168" spans="1:11">
@@ -6902,13 +6971,13 @@
         <v>51</v>
       </c>
       <c r="B168" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="C168">
         <v>3</v>
       </c>
       <c r="D168" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E168">
         <v>0</v>
@@ -6929,7 +6998,7 @@
         <v>4</v>
       </c>
       <c r="K168" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="169" spans="1:11">
@@ -6937,13 +7006,13 @@
         <v>52</v>
       </c>
       <c r="B169" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C169">
         <v>3</v>
       </c>
       <c r="D169" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E169">
         <v>0</v>
@@ -6964,7 +7033,7 @@
         <v>2</v>
       </c>
       <c r="K169" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="170" spans="1:11">
@@ -6972,13 +7041,13 @@
         <v>52</v>
       </c>
       <c r="B170" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C170">
         <v>3</v>
       </c>
       <c r="D170" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E170">
         <v>0</v>
@@ -6999,7 +7068,7 @@
         <v>2</v>
       </c>
       <c r="K170" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="171" spans="1:11">
@@ -7007,13 +7076,13 @@
         <v>52</v>
       </c>
       <c r="B171" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C171">
         <v>3</v>
       </c>
       <c r="D171" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -7034,7 +7103,7 @@
         <v>2</v>
       </c>
       <c r="K171" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="172" spans="1:11">
@@ -7042,13 +7111,13 @@
         <v>52</v>
       </c>
       <c r="B172" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="C172">
         <v>3</v>
       </c>
       <c r="D172" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E172">
         <v>0</v>
@@ -7069,7 +7138,7 @@
         <v>4</v>
       </c>
       <c r="K172" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="173" spans="1:11">
@@ -7077,13 +7146,13 @@
         <v>52</v>
       </c>
       <c r="B173" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="C173">
         <v>3</v>
       </c>
       <c r="D173" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E173">
         <v>0</v>
@@ -7104,7 +7173,7 @@
         <v>4</v>
       </c>
       <c r="K173" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="174" spans="1:11">
@@ -7112,13 +7181,13 @@
         <v>52</v>
       </c>
       <c r="B174" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="C174">
         <v>3</v>
       </c>
       <c r="D174" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E174">
         <v>0</v>
@@ -7139,7 +7208,7 @@
         <v>4</v>
       </c>
       <c r="K174" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="175" spans="1:11">
@@ -7147,13 +7216,13 @@
         <v>53</v>
       </c>
       <c r="B175" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C175">
         <v>3</v>
       </c>
       <c r="D175" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E175">
         <v>0</v>
@@ -7174,7 +7243,7 @@
         <v>3</v>
       </c>
       <c r="K175" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="176" spans="1:11">
@@ -7182,13 +7251,13 @@
         <v>53</v>
       </c>
       <c r="B176" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C176">
         <v>3</v>
       </c>
       <c r="D176" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E176">
         <v>0</v>
@@ -7209,7 +7278,7 @@
         <v>3</v>
       </c>
       <c r="K176" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="177" spans="1:11">
@@ -7217,13 +7286,13 @@
         <v>53</v>
       </c>
       <c r="B177" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C177">
         <v>3</v>
       </c>
       <c r="D177" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E177">
         <v>0</v>
@@ -7244,7 +7313,7 @@
         <v>3</v>
       </c>
       <c r="K177" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="178" spans="1:11">
@@ -7252,13 +7321,13 @@
         <v>53</v>
       </c>
       <c r="B178" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="C178">
         <v>3</v>
       </c>
       <c r="D178" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E178">
         <v>0</v>
@@ -7279,7 +7348,7 @@
         <v>4</v>
       </c>
       <c r="K178" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="179" spans="1:11">
@@ -7287,13 +7356,13 @@
         <v>53</v>
       </c>
       <c r="B179" t="s">
-        <v>139</v>
+        <v>146</v>
       </c>
       <c r="C179">
         <v>3</v>
       </c>
       <c r="D179" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E179">
         <v>0</v>
@@ -7314,7 +7383,7 @@
         <v>4</v>
       </c>
       <c r="K179" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="180" spans="1:11">
@@ -7322,13 +7391,13 @@
         <v>53</v>
       </c>
       <c r="B180" t="s">
-        <v>141</v>
+        <v>148</v>
       </c>
       <c r="C180">
         <v>3</v>
       </c>
       <c r="D180" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E180">
         <v>0</v>
@@ -7349,7 +7418,7 @@
         <v>4</v>
       </c>
       <c r="K180" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="181" spans="1:11">
@@ -7357,13 +7426,13 @@
         <v>54</v>
       </c>
       <c r="B181" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C181">
         <v>3</v>
       </c>
       <c r="D181" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E181">
         <v>0</v>
@@ -7384,7 +7453,7 @@
         <v>2</v>
       </c>
       <c r="K181" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="182" spans="1:11">
@@ -7392,13 +7461,13 @@
         <v>54</v>
       </c>
       <c r="B182" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C182">
         <v>3</v>
       </c>
       <c r="D182" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E182">
         <v>0</v>
@@ -7419,7 +7488,7 @@
         <v>2</v>
       </c>
       <c r="K182" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="183" spans="1:11">
@@ -7427,13 +7496,13 @@
         <v>54</v>
       </c>
       <c r="B183" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C183">
         <v>3</v>
       </c>
       <c r="D183" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E183">
         <v>0</v>
@@ -7454,7 +7523,7 @@
         <v>2</v>
       </c>
       <c r="K183" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="184" spans="1:11">
@@ -7462,13 +7531,13 @@
         <v>54</v>
       </c>
       <c r="B184" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C184">
         <v>1.5</v>
       </c>
       <c r="D184" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E184">
         <v>0</v>
@@ -7489,7 +7558,7 @@
         <v>1</v>
       </c>
       <c r="K184" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="185" spans="1:11">
@@ -7497,13 +7566,13 @@
         <v>54</v>
       </c>
       <c r="B185" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C185">
         <v>1</v>
       </c>
       <c r="D185" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E185">
         <v>0</v>
@@ -7524,7 +7593,7 @@
         <v>1</v>
       </c>
       <c r="K185" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="186" spans="1:11">
@@ -7532,13 +7601,13 @@
         <v>55</v>
       </c>
       <c r="B186" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C186">
         <v>3</v>
       </c>
       <c r="D186" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E186">
         <v>0</v>
@@ -7559,7 +7628,7 @@
         <v>3</v>
       </c>
       <c r="K186" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="187" spans="1:11">
@@ -7567,13 +7636,13 @@
         <v>55</v>
       </c>
       <c r="B187" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C187">
         <v>1.5</v>
       </c>
       <c r="D187" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E187">
         <v>0</v>
@@ -7594,7 +7663,7 @@
         <v>2</v>
       </c>
       <c r="K187" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="188" spans="1:11">
@@ -7602,13 +7671,13 @@
         <v>55</v>
       </c>
       <c r="B188" t="s">
-        <v>142</v>
+        <v>149</v>
       </c>
       <c r="C188">
         <v>3</v>
       </c>
       <c r="D188" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E188">
         <v>0</v>
@@ -7629,7 +7698,7 @@
         <v>4</v>
       </c>
       <c r="K188" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="189" spans="1:11">
@@ -7637,13 +7706,13 @@
         <v>55</v>
       </c>
       <c r="B189" t="s">
-        <v>143</v>
+        <v>150</v>
       </c>
       <c r="C189">
         <v>1.5</v>
       </c>
       <c r="D189" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E189">
         <v>0</v>
@@ -7664,7 +7733,7 @@
         <v>2</v>
       </c>
       <c r="K189" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="190" spans="1:11">
@@ -7672,13 +7741,13 @@
         <v>56</v>
       </c>
       <c r="B190" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C190">
         <v>3</v>
       </c>
       <c r="D190" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E190">
         <v>0</v>
@@ -7699,7 +7768,7 @@
         <v>2</v>
       </c>
       <c r="K190" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="191" spans="1:11">
@@ -7707,13 +7776,13 @@
         <v>56</v>
       </c>
       <c r="B191" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C191">
         <v>3</v>
       </c>
       <c r="D191" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E191">
         <v>0</v>
@@ -7734,7 +7803,7 @@
         <v>2</v>
       </c>
       <c r="K191" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="192" spans="1:11">
@@ -7742,13 +7811,13 @@
         <v>57</v>
       </c>
       <c r="B192" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C192">
         <v>4</v>
       </c>
       <c r="D192" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E192">
         <v>0</v>
@@ -7769,7 +7838,7 @@
         <v>2</v>
       </c>
       <c r="K192" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="193" spans="1:11">
@@ -7777,13 +7846,13 @@
         <v>57</v>
       </c>
       <c r="B193" t="s">
-        <v>140</v>
+        <v>147</v>
       </c>
       <c r="C193">
         <v>4</v>
       </c>
       <c r="D193" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E193">
         <v>0</v>
@@ -7804,7 +7873,7 @@
         <v>3</v>
       </c>
       <c r="K193" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="194" spans="1:11">
@@ -7812,13 +7881,13 @@
         <v>57</v>
       </c>
       <c r="B194" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C194">
         <v>3.001</v>
       </c>
       <c r="D194" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E194">
         <v>0</v>
@@ -7839,7 +7908,7 @@
         <v>3</v>
       </c>
       <c r="K194" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="195" spans="1:11">
@@ -7847,13 +7916,13 @@
         <v>57</v>
       </c>
       <c r="B195" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C195">
         <v>3.001</v>
       </c>
       <c r="D195" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E195">
         <v>0</v>
@@ -7874,7 +7943,7 @@
         <v>3</v>
       </c>
       <c r="K195" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="196" spans="1:11">
@@ -7882,13 +7951,13 @@
         <v>57</v>
       </c>
       <c r="B196" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C196">
         <v>1.3</v>
       </c>
       <c r="D196" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E196">
         <v>0</v>
@@ -7909,7 +7978,7 @@
         <v>1</v>
       </c>
       <c r="K196" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="197" spans="1:11">
@@ -7917,13 +7986,13 @@
         <v>57</v>
       </c>
       <c r="B197" t="s">
-        <v>119</v>
+        <v>126</v>
       </c>
       <c r="C197">
         <v>3.099</v>
       </c>
       <c r="D197" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E197">
         <v>0</v>
@@ -7944,7 +8013,7 @@
         <v>4</v>
       </c>
       <c r="K197" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="198" spans="1:11">
@@ -7952,13 +8021,13 @@
         <v>57</v>
       </c>
       <c r="B198" t="s">
-        <v>120</v>
+        <v>127</v>
       </c>
       <c r="C198">
         <v>3.093</v>
       </c>
       <c r="D198" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E198">
         <v>0</v>
@@ -7979,7 +8048,7 @@
         <v>4</v>
       </c>
       <c r="K198" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="199" spans="1:11">
@@ -7987,13 +8056,13 @@
         <v>57</v>
       </c>
       <c r="B199" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="C199">
         <v>3.087</v>
       </c>
       <c r="D199" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E199">
         <v>0</v>
@@ -8014,7 +8083,7 @@
         <v>4</v>
       </c>
       <c r="K199" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="200" spans="1:11">
@@ -8022,13 +8091,13 @@
         <v>58</v>
       </c>
       <c r="B200" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C200">
         <v>3.055</v>
       </c>
       <c r="D200" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E200">
         <v>0</v>
@@ -8049,7 +8118,7 @@
         <v>2</v>
       </c>
       <c r="K200" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="201" spans="1:11">
@@ -8057,13 +8126,13 @@
         <v>58</v>
       </c>
       <c r="B201" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C201">
         <v>3.127</v>
       </c>
       <c r="D201" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E201">
         <v>0</v>
@@ -8084,7 +8153,7 @@
         <v>3</v>
       </c>
       <c r="K201" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="202" spans="1:11">
@@ -8092,13 +8161,13 @@
         <v>58</v>
       </c>
       <c r="B202" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C202">
         <v>3.089</v>
       </c>
       <c r="D202" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E202">
         <v>0</v>
@@ -8119,7 +8188,7 @@
         <v>3</v>
       </c>
       <c r="K202" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="203" spans="1:11">
@@ -8127,13 +8196,13 @@
         <v>59</v>
       </c>
       <c r="B203" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C203">
         <v>3.002</v>
       </c>
       <c r="D203" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E203">
         <v>0</v>
@@ -8154,7 +8223,7 @@
         <v>3</v>
       </c>
       <c r="K203" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="204" spans="1:11">
@@ -8162,13 +8231,13 @@
         <v>59</v>
       </c>
       <c r="B204" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C204">
         <v>3.004</v>
       </c>
       <c r="D204" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E204">
         <v>0</v>
@@ -8189,7 +8258,7 @@
         <v>3</v>
       </c>
       <c r="K204" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="205" spans="1:11">
@@ -8197,13 +8266,13 @@
         <v>59</v>
       </c>
       <c r="B205" t="s">
-        <v>154</v>
+        <v>161</v>
       </c>
       <c r="C205">
         <v>3.038</v>
       </c>
       <c r="D205" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E205">
         <v>0</v>
@@ -8224,7 +8293,7 @@
         <v>2</v>
       </c>
       <c r="K205" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="206" spans="1:11">
@@ -8232,13 +8301,13 @@
         <v>59</v>
       </c>
       <c r="B206" t="s">
-        <v>155</v>
+        <v>162</v>
       </c>
       <c r="C206">
         <v>3.025</v>
       </c>
       <c r="D206" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -8259,7 +8328,7 @@
         <v>3</v>
       </c>
       <c r="K206" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="207" spans="1:11">
@@ -8267,13 +8336,13 @@
         <v>59</v>
       </c>
       <c r="B207" t="s">
-        <v>156</v>
+        <v>163</v>
       </c>
       <c r="C207">
         <v>3.03</v>
       </c>
       <c r="D207" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E207">
         <v>0</v>
@@ -8294,7 +8363,7 @@
         <v>3</v>
       </c>
       <c r="K207" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="208" spans="1:11">
@@ -8302,13 +8371,13 @@
         <v>60</v>
       </c>
       <c r="B208" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C208">
         <v>3.136</v>
       </c>
       <c r="D208" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E208">
         <v>0</v>
@@ -8329,7 +8398,7 @@
         <v>3</v>
       </c>
       <c r="K208" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="209" spans="1:11">
@@ -8337,13 +8406,13 @@
         <v>60</v>
       </c>
       <c r="B209" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C209">
         <v>3.141</v>
       </c>
       <c r="D209" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E209">
         <v>0</v>
@@ -8364,7 +8433,7 @@
         <v>3</v>
       </c>
       <c r="K209" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="210" spans="1:11">
@@ -8372,13 +8441,13 @@
         <v>60</v>
       </c>
       <c r="B210" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C210">
         <v>2.697</v>
       </c>
       <c r="D210" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E210">
         <v>0</v>
@@ -8399,7 +8468,7 @@
         <v>2</v>
       </c>
       <c r="K210" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="211" spans="1:11">
@@ -8407,13 +8476,13 @@
         <v>60</v>
       </c>
       <c r="B211" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C211">
         <v>3.004</v>
       </c>
       <c r="D211" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E211">
         <v>0</v>
@@ -8434,7 +8503,7 @@
         <v>2</v>
       </c>
       <c r="K211" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="212" spans="1:11">
@@ -8442,13 +8511,13 @@
         <v>60</v>
       </c>
       <c r="B212" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C212">
         <v>3.005</v>
       </c>
       <c r="D212" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E212">
         <v>0</v>
@@ -8469,7 +8538,7 @@
         <v>2</v>
       </c>
       <c r="K212" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="213" spans="1:11">
@@ -8477,13 +8546,13 @@
         <v>61</v>
       </c>
       <c r="B213" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C213">
         <v>3.001</v>
       </c>
       <c r="D213" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E213">
         <v>0</v>
@@ -8504,7 +8573,7 @@
         <v>3</v>
       </c>
       <c r="K213" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="214" spans="1:11">
@@ -8512,13 +8581,13 @@
         <v>61</v>
       </c>
       <c r="B214" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C214">
         <v>3.001</v>
       </c>
       <c r="D214" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E214">
         <v>0</v>
@@ -8539,7 +8608,7 @@
         <v>3</v>
       </c>
       <c r="K214" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="215" spans="1:11">
@@ -8547,13 +8616,13 @@
         <v>61</v>
       </c>
       <c r="B215" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C215">
         <v>1.3</v>
       </c>
       <c r="D215" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E215">
         <v>0</v>
@@ -8574,7 +8643,7 @@
         <v>2</v>
       </c>
       <c r="K215" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="216" spans="1:11">
@@ -8582,13 +8651,13 @@
         <v>61</v>
       </c>
       <c r="B216" t="s">
-        <v>157</v>
+        <v>164</v>
       </c>
       <c r="C216">
         <v>3.03</v>
       </c>
       <c r="D216" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E216">
         <v>0</v>
@@ -8609,7 +8678,7 @@
         <v>2</v>
       </c>
       <c r="K216" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="217" spans="1:11">
@@ -8617,13 +8686,13 @@
         <v>61</v>
       </c>
       <c r="B217" t="s">
-        <v>158</v>
+        <v>165</v>
       </c>
       <c r="C217">
         <v>3.005</v>
       </c>
       <c r="D217" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E217">
         <v>0</v>
@@ -8644,7 +8713,7 @@
         <v>2</v>
       </c>
       <c r="K217" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="218" spans="1:11">
@@ -8652,13 +8721,13 @@
         <v>61</v>
       </c>
       <c r="B218" t="s">
-        <v>159</v>
+        <v>166</v>
       </c>
       <c r="C218">
         <v>3.011</v>
       </c>
       <c r="D218" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E218">
         <v>0</v>
@@ -8679,7 +8748,7 @@
         <v>2</v>
       </c>
       <c r="K218" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="219" spans="1:11">
@@ -8687,13 +8756,13 @@
         <v>61</v>
       </c>
       <c r="B219" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="C219">
         <v>1.011</v>
       </c>
       <c r="D219" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E219">
         <v>0</v>
@@ -8714,7 +8783,7 @@
         <v>1</v>
       </c>
       <c r="K219" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="220" spans="1:11">
@@ -8722,13 +8791,13 @@
         <v>62</v>
       </c>
       <c r="B220" t="s">
-        <v>121</v>
+        <v>128</v>
       </c>
       <c r="C220">
         <v>3.001</v>
       </c>
       <c r="D220" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E220">
         <v>0</v>
@@ -8749,7 +8818,7 @@
         <v>2</v>
       </c>
       <c r="K220" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="221" spans="1:11">
@@ -8757,13 +8826,13 @@
         <v>62</v>
       </c>
       <c r="B221" t="s">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="C221" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="D221" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="E221">
         <v>0</v>
@@ -8784,7 +8853,7 @@
         <v>2</v>
       </c>
       <c r="K221" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="222" spans="1:11">
@@ -8792,13 +8861,13 @@
         <v>62</v>
       </c>
       <c r="B222" t="s">
-        <v>134</v>
+        <v>141</v>
       </c>
       <c r="C222" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="D222" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E222">
         <v>0</v>
@@ -8819,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="K222" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="223" spans="1:11">
@@ -8827,13 +8896,13 @@
         <v>63</v>
       </c>
       <c r="B223" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C223" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D223" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E223">
         <v>0</v>
@@ -8854,7 +8923,7 @@
         <v>3</v>
       </c>
       <c r="K223" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="224" spans="1:11">
@@ -8862,13 +8931,13 @@
         <v>63</v>
       </c>
       <c r="B224" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C224" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D224" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E224">
         <v>0</v>
@@ -8889,7 +8958,7 @@
         <v>3</v>
       </c>
       <c r="K224" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="225" spans="1:11">
@@ -8897,13 +8966,13 @@
         <v>63</v>
       </c>
       <c r="B225" t="s">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="C225" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D225" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E225">
         <v>0</v>
@@ -8924,7 +8993,7 @@
         <v>4</v>
       </c>
       <c r="K225" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="226" spans="1:11">
@@ -8932,13 +9001,13 @@
         <v>63</v>
       </c>
       <c r="B226" t="s">
-        <v>153</v>
+        <v>160</v>
       </c>
       <c r="C226" t="s">
-        <v>190</v>
+        <v>203</v>
       </c>
       <c r="D226" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="E226">
         <v>0</v>
@@ -8959,7 +9028,7 @@
         <v>4</v>
       </c>
       <c r="K226" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="227" spans="1:11">
@@ -8967,13 +9036,13 @@
         <v>63</v>
       </c>
       <c r="B227" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C227" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D227" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E227">
         <v>0</v>
@@ -8994,7 +9063,7 @@
         <v>2</v>
       </c>
       <c r="K227" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="228" spans="1:11">
@@ -9002,13 +9071,13 @@
         <v>63</v>
       </c>
       <c r="B228" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C228" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D228" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E228">
         <v>0</v>
@@ -9029,7 +9098,7 @@
         <v>2</v>
       </c>
       <c r="K228" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="229" spans="1:11">
@@ -9037,13 +9106,13 @@
         <v>63</v>
       </c>
       <c r="B229" t="s">
-        <v>128</v>
+        <v>135</v>
       </c>
       <c r="C229" t="s">
-        <v>191</v>
+        <v>204</v>
       </c>
       <c r="D229" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E229">
         <v>0</v>
@@ -9064,7 +9133,7 @@
         <v>4</v>
       </c>
       <c r="K229" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="230" spans="1:11">
@@ -9072,13 +9141,13 @@
         <v>63</v>
       </c>
       <c r="B230" t="s">
-        <v>129</v>
+        <v>136</v>
       </c>
       <c r="C230" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D230" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E230">
         <v>0</v>
@@ -9099,7 +9168,7 @@
         <v>4</v>
       </c>
       <c r="K230" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="231" spans="1:11">
@@ -9107,13 +9176,13 @@
         <v>64</v>
       </c>
       <c r="B231" t="s">
-        <v>123</v>
+        <v>130</v>
       </c>
       <c r="C231" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D231" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E231">
         <v>0</v>
@@ -9134,7 +9203,7 @@
         <v>2</v>
       </c>
       <c r="K231" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="232" spans="1:11">
@@ -9142,13 +9211,13 @@
         <v>64</v>
       </c>
       <c r="B232" t="s">
-        <v>124</v>
+        <v>131</v>
       </c>
       <c r="C232" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="D232" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E232">
         <v>0</v>
@@ -9169,7 +9238,7 @@
         <v>2</v>
       </c>
       <c r="K232" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="233" spans="1:11">
@@ -9177,13 +9246,13 @@
         <v>64</v>
       </c>
       <c r="B233" t="s">
-        <v>118</v>
+        <v>125</v>
       </c>
       <c r="C233" t="s">
-        <v>195</v>
+        <v>208</v>
       </c>
       <c r="D233" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E233">
         <v>0</v>
@@ -9204,7 +9273,7 @@
         <v>2</v>
       </c>
       <c r="K233" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="234" spans="1:11">
@@ -9212,13 +9281,13 @@
         <v>64</v>
       </c>
       <c r="B234" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C234" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D234" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E234">
         <v>0</v>
@@ -9239,7 +9308,7 @@
         <v>3</v>
       </c>
       <c r="K234" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="235" spans="1:11">
@@ -9247,13 +9316,13 @@
         <v>64</v>
       </c>
       <c r="B235" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C235" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D235" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E235">
         <v>0</v>
@@ -9274,7 +9343,7 @@
         <v>3</v>
       </c>
       <c r="K235" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="236" spans="1:11">
@@ -9282,13 +9351,13 @@
         <v>64</v>
       </c>
       <c r="B236" t="s">
-        <v>130</v>
+        <v>137</v>
       </c>
       <c r="C236" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D236" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E236">
         <v>0</v>
@@ -9309,7 +9378,7 @@
         <v>4</v>
       </c>
       <c r="K236" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="237" spans="1:11">
@@ -9317,13 +9386,13 @@
         <v>64</v>
       </c>
       <c r="B237" t="s">
-        <v>131</v>
+        <v>138</v>
       </c>
       <c r="C237" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D237" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E237">
         <v>0</v>
@@ -9344,7 +9413,7 @@
         <v>4</v>
       </c>
       <c r="K237" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="238" spans="1:11">
@@ -9352,13 +9421,13 @@
         <v>65</v>
       </c>
       <c r="B238" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="C238" t="s">
-        <v>197</v>
+        <v>210</v>
       </c>
       <c r="D238" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E238">
         <v>0</v>
@@ -9379,7 +9448,7 @@
         <v>1</v>
       </c>
       <c r="K238" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="239" spans="1:11">
@@ -9387,13 +9456,13 @@
         <v>65</v>
       </c>
       <c r="B239" t="s">
-        <v>162</v>
+        <v>169</v>
       </c>
       <c r="C239" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D239" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E239">
         <v>0</v>
@@ -9414,7 +9483,7 @@
         <v>2</v>
       </c>
       <c r="K239" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="240" spans="1:11">
@@ -9422,13 +9491,13 @@
         <v>65</v>
       </c>
       <c r="B240" t="s">
-        <v>163</v>
+        <v>170</v>
       </c>
       <c r="C240" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D240" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E240">
         <v>0</v>
@@ -9449,7 +9518,7 @@
         <v>2</v>
       </c>
       <c r="K240" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="241" spans="1:11">
@@ -9457,13 +9526,13 @@
         <v>65</v>
       </c>
       <c r="B241" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C241" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D241" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E241">
         <v>0</v>
@@ -9484,7 +9553,7 @@
         <v>2</v>
       </c>
       <c r="K241" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="242" spans="1:11">
@@ -9492,13 +9561,13 @@
         <v>65</v>
       </c>
       <c r="B242" t="s">
-        <v>165</v>
+        <v>172</v>
       </c>
       <c r="C242" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D242" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E242">
         <v>0</v>
@@ -9519,7 +9588,7 @@
         <v>2</v>
       </c>
       <c r="K242" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="243" spans="1:11">
@@ -9527,13 +9596,13 @@
         <v>65</v>
       </c>
       <c r="B243" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="C243" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D243" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E243">
         <v>0</v>
@@ -9554,7 +9623,7 @@
         <v>2</v>
       </c>
       <c r="K243" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="244" spans="1:11">
@@ -9562,13 +9631,13 @@
         <v>65</v>
       </c>
       <c r="B244" t="s">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="C244" t="s">
-        <v>189</v>
+        <v>202</v>
       </c>
       <c r="D244" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E244">
         <v>0</v>
@@ -9589,7 +9658,7 @@
         <v>2</v>
       </c>
       <c r="K244" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="245" spans="1:11">
@@ -9597,13 +9666,13 @@
         <v>66</v>
       </c>
       <c r="B245" t="s">
-        <v>132</v>
+        <v>139</v>
       </c>
       <c r="C245" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="D245" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E245">
         <v>0</v>
@@ -9624,7 +9693,7 @@
         <v>4</v>
       </c>
       <c r="K245" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="246" spans="1:11">
@@ -9632,13 +9701,13 @@
         <v>66</v>
       </c>
       <c r="B246" t="s">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="C246" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="D246" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="E246">
         <v>0</v>
@@ -9659,7 +9728,7 @@
         <v>4</v>
       </c>
       <c r="K246" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="247" spans="1:11">
@@ -9667,13 +9736,13 @@
         <v>66</v>
       </c>
       <c r="B247" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C247" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D247" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E247">
         <v>0</v>
@@ -9694,7 +9763,7 @@
         <v>3</v>
       </c>
       <c r="K247" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="248" spans="1:11">
@@ -9702,13 +9771,13 @@
         <v>66</v>
       </c>
       <c r="B248" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C248" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D248" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E248">
         <v>0</v>
@@ -9729,7 +9798,7 @@
         <v>4</v>
       </c>
       <c r="K248" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="249" spans="1:11">
@@ -9737,13 +9806,13 @@
         <v>66</v>
       </c>
       <c r="B249" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="C249" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D249" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E249">
         <v>0</v>
@@ -9764,7 +9833,7 @@
         <v>4</v>
       </c>
       <c r="K249" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="250" spans="1:11">
@@ -9772,13 +9841,13 @@
         <v>66</v>
       </c>
       <c r="B250" t="s">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="C250" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D250" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E250">
         <v>0</v>
@@ -9799,7 +9868,7 @@
         <v>3</v>
       </c>
       <c r="K250" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="251" spans="1:11">
@@ -9807,13 +9876,13 @@
         <v>67</v>
       </c>
       <c r="B251" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C251" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D251" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E251">
         <v>0</v>
@@ -9834,7 +9903,7 @@
         <v>3</v>
       </c>
       <c r="K251" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="252" spans="1:11">
@@ -9842,13 +9911,13 @@
         <v>67</v>
       </c>
       <c r="B252" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C252" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D252" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E252">
         <v>0</v>
@@ -9869,7 +9938,7 @@
         <v>3</v>
       </c>
       <c r="K252" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="253" spans="1:11">
@@ -9877,13 +9946,13 @@
         <v>67</v>
       </c>
       <c r="B253" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C253" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D253" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E253">
         <v>0</v>
@@ -9904,7 +9973,7 @@
         <v>3</v>
       </c>
       <c r="K253" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="254" spans="1:11">
@@ -9912,13 +9981,13 @@
         <v>67</v>
       </c>
       <c r="B254" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C254" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D254" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E254">
         <v>0</v>
@@ -9939,7 +10008,7 @@
         <v>2</v>
       </c>
       <c r="K254" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="255" spans="1:11">
@@ -9947,13 +10016,13 @@
         <v>67</v>
       </c>
       <c r="B255" t="s">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="C255" t="s">
-        <v>203</v>
+        <v>216</v>
       </c>
       <c r="D255" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E255">
         <v>0</v>
@@ -9974,7 +10043,7 @@
         <v>4</v>
       </c>
       <c r="K255" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="256" spans="1:11">
@@ -9982,13 +10051,13 @@
         <v>67</v>
       </c>
       <c r="B256" t="s">
-        <v>145</v>
+        <v>152</v>
       </c>
       <c r="C256" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="D256" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E256">
         <v>0</v>
@@ -10009,7 +10078,7 @@
         <v>4</v>
       </c>
       <c r="K256" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="257" spans="1:11">
@@ -10017,13 +10086,13 @@
         <v>67</v>
       </c>
       <c r="B257" t="s">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="C257" t="s">
-        <v>200</v>
+        <v>213</v>
       </c>
       <c r="D257" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E257">
         <v>0</v>
@@ -10044,7 +10113,7 @@
         <v>4</v>
       </c>
       <c r="K257" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="258" spans="1:11">
@@ -10052,13 +10121,13 @@
         <v>67</v>
       </c>
       <c r="B258" t="s">
-        <v>150</v>
+        <v>157</v>
       </c>
       <c r="C258" t="s">
-        <v>205</v>
+        <v>218</v>
       </c>
       <c r="D258" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E258">
         <v>0</v>
@@ -10079,7 +10148,7 @@
         <v>2</v>
       </c>
       <c r="K258" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="259" spans="1:11">
@@ -10087,13 +10156,13 @@
         <v>68</v>
       </c>
       <c r="B259" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C259" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D259" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E259">
         <v>0</v>
@@ -10114,7 +10183,7 @@
         <v>3</v>
       </c>
       <c r="K259" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="260" spans="1:11">
@@ -10122,13 +10191,13 @@
         <v>68</v>
       </c>
       <c r="B260" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C260" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="D260" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E260">
         <v>0</v>
@@ -10149,7 +10218,7 @@
         <v>1</v>
       </c>
       <c r="K260" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="261" spans="1:11">
@@ -10157,13 +10226,13 @@
         <v>68</v>
       </c>
       <c r="B261" t="s">
-        <v>146</v>
+        <v>153</v>
       </c>
       <c r="C261" t="s">
-        <v>206</v>
+        <v>219</v>
       </c>
       <c r="D261" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E261">
         <v>0</v>
@@ -10184,7 +10253,7 @@
         <v>4</v>
       </c>
       <c r="K261" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="262" spans="1:11">
@@ -10192,13 +10261,13 @@
         <v>68</v>
       </c>
       <c r="B262" t="s">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="C262" t="s">
-        <v>207</v>
+        <v>220</v>
       </c>
       <c r="D262" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E262">
         <v>0</v>
@@ -10219,7 +10288,7 @@
         <v>1</v>
       </c>
       <c r="K262" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="263" spans="1:11">
@@ -10227,13 +10296,13 @@
         <v>68</v>
       </c>
       <c r="B263" t="s">
-        <v>168</v>
+        <v>175</v>
       </c>
       <c r="C263" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D263" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E263">
         <v>0</v>
@@ -10254,7 +10323,7 @@
         <v>2</v>
       </c>
       <c r="K263" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="264" spans="1:11">
@@ -10262,13 +10331,13 @@
         <v>68</v>
       </c>
       <c r="B264" t="s">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="C264" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D264" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E264">
         <v>0</v>
@@ -10289,7 +10358,7 @@
         <v>2</v>
       </c>
       <c r="K264" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="265" spans="1:11">
@@ -10297,13 +10366,13 @@
         <v>68</v>
       </c>
       <c r="B265" t="s">
-        <v>170</v>
+        <v>177</v>
       </c>
       <c r="C265" t="s">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="D265" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E265">
         <v>0</v>
@@ -10324,7 +10393,7 @@
         <v>2</v>
       </c>
       <c r="K265" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="266" spans="1:11">
@@ -10332,13 +10401,13 @@
         <v>69</v>
       </c>
       <c r="B266" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C266" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D266" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E266">
         <v>0</v>
@@ -10359,7 +10428,7 @@
         <v>2</v>
       </c>
       <c r="K266" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="267" spans="1:11">
@@ -10367,13 +10436,13 @@
         <v>69</v>
       </c>
       <c r="B267" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C267" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D267" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E267">
         <v>0</v>
@@ -10394,7 +10463,7 @@
         <v>2</v>
       </c>
       <c r="K267" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="268" spans="1:11">
@@ -10402,13 +10471,13 @@
         <v>69</v>
       </c>
       <c r="B268" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C268" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D268" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E268">
         <v>0</v>
@@ -10429,7 +10498,7 @@
         <v>2</v>
       </c>
       <c r="K268" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="269" spans="1:11">
@@ -10437,13 +10506,13 @@
         <v>69</v>
       </c>
       <c r="B269" t="s">
-        <v>174</v>
+        <v>181</v>
       </c>
       <c r="C269" t="s">
-        <v>209</v>
+        <v>222</v>
       </c>
       <c r="D269" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E269">
         <v>0</v>
@@ -10464,7 +10533,7 @@
         <v>2</v>
       </c>
       <c r="K269" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="270" spans="1:11">
@@ -10472,13 +10541,13 @@
         <v>69</v>
       </c>
       <c r="B270" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
       <c r="C270" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="D270" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E270">
         <v>0</v>
@@ -10499,7 +10568,7 @@
         <v>2</v>
       </c>
       <c r="K270" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="271" spans="1:11">
@@ -10507,13 +10576,13 @@
         <v>69</v>
       </c>
       <c r="B271" t="s">
-        <v>176</v>
+        <v>183</v>
       </c>
       <c r="C271" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D271" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E271">
         <v>0</v>
@@ -10534,7 +10603,7 @@
         <v>2</v>
       </c>
       <c r="K271" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="272" spans="1:11">
@@ -10542,13 +10611,13 @@
         <v>69</v>
       </c>
       <c r="B272" t="s">
-        <v>125</v>
+        <v>132</v>
       </c>
       <c r="C272" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
       <c r="D272" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E272">
         <v>0</v>
@@ -10569,7 +10638,7 @@
         <v>2</v>
       </c>
       <c r="K272" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="273" spans="1:11">
@@ -10577,13 +10646,13 @@
         <v>69</v>
       </c>
       <c r="B273" t="s">
-        <v>126</v>
+        <v>133</v>
       </c>
       <c r="C273" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D273" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E273">
         <v>0</v>
@@ -10604,7 +10673,7 @@
         <v>2</v>
       </c>
       <c r="K273" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="274" spans="1:11">
@@ -10612,13 +10681,13 @@
         <v>69</v>
       </c>
       <c r="B274" t="s">
-        <v>127</v>
+        <v>134</v>
       </c>
       <c r="C274" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D274" t="s">
-        <v>221</v>
+        <v>244</v>
       </c>
       <c r="E274">
         <v>0</v>
@@ -10639,7 +10708,7 @@
         <v>1</v>
       </c>
       <c r="K274" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="275" spans="1:11">
@@ -10647,13 +10716,13 @@
         <v>70</v>
       </c>
       <c r="B275" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C275" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D275" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E275">
         <v>0</v>
@@ -10674,7 +10743,7 @@
         <v>2</v>
       </c>
       <c r="K275" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="276" spans="1:11">
@@ -10682,13 +10751,13 @@
         <v>70</v>
       </c>
       <c r="B276" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C276" t="s">
-        <v>214</v>
+        <v>227</v>
       </c>
       <c r="D276" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E276">
         <v>0</v>
@@ -10709,7 +10778,7 @@
         <v>1</v>
       </c>
       <c r="K276" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="277" spans="1:11">
@@ -10717,13 +10786,13 @@
         <v>70</v>
       </c>
       <c r="B277" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C277" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="D277" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E277">
         <v>0</v>
@@ -10744,7 +10813,7 @@
         <v>1</v>
       </c>
       <c r="K277" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="278" spans="1:11">
@@ -10752,13 +10821,13 @@
         <v>70</v>
       </c>
       <c r="B278" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C278" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D278" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E278">
         <v>0</v>
@@ -10779,7 +10848,7 @@
         <v>1</v>
       </c>
       <c r="K278" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="279" spans="1:11">
@@ -10787,13 +10856,13 @@
         <v>70</v>
       </c>
       <c r="B279" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C279" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D279" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E279">
         <v>0</v>
@@ -10814,7 +10883,7 @@
         <v>1</v>
       </c>
       <c r="K279" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="280" spans="1:11">
@@ -10822,13 +10891,13 @@
         <v>70</v>
       </c>
       <c r="B280" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C280" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D280" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E280">
         <v>0</v>
@@ -10849,7 +10918,7 @@
         <v>1</v>
       </c>
       <c r="K280" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="281" spans="1:11">
@@ -10857,13 +10926,13 @@
         <v>70</v>
       </c>
       <c r="B281" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C281" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D281" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E281">
         <v>0</v>
@@ -10884,7 +10953,7 @@
         <v>1</v>
       </c>
       <c r="K281" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="282" spans="1:11">
@@ -10892,13 +10961,13 @@
         <v>71</v>
       </c>
       <c r="B282" t="s">
-        <v>183</v>
+        <v>190</v>
       </c>
       <c r="C282" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="D282" t="s">
-        <v>225</v>
+        <v>248</v>
       </c>
       <c r="E282">
         <v>0</v>
@@ -10919,7 +10988,7 @@
         <v>1</v>
       </c>
       <c r="K282" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="283" spans="1:11">
@@ -10927,13 +10996,13 @@
         <v>71</v>
       </c>
       <c r="B283" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="C283" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="D283" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E283">
         <v>0</v>
@@ -10954,7 +11023,7 @@
         <v>1</v>
       </c>
       <c r="K283" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="284" spans="1:11">
@@ -10962,13 +11031,13 @@
         <v>71</v>
       </c>
       <c r="B284" t="s">
-        <v>185</v>
+        <v>192</v>
       </c>
       <c r="C284" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D284" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E284">
         <v>0</v>
@@ -10989,7 +11058,7 @@
         <v>1</v>
       </c>
       <c r="K284" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="285" spans="1:11">
@@ -10997,13 +11066,13 @@
         <v>71</v>
       </c>
       <c r="B285" t="s">
-        <v>186</v>
+        <v>193</v>
       </c>
       <c r="C285" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="D285" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E285">
         <v>0</v>
@@ -11024,7 +11093,7 @@
         <v>1</v>
       </c>
       <c r="K285" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="286" spans="1:11">
@@ -11032,13 +11101,13 @@
         <v>72</v>
       </c>
       <c r="B286" t="s">
-        <v>177</v>
+        <v>184</v>
       </c>
       <c r="C286" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D286" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E286">
         <v>0</v>
@@ -11059,7 +11128,7 @@
         <v>5</v>
       </c>
       <c r="K286" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="287" spans="1:11">
@@ -11067,13 +11136,13 @@
         <v>72</v>
       </c>
       <c r="B287" t="s">
-        <v>178</v>
+        <v>185</v>
       </c>
       <c r="C287" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D287" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E287">
         <v>0</v>
@@ -11094,7 +11163,7 @@
         <v>4</v>
       </c>
       <c r="K287" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="288" spans="1:11">
@@ -11102,13 +11171,13 @@
         <v>72</v>
       </c>
       <c r="B288" t="s">
-        <v>171</v>
+        <v>178</v>
       </c>
       <c r="C288" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D288" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E288">
         <v>0</v>
@@ -11129,7 +11198,7 @@
         <v>4</v>
       </c>
       <c r="K288" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="289" spans="1:11">
@@ -11137,13 +11206,13 @@
         <v>72</v>
       </c>
       <c r="B289" t="s">
-        <v>172</v>
+        <v>179</v>
       </c>
       <c r="C289" t="s">
-        <v>198</v>
+        <v>211</v>
       </c>
       <c r="D289" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E289">
         <v>0</v>
@@ -11164,7 +11233,7 @@
         <v>4</v>
       </c>
       <c r="K289" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="290" spans="1:11">
@@ -11172,13 +11241,13 @@
         <v>72</v>
       </c>
       <c r="B290" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
       <c r="C290" t="s">
-        <v>215</v>
+        <v>228</v>
       </c>
       <c r="D290" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E290">
         <v>0</v>
@@ -11199,7 +11268,7 @@
         <v>2</v>
       </c>
       <c r="K290" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="291" spans="1:11">
@@ -11207,13 +11276,13 @@
         <v>72</v>
       </c>
       <c r="B291" t="s">
-        <v>180</v>
+        <v>187</v>
       </c>
       <c r="C291" t="s">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="D291" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E291">
         <v>0</v>
@@ -11234,7 +11303,7 @@
         <v>2</v>
       </c>
       <c r="K291" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="292" spans="1:11">
@@ -11242,13 +11311,13 @@
         <v>72</v>
       </c>
       <c r="B292" t="s">
-        <v>181</v>
+        <v>188</v>
       </c>
       <c r="C292" t="s">
-        <v>202</v>
+        <v>215</v>
       </c>
       <c r="D292" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E292">
         <v>0</v>
@@ -11269,7 +11338,7 @@
         <v>2</v>
       </c>
       <c r="K292" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="293" spans="1:11">
@@ -11277,13 +11346,13 @@
         <v>72</v>
       </c>
       <c r="B293" t="s">
-        <v>182</v>
+        <v>189</v>
       </c>
       <c r="C293" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="D293" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E293">
         <v>0</v>
@@ -11304,7 +11373,7 @@
         <v>2</v>
       </c>
       <c r="K293" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="294" spans="1:11">
@@ -11312,13 +11381,13 @@
         <v>73</v>
       </c>
       <c r="B294" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C294" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D294" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E294">
         <v>0</v>
@@ -11339,7 +11408,7 @@
         <v>2</v>
       </c>
       <c r="K294" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="295" spans="1:11">
@@ -11347,13 +11416,13 @@
         <v>73</v>
       </c>
       <c r="B295" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C295" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D295" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E295">
         <v>0</v>
@@ -11374,7 +11443,7 @@
         <v>2</v>
       </c>
       <c r="K295" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="296" spans="1:11">
@@ -11382,13 +11451,13 @@
         <v>73</v>
       </c>
       <c r="B296" t="s">
-        <v>173</v>
+        <v>180</v>
       </c>
       <c r="C296" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D296" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E296">
         <v>0</v>
@@ -11409,7 +11478,7 @@
         <v>4</v>
       </c>
       <c r="K296" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="297" spans="1:11">
@@ -11417,13 +11486,13 @@
         <v>73</v>
       </c>
       <c r="B297" t="s">
-        <v>164</v>
+        <v>171</v>
       </c>
       <c r="C297" t="s">
-        <v>199</v>
+        <v>212</v>
       </c>
       <c r="D297" t="s">
-        <v>222</v>
+        <v>245</v>
       </c>
       <c r="E297">
         <v>0</v>
@@ -11444,7 +11513,7 @@
         <v>4</v>
       </c>
       <c r="K297" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
     </row>
     <row r="298" spans="1:11">
@@ -11452,34 +11521,1568 @@
         <v>74</v>
       </c>
       <c r="B298" t="s">
+        <v>170</v>
+      </c>
+      <c r="C298" t="s">
+        <v>212</v>
+      </c>
+      <c r="D298" t="s">
+        <v>245</v>
+      </c>
+      <c r="E298">
+        <v>0</v>
+      </c>
+      <c r="F298">
+        <v>5</v>
+      </c>
+      <c r="G298">
+        <v>0</v>
+      </c>
+      <c r="H298">
+        <v>0</v>
+      </c>
+      <c r="I298">
+        <v>6</v>
+      </c>
+      <c r="J298">
+        <v>2</v>
+      </c>
+      <c r="K298" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11">
+      <c r="A299" t="s">
+        <v>74</v>
+      </c>
+      <c r="B299" t="s">
+        <v>169</v>
+      </c>
+      <c r="C299" t="s">
+        <v>211</v>
+      </c>
+      <c r="D299" t="s">
+        <v>245</v>
+      </c>
+      <c r="E299">
+        <v>0</v>
+      </c>
+      <c r="F299">
+        <v>5</v>
+      </c>
+      <c r="G299">
+        <v>0</v>
+      </c>
+      <c r="H299">
+        <v>0</v>
+      </c>
+      <c r="I299">
+        <v>6</v>
+      </c>
+      <c r="J299">
+        <v>2</v>
+      </c>
+      <c r="K299" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11">
+      <c r="A300" t="s">
+        <v>74</v>
+      </c>
+      <c r="B300" t="s">
+        <v>168</v>
+      </c>
+      <c r="C300" t="s">
+        <v>210</v>
+      </c>
+      <c r="D300" t="s">
+        <v>245</v>
+      </c>
+      <c r="E300">
+        <v>0</v>
+      </c>
+      <c r="F300">
+        <v>1</v>
+      </c>
+      <c r="G300">
+        <v>0</v>
+      </c>
+      <c r="H300">
+        <v>0</v>
+      </c>
+      <c r="I300">
+        <v>1</v>
+      </c>
+      <c r="J300">
+        <v>1</v>
+      </c>
+      <c r="K300" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11">
+      <c r="A301" t="s">
+        <v>74</v>
+      </c>
+      <c r="B301" t="s">
+        <v>170</v>
+      </c>
+      <c r="C301" t="s">
+        <v>212</v>
+      </c>
+      <c r="D301" t="s">
+        <v>245</v>
+      </c>
+      <c r="E301">
+        <v>0</v>
+      </c>
+      <c r="F301">
+        <v>5</v>
+      </c>
+      <c r="G301">
+        <v>0</v>
+      </c>
+      <c r="H301">
+        <v>0</v>
+      </c>
+      <c r="I301">
+        <v>9</v>
+      </c>
+      <c r="J301">
+        <v>3</v>
+      </c>
+      <c r="K301" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11">
+      <c r="A302" t="s">
+        <v>74</v>
+      </c>
+      <c r="B302" t="s">
+        <v>169</v>
+      </c>
+      <c r="C302" t="s">
+        <v>211</v>
+      </c>
+      <c r="D302" t="s">
+        <v>245</v>
+      </c>
+      <c r="E302">
+        <v>0</v>
+      </c>
+      <c r="F302">
+        <v>5</v>
+      </c>
+      <c r="G302">
+        <v>0</v>
+      </c>
+      <c r="H302">
+        <v>0</v>
+      </c>
+      <c r="I302">
+        <v>9</v>
+      </c>
+      <c r="K302" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="303" spans="1:11">
+      <c r="A303" t="s">
+        <v>74</v>
+      </c>
+      <c r="B303" t="s">
+        <v>168</v>
+      </c>
+      <c r="C303" t="s">
+        <v>210</v>
+      </c>
+      <c r="D303" t="s">
+        <v>245</v>
+      </c>
+      <c r="E303">
+        <v>0</v>
+      </c>
+      <c r="F303">
+        <v>1</v>
+      </c>
+      <c r="G303">
+        <v>0</v>
+      </c>
+      <c r="H303">
+        <v>0</v>
+      </c>
+      <c r="I303">
+        <v>1</v>
+      </c>
+      <c r="J303">
+        <v>1</v>
+      </c>
+      <c r="K303" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="304" spans="1:11">
+      <c r="A304" t="s">
+        <v>74</v>
+      </c>
+      <c r="B304" t="s">
+        <v>190</v>
+      </c>
+      <c r="C304" t="s">
+        <v>231</v>
+      </c>
+      <c r="D304" t="s">
+        <v>248</v>
+      </c>
+      <c r="E304">
+        <v>0</v>
+      </c>
+      <c r="F304">
+        <v>0</v>
+      </c>
+      <c r="G304">
+        <v>6</v>
+      </c>
+      <c r="H304">
+        <v>0</v>
+      </c>
+      <c r="I304">
+        <v>0</v>
+      </c>
+      <c r="J304">
+        <v>2</v>
+      </c>
+      <c r="K304" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="305" spans="1:11">
+      <c r="A305" t="s">
+        <v>74</v>
+      </c>
+      <c r="B305" t="s">
+        <v>194</v>
+      </c>
+      <c r="C305" t="s">
+        <v>234</v>
+      </c>
+      <c r="D305" t="s">
+        <v>248</v>
+      </c>
+      <c r="E305">
+        <v>0</v>
+      </c>
+      <c r="F305">
+        <v>3</v>
+      </c>
+      <c r="G305">
+        <v>6</v>
+      </c>
+      <c r="H305">
+        <v>0</v>
+      </c>
+      <c r="I305">
+        <v>0</v>
+      </c>
+      <c r="J305">
+        <v>3</v>
+      </c>
+      <c r="K305" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="306" spans="1:11">
+      <c r="A306" t="s">
+        <v>74</v>
+      </c>
+      <c r="B306" t="s">
+        <v>195</v>
+      </c>
+      <c r="C306" t="s">
+        <v>235</v>
+      </c>
+      <c r="D306" t="s">
+        <v>248</v>
+      </c>
+      <c r="E306">
+        <v>0</v>
+      </c>
+      <c r="F306">
+        <v>3</v>
+      </c>
+      <c r="G306">
+        <v>6</v>
+      </c>
+      <c r="H306">
+        <v>0</v>
+      </c>
+      <c r="I306">
+        <v>0</v>
+      </c>
+      <c r="J306">
+        <v>3</v>
+      </c>
+      <c r="K306" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="307" spans="1:11">
+      <c r="A307" t="s">
+        <v>74</v>
+      </c>
+      <c r="B307" t="s">
+        <v>196</v>
+      </c>
+      <c r="C307" t="s">
+        <v>205</v>
+      </c>
+      <c r="D307" t="s">
+        <v>248</v>
+      </c>
+      <c r="E307">
+        <v>0</v>
+      </c>
+      <c r="F307">
+        <v>3</v>
+      </c>
+      <c r="G307">
+        <v>6</v>
+      </c>
+      <c r="H307">
+        <v>0</v>
+      </c>
+      <c r="I307">
+        <v>0</v>
+      </c>
+      <c r="J307">
+        <v>3</v>
+      </c>
+      <c r="K307" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="308" spans="1:11">
+      <c r="A308" t="s">
+        <v>74</v>
+      </c>
+      <c r="B308" t="s">
+        <v>197</v>
+      </c>
+      <c r="C308" t="s">
+        <v>236</v>
+      </c>
+      <c r="D308" t="s">
+        <v>248</v>
+      </c>
+      <c r="E308">
+        <v>0</v>
+      </c>
+      <c r="F308">
+        <v>1</v>
+      </c>
+      <c r="G308">
+        <v>1</v>
+      </c>
+      <c r="H308">
+        <v>0</v>
+      </c>
+      <c r="I308">
+        <v>0</v>
+      </c>
+      <c r="J308">
+        <v>1</v>
+      </c>
+      <c r="K308" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="309" spans="1:11">
+      <c r="A309" t="s">
+        <v>74</v>
+      </c>
+      <c r="B309" t="s">
+        <v>175</v>
+      </c>
+      <c r="C309" t="s">
+        <v>214</v>
+      </c>
+      <c r="D309" t="s">
+        <v>248</v>
+      </c>
+      <c r="E309">
+        <v>0</v>
+      </c>
+      <c r="F309">
+        <v>5</v>
+      </c>
+      <c r="G309">
+        <v>0</v>
+      </c>
+      <c r="H309">
+        <v>0</v>
+      </c>
+      <c r="I309">
+        <v>6</v>
+      </c>
+      <c r="J309">
+        <v>3</v>
+      </c>
+      <c r="K309" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="310" spans="1:11">
+      <c r="A310" t="s">
+        <v>74</v>
+      </c>
+      <c r="B310" t="s">
+        <v>176</v>
+      </c>
+      <c r="C310" t="s">
+        <v>214</v>
+      </c>
+      <c r="D310" t="s">
+        <v>248</v>
+      </c>
+      <c r="E310">
+        <v>0</v>
+      </c>
+      <c r="F310">
+        <v>5</v>
+      </c>
+      <c r="G310">
+        <v>0</v>
+      </c>
+      <c r="H310">
+        <v>0</v>
+      </c>
+      <c r="I310">
+        <v>6</v>
+      </c>
+      <c r="J310">
+        <v>3</v>
+      </c>
+      <c r="K310" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="311" spans="1:11">
+      <c r="A311" t="s">
+        <v>74</v>
+      </c>
+      <c r="B311" t="s">
+        <v>177</v>
+      </c>
+      <c r="C311" t="s">
+        <v>221</v>
+      </c>
+      <c r="D311" t="s">
+        <v>248</v>
+      </c>
+      <c r="E311">
+        <v>0</v>
+      </c>
+      <c r="F311">
+        <v>5</v>
+      </c>
+      <c r="G311">
+        <v>0</v>
+      </c>
+      <c r="H311">
+        <v>0</v>
+      </c>
+      <c r="I311">
+        <v>6</v>
+      </c>
+      <c r="J311">
+        <v>3</v>
+      </c>
+      <c r="K311" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="312" spans="1:11">
+      <c r="A312" t="s">
+        <v>74</v>
+      </c>
+      <c r="B312" t="s">
+        <v>190</v>
+      </c>
+      <c r="C312" t="s">
+        <v>231</v>
+      </c>
+      <c r="D312" t="s">
+        <v>248</v>
+      </c>
+      <c r="E312">
+        <v>0</v>
+      </c>
+      <c r="F312">
+        <v>5</v>
+      </c>
+      <c r="G312">
+        <v>0</v>
+      </c>
+      <c r="H312">
+        <v>0</v>
+      </c>
+      <c r="I312">
+        <v>6</v>
+      </c>
+      <c r="J312">
+        <v>4</v>
+      </c>
+      <c r="K312" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="313" spans="1:11">
+      <c r="A313" t="s">
+        <v>74</v>
+      </c>
+      <c r="B313" t="s">
+        <v>175</v>
+      </c>
+      <c r="C313" t="s">
+        <v>214</v>
+      </c>
+      <c r="D313" t="s">
+        <v>248</v>
+      </c>
+      <c r="E313">
+        <v>0</v>
+      </c>
+      <c r="F313">
+        <v>5</v>
+      </c>
+      <c r="G313">
+        <v>0</v>
+      </c>
+      <c r="H313">
+        <v>0</v>
+      </c>
+      <c r="I313">
+        <v>9</v>
+      </c>
+      <c r="J313">
+        <v>4</v>
+      </c>
+      <c r="K313" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="314" spans="1:11">
+      <c r="A314" t="s">
+        <v>74</v>
+      </c>
+      <c r="B314" t="s">
+        <v>176</v>
+      </c>
+      <c r="C314" t="s">
+        <v>214</v>
+      </c>
+      <c r="D314" t="s">
+        <v>248</v>
+      </c>
+      <c r="E314">
+        <v>0</v>
+      </c>
+      <c r="F314">
+        <v>5</v>
+      </c>
+      <c r="G314">
+        <v>0</v>
+      </c>
+      <c r="H314">
+        <v>0</v>
+      </c>
+      <c r="I314">
+        <v>9</v>
+      </c>
+      <c r="K314" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="315" spans="1:11">
+      <c r="A315" t="s">
+        <v>74</v>
+      </c>
+      <c r="B315" t="s">
+        <v>177</v>
+      </c>
+      <c r="C315" t="s">
+        <v>221</v>
+      </c>
+      <c r="D315" t="s">
+        <v>248</v>
+      </c>
+      <c r="E315">
+        <v>0</v>
+      </c>
+      <c r="F315">
+        <v>5</v>
+      </c>
+      <c r="G315">
+        <v>0</v>
+      </c>
+      <c r="H315">
+        <v>0</v>
+      </c>
+      <c r="I315">
+        <v>9</v>
+      </c>
+      <c r="J315">
+        <v>4</v>
+      </c>
+      <c r="K315" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="316" spans="1:11">
+      <c r="A316" t="s">
+        <v>74</v>
+      </c>
+      <c r="B316" t="s">
+        <v>190</v>
+      </c>
+      <c r="C316" t="s">
+        <v>231</v>
+      </c>
+      <c r="D316" t="s">
+        <v>248</v>
+      </c>
+      <c r="E316">
+        <v>0</v>
+      </c>
+      <c r="F316">
+        <v>5</v>
+      </c>
+      <c r="G316">
+        <v>0</v>
+      </c>
+      <c r="H316">
+        <v>0</v>
+      </c>
+      <c r="I316">
+        <v>9</v>
+      </c>
+      <c r="J316">
+        <v>4</v>
+      </c>
+      <c r="K316" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="317" spans="1:11">
+      <c r="A317" t="s">
+        <v>75</v>
+      </c>
+      <c r="B317" t="s">
+        <v>172</v>
+      </c>
+      <c r="C317" t="s">
+        <v>213</v>
+      </c>
+      <c r="D317" t="s">
+        <v>248</v>
+      </c>
+      <c r="E317">
+        <v>0</v>
+      </c>
+      <c r="F317">
+        <v>10</v>
+      </c>
+      <c r="G317">
+        <v>0</v>
+      </c>
+      <c r="H317">
+        <v>0</v>
+      </c>
+      <c r="I317">
+        <v>14</v>
+      </c>
+      <c r="J317">
+        <v>6</v>
+      </c>
+      <c r="K317" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="318" spans="1:11">
+      <c r="A318" t="s">
+        <v>75</v>
+      </c>
+      <c r="B318" t="s">
+        <v>173</v>
+      </c>
+      <c r="C318" t="s">
+        <v>214</v>
+      </c>
+      <c r="D318" t="s">
+        <v>248</v>
+      </c>
+      <c r="E318">
+        <v>0</v>
+      </c>
+      <c r="F318">
+        <v>10</v>
+      </c>
+      <c r="G318">
+        <v>0</v>
+      </c>
+      <c r="H318">
+        <v>0</v>
+      </c>
+      <c r="I318">
+        <v>14</v>
+      </c>
+      <c r="J318">
+        <v>5</v>
+      </c>
+      <c r="K318" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="319" spans="1:11">
+      <c r="A319" t="s">
+        <v>75</v>
+      </c>
+      <c r="B319" t="s">
+        <v>174</v>
+      </c>
+      <c r="C319" t="s">
+        <v>202</v>
+      </c>
+      <c r="D319" t="s">
+        <v>248</v>
+      </c>
+      <c r="E319">
+        <v>0</v>
+      </c>
+      <c r="F319">
+        <v>10</v>
+      </c>
+      <c r="G319">
+        <v>0</v>
+      </c>
+      <c r="H319">
+        <v>0</v>
+      </c>
+      <c r="I319">
+        <v>14</v>
+      </c>
+      <c r="J319">
+        <v>5</v>
+      </c>
+      <c r="K319" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="320" spans="1:11">
+      <c r="A320" t="s">
+        <v>76</v>
+      </c>
+      <c r="B320" t="s">
+        <v>186</v>
+      </c>
+      <c r="C320" t="s">
+        <v>228</v>
+      </c>
+      <c r="D320" t="s">
+        <v>245</v>
+      </c>
+      <c r="E320">
+        <v>0</v>
+      </c>
+      <c r="F320">
+        <v>10</v>
+      </c>
+      <c r="G320">
+        <v>0</v>
+      </c>
+      <c r="H320">
+        <v>0</v>
+      </c>
+      <c r="I320">
+        <v>15</v>
+      </c>
+      <c r="J320">
+        <v>5</v>
+      </c>
+      <c r="K320" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="321" spans="1:11">
+      <c r="A321" t="s">
+        <v>76</v>
+      </c>
+      <c r="B321" t="s">
+        <v>187</v>
+      </c>
+      <c r="C321" t="s">
+        <v>229</v>
+      </c>
+      <c r="D321" t="s">
+        <v>245</v>
+      </c>
+      <c r="E321">
+        <v>0</v>
+      </c>
+      <c r="F321">
+        <v>10</v>
+      </c>
+      <c r="G321">
+        <v>0</v>
+      </c>
+      <c r="H321">
+        <v>0</v>
+      </c>
+      <c r="I321">
+        <v>15</v>
+      </c>
+      <c r="J321">
+        <v>6</v>
+      </c>
+      <c r="K321" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="322" spans="1:11">
+      <c r="A322" t="s">
+        <v>76</v>
+      </c>
+      <c r="B322" t="s">
+        <v>188</v>
+      </c>
+      <c r="C322" t="s">
+        <v>215</v>
+      </c>
+      <c r="D322" t="s">
+        <v>245</v>
+      </c>
+      <c r="E322">
+        <v>0</v>
+      </c>
+      <c r="F322">
+        <v>10</v>
+      </c>
+      <c r="G322">
+        <v>0</v>
+      </c>
+      <c r="H322">
+        <v>0</v>
+      </c>
+      <c r="I322">
+        <v>15</v>
+      </c>
+      <c r="J322">
+        <v>6</v>
+      </c>
+      <c r="K322" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="323" spans="1:11">
+      <c r="A323" t="s">
+        <v>76</v>
+      </c>
+      <c r="B323" t="s">
+        <v>189</v>
+      </c>
+      <c r="C323" t="s">
+        <v>230</v>
+      </c>
+      <c r="D323" t="s">
+        <v>245</v>
+      </c>
+      <c r="E323">
+        <v>0</v>
+      </c>
+      <c r="F323">
+        <v>10</v>
+      </c>
+      <c r="G323">
+        <v>0</v>
+      </c>
+      <c r="H323">
+        <v>0</v>
+      </c>
+      <c r="I323">
+        <v>15</v>
+      </c>
+      <c r="J323">
+        <v>6</v>
+      </c>
+      <c r="K323" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="324" spans="1:11">
+      <c r="A324" t="s">
+        <v>77</v>
+      </c>
+      <c r="B324" t="s">
+        <v>191</v>
+      </c>
+      <c r="C324" t="s">
+        <v>232</v>
+      </c>
+      <c r="D324" t="s">
+        <v>245</v>
+      </c>
+      <c r="E324">
+        <v>0</v>
+      </c>
+      <c r="F324">
+        <v>10</v>
+      </c>
+      <c r="G324">
+        <v>6</v>
+      </c>
+      <c r="H324">
+        <v>0</v>
+      </c>
+      <c r="I324">
+        <v>15</v>
+      </c>
+      <c r="J324">
+        <v>6</v>
+      </c>
+      <c r="K324" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="325" spans="1:11">
+      <c r="A325" t="s">
+        <v>77</v>
+      </c>
+      <c r="B325" t="s">
+        <v>192</v>
+      </c>
+      <c r="C325" t="s">
+        <v>233</v>
+      </c>
+      <c r="D325" t="s">
+        <v>245</v>
+      </c>
+      <c r="E325">
+        <v>0</v>
+      </c>
+      <c r="F325">
+        <v>10</v>
+      </c>
+      <c r="G325">
+        <v>6</v>
+      </c>
+      <c r="H325">
+        <v>0</v>
+      </c>
+      <c r="I325">
+        <v>15</v>
+      </c>
+      <c r="J325">
+        <v>6</v>
+      </c>
+      <c r="K325" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="326" spans="1:11">
+      <c r="A326" t="s">
+        <v>77</v>
+      </c>
+      <c r="B326" t="s">
+        <v>193</v>
+      </c>
+      <c r="C326" t="s">
+        <v>233</v>
+      </c>
+      <c r="D326" t="s">
+        <v>245</v>
+      </c>
+      <c r="E326">
+        <v>0</v>
+      </c>
+      <c r="F326">
+        <v>10</v>
+      </c>
+      <c r="G326">
+        <v>6</v>
+      </c>
+      <c r="H326">
+        <v>0</v>
+      </c>
+      <c r="I326">
+        <v>15</v>
+      </c>
+      <c r="J326">
+        <v>6</v>
+      </c>
+      <c r="K326" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="327" spans="1:11">
+      <c r="A327" t="s">
+        <v>77</v>
+      </c>
+      <c r="B327" t="s">
+        <v>198</v>
+      </c>
+      <c r="C327" t="s">
+        <v>237</v>
+      </c>
+      <c r="D327" t="s">
+        <v>245</v>
+      </c>
+      <c r="E327">
+        <v>0</v>
+      </c>
+      <c r="F327">
+        <v>3</v>
+      </c>
+      <c r="G327">
+        <v>1</v>
+      </c>
+      <c r="H327">
+        <v>0</v>
+      </c>
+      <c r="I327">
+        <v>3</v>
+      </c>
+      <c r="J327">
+        <v>2</v>
+      </c>
+      <c r="K327" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="328" spans="1:11">
+      <c r="A328" t="s">
+        <v>78</v>
+      </c>
+      <c r="B328" t="s">
         <v>163</v>
       </c>
-      <c r="C298" t="s">
+      <c r="C328" t="s">
+        <v>238</v>
+      </c>
+      <c r="D328" t="s">
+        <v>248</v>
+      </c>
+      <c r="E328">
+        <v>0</v>
+      </c>
+      <c r="F328">
+        <v>13</v>
+      </c>
+      <c r="G328">
+        <v>0</v>
+      </c>
+      <c r="H328">
+        <v>0</v>
+      </c>
+      <c r="I328">
+        <v>15</v>
+      </c>
+      <c r="J328">
+        <v>8</v>
+      </c>
+      <c r="K328" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="329" spans="1:11">
+      <c r="A329" t="s">
+        <v>78</v>
+      </c>
+      <c r="B329" t="s">
+        <v>164</v>
+      </c>
+      <c r="C329" t="s">
+        <v>238</v>
+      </c>
+      <c r="D329" t="s">
+        <v>248</v>
+      </c>
+      <c r="E329">
+        <v>0</v>
+      </c>
+      <c r="F329">
+        <v>13</v>
+      </c>
+      <c r="G329">
+        <v>0</v>
+      </c>
+      <c r="H329">
+        <v>0</v>
+      </c>
+      <c r="I329">
+        <v>15</v>
+      </c>
+      <c r="J329">
+        <v>8</v>
+      </c>
+      <c r="K329" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="330" spans="1:11">
+      <c r="A330" t="s">
+        <v>78</v>
+      </c>
+      <c r="B330" t="s">
+        <v>165</v>
+      </c>
+      <c r="C330" t="s">
+        <v>209</v>
+      </c>
+      <c r="D330" t="s">
+        <v>248</v>
+      </c>
+      <c r="E330">
+        <v>0</v>
+      </c>
+      <c r="F330">
+        <v>13</v>
+      </c>
+      <c r="G330">
+        <v>0</v>
+      </c>
+      <c r="H330">
+        <v>0</v>
+      </c>
+      <c r="I330">
+        <v>15</v>
+      </c>
+      <c r="J330">
+        <v>8</v>
+      </c>
+      <c r="K330" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="331" spans="1:11">
+      <c r="A331" t="s">
+        <v>78</v>
+      </c>
+      <c r="B331" t="s">
+        <v>166</v>
+      </c>
+      <c r="C331" t="s">
+        <v>239</v>
+      </c>
+      <c r="D331" t="s">
+        <v>248</v>
+      </c>
+      <c r="E331">
+        <v>0</v>
+      </c>
+      <c r="F331">
+        <v>13</v>
+      </c>
+      <c r="G331">
+        <v>0</v>
+      </c>
+      <c r="H331">
+        <v>0</v>
+      </c>
+      <c r="I331">
+        <v>15</v>
+      </c>
+      <c r="J331">
+        <v>8</v>
+      </c>
+      <c r="K331" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="332" spans="1:11">
+      <c r="A332" t="s">
+        <v>78</v>
+      </c>
+      <c r="B332" t="s">
+        <v>167</v>
+      </c>
+      <c r="C332" t="s">
+        <v>240</v>
+      </c>
+      <c r="D332" t="s">
+        <v>248</v>
+      </c>
+      <c r="E332">
+        <v>0</v>
+      </c>
+      <c r="F332">
+        <v>5</v>
+      </c>
+      <c r="G332">
+        <v>0</v>
+      </c>
+      <c r="H332">
+        <v>0</v>
+      </c>
+      <c r="I332">
+        <v>5</v>
+      </c>
+      <c r="J332">
+        <v>3</v>
+      </c>
+      <c r="K332" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="333" spans="1:11">
+      <c r="A333" t="s">
+        <v>79</v>
+      </c>
+      <c r="B333" t="s">
+        <v>161</v>
+      </c>
+      <c r="C333" t="s">
+        <v>241</v>
+      </c>
+      <c r="D333" t="s">
+        <v>248</v>
+      </c>
+      <c r="E333">
+        <v>0</v>
+      </c>
+      <c r="F333">
+        <v>13</v>
+      </c>
+      <c r="G333">
+        <v>0</v>
+      </c>
+      <c r="H333">
+        <v>0</v>
+      </c>
+      <c r="I333">
+        <v>15</v>
+      </c>
+      <c r="J333">
+        <v>8</v>
+      </c>
+      <c r="K333" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="334" spans="1:11">
+      <c r="A334" t="s">
+        <v>79</v>
+      </c>
+      <c r="B334" t="s">
+        <v>162</v>
+      </c>
+      <c r="C334" t="s">
+        <v>242</v>
+      </c>
+      <c r="D334" t="s">
+        <v>248</v>
+      </c>
+      <c r="E334">
+        <v>0</v>
+      </c>
+      <c r="F334">
+        <v>13</v>
+      </c>
+      <c r="G334">
+        <v>0</v>
+      </c>
+      <c r="H334">
+        <v>0</v>
+      </c>
+      <c r="I334">
+        <v>15</v>
+      </c>
+      <c r="J334">
+        <v>8</v>
+      </c>
+      <c r="K334" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="335" spans="1:11">
+      <c r="A335" t="s">
+        <v>79</v>
+      </c>
+      <c r="B335" t="s">
+        <v>181</v>
+      </c>
+      <c r="C335" t="s">
+        <v>222</v>
+      </c>
+      <c r="D335" t="s">
+        <v>248</v>
+      </c>
+      <c r="E335">
+        <v>0</v>
+      </c>
+      <c r="F335">
+        <v>13</v>
+      </c>
+      <c r="G335">
+        <v>0</v>
+      </c>
+      <c r="H335">
+        <v>0</v>
+      </c>
+      <c r="I335">
+        <v>15</v>
+      </c>
+      <c r="J335">
+        <v>8</v>
+      </c>
+      <c r="K335" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="336" spans="1:11">
+      <c r="A336" t="s">
+        <v>79</v>
+      </c>
+      <c r="B336" t="s">
+        <v>182</v>
+      </c>
+      <c r="C336" t="s">
+        <v>206</v>
+      </c>
+      <c r="D336" t="s">
+        <v>248</v>
+      </c>
+      <c r="E336">
+        <v>0</v>
+      </c>
+      <c r="F336">
+        <v>13</v>
+      </c>
+      <c r="G336">
+        <v>0</v>
+      </c>
+      <c r="H336">
+        <v>0</v>
+      </c>
+      <c r="I336">
+        <v>15</v>
+      </c>
+      <c r="J336">
+        <v>8</v>
+      </c>
+      <c r="K336" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="337" spans="1:11">
+      <c r="A337" t="s">
+        <v>79</v>
+      </c>
+      <c r="B337" t="s">
+        <v>183</v>
+      </c>
+      <c r="C337" t="s">
+        <v>223</v>
+      </c>
+      <c r="D337" t="s">
+        <v>248</v>
+      </c>
+      <c r="E337">
+        <v>0</v>
+      </c>
+      <c r="F337">
+        <v>10</v>
+      </c>
+      <c r="G337">
+        <v>0</v>
+      </c>
+      <c r="H337">
+        <v>0</v>
+      </c>
+      <c r="I337">
+        <v>15</v>
+      </c>
+      <c r="J337">
+        <v>6</v>
+      </c>
+      <c r="K337" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="338" spans="1:11">
+      <c r="A338" t="s">
+        <v>80</v>
+      </c>
+      <c r="B338" t="s">
+        <v>194</v>
+      </c>
+      <c r="C338" t="s">
+        <v>234</v>
+      </c>
+      <c r="D338" t="s">
+        <v>248</v>
+      </c>
+      <c r="E338">
+        <v>0</v>
+      </c>
+      <c r="F338">
+        <v>10</v>
+      </c>
+      <c r="G338">
+        <v>0</v>
+      </c>
+      <c r="H338">
+        <v>0</v>
+      </c>
+      <c r="I338">
+        <v>15</v>
+      </c>
+      <c r="J338">
+        <v>6</v>
+      </c>
+      <c r="K338" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="339" spans="1:11">
+      <c r="A339" t="s">
+        <v>80</v>
+      </c>
+      <c r="B339" t="s">
+        <v>195</v>
+      </c>
+      <c r="C339" t="s">
+        <v>235</v>
+      </c>
+      <c r="D339" t="s">
+        <v>248</v>
+      </c>
+      <c r="E339">
+        <v>0</v>
+      </c>
+      <c r="F339">
+        <v>10</v>
+      </c>
+      <c r="G339">
+        <v>0</v>
+      </c>
+      <c r="H339">
+        <v>0</v>
+      </c>
+      <c r="I339">
+        <v>15</v>
+      </c>
+      <c r="J339">
+        <v>6</v>
+      </c>
+      <c r="K339" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="340" spans="1:11">
+      <c r="A340" t="s">
+        <v>80</v>
+      </c>
+      <c r="B340" t="s">
+        <v>196</v>
+      </c>
+      <c r="C340" t="s">
+        <v>205</v>
+      </c>
+      <c r="D340" t="s">
+        <v>248</v>
+      </c>
+      <c r="E340">
+        <v>0</v>
+      </c>
+      <c r="F340">
+        <v>10</v>
+      </c>
+      <c r="G340">
+        <v>0</v>
+      </c>
+      <c r="H340">
+        <v>0</v>
+      </c>
+      <c r="I340">
+        <v>15</v>
+      </c>
+      <c r="J340">
+        <v>6</v>
+      </c>
+      <c r="K340" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="341" spans="1:11">
+      <c r="A341" t="s">
+        <v>80</v>
+      </c>
+      <c r="B341" t="s">
+        <v>197</v>
+      </c>
+      <c r="C341" t="s">
+        <v>236</v>
+      </c>
+      <c r="D341" t="s">
+        <v>248</v>
+      </c>
+      <c r="E341">
+        <v>0</v>
+      </c>
+      <c r="F341">
+        <v>2</v>
+      </c>
+      <c r="G341">
+        <v>0</v>
+      </c>
+      <c r="H341">
+        <v>0</v>
+      </c>
+      <c r="I341">
+        <v>2</v>
+      </c>
+      <c r="J341">
+        <v>1</v>
+      </c>
+      <c r="K341" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="342" spans="1:11">
+      <c r="A342" t="s">
+        <v>81</v>
+      </c>
+      <c r="B342" t="s">
         <v>199</v>
       </c>
-      <c r="D298" t="s">
-        <v>222</v>
-      </c>
-      <c r="E298">
-        <v>0</v>
-      </c>
-      <c r="F298">
-        <v>5</v>
-      </c>
-      <c r="G298">
-        <v>0</v>
-      </c>
-      <c r="H298">
-        <v>0</v>
-      </c>
-      <c r="I298">
-        <v>6</v>
-      </c>
-      <c r="J298">
-        <v>2</v>
-      </c>
-      <c r="K298" t="s">
-        <v>226</v>
+      <c r="C342" t="s">
+        <v>243</v>
+      </c>
+      <c r="D342" t="s">
+        <v>248</v>
+      </c>
+      <c r="E342">
+        <v>0</v>
+      </c>
+      <c r="F342">
+        <v>8</v>
+      </c>
+      <c r="G342">
+        <v>4</v>
+      </c>
+      <c r="H342">
+        <v>0</v>
+      </c>
+      <c r="I342">
+        <v>10</v>
+      </c>
+      <c r="J342">
+        <v>5</v>
+      </c>
+      <c r="K342" t="s">
+        <v>249</v>
       </c>
     </row>
   </sheetData>

--- a/data/fertilizer_records.xlsx
+++ b/data/fertilizer_records.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12000"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="10695" windowHeight="7290"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10061" uniqueCount="925">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10275" uniqueCount="940">
   <si>
     <t>Date</t>
   </si>
@@ -2691,6 +2691,12 @@
     <t>2026-01-14</t>
   </si>
   <si>
+    <t>2026-01-30</t>
+  </si>
+  <si>
+    <t>2026-01-31</t>
+  </si>
+  <si>
     <t>2026-05-18</t>
   </si>
   <si>
@@ -2794,6 +2800,45 @@
   </si>
   <si>
     <t>2026-07-31</t>
+  </si>
+  <si>
+    <t>2026-08-07</t>
+  </si>
+  <si>
+    <t>3.043</t>
+  </si>
+  <si>
+    <t>2026-08-06</t>
+  </si>
+  <si>
+    <t>2026-08-10</t>
+  </si>
+  <si>
+    <t>2026-08-11</t>
+  </si>
+  <si>
+    <t>0.084</t>
+  </si>
+  <si>
+    <t>2026-08-12</t>
+  </si>
+  <si>
+    <t>1.668</t>
+  </si>
+  <si>
+    <t>2026-02-03</t>
+  </si>
+  <si>
+    <t>2026-02-04</t>
+  </si>
+  <si>
+    <t>2026-02-05</t>
+  </si>
+  <si>
+    <t>LP08004</t>
+  </si>
+  <si>
+    <t>LF08017</t>
   </si>
 </sst>
 </file>
@@ -3156,8 +3201,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2055"/>
+  <dimension ref="A1:K2128"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="10.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
@@ -68739,34 +68787,34 @@
         <v>890</v>
       </c>
       <c r="B1893" t="s">
-        <v>657</v>
+        <v>197</v>
       </c>
       <c r="C1893" t="s">
-        <v>265</v>
+        <v>198</v>
       </c>
       <c r="D1893" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E1893">
+        <v>0</v>
+      </c>
+      <c r="F1893">
+        <v>12</v>
+      </c>
+      <c r="G1893">
+        <v>0</v>
+      </c>
+      <c r="H1893">
+        <v>0</v>
+      </c>
+      <c r="I1893">
         <v>15</v>
       </c>
-      <c r="F1893">
-        <v>6</v>
-      </c>
-      <c r="G1893">
-        <v>6</v>
-      </c>
-      <c r="H1893">
-        <v>0</v>
-      </c>
-      <c r="I1893">
-        <v>0</v>
-      </c>
       <c r="J1893">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K1893" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1894" spans="1:11" x14ac:dyDescent="0.25">
@@ -68774,1938 +68822,893 @@
         <v>890</v>
       </c>
       <c r="B1894" t="s">
-        <v>658</v>
+        <v>199</v>
       </c>
       <c r="C1894" t="s">
-        <v>220</v>
+        <v>163</v>
       </c>
       <c r="D1894" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E1894">
+        <v>0</v>
+      </c>
+      <c r="F1894">
+        <v>12</v>
+      </c>
+      <c r="G1894">
+        <v>0</v>
+      </c>
+      <c r="H1894">
+        <v>0</v>
+      </c>
+      <c r="I1894">
         <v>15</v>
       </c>
-      <c r="F1894">
-        <v>6</v>
-      </c>
-      <c r="G1894">
-        <v>6</v>
-      </c>
-      <c r="H1894">
-        <v>0</v>
-      </c>
-      <c r="I1894">
-        <v>0</v>
-      </c>
       <c r="J1894">
         <v>6</v>
       </c>
       <c r="K1894" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1895" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1895" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="B1895" t="s">
-        <v>659</v>
+        <v>728</v>
       </c>
       <c r="C1895" t="s">
-        <v>155</v>
+        <v>729</v>
       </c>
       <c r="D1895" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1895">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1895">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1895">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1895">
         <v>0</v>
       </c>
       <c r="I1895">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1895">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="K1895" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1896" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1896" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B1896" t="s">
-        <v>660</v>
+        <v>740</v>
       </c>
       <c r="C1896" t="s">
-        <v>403</v>
+        <v>741</v>
       </c>
       <c r="D1896" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1896">
         <v>0</v>
       </c>
       <c r="F1896">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1896">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1896">
         <v>0</v>
       </c>
       <c r="I1896">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1896">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1896" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1897" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1897" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B1897" t="s">
-        <v>661</v>
+        <v>745</v>
       </c>
       <c r="C1897" t="s">
-        <v>155</v>
+        <v>746</v>
       </c>
       <c r="D1897" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1897">
         <v>0</v>
       </c>
       <c r="F1897">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1897">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H1897">
         <v>0</v>
       </c>
       <c r="I1897">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1897">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1897" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1898" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1898" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B1898" t="s">
-        <v>126</v>
+        <v>738</v>
       </c>
       <c r="C1898" t="s">
-        <v>361</v>
+        <v>739</v>
       </c>
       <c r="D1898" t="s">
         <v>79</v>
       </c>
       <c r="E1898">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1898">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1898">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1898">
         <v>0</v>
       </c>
       <c r="I1898">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1898">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1898" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1899" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1899" t="s">
-        <v>893</v>
+        <v>935</v>
       </c>
       <c r="B1899" t="s">
-        <v>127</v>
+        <v>97</v>
       </c>
       <c r="C1899" t="s">
-        <v>357</v>
+        <v>327</v>
       </c>
       <c r="D1899" t="s">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="E1899">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1899">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1899">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1899">
         <v>0</v>
       </c>
       <c r="I1899">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1899">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1899" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1900" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1900" t="s">
-        <v>894</v>
+        <v>935</v>
       </c>
       <c r="B1900" t="s">
-        <v>128</v>
+        <v>99</v>
       </c>
       <c r="C1900" t="s">
-        <v>215</v>
+        <v>325</v>
       </c>
       <c r="D1900" t="s">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="E1900">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1900">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1900">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1900">
         <v>0</v>
       </c>
       <c r="I1900">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1900">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1900" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1901" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1901" t="s">
-        <v>894</v>
+        <v>935</v>
       </c>
       <c r="B1901" t="s">
-        <v>135</v>
+        <v>100</v>
       </c>
       <c r="C1901" t="s">
-        <v>500</v>
+        <v>325</v>
       </c>
       <c r="D1901" t="s">
-        <v>79</v>
+        <v>463</v>
       </c>
       <c r="E1901">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F1901">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1901">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1901">
         <v>0</v>
       </c>
       <c r="I1901">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1901">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1901" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1902" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1902" t="s">
-        <v>895</v>
+        <v>935</v>
       </c>
       <c r="B1902" t="s">
-        <v>25</v>
+        <v>105</v>
       </c>
       <c r="C1902" t="s">
-        <v>244</v>
+        <v>327</v>
       </c>
       <c r="D1902" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
       <c r="E1902">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1902">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1902">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1902">
         <v>0</v>
       </c>
       <c r="I1902">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1902">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K1902" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1903" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1903" t="s">
-        <v>895</v>
+        <v>935</v>
       </c>
       <c r="B1903" t="s">
-        <v>26</v>
+        <v>106</v>
       </c>
       <c r="C1903" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="D1903" t="s">
-        <v>13</v>
+        <v>463</v>
       </c>
       <c r="E1903">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1903">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1903">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1903">
         <v>0</v>
       </c>
       <c r="I1903">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1903">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1903" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1904" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1904" t="s">
-        <v>895</v>
+        <v>936</v>
       </c>
       <c r="B1904" t="s">
-        <v>27</v>
+        <v>568</v>
       </c>
       <c r="C1904" t="s">
-        <v>159</v>
+        <v>569</v>
       </c>
       <c r="D1904" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="E1904">
+        <v>0</v>
+      </c>
+      <c r="F1904">
+        <v>0</v>
+      </c>
+      <c r="G1904">
+        <v>0</v>
+      </c>
+      <c r="H1904">
+        <v>0</v>
+      </c>
+      <c r="I1904">
         <v>15</v>
       </c>
-      <c r="F1904">
-        <v>0</v>
-      </c>
-      <c r="G1904">
-        <v>6</v>
-      </c>
-      <c r="H1904">
-        <v>0</v>
-      </c>
-      <c r="I1904">
-        <v>0</v>
-      </c>
       <c r="J1904">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="K1904" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1905" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1905" t="s">
-        <v>896</v>
+        <v>936</v>
       </c>
       <c r="B1905" t="s">
-        <v>59</v>
+        <v>570</v>
       </c>
       <c r="C1905" t="s">
-        <v>256</v>
+        <v>571</v>
       </c>
       <c r="D1905" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="E1905">
+        <v>0</v>
+      </c>
+      <c r="F1905">
+        <v>0</v>
+      </c>
+      <c r="G1905">
+        <v>0</v>
+      </c>
+      <c r="H1905">
+        <v>0</v>
+      </c>
+      <c r="I1905">
         <v>15</v>
       </c>
-      <c r="F1905">
-        <v>0</v>
-      </c>
-      <c r="G1905">
-        <v>6</v>
-      </c>
-      <c r="H1905">
-        <v>0</v>
-      </c>
-      <c r="I1905">
-        <v>0</v>
-      </c>
       <c r="J1905">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K1905" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1906" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1906" t="s">
-        <v>896</v>
+        <v>936</v>
       </c>
       <c r="B1906" t="s">
-        <v>60</v>
+        <v>576</v>
       </c>
       <c r="C1906" t="s">
-        <v>272</v>
+        <v>535</v>
       </c>
       <c r="D1906" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="E1906">
+        <v>0</v>
+      </c>
+      <c r="F1906">
+        <v>0</v>
+      </c>
+      <c r="G1906">
+        <v>0</v>
+      </c>
+      <c r="H1906">
+        <v>0</v>
+      </c>
+      <c r="I1906">
         <v>15</v>
       </c>
-      <c r="F1906">
-        <v>0</v>
-      </c>
-      <c r="G1906">
-        <v>6</v>
-      </c>
-      <c r="H1906">
-        <v>0</v>
-      </c>
-      <c r="I1906">
-        <v>0</v>
-      </c>
       <c r="J1906">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K1906" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1907" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1907" t="s">
-        <v>896</v>
+        <v>936</v>
       </c>
       <c r="B1907" t="s">
-        <v>61</v>
+        <v>577</v>
       </c>
       <c r="C1907" t="s">
-        <v>273</v>
+        <v>578</v>
       </c>
       <c r="D1907" t="s">
-        <v>13</v>
+        <v>72</v>
       </c>
       <c r="E1907">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1907">
         <v>0</v>
       </c>
       <c r="G1907">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1907">
         <v>0</v>
       </c>
       <c r="I1907">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J1907">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1907" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1908" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1908" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="B1908" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1908" t="s">
-        <v>290</v>
+        <v>938</v>
+      </c>
+      <c r="C1908">
+        <v>4.343</v>
       </c>
       <c r="D1908" t="s">
         <v>13</v>
       </c>
       <c r="E1908">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1908">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1908">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H1908">
         <v>0</v>
       </c>
       <c r="I1908">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="J1908">
         <v>5</v>
       </c>
       <c r="K1908" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1909" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1909" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="B1909" t="s">
-        <v>65</v>
+        <v>760</v>
       </c>
       <c r="C1909" t="s">
-        <v>290</v>
+        <v>761</v>
       </c>
       <c r="D1909" t="s">
         <v>13</v>
       </c>
       <c r="E1909">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1909">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1909">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H1909">
         <v>0</v>
       </c>
       <c r="I1909">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1909">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K1909" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1910" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1910" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="B1910" t="s">
-        <v>66</v>
+        <v>765</v>
       </c>
       <c r="C1910" t="s">
-        <v>291</v>
+        <v>766</v>
       </c>
       <c r="D1910" t="s">
         <v>13</v>
       </c>
       <c r="E1910">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1910">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1910">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1910">
         <v>0</v>
       </c>
       <c r="I1910">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1910">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1910" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1911" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1911" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="B1911" t="s">
-        <v>67</v>
+        <v>767</v>
       </c>
       <c r="C1911" t="s">
-        <v>292</v>
+        <v>768</v>
       </c>
       <c r="D1911" t="s">
         <v>13</v>
       </c>
       <c r="E1911">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1911">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1911">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1911">
         <v>0</v>
       </c>
       <c r="I1911">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J1911">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K1911" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1912" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1912" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="B1912" t="s">
-        <v>28</v>
-      </c>
-      <c r="C1912" t="s">
-        <v>159</v>
+        <v>939</v>
+      </c>
+      <c r="C1912">
+        <v>1.0009999999999999</v>
       </c>
       <c r="D1912" t="s">
         <v>13</v>
       </c>
       <c r="E1912">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="F1912">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1912">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H1912">
         <v>0</v>
       </c>
       <c r="I1912">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1912">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1912" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1913" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1913" t="s">
-        <v>897</v>
+        <v>937</v>
       </c>
       <c r="B1913" t="s">
-        <v>30</v>
+        <v>769</v>
       </c>
       <c r="C1913" t="s">
-        <v>244</v>
+        <v>770</v>
       </c>
       <c r="D1913" t="s">
         <v>13</v>
       </c>
       <c r="E1913">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1913">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1913">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H1913">
         <v>0</v>
       </c>
       <c r="I1913">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J1913">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1913" t="s">
-        <v>891</v>
+        <v>774</v>
       </c>
     </row>
     <row r="1914" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1914" t="s">
-        <v>897</v>
-      </c>
-      <c r="B1914" t="s">
-        <v>31</v>
-      </c>
-      <c r="C1914" t="s">
-        <v>244</v>
-      </c>
       <c r="D1914" t="s">
         <v>13</v>
       </c>
-      <c r="E1914">
-        <v>15</v>
-      </c>
-      <c r="F1914">
-        <v>0</v>
-      </c>
-      <c r="G1914">
-        <v>6</v>
-      </c>
-      <c r="H1914">
-        <v>0</v>
-      </c>
-      <c r="I1914">
-        <v>0</v>
-      </c>
-      <c r="J1914">
-        <v>5</v>
-      </c>
-      <c r="K1914" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1915" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1915" t="s">
-        <v>897</v>
-      </c>
-      <c r="B1915" t="s">
-        <v>33</v>
-      </c>
-      <c r="C1915" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1915" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1915">
-        <v>15</v>
-      </c>
-      <c r="F1915">
-        <v>0</v>
-      </c>
-      <c r="G1915">
-        <v>6</v>
-      </c>
-      <c r="H1915">
-        <v>0</v>
-      </c>
-      <c r="I1915">
-        <v>0</v>
-      </c>
-      <c r="J1915">
-        <v>5</v>
-      </c>
-      <c r="K1915" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1916" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1916" t="s">
-        <v>897</v>
-      </c>
-      <c r="B1916" t="s">
-        <v>34</v>
-      </c>
-      <c r="C1916" t="s">
-        <v>265</v>
-      </c>
-      <c r="D1916" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1916">
-        <v>15</v>
-      </c>
-      <c r="F1916">
-        <v>0</v>
-      </c>
-      <c r="G1916">
-        <v>6</v>
-      </c>
-      <c r="H1916">
-        <v>0</v>
-      </c>
-      <c r="I1916">
-        <v>0</v>
-      </c>
-      <c r="J1916">
-        <v>5</v>
-      </c>
-      <c r="K1916" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1917" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1917" t="s">
-        <v>897</v>
-      </c>
-      <c r="B1917" t="s">
-        <v>35</v>
-      </c>
-      <c r="C1917" t="s">
-        <v>266</v>
-      </c>
-      <c r="D1917" t="s">
-        <v>13</v>
-      </c>
-      <c r="E1917">
-        <v>4</v>
-      </c>
-      <c r="F1917">
-        <v>0</v>
-      </c>
-      <c r="G1917">
-        <v>2</v>
-      </c>
-      <c r="H1917">
-        <v>0</v>
-      </c>
-      <c r="I1917">
-        <v>0</v>
-      </c>
-      <c r="J1917">
-        <v>2</v>
-      </c>
-      <c r="K1917" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1918" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1918" t="s">
-        <v>898</v>
-      </c>
-      <c r="B1918" t="s">
-        <v>657</v>
-      </c>
-      <c r="C1918" t="s">
-        <v>265</v>
-      </c>
-      <c r="D1918" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1918">
-        <v>0</v>
-      </c>
-      <c r="F1918">
-        <v>6</v>
-      </c>
-      <c r="G1918">
-        <v>0</v>
-      </c>
-      <c r="H1918">
-        <v>0</v>
-      </c>
-      <c r="I1918">
-        <v>8</v>
-      </c>
-      <c r="J1918">
-        <v>3</v>
-      </c>
-      <c r="K1918" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1919" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1919" t="s">
-        <v>898</v>
-      </c>
-      <c r="B1919" t="s">
-        <v>658</v>
-      </c>
-      <c r="C1919" t="s">
-        <v>220</v>
-      </c>
-      <c r="D1919" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1919">
-        <v>0</v>
-      </c>
-      <c r="F1919">
-        <v>6</v>
-      </c>
-      <c r="G1919">
-        <v>0</v>
-      </c>
-      <c r="H1919">
-        <v>0</v>
-      </c>
-      <c r="I1919">
-        <v>8</v>
-      </c>
-      <c r="J1919">
-        <v>3</v>
-      </c>
-      <c r="K1919" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1920" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1920" t="s">
-        <v>899</v>
-      </c>
-      <c r="B1920" t="s">
-        <v>659</v>
-      </c>
-      <c r="C1920" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1920" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1920">
-        <v>0</v>
-      </c>
-      <c r="F1920">
-        <v>6</v>
-      </c>
-      <c r="G1920">
-        <v>0</v>
-      </c>
-      <c r="H1920">
-        <v>0</v>
-      </c>
-      <c r="I1920">
-        <v>8</v>
-      </c>
-      <c r="J1920">
-        <v>3</v>
-      </c>
-      <c r="K1920" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1921" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1921" t="s">
-        <v>899</v>
-      </c>
-      <c r="B1921" t="s">
-        <v>660</v>
-      </c>
-      <c r="C1921" t="s">
-        <v>403</v>
-      </c>
-      <c r="D1921" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1921">
-        <v>15</v>
-      </c>
-      <c r="F1921">
-        <v>6</v>
-      </c>
-      <c r="G1921">
-        <v>0</v>
-      </c>
-      <c r="H1921">
-        <v>0</v>
-      </c>
-      <c r="I1921">
-        <v>8</v>
-      </c>
-      <c r="J1921">
-        <v>6</v>
-      </c>
-      <c r="K1921" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1922" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1922" t="s">
-        <v>899</v>
-      </c>
-      <c r="B1922" t="s">
-        <v>661</v>
-      </c>
-      <c r="C1922" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1922" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1922">
-        <v>15</v>
-      </c>
-      <c r="F1922">
-        <v>6</v>
-      </c>
-      <c r="G1922">
-        <v>0</v>
-      </c>
-      <c r="H1922">
-        <v>0</v>
-      </c>
-      <c r="I1922">
-        <v>8</v>
-      </c>
-      <c r="J1922">
-        <v>6</v>
-      </c>
-      <c r="K1922" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1923" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1923" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1923" t="s">
-        <v>114</v>
-      </c>
-      <c r="C1923" t="s">
-        <v>367</v>
-      </c>
-      <c r="D1923" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1923">
-        <v>14</v>
-      </c>
-      <c r="F1923">
-        <v>0</v>
-      </c>
-      <c r="G1923">
-        <v>5</v>
-      </c>
-      <c r="H1923">
-        <v>2</v>
-      </c>
-      <c r="I1923">
-        <v>0</v>
-      </c>
-      <c r="J1923">
-        <v>5</v>
-      </c>
-      <c r="K1923" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1924" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1924" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1924" t="s">
-        <v>139</v>
-      </c>
-      <c r="C1924" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1924" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1924">
-        <v>15</v>
-      </c>
-      <c r="F1924">
-        <v>0</v>
-      </c>
-      <c r="G1924">
-        <v>6</v>
-      </c>
-      <c r="H1924">
-        <v>3</v>
-      </c>
-      <c r="I1924">
-        <v>0</v>
-      </c>
-      <c r="J1924">
-        <v>5</v>
-      </c>
-      <c r="K1924" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1925" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1925" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1925" t="s">
-        <v>36</v>
-      </c>
-      <c r="C1925" t="s">
-        <v>218</v>
-      </c>
-      <c r="D1925" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1925">
-        <v>15</v>
-      </c>
-      <c r="F1925">
-        <v>0</v>
-      </c>
-      <c r="G1925">
-        <v>6</v>
-      </c>
-      <c r="H1925">
-        <v>0</v>
-      </c>
-      <c r="I1925">
-        <v>0</v>
-      </c>
-      <c r="J1925">
-        <v>4</v>
-      </c>
-      <c r="K1925" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1926" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1926" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1926" t="s">
-        <v>42</v>
-      </c>
-      <c r="C1926" t="s">
-        <v>268</v>
-      </c>
-      <c r="D1926" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1926">
-        <v>15</v>
-      </c>
-      <c r="F1926">
-        <v>0</v>
-      </c>
-      <c r="G1926">
-        <v>6</v>
-      </c>
-      <c r="H1926">
-        <v>0</v>
-      </c>
-      <c r="I1926">
-        <v>0</v>
-      </c>
-      <c r="J1926">
-        <v>4</v>
-      </c>
-      <c r="K1926" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1927" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1927" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1927" t="s">
-        <v>168</v>
-      </c>
-      <c r="C1927" t="s">
-        <v>169</v>
-      </c>
-      <c r="D1927" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1927">
-        <v>1</v>
-      </c>
-      <c r="F1927">
-        <v>0</v>
-      </c>
-      <c r="G1927">
-        <v>1</v>
-      </c>
-      <c r="H1927">
-        <v>0</v>
-      </c>
-      <c r="I1927">
-        <v>0</v>
-      </c>
-      <c r="J1927">
-        <v>1</v>
-      </c>
-      <c r="K1927" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1928" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1928" t="s">
-        <v>900</v>
-      </c>
-      <c r="B1928" t="s">
-        <v>170</v>
-      </c>
-      <c r="C1928" t="s">
-        <v>171</v>
-      </c>
-      <c r="D1928" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1928">
-        <v>12</v>
-      </c>
-      <c r="F1928">
-        <v>0</v>
-      </c>
-      <c r="G1928">
-        <v>5</v>
-      </c>
-      <c r="H1928">
-        <v>0</v>
-      </c>
-      <c r="I1928">
-        <v>0</v>
-      </c>
-      <c r="J1928">
-        <v>3</v>
-      </c>
-      <c r="K1928" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1929" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1929" t="s">
-        <v>901</v>
-      </c>
-      <c r="B1929" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1929" t="s">
-        <v>158</v>
-      </c>
-      <c r="D1929" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1929">
-        <v>15</v>
-      </c>
-      <c r="F1929">
-        <v>0</v>
-      </c>
-      <c r="G1929">
-        <v>6</v>
-      </c>
-      <c r="H1929">
-        <v>3</v>
-      </c>
-      <c r="I1929">
-        <v>0</v>
-      </c>
-      <c r="J1929">
-        <v>6</v>
-      </c>
-      <c r="K1929" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1930" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1930" t="s">
-        <v>901</v>
-      </c>
-      <c r="B1930" t="s">
-        <v>43</v>
-      </c>
-      <c r="C1930" t="s">
-        <v>159</v>
-      </c>
-      <c r="D1930" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1930">
-        <v>15</v>
-      </c>
-      <c r="F1930">
-        <v>0</v>
-      </c>
-      <c r="G1930">
-        <v>6</v>
-      </c>
-      <c r="H1930">
-        <v>0</v>
-      </c>
-      <c r="I1930">
-        <v>0</v>
-      </c>
-      <c r="J1930">
-        <v>5</v>
-      </c>
-      <c r="K1930" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1931" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1931" t="s">
-        <v>901</v>
-      </c>
-      <c r="B1931" t="s">
-        <v>44</v>
-      </c>
-      <c r="C1931" t="s">
-        <v>269</v>
-      </c>
-      <c r="D1931" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1931">
-        <v>15</v>
-      </c>
-      <c r="F1931">
-        <v>0</v>
-      </c>
-      <c r="G1931">
-        <v>6</v>
-      </c>
-      <c r="H1931">
-        <v>0</v>
-      </c>
-      <c r="I1931">
-        <v>0</v>
-      </c>
-      <c r="J1931">
-        <v>5</v>
-      </c>
-      <c r="K1931" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1932" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1932" t="s">
-        <v>901</v>
-      </c>
-      <c r="B1932" t="s">
-        <v>45</v>
-      </c>
-      <c r="C1932" t="s">
-        <v>270</v>
-      </c>
-      <c r="D1932" t="s">
-        <v>87</v>
-      </c>
-      <c r="E1932">
-        <v>3</v>
-      </c>
-      <c r="F1932">
-        <v>0</v>
-      </c>
-      <c r="G1932">
-        <v>1</v>
-      </c>
-      <c r="H1932">
-        <v>0</v>
-      </c>
-      <c r="I1932">
-        <v>0</v>
-      </c>
-      <c r="J1932">
-        <v>1</v>
-      </c>
-      <c r="K1932" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1933" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1933" t="s">
-        <v>902</v>
-      </c>
-      <c r="B1933" t="s">
-        <v>657</v>
-      </c>
-      <c r="C1933" t="s">
-        <v>265</v>
-      </c>
-      <c r="D1933" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1933">
-        <v>0</v>
-      </c>
-      <c r="F1933">
-        <v>0</v>
-      </c>
-      <c r="G1933">
-        <v>0</v>
-      </c>
-      <c r="H1933">
-        <v>0</v>
-      </c>
-      <c r="I1933">
-        <v>7</v>
-      </c>
-      <c r="J1933">
-        <v>2</v>
-      </c>
-      <c r="K1933" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1934" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1934" t="s">
-        <v>902</v>
-      </c>
-      <c r="B1934" t="s">
-        <v>658</v>
-      </c>
-      <c r="C1934" t="s">
-        <v>220</v>
-      </c>
-      <c r="D1934" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1934">
-        <v>0</v>
-      </c>
-      <c r="F1934">
-        <v>0</v>
-      </c>
-      <c r="G1934">
-        <v>0</v>
-      </c>
-      <c r="H1934">
-        <v>0</v>
-      </c>
-      <c r="I1934">
-        <v>7</v>
-      </c>
-      <c r="J1934">
-        <v>2</v>
-      </c>
-      <c r="K1934" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1935" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1935" t="s">
-        <v>902</v>
-      </c>
-      <c r="B1935" t="s">
-        <v>659</v>
-      </c>
-      <c r="C1935" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1935" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1935">
-        <v>0</v>
-      </c>
-      <c r="F1935">
-        <v>0</v>
-      </c>
-      <c r="G1935">
-        <v>0</v>
-      </c>
-      <c r="H1935">
-        <v>0</v>
-      </c>
-      <c r="I1935">
-        <v>7</v>
-      </c>
-      <c r="J1935">
-        <v>2</v>
-      </c>
-      <c r="K1935" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1936" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1936" t="s">
-        <v>902</v>
-      </c>
-      <c r="B1936" t="s">
-        <v>131</v>
-      </c>
-      <c r="C1936" t="s">
-        <v>176</v>
-      </c>
-      <c r="D1936" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1936">
-        <v>15</v>
-      </c>
-      <c r="F1936">
-        <v>0</v>
-      </c>
-      <c r="G1936">
-        <v>0</v>
-      </c>
-      <c r="H1936">
-        <v>0</v>
-      </c>
-      <c r="I1936">
-        <v>0</v>
-      </c>
-      <c r="J1936">
-        <v>4</v>
-      </c>
-      <c r="K1936" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1937" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1937" t="s">
-        <v>902</v>
-      </c>
-      <c r="B1937" t="s">
-        <v>132</v>
-      </c>
-      <c r="C1937" t="s">
-        <v>181</v>
-      </c>
-      <c r="D1937" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1937">
-        <v>15</v>
-      </c>
-      <c r="F1937">
-        <v>0</v>
-      </c>
-      <c r="G1937">
-        <v>0</v>
-      </c>
-      <c r="H1937">
-        <v>0</v>
-      </c>
-      <c r="I1937">
-        <v>0</v>
-      </c>
-      <c r="J1937">
-        <v>3</v>
-      </c>
-      <c r="K1937" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1938" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1938" t="s">
-        <v>902</v>
-      </c>
-      <c r="B1938" t="s">
-        <v>133</v>
-      </c>
-      <c r="C1938" t="s">
-        <v>176</v>
-      </c>
-      <c r="D1938" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1938">
-        <v>15</v>
-      </c>
-      <c r="F1938">
-        <v>0</v>
-      </c>
-      <c r="G1938">
-        <v>0</v>
-      </c>
-      <c r="H1938">
-        <v>0</v>
-      </c>
-      <c r="I1938">
-        <v>0</v>
-      </c>
-      <c r="J1938">
-        <v>3</v>
-      </c>
-      <c r="K1938" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1939" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1939" t="s">
-        <v>902</v>
-      </c>
-      <c r="B1939" t="s">
-        <v>134</v>
-      </c>
-      <c r="C1939" t="s">
-        <v>185</v>
-      </c>
-      <c r="D1939" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1939">
-        <v>11</v>
-      </c>
-      <c r="F1939">
-        <v>0</v>
-      </c>
-      <c r="G1939">
-        <v>0</v>
-      </c>
-      <c r="H1939">
-        <v>0</v>
-      </c>
-      <c r="I1939">
-        <v>0</v>
-      </c>
-      <c r="J1939">
-        <v>3</v>
-      </c>
-      <c r="K1939" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1940" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1940" t="s">
-        <v>903</v>
-      </c>
-      <c r="B1940" t="s">
-        <v>660</v>
-      </c>
-      <c r="C1940" t="s">
-        <v>403</v>
-      </c>
-      <c r="D1940" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1940">
-        <v>0</v>
-      </c>
-      <c r="F1940">
-        <v>0</v>
-      </c>
-      <c r="G1940">
-        <v>0</v>
-      </c>
-      <c r="H1940">
-        <v>0</v>
-      </c>
-      <c r="I1940">
-        <v>7</v>
-      </c>
-      <c r="J1940">
-        <v>2</v>
-      </c>
-      <c r="K1940" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1941" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1941" t="s">
-        <v>903</v>
-      </c>
-      <c r="B1941" t="s">
-        <v>661</v>
-      </c>
-      <c r="C1941" t="s">
-        <v>155</v>
-      </c>
-      <c r="D1941" t="s">
-        <v>72</v>
-      </c>
-      <c r="E1941">
-        <v>0</v>
-      </c>
-      <c r="F1941">
-        <v>0</v>
-      </c>
-      <c r="G1941">
-        <v>0</v>
-      </c>
-      <c r="H1941">
-        <v>0</v>
-      </c>
-      <c r="I1941">
-        <v>7</v>
-      </c>
-      <c r="J1941">
-        <v>2</v>
-      </c>
-      <c r="K1941" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1942" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1942" t="s">
-        <v>904</v>
-      </c>
-      <c r="B1942" t="s">
-        <v>126</v>
-      </c>
-      <c r="C1942" t="s">
-        <v>361</v>
-      </c>
-      <c r="D1942" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1942">
-        <v>0</v>
-      </c>
-      <c r="F1942">
-        <v>6</v>
-      </c>
-      <c r="G1942">
-        <v>0</v>
-      </c>
-      <c r="H1942">
-        <v>0</v>
-      </c>
-      <c r="I1942">
-        <v>7</v>
-      </c>
-      <c r="J1942">
-        <v>3</v>
-      </c>
-      <c r="K1942" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="1943" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A1943" t="s">
-        <v>904</v>
-      </c>
-      <c r="B1943" t="s">
-        <v>127</v>
-      </c>
-      <c r="C1943" t="s">
-        <v>357</v>
-      </c>
-      <c r="D1943" t="s">
-        <v>79</v>
-      </c>
-      <c r="E1943">
-        <v>0</v>
-      </c>
-      <c r="F1943">
-        <v>6</v>
-      </c>
-      <c r="G1943">
-        <v>0</v>
-      </c>
-      <c r="H1943">
-        <v>0</v>
-      </c>
-      <c r="I1943">
-        <v>7</v>
-      </c>
-      <c r="J1943">
-        <v>4</v>
-      </c>
-      <c r="K1943" t="s">
-        <v>891</v>
-      </c>
     </row>
     <row r="1944" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1944" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="B1944" t="s">
-        <v>128</v>
+        <v>657</v>
       </c>
       <c r="C1944" t="s">
-        <v>215</v>
+        <v>265</v>
       </c>
       <c r="D1944" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1944">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1944">
         <v>6</v>
       </c>
       <c r="G1944">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1944">
         <v>0</v>
       </c>
       <c r="I1944">
+        <v>0</v>
+      </c>
+      <c r="J1944">
         <v>7</v>
       </c>
-      <c r="J1944">
-        <v>4</v>
-      </c>
       <c r="K1944" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1945" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1945" t="s">
-        <v>904</v>
+        <v>892</v>
       </c>
       <c r="B1945" t="s">
-        <v>135</v>
+        <v>658</v>
       </c>
       <c r="C1945" t="s">
-        <v>500</v>
+        <v>220</v>
       </c>
       <c r="D1945" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1945">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1945">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1945">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1945">
         <v>0</v>
       </c>
       <c r="I1945">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J1945">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="K1945" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1946" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1946" t="s">
-        <v>905</v>
+        <v>892</v>
       </c>
       <c r="B1946" t="s">
-        <v>53</v>
+        <v>659</v>
       </c>
       <c r="C1946" t="s">
-        <v>311</v>
+        <v>155</v>
       </c>
       <c r="D1946" t="s">
         <v>72</v>
       </c>
       <c r="E1946">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F1946">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1946">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="H1946">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I1946">
         <v>0</v>
       </c>
       <c r="J1946">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="K1946" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1947" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1947" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B1947" t="s">
-        <v>52</v>
+        <v>660</v>
       </c>
       <c r="C1947" t="s">
-        <v>310</v>
+        <v>403</v>
       </c>
       <c r="D1947" t="s">
         <v>72</v>
       </c>
       <c r="E1947">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1947">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1947">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1947">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1947">
         <v>0</v>
       </c>
       <c r="J1947">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1947" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1948" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1948" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B1948" t="s">
-        <v>51</v>
+        <v>661</v>
       </c>
       <c r="C1948" t="s">
-        <v>309</v>
+        <v>155</v>
       </c>
       <c r="D1948" t="s">
         <v>72</v>
       </c>
       <c r="E1948">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1948">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1948">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1948">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1948">
         <v>0</v>
       </c>
       <c r="J1948">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1948" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1949" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1949" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="B1949" t="s">
-        <v>12</v>
+        <v>126</v>
       </c>
       <c r="C1949" t="s">
-        <v>250</v>
+        <v>361</v>
       </c>
       <c r="D1949" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1949">
         <v>15</v>
@@ -70726,21 +69729,21 @@
         <v>5</v>
       </c>
       <c r="K1949" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1950" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1950" t="s">
-        <v>905</v>
+        <v>895</v>
       </c>
       <c r="B1950" t="s">
-        <v>15</v>
+        <v>127</v>
       </c>
       <c r="C1950" t="s">
-        <v>252</v>
+        <v>357</v>
       </c>
       <c r="D1950" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1950">
         <v>15</v>
@@ -70758,24 +69761,24 @@
         <v>0</v>
       </c>
       <c r="J1950">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1950" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1951" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1951" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="B1951" t="s">
-        <v>16</v>
+        <v>128</v>
       </c>
       <c r="C1951" t="s">
-        <v>253</v>
+        <v>215</v>
       </c>
       <c r="D1951" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1951">
         <v>15</v>
@@ -70793,33 +69796,33 @@
         <v>0</v>
       </c>
       <c r="J1951">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1951" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1952" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1952" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="B1952" t="s">
-        <v>17</v>
+        <v>135</v>
       </c>
       <c r="C1952" t="s">
-        <v>254</v>
+        <v>500</v>
       </c>
       <c r="D1952" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E1952">
-        <v>24</v>
+        <v>4</v>
       </c>
       <c r="F1952">
         <v>0</v>
       </c>
       <c r="G1952">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1952">
         <v>0</v>
@@ -70828,24 +69831,24 @@
         <v>0</v>
       </c>
       <c r="J1952">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1952" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1953" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1953" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="B1953" t="s">
-        <v>205</v>
+        <v>25</v>
       </c>
       <c r="C1953" t="s">
-        <v>206</v>
+        <v>244</v>
       </c>
       <c r="D1953" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E1953">
         <v>15</v>
@@ -70854,7 +69857,7 @@
         <v>0</v>
       </c>
       <c r="G1953">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1953">
         <v>0</v>
@@ -70863,24 +69866,24 @@
         <v>0</v>
       </c>
       <c r="J1953">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1953" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1954" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1954" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="B1954" t="s">
-        <v>49</v>
+        <v>26</v>
       </c>
       <c r="C1954" t="s">
-        <v>229</v>
+        <v>159</v>
       </c>
       <c r="D1954" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E1954">
         <v>15</v>
@@ -70889,33 +69892,33 @@
         <v>0</v>
       </c>
       <c r="G1954">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1954">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1954">
         <v>0</v>
       </c>
       <c r="J1954">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1954" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1955" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1955" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="B1955" t="s">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="C1955" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D1955" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E1955">
         <v>15</v>
@@ -70924,10 +69927,10 @@
         <v>0</v>
       </c>
       <c r="G1955">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1955">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1955">
         <v>0</v>
@@ -70936,21 +69939,21 @@
         <v>4</v>
       </c>
       <c r="K1955" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1956" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1956" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="B1956" t="s">
-        <v>47</v>
+        <v>59</v>
       </c>
       <c r="C1956" t="s">
-        <v>198</v>
+        <v>256</v>
       </c>
       <c r="D1956" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E1956">
         <v>15</v>
@@ -70959,30 +69962,30 @@
         <v>0</v>
       </c>
       <c r="G1956">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1956">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1956">
         <v>0</v>
       </c>
       <c r="J1956">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1956" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1957" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1957" t="s">
-        <v>908</v>
+        <v>898</v>
       </c>
       <c r="B1957" t="s">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="C1957" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="D1957" t="s">
         <v>13</v>
@@ -70994,243 +69997,243 @@
         <v>0</v>
       </c>
       <c r="G1957">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1957">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I1957">
         <v>0</v>
       </c>
       <c r="J1957">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1957" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1958" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1958" t="s">
-        <v>909</v>
+        <v>898</v>
       </c>
       <c r="B1958" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C1958" t="s">
-        <v>256</v>
+        <v>273</v>
       </c>
       <c r="D1958" t="s">
         <v>13</v>
       </c>
       <c r="E1958">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1958">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1958">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1958">
         <v>0</v>
       </c>
       <c r="I1958">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1958">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1958" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1959" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1959" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="B1959" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C1959" t="s">
-        <v>272</v>
+        <v>290</v>
       </c>
       <c r="D1959" t="s">
         <v>13</v>
       </c>
       <c r="E1959">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1959">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1959">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1959">
         <v>0</v>
       </c>
       <c r="I1959">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1959">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1959" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1960" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1960" t="s">
-        <v>909</v>
+        <v>899</v>
       </c>
       <c r="B1960" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C1960" t="s">
-        <v>273</v>
+        <v>290</v>
       </c>
       <c r="D1960" t="s">
         <v>13</v>
       </c>
       <c r="E1960">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1960">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1960">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1960">
         <v>0</v>
       </c>
       <c r="I1960">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1960">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1960" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1961" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1961" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="B1961" t="s">
-        <v>25</v>
+        <v>66</v>
       </c>
       <c r="C1961" t="s">
-        <v>244</v>
+        <v>291</v>
       </c>
       <c r="D1961" t="s">
         <v>13</v>
       </c>
       <c r="E1961">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1961">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1961">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1961">
         <v>0</v>
       </c>
       <c r="I1961">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1961">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1961" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1962" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1962" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="B1962" t="s">
-        <v>26</v>
+        <v>67</v>
       </c>
       <c r="C1962" t="s">
-        <v>159</v>
+        <v>292</v>
       </c>
       <c r="D1962" t="s">
         <v>13</v>
       </c>
       <c r="E1962">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1962">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1962">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1962">
         <v>0</v>
       </c>
       <c r="I1962">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1962">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1962" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1963" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1963" t="s">
-        <v>910</v>
+        <v>899</v>
       </c>
       <c r="B1963" t="s">
-        <v>62</v>
+        <v>28</v>
       </c>
       <c r="C1963" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="D1963" t="s">
         <v>13</v>
       </c>
       <c r="E1963">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="F1963">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1963">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1963">
         <v>0</v>
       </c>
       <c r="I1963">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1963">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1963" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1964" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1964" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="B1964" t="s">
-        <v>591</v>
+        <v>30</v>
       </c>
       <c r="C1964" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="D1964" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="E1964">
         <v>15</v>
@@ -71251,91 +70254,91 @@
         <v>5</v>
       </c>
       <c r="K1964" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1965" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1965" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B1965" t="s">
-        <v>591</v>
+        <v>31</v>
       </c>
       <c r="C1965" t="s">
-        <v>290</v>
+        <v>244</v>
       </c>
       <c r="D1965" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="E1965">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1965">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1965">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1965">
         <v>0</v>
       </c>
       <c r="I1965">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1965">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1965" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1966" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1966" t="s">
-        <v>906</v>
+        <v>899</v>
       </c>
       <c r="B1966" t="s">
-        <v>591</v>
+        <v>33</v>
       </c>
       <c r="C1966" t="s">
-        <v>290</v>
+        <v>159</v>
       </c>
       <c r="D1966" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="E1966">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1966">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1966">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1966">
         <v>0</v>
       </c>
       <c r="I1966">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1966">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1966" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1967" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1967" t="s">
-        <v>890</v>
+        <v>899</v>
       </c>
       <c r="B1967" t="s">
-        <v>597</v>
+        <v>34</v>
       </c>
       <c r="C1967" t="s">
-        <v>410</v>
+        <v>265</v>
       </c>
       <c r="D1967" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="E1967">
         <v>15</v>
@@ -71356,56 +70359,56 @@
         <v>5</v>
       </c>
       <c r="K1967" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1968" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1968" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B1968" t="s">
-        <v>597</v>
+        <v>35</v>
       </c>
       <c r="C1968" t="s">
-        <v>410</v>
+        <v>266</v>
       </c>
       <c r="D1968" t="s">
-        <v>79</v>
+        <v>13</v>
       </c>
       <c r="E1968">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F1968">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1968">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1968">
         <v>0</v>
       </c>
       <c r="I1968">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1968">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1968" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1969" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1969" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="B1969" t="s">
-        <v>597</v>
+        <v>657</v>
       </c>
       <c r="C1969" t="s">
-        <v>410</v>
+        <v>265</v>
       </c>
       <c r="D1969" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1969">
         <v>0</v>
@@ -71426,59 +70429,59 @@
         <v>3</v>
       </c>
       <c r="K1969" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1970" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1970" t="s">
-        <v>911</v>
+        <v>900</v>
       </c>
       <c r="B1970" t="s">
-        <v>601</v>
+        <v>658</v>
       </c>
       <c r="C1970" t="s">
-        <v>275</v>
+        <v>220</v>
       </c>
       <c r="D1970" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1970">
         <v>0</v>
       </c>
       <c r="F1970">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1970">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1970">
         <v>0</v>
       </c>
       <c r="I1970">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1970">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1970" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1971" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1971" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="B1971" t="s">
-        <v>601</v>
+        <v>659</v>
       </c>
       <c r="C1971" t="s">
-        <v>275</v>
+        <v>155</v>
       </c>
       <c r="D1971" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1971">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1971">
         <v>6</v>
@@ -71490,30 +70493,30 @@
         <v>0</v>
       </c>
       <c r="I1971">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J1971">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K1971" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1972" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1972" t="s">
-        <v>906</v>
+        <v>901</v>
       </c>
       <c r="B1972" t="s">
-        <v>601</v>
+        <v>660</v>
       </c>
       <c r="C1972" t="s">
-        <v>275</v>
+        <v>403</v>
       </c>
       <c r="D1972" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1972">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1972">
         <v>6</v>
@@ -71528,138 +70531,138 @@
         <v>8</v>
       </c>
       <c r="J1972">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K1972" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1973" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1973" t="s">
-        <v>911</v>
+        <v>901</v>
       </c>
       <c r="B1973" t="s">
-        <v>611</v>
+        <v>661</v>
       </c>
       <c r="C1973" t="s">
-        <v>273</v>
+        <v>155</v>
       </c>
       <c r="D1973" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1973">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1973">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1973">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1973">
         <v>0</v>
       </c>
       <c r="I1973">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J1973">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K1973" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1974" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1974" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B1974" t="s">
-        <v>611</v>
+        <v>114</v>
       </c>
       <c r="C1974" t="s">
-        <v>273</v>
+        <v>367</v>
       </c>
       <c r="D1974" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1974">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F1974">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1974">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H1974">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I1974">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1974">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K1974" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1975" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1975" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="B1975" t="s">
-        <v>611</v>
+        <v>139</v>
       </c>
       <c r="C1975" t="s">
-        <v>273</v>
+        <v>159</v>
       </c>
       <c r="D1975" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1975">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1975">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1975">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1975">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1975">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1975">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1975" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1976" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1976" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B1976" t="s">
-        <v>619</v>
+        <v>36</v>
       </c>
       <c r="C1976" t="s">
-        <v>620</v>
+        <v>218</v>
       </c>
       <c r="D1976" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E1976">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1976">
         <v>0</v>
       </c>
       <c r="G1976">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H1976">
         <v>0</v>
@@ -71668,103 +70671,103 @@
         <v>0</v>
       </c>
       <c r="J1976">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="K1976" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1977" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1977" t="s">
-        <v>900</v>
+        <v>902</v>
       </c>
       <c r="B1977" t="s">
-        <v>619</v>
+        <v>42</v>
       </c>
       <c r="C1977" t="s">
-        <v>620</v>
+        <v>268</v>
       </c>
       <c r="D1977" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E1977">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F1977">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1977">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1977">
         <v>0</v>
       </c>
       <c r="I1977">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1977">
         <v>4</v>
       </c>
       <c r="K1977" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1978" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1978" t="s">
-        <v>912</v>
+        <v>902</v>
       </c>
       <c r="B1978" t="s">
-        <v>619</v>
+        <v>168</v>
       </c>
       <c r="C1978" t="s">
-        <v>620</v>
+        <v>169</v>
       </c>
       <c r="D1978" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1978">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F1978">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1978">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1978">
         <v>0</v>
       </c>
       <c r="I1978">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="J1978">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1978" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1979" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1979" t="s">
-        <v>913</v>
+        <v>902</v>
       </c>
       <c r="B1979" t="s">
-        <v>662</v>
+        <v>170</v>
       </c>
       <c r="C1979" t="s">
-        <v>244</v>
+        <v>171</v>
       </c>
       <c r="D1979" t="s">
         <v>79</v>
       </c>
       <c r="E1979">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F1979">
         <v>0</v>
       </c>
       <c r="G1979">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H1979">
         <v>0</v>
@@ -71773,94 +70776,94 @@
         <v>0</v>
       </c>
       <c r="J1979">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="K1979" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1980" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1980" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="B1980" t="s">
-        <v>662</v>
+        <v>138</v>
       </c>
       <c r="C1980" t="s">
-        <v>244</v>
+        <v>158</v>
       </c>
       <c r="D1980" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1980">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1980">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1980">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1980">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1980">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1980">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="K1980" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1981" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1981" t="s">
-        <v>907</v>
+        <v>903</v>
       </c>
       <c r="B1981" t="s">
-        <v>662</v>
+        <v>43</v>
       </c>
       <c r="C1981" t="s">
-        <v>244</v>
+        <v>159</v>
       </c>
       <c r="D1981" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E1981">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1981">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1981">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1981">
         <v>0</v>
       </c>
       <c r="I1981">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1981">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K1981" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1982" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1982" t="s">
-        <v>913</v>
+        <v>903</v>
       </c>
       <c r="B1982" t="s">
-        <v>663</v>
+        <v>44</v>
       </c>
       <c r="C1982" t="s">
-        <v>410</v>
+        <v>269</v>
       </c>
       <c r="D1982" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E1982">
         <v>15</v>
@@ -71878,65 +70881,65 @@
         <v>0</v>
       </c>
       <c r="J1982">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K1982" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1983" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1983" t="s">
-        <v>898</v>
+        <v>903</v>
       </c>
       <c r="B1983" t="s">
-        <v>663</v>
+        <v>45</v>
       </c>
       <c r="C1983" t="s">
-        <v>410</v>
+        <v>270</v>
       </c>
       <c r="D1983" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="E1983">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F1983">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1983">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1983">
         <v>0</v>
       </c>
       <c r="I1983">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1983">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K1983" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1984" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1984" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B1984" t="s">
-        <v>663</v>
+        <v>657</v>
       </c>
       <c r="C1984" t="s">
-        <v>410</v>
+        <v>265</v>
       </c>
       <c r="D1984" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1984">
         <v>0</v>
       </c>
       <c r="F1984">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1984">
         <v>0</v>
@@ -71945,68 +70948,68 @@
         <v>0</v>
       </c>
       <c r="I1984">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J1984">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1984" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1985" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1985" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="B1985" t="s">
-        <v>664</v>
+        <v>658</v>
       </c>
       <c r="C1985" t="s">
-        <v>324</v>
+        <v>220</v>
       </c>
       <c r="D1985" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1985">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1985">
         <v>0</v>
       </c>
       <c r="G1985">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1985">
         <v>0</v>
       </c>
       <c r="I1985">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1985">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K1985" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1986" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1986" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B1986" t="s">
-        <v>664</v>
+        <v>659</v>
       </c>
       <c r="C1986" t="s">
-        <v>324</v>
+        <v>155</v>
       </c>
       <c r="D1986" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1986">
         <v>0</v>
       </c>
       <c r="F1986">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1986">
         <v>0</v>
@@ -72018,30 +71021,30 @@
         <v>7</v>
       </c>
       <c r="J1986">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1986" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1987" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1987" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B1987" t="s">
-        <v>664</v>
+        <v>131</v>
       </c>
       <c r="C1987" t="s">
-        <v>324</v>
+        <v>176</v>
       </c>
       <c r="D1987" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1987">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1987">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1987">
         <v>0</v>
@@ -72050,36 +71053,36 @@
         <v>0</v>
       </c>
       <c r="I1987">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1987">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1987" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1988" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1988" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="B1988" t="s">
-        <v>665</v>
+        <v>132</v>
       </c>
       <c r="C1988" t="s">
-        <v>666</v>
+        <v>181</v>
       </c>
       <c r="D1988" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1988">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1988">
         <v>0</v>
       </c>
       <c r="G1988">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H1988">
         <v>0</v>
@@ -72088,30 +71091,30 @@
         <v>0</v>
       </c>
       <c r="J1988">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K1988" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1989" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1989" t="s">
-        <v>899</v>
+        <v>904</v>
       </c>
       <c r="B1989" t="s">
-        <v>665</v>
+        <v>133</v>
       </c>
       <c r="C1989" t="s">
-        <v>666</v>
+        <v>176</v>
       </c>
       <c r="D1989" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1989">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="F1989">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1989">
         <v>0</v>
@@ -72120,33 +71123,33 @@
         <v>0</v>
       </c>
       <c r="I1989">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="J1989">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K1989" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1990" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1990" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="B1990" t="s">
-        <v>665</v>
+        <v>134</v>
       </c>
       <c r="C1990" t="s">
-        <v>666</v>
+        <v>185</v>
       </c>
       <c r="D1990" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="E1990">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F1990">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1990">
         <v>0</v>
@@ -72155,68 +71158,68 @@
         <v>0</v>
       </c>
       <c r="I1990">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="J1990">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K1990" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1991" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1991" t="s">
-        <v>896</v>
+        <v>905</v>
       </c>
       <c r="B1991" t="s">
-        <v>377</v>
+        <v>660</v>
       </c>
       <c r="C1991" t="s">
-        <v>378</v>
+        <v>403</v>
       </c>
       <c r="D1991" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E1991">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1991">
         <v>0</v>
       </c>
       <c r="G1991">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1991">
         <v>0</v>
       </c>
       <c r="I1991">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1991">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K1991" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1992" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1992" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="B1992" t="s">
-        <v>377</v>
+        <v>661</v>
       </c>
       <c r="C1992" t="s">
-        <v>378</v>
+        <v>155</v>
       </c>
       <c r="D1992" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E1992">
         <v>0</v>
       </c>
       <c r="F1992">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1992">
         <v>0</v>
@@ -72228,59 +71231,59 @@
         <v>7</v>
       </c>
       <c r="J1992">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1992" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1993" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1993" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="B1993" t="s">
-        <v>379</v>
+        <v>126</v>
       </c>
       <c r="C1993" t="s">
-        <v>380</v>
+        <v>361</v>
       </c>
       <c r="D1993" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="E1993">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1993">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1993">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1993">
         <v>0</v>
       </c>
       <c r="I1993">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1993">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K1993" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1994" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1994" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="B1994" t="s">
-        <v>379</v>
+        <v>127</v>
       </c>
       <c r="C1994" t="s">
-        <v>380</v>
+        <v>357</v>
       </c>
       <c r="D1994" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="E1994">
         <v>0</v>
@@ -72298,199 +71301,199 @@
         <v>7</v>
       </c>
       <c r="J1994">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K1994" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1995" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1995" t="s">
-        <v>896</v>
+        <v>906</v>
       </c>
       <c r="B1995" t="s">
-        <v>402</v>
+        <v>128</v>
       </c>
       <c r="C1995" t="s">
-        <v>403</v>
+        <v>215</v>
       </c>
       <c r="D1995" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="E1995">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1995">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1995">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1995">
         <v>0</v>
       </c>
       <c r="I1995">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J1995">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K1995" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1996" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1996" t="s">
-        <v>914</v>
+        <v>906</v>
       </c>
       <c r="B1996" t="s">
-        <v>402</v>
+        <v>135</v>
       </c>
       <c r="C1996" t="s">
-        <v>403</v>
+        <v>500</v>
       </c>
       <c r="D1996" t="s">
-        <v>145</v>
+        <v>79</v>
       </c>
       <c r="E1996">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F1996">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1996">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1996">
         <v>0</v>
       </c>
       <c r="I1996">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J1996">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K1996" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1997" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1997" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="B1997" t="s">
-        <v>402</v>
+        <v>53</v>
       </c>
       <c r="C1997" t="s">
-        <v>403</v>
+        <v>311</v>
       </c>
       <c r="D1997" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E1997">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F1997">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G1997">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1997">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I1997">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J1997">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K1997" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1998" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1998" t="s">
-        <v>896</v>
+        <v>907</v>
       </c>
       <c r="B1998" t="s">
-        <v>404</v>
+        <v>52</v>
       </c>
       <c r="C1998" t="s">
-        <v>405</v>
+        <v>310</v>
       </c>
       <c r="D1998" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E1998">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F1998">
         <v>0</v>
       </c>
       <c r="G1998">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H1998">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1998">
         <v>0</v>
       </c>
       <c r="J1998">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K1998" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="1999" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1999" t="s">
-        <v>914</v>
+        <v>907</v>
       </c>
       <c r="B1999" t="s">
-        <v>404</v>
+        <v>51</v>
       </c>
       <c r="C1999" t="s">
-        <v>405</v>
+        <v>309</v>
       </c>
       <c r="D1999" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E1999">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F1999">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1999">
         <v>0</v>
       </c>
       <c r="H1999">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I1999">
+        <v>0</v>
+      </c>
+      <c r="J1999">
         <v>4</v>
       </c>
-      <c r="J1999">
-        <v>2</v>
-      </c>
       <c r="K1999" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2000" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2000" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="B2000" t="s">
-        <v>406</v>
+        <v>12</v>
       </c>
       <c r="C2000" t="s">
-        <v>384</v>
+        <v>250</v>
       </c>
       <c r="D2000" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2000">
         <v>15</v>
@@ -72511,21 +71514,21 @@
         <v>5</v>
       </c>
       <c r="K2000" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2001" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2001" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="B2001" t="s">
-        <v>383</v>
+        <v>15</v>
       </c>
       <c r="C2001" t="s">
-        <v>431</v>
+        <v>252</v>
       </c>
       <c r="D2001" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2001">
         <v>15</v>
@@ -72546,21 +71549,21 @@
         <v>5</v>
       </c>
       <c r="K2001" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2002" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2002" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="B2002" t="s">
-        <v>385</v>
+        <v>16</v>
       </c>
       <c r="C2002" t="s">
-        <v>386</v>
+        <v>253</v>
       </c>
       <c r="D2002" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2002">
         <v>15</v>
@@ -72581,30 +71584,30 @@
         <v>5</v>
       </c>
       <c r="K2002" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2003" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2003" t="s">
-        <v>915</v>
+        <v>907</v>
       </c>
       <c r="B2003" t="s">
-        <v>387</v>
+        <v>17</v>
       </c>
       <c r="C2003" t="s">
-        <v>386</v>
+        <v>254</v>
       </c>
       <c r="D2003" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2003">
-        <v>15</v>
+        <v>24</v>
       </c>
       <c r="F2003">
         <v>0</v>
       </c>
       <c r="G2003">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2003">
         <v>0</v>
@@ -72613,24 +71616,24 @@
         <v>0</v>
       </c>
       <c r="J2003">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2003" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2004" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2004" t="s">
-        <v>916</v>
+        <v>908</v>
       </c>
       <c r="B2004" t="s">
-        <v>389</v>
+        <v>205</v>
       </c>
       <c r="C2004" t="s">
-        <v>386</v>
+        <v>206</v>
       </c>
       <c r="D2004" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2004">
         <v>15</v>
@@ -72639,7 +71642,7 @@
         <v>0</v>
       </c>
       <c r="G2004">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2004">
         <v>0</v>
@@ -72648,24 +71651,24 @@
         <v>0</v>
       </c>
       <c r="J2004">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2004" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2005" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2005" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="B2005" t="s">
-        <v>390</v>
+        <v>49</v>
       </c>
       <c r="C2005" t="s">
-        <v>386</v>
+        <v>229</v>
       </c>
       <c r="D2005" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2005">
         <v>15</v>
@@ -72674,10 +71677,10 @@
         <v>0</v>
       </c>
       <c r="G2005">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2005">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2005">
         <v>0</v>
@@ -72686,21 +71689,21 @@
         <v>4</v>
       </c>
       <c r="K2005" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2006" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2006" t="s">
-        <v>899</v>
+        <v>909</v>
       </c>
       <c r="B2006" t="s">
-        <v>391</v>
+        <v>48</v>
       </c>
       <c r="C2006" t="s">
-        <v>386</v>
+        <v>163</v>
       </c>
       <c r="D2006" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2006">
         <v>15</v>
@@ -72709,33 +71712,33 @@
         <v>0</v>
       </c>
       <c r="G2006">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2006">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2006">
         <v>0</v>
       </c>
       <c r="J2006">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2006" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2007" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2007" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="B2007" t="s">
-        <v>413</v>
+        <v>47</v>
       </c>
       <c r="C2007" t="s">
-        <v>386</v>
+        <v>198</v>
       </c>
       <c r="D2007" t="s">
-        <v>145</v>
+        <v>72</v>
       </c>
       <c r="E2007">
         <v>15</v>
@@ -72744,33 +71747,33 @@
         <v>0</v>
       </c>
       <c r="G2007">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2007">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2007">
         <v>0</v>
       </c>
       <c r="J2007">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2007" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2008" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2008" t="s">
-        <v>917</v>
+        <v>910</v>
       </c>
       <c r="B2008" t="s">
-        <v>414</v>
+        <v>40</v>
       </c>
       <c r="C2008" t="s">
-        <v>386</v>
+        <v>277</v>
       </c>
       <c r="D2008" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="E2008">
         <v>15</v>
@@ -72779,243 +71782,243 @@
         <v>0</v>
       </c>
       <c r="G2008">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H2008">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I2008">
         <v>0</v>
       </c>
       <c r="J2008">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2008" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2009" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2009" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B2009" t="s">
-        <v>415</v>
+        <v>59</v>
       </c>
       <c r="C2009" t="s">
-        <v>210</v>
+        <v>256</v>
       </c>
       <c r="D2009" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="E2009">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2009">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2009">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2009">
         <v>0</v>
       </c>
       <c r="I2009">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2009">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2009" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2010" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2010" t="s">
-        <v>917</v>
+        <v>911</v>
       </c>
       <c r="B2010" t="s">
-        <v>416</v>
+        <v>60</v>
       </c>
       <c r="C2010" t="s">
-        <v>417</v>
+        <v>272</v>
       </c>
       <c r="D2010" t="s">
-        <v>145</v>
+        <v>13</v>
       </c>
       <c r="E2010">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F2010">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2010">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2010">
         <v>0</v>
       </c>
       <c r="I2010">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2010">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K2010" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2011" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2011" t="s">
-        <v>898</v>
+        <v>911</v>
       </c>
       <c r="B2011" t="s">
-        <v>603</v>
+        <v>61</v>
       </c>
       <c r="C2011" t="s">
-        <v>604</v>
+        <v>273</v>
       </c>
       <c r="D2011" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E2011">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2011">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2011">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2011">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2011">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2011">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2011" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2012" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2012" t="s">
-        <v>898</v>
+        <v>912</v>
       </c>
       <c r="B2012" t="s">
-        <v>605</v>
+        <v>25</v>
       </c>
       <c r="C2012" t="s">
-        <v>606</v>
+        <v>244</v>
       </c>
       <c r="D2012" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E2012">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2012">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2012">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2012">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2012">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2012">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2012" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2013" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2013" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="B2013" t="s">
-        <v>607</v>
+        <v>26</v>
       </c>
       <c r="C2013" t="s">
-        <v>608</v>
+        <v>159</v>
       </c>
       <c r="D2013" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E2013">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2013">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2013">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2013">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2013">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2013">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K2013" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2014" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2014" t="s">
-        <v>895</v>
+        <v>912</v>
       </c>
       <c r="B2014" t="s">
-        <v>612</v>
+        <v>62</v>
       </c>
       <c r="C2014" t="s">
-        <v>613</v>
+        <v>290</v>
       </c>
       <c r="D2014" t="s">
-        <v>72</v>
+        <v>13</v>
       </c>
       <c r="E2014">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2014">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2014">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2014">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2014">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2014">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="K2014" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2015" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2015" t="s">
-        <v>895</v>
+        <v>892</v>
       </c>
       <c r="B2015" t="s">
-        <v>614</v>
+        <v>591</v>
       </c>
       <c r="C2015" t="s">
-        <v>571</v>
+        <v>290</v>
       </c>
       <c r="D2015" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2015">
         <v>15</v>
@@ -73027,176 +72030,176 @@
         <v>6</v>
       </c>
       <c r="H2015">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2015">
         <v>0</v>
       </c>
       <c r="J2015">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="K2015" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2016" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2016" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="B2016" t="s">
-        <v>615</v>
+        <v>591</v>
       </c>
       <c r="C2016" t="s">
-        <v>616</v>
+        <v>290</v>
       </c>
       <c r="D2016" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2016">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2016">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2016">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2016">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2016">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2016">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2016" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2017" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2017" t="s">
-        <v>894</v>
+        <v>908</v>
       </c>
       <c r="B2017" t="s">
-        <v>621</v>
+        <v>591</v>
       </c>
       <c r="C2017" t="s">
-        <v>622</v>
+        <v>290</v>
       </c>
       <c r="D2017" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2017">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2017">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2017">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2017">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2017">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2017">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="K2017" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2018" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2018" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="B2018" t="s">
-        <v>623</v>
+        <v>597</v>
       </c>
       <c r="C2018" t="s">
-        <v>624</v>
+        <v>410</v>
       </c>
       <c r="D2018" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2018">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F2018">
         <v>0</v>
       </c>
       <c r="G2018">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2018">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I2018">
         <v>0</v>
       </c>
       <c r="J2018">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2018" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2019" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2019" t="s">
-        <v>918</v>
+        <v>900</v>
       </c>
       <c r="B2019" t="s">
-        <v>392</v>
+        <v>597</v>
       </c>
       <c r="C2019" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="D2019" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E2019">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F2019">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2019">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H2019">
         <v>0</v>
       </c>
       <c r="I2019">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2019">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="K2019" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2020" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2020" t="s">
-        <v>919</v>
+        <v>908</v>
       </c>
       <c r="B2020" t="s">
-        <v>392</v>
+        <v>597</v>
       </c>
       <c r="C2020" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="D2020" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E2020">
         <v>0</v>
       </c>
       <c r="F2020">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G2020">
         <v>0</v>
@@ -73205,36 +72208,36 @@
         <v>0</v>
       </c>
       <c r="I2020">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="J2020">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2020" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2021" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2021" t="s">
-        <v>917</v>
+        <v>913</v>
       </c>
       <c r="B2021" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="C2021" t="s">
-        <v>578</v>
+        <v>275</v>
       </c>
       <c r="D2021" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2021">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F2021">
         <v>0</v>
       </c>
       <c r="G2021">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H2021">
         <v>0</v>
@@ -73243,30 +72246,30 @@
         <v>0</v>
       </c>
       <c r="J2021">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2021" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2022" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2022" t="s">
-        <v>909</v>
+        <v>902</v>
       </c>
       <c r="B2022" t="s">
-        <v>577</v>
+        <v>601</v>
       </c>
       <c r="C2022" t="s">
-        <v>578</v>
+        <v>275</v>
       </c>
       <c r="D2022" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2022">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2022">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G2022">
         <v>0</v>
@@ -73275,65 +72278,65 @@
         <v>0</v>
       </c>
       <c r="I2022">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="J2022">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="K2022" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2023" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2023" t="s">
-        <v>920</v>
+        <v>908</v>
       </c>
       <c r="B2023" t="s">
-        <v>408</v>
+        <v>601</v>
       </c>
       <c r="C2023" t="s">
-        <v>244</v>
+        <v>275</v>
       </c>
       <c r="D2023" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2023">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2023">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2023">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2023">
         <v>0</v>
       </c>
       <c r="I2023">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2023">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2023" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2024" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2024" t="s">
-        <v>920</v>
+        <v>913</v>
       </c>
       <c r="B2024" t="s">
-        <v>409</v>
+        <v>611</v>
       </c>
       <c r="C2024" t="s">
-        <v>410</v>
+        <v>273</v>
       </c>
       <c r="D2024" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2024">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2024">
         <v>0</v>
@@ -73348,103 +72351,103 @@
         <v>0</v>
       </c>
       <c r="J2024">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K2024" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2025" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2025" t="s">
-        <v>920</v>
+        <v>902</v>
       </c>
       <c r="B2025" t="s">
-        <v>411</v>
+        <v>611</v>
       </c>
       <c r="C2025" t="s">
-        <v>239</v>
+        <v>273</v>
       </c>
       <c r="D2025" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2025">
         <v>15</v>
       </c>
       <c r="F2025">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2025">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2025">
         <v>0</v>
       </c>
       <c r="I2025">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2025">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2025" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2026" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2026" t="s">
-        <v>920</v>
+        <v>914</v>
       </c>
       <c r="B2026" t="s">
-        <v>418</v>
+        <v>611</v>
       </c>
       <c r="C2026" t="s">
-        <v>419</v>
+        <v>273</v>
       </c>
       <c r="D2026" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2026">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="F2026">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2026">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H2026">
         <v>0</v>
       </c>
       <c r="I2026">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2026">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="K2026" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2027" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2027" t="s">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="B2027" t="s">
-        <v>461</v>
+        <v>619</v>
       </c>
       <c r="C2027" t="s">
-        <v>462</v>
+        <v>620</v>
       </c>
       <c r="D2027" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2027">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2027">
         <v>0</v>
       </c>
       <c r="G2027">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H2027">
         <v>0</v>
@@ -73453,65 +72456,65 @@
         <v>0</v>
       </c>
       <c r="J2027">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K2027" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2028" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2028" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
       <c r="B2028" t="s">
-        <v>464</v>
+        <v>619</v>
       </c>
       <c r="C2028" t="s">
-        <v>300</v>
+        <v>620</v>
       </c>
       <c r="D2028" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2028">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2028">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G2028">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2028">
         <v>0</v>
       </c>
       <c r="I2028">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J2028">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2028" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2029" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2029" t="s">
-        <v>921</v>
+        <v>914</v>
       </c>
       <c r="B2029" t="s">
-        <v>464</v>
+        <v>619</v>
       </c>
       <c r="C2029" t="s">
-        <v>300</v>
+        <v>620</v>
       </c>
       <c r="D2029" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2029">
         <v>0</v>
       </c>
       <c r="F2029">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G2029">
         <v>0</v>
@@ -73520,27 +72523,27 @@
         <v>0</v>
       </c>
       <c r="I2029">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J2029">
         <v>3</v>
       </c>
       <c r="K2029" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2030" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2030" t="s">
-        <v>901</v>
+        <v>915</v>
       </c>
       <c r="B2030" t="s">
-        <v>465</v>
+        <v>662</v>
       </c>
       <c r="C2030" t="s">
-        <v>466</v>
+        <v>244</v>
       </c>
       <c r="D2030" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2030">
         <v>15</v>
@@ -73558,24 +72561,24 @@
         <v>0</v>
       </c>
       <c r="J2030">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K2030" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2031" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2031" t="s">
-        <v>922</v>
+        <v>900</v>
       </c>
       <c r="B2031" t="s">
-        <v>465</v>
+        <v>662</v>
       </c>
       <c r="C2031" t="s">
-        <v>466</v>
+        <v>244</v>
       </c>
       <c r="D2031" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2031">
         <v>0</v>
@@ -73596,56 +72599,56 @@
         <v>3</v>
       </c>
       <c r="K2031" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2032" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2032" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="B2032" t="s">
-        <v>477</v>
+        <v>662</v>
       </c>
       <c r="C2032" t="s">
-        <v>478</v>
+        <v>244</v>
       </c>
       <c r="D2032" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2032">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2032">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2032">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2032">
         <v>0</v>
       </c>
       <c r="I2032">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2032">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2032" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2033" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2033" t="s">
-        <v>922</v>
+        <v>915</v>
       </c>
       <c r="B2033" t="s">
-        <v>479</v>
+        <v>663</v>
       </c>
       <c r="C2033" t="s">
-        <v>466</v>
+        <v>410</v>
       </c>
       <c r="D2033" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2033">
         <v>15</v>
@@ -73663,94 +72666,94 @@
         <v>0</v>
       </c>
       <c r="J2033">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2033" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2034" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2034" t="s">
-        <v>922</v>
+        <v>900</v>
       </c>
       <c r="B2034" t="s">
-        <v>480</v>
+        <v>663</v>
       </c>
       <c r="C2034" t="s">
-        <v>440</v>
+        <v>410</v>
       </c>
       <c r="D2034" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2034">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2034">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2034">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2034">
         <v>0</v>
       </c>
       <c r="I2034">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2034">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2034" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2035" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2035" t="s">
-        <v>922</v>
+        <v>909</v>
       </c>
       <c r="B2035" t="s">
-        <v>481</v>
+        <v>663</v>
       </c>
       <c r="C2035" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="D2035" t="s">
-        <v>463</v>
+        <v>79</v>
       </c>
       <c r="E2035">
+        <v>0</v>
+      </c>
+      <c r="F2035">
+        <v>6</v>
+      </c>
+      <c r="G2035">
+        <v>0</v>
+      </c>
+      <c r="H2035">
+        <v>0</v>
+      </c>
+      <c r="I2035">
         <v>8</v>
       </c>
-      <c r="F2035">
-        <v>0</v>
-      </c>
-      <c r="G2035">
-        <v>3</v>
-      </c>
-      <c r="H2035">
-        <v>0</v>
-      </c>
-      <c r="I2035">
-        <v>0</v>
-      </c>
       <c r="J2035">
         <v>3</v>
       </c>
       <c r="K2035" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2036" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2036" t="s">
-        <v>923</v>
+        <v>915</v>
       </c>
       <c r="B2036" t="s">
-        <v>443</v>
+        <v>664</v>
       </c>
       <c r="C2036" t="s">
-        <v>198</v>
+        <v>324</v>
       </c>
       <c r="D2036" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E2036">
         <v>15</v>
@@ -73759,7 +72762,7 @@
         <v>0</v>
       </c>
       <c r="G2036">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2036">
         <v>0</v>
@@ -73768,30 +72771,30 @@
         <v>0</v>
       </c>
       <c r="J2036">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2036" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2037" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2037" t="s">
-        <v>923</v>
+        <v>901</v>
       </c>
       <c r="B2037" t="s">
-        <v>434</v>
+        <v>664</v>
       </c>
       <c r="C2037" t="s">
-        <v>435</v>
+        <v>324</v>
       </c>
       <c r="D2037" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E2037">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2037">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2037">
         <v>0</v>
@@ -73800,33 +72803,33 @@
         <v>0</v>
       </c>
       <c r="I2037">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2037">
         <v>3</v>
       </c>
       <c r="K2037" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2038" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2038" t="s">
-        <v>914</v>
+        <v>909</v>
       </c>
       <c r="B2038" t="s">
-        <v>436</v>
+        <v>664</v>
       </c>
       <c r="C2038" t="s">
-        <v>275</v>
+        <v>324</v>
       </c>
       <c r="D2038" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E2038">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2038">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2038">
         <v>0</v>
@@ -73835,36 +72838,36 @@
         <v>0</v>
       </c>
       <c r="I2038">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2038">
         <v>3</v>
       </c>
       <c r="K2038" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2039" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2039" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B2039" t="s">
-        <v>790</v>
+        <v>665</v>
       </c>
       <c r="C2039" t="s">
-        <v>384</v>
+        <v>666</v>
       </c>
       <c r="D2039" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2039">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2039">
         <v>0</v>
       </c>
       <c r="G2039">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H2039">
         <v>0</v>
@@ -73873,30 +72876,30 @@
         <v>0</v>
       </c>
       <c r="J2039">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K2039" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2040" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2040" t="s">
-        <v>923</v>
+        <v>901</v>
       </c>
       <c r="B2040" t="s">
-        <v>373</v>
+        <v>665</v>
       </c>
       <c r="C2040" t="s">
-        <v>374</v>
+        <v>666</v>
       </c>
       <c r="D2040" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2040">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F2040">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G2040">
         <v>0</v>
@@ -73905,33 +72908,33 @@
         <v>0</v>
       </c>
       <c r="I2040">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J2040">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K2040" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2041" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2041" t="s">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="B2041" t="s">
-        <v>394</v>
+        <v>665</v>
       </c>
       <c r="C2041" t="s">
-        <v>395</v>
+        <v>666</v>
       </c>
       <c r="D2041" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="E2041">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2041">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2041">
         <v>0</v>
@@ -73940,27 +72943,27 @@
         <v>0</v>
       </c>
       <c r="I2041">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="J2041">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2041" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2042" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2042" t="s">
-        <v>921</v>
+        <v>898</v>
       </c>
       <c r="B2042" t="s">
-        <v>396</v>
+        <v>377</v>
       </c>
       <c r="C2042" t="s">
-        <v>299</v>
+        <v>378</v>
       </c>
       <c r="D2042" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E2042">
         <v>15</v>
@@ -73978,100 +72981,100 @@
         <v>0</v>
       </c>
       <c r="J2042">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K2042" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2043" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2043" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B2043" t="s">
-        <v>397</v>
+        <v>377</v>
       </c>
       <c r="C2043" t="s">
-        <v>229</v>
+        <v>378</v>
       </c>
       <c r="D2043" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E2043">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2043">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2043">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2043">
         <v>0</v>
       </c>
       <c r="I2043">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2043">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K2043" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2044" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2044" t="s">
-        <v>921</v>
+        <v>898</v>
       </c>
       <c r="B2044" t="s">
-        <v>398</v>
+        <v>379</v>
       </c>
       <c r="C2044" t="s">
-        <v>399</v>
+        <v>380</v>
       </c>
       <c r="D2044" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E2044">
+        <v>15</v>
+      </c>
+      <c r="F2044">
+        <v>0</v>
+      </c>
+      <c r="G2044">
+        <v>6</v>
+      </c>
+      <c r="H2044">
+        <v>0</v>
+      </c>
+      <c r="I2044">
+        <v>0</v>
+      </c>
+      <c r="J2044">
         <v>5</v>
       </c>
-      <c r="F2044">
-        <v>0</v>
-      </c>
-      <c r="G2044">
-        <v>2</v>
-      </c>
-      <c r="H2044">
-        <v>0</v>
-      </c>
-      <c r="I2044">
-        <v>0</v>
-      </c>
-      <c r="J2044">
-        <v>1</v>
-      </c>
       <c r="K2044" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2045" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2045" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="B2045" t="s">
-        <v>534</v>
+        <v>379</v>
       </c>
       <c r="C2045" t="s">
-        <v>535</v>
+        <v>380</v>
       </c>
       <c r="D2045" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="E2045">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2045">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2045">
         <v>0</v>
@@ -74080,27 +73083,27 @@
         <v>0</v>
       </c>
       <c r="I2045">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2045">
         <v>3</v>
       </c>
       <c r="K2045" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2046" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2046" t="s">
-        <v>910</v>
+        <v>898</v>
       </c>
       <c r="B2046" t="s">
-        <v>532</v>
+        <v>402</v>
       </c>
       <c r="C2046" t="s">
-        <v>533</v>
+        <v>403</v>
       </c>
       <c r="D2046" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="E2046">
         <v>15</v>
@@ -74109,7 +73112,7 @@
         <v>0</v>
       </c>
       <c r="G2046">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2046">
         <v>0</v>
@@ -74118,24 +73121,24 @@
         <v>0</v>
       </c>
       <c r="J2046">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2046" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2047" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2047" t="s">
-        <v>910</v>
+        <v>916</v>
       </c>
       <c r="B2047" t="s">
-        <v>528</v>
+        <v>402</v>
       </c>
       <c r="C2047" t="s">
-        <v>529</v>
+        <v>403</v>
       </c>
       <c r="D2047" t="s">
-        <v>79</v>
+        <v>145</v>
       </c>
       <c r="E2047">
         <v>15</v>
@@ -74144,7 +73147,7 @@
         <v>0</v>
       </c>
       <c r="G2047">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2047">
         <v>0</v>
@@ -74153,100 +73156,100 @@
         <v>0</v>
       </c>
       <c r="J2047">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2047" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2048" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2048" t="s">
-        <v>924</v>
+        <v>916</v>
       </c>
       <c r="B2048" t="s">
-        <v>39</v>
+        <v>402</v>
       </c>
       <c r="C2048" t="s">
-        <v>276</v>
+        <v>403</v>
       </c>
       <c r="D2048" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E2048">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F2048">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G2048">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H2048">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2048">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J2048">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K2048" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2049" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2049" t="s">
-        <v>924</v>
+        <v>898</v>
       </c>
       <c r="B2049" t="s">
-        <v>38</v>
+        <v>404</v>
       </c>
       <c r="C2049" t="s">
-        <v>198</v>
+        <v>405</v>
       </c>
       <c r="D2049" t="s">
-        <v>72</v>
+        <v>145</v>
       </c>
       <c r="E2049">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F2049">
         <v>0</v>
       </c>
       <c r="G2049">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H2049">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I2049">
         <v>0</v>
       </c>
       <c r="J2049">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="K2049" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2050" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2050" t="s">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="B2050" t="s">
-        <v>27</v>
+        <v>404</v>
       </c>
       <c r="C2050" t="s">
-        <v>159</v>
+        <v>405</v>
       </c>
       <c r="D2050" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E2050">
         <v>0</v>
       </c>
       <c r="F2050">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G2050">
         <v>0</v>
@@ -74255,188 +73258,2743 @@
         <v>0</v>
       </c>
       <c r="I2050">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="J2050">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K2050" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2051" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2051" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B2051" t="s">
-        <v>28</v>
+        <v>406</v>
       </c>
       <c r="C2051" t="s">
-        <v>159</v>
+        <v>384</v>
       </c>
       <c r="D2051" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E2051">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2051">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2051">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2051">
         <v>0</v>
       </c>
       <c r="I2051">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2051">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2051" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2052" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2052" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B2052" t="s">
-        <v>30</v>
+        <v>383</v>
       </c>
       <c r="C2052" t="s">
-        <v>244</v>
+        <v>431</v>
       </c>
       <c r="D2052" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E2052">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2052">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2052">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2052">
         <v>0</v>
       </c>
       <c r="I2052">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2052">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K2052" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2053" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2053" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B2053" t="s">
-        <v>65</v>
+        <v>385</v>
       </c>
       <c r="C2053" t="s">
-        <v>290</v>
+        <v>386</v>
       </c>
       <c r="D2053" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E2053">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2053">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2053">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2053">
         <v>0</v>
       </c>
       <c r="I2053">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2053">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2053" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2054" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2054" t="s">
-        <v>921</v>
+        <v>917</v>
       </c>
       <c r="B2054" t="s">
-        <v>66</v>
+        <v>387</v>
       </c>
       <c r="C2054" t="s">
-        <v>291</v>
+        <v>386</v>
       </c>
       <c r="D2054" t="s">
-        <v>13</v>
+        <v>145</v>
       </c>
       <c r="E2054">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F2054">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="G2054">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2054">
         <v>0</v>
       </c>
       <c r="I2054">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="J2054">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K2054" t="s">
-        <v>891</v>
+        <v>893</v>
       </c>
     </row>
     <row r="2055" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2055" t="s">
+        <v>918</v>
+      </c>
+      <c r="B2055" t="s">
+        <v>389</v>
+      </c>
+      <c r="C2055" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2055" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2055">
+        <v>15</v>
+      </c>
+      <c r="F2055">
+        <v>0</v>
+      </c>
+      <c r="G2055">
+        <v>6</v>
+      </c>
+      <c r="H2055">
+        <v>0</v>
+      </c>
+      <c r="I2055">
+        <v>0</v>
+      </c>
+      <c r="J2055">
+        <v>5</v>
+      </c>
+      <c r="K2055" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2056" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2056" t="s">
+        <v>901</v>
+      </c>
+      <c r="B2056" t="s">
+        <v>390</v>
+      </c>
+      <c r="C2056" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2056" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2056">
+        <v>15</v>
+      </c>
+      <c r="F2056">
+        <v>0</v>
+      </c>
+      <c r="G2056">
+        <v>6</v>
+      </c>
+      <c r="H2056">
+        <v>0</v>
+      </c>
+      <c r="I2056">
+        <v>0</v>
+      </c>
+      <c r="J2056">
+        <v>4</v>
+      </c>
+      <c r="K2056" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2057" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2057" t="s">
+        <v>901</v>
+      </c>
+      <c r="B2057" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2057" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2057" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2057">
+        <v>15</v>
+      </c>
+      <c r="F2057">
+        <v>0</v>
+      </c>
+      <c r="G2057">
+        <v>6</v>
+      </c>
+      <c r="H2057">
+        <v>0</v>
+      </c>
+      <c r="I2057">
+        <v>0</v>
+      </c>
+      <c r="J2057">
+        <v>5</v>
+      </c>
+      <c r="K2057" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2058" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2058" t="s">
+        <v>919</v>
+      </c>
+      <c r="B2058" t="s">
+        <v>413</v>
+      </c>
+      <c r="C2058" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2058" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2058">
+        <v>15</v>
+      </c>
+      <c r="F2058">
+        <v>0</v>
+      </c>
+      <c r="G2058">
+        <v>6</v>
+      </c>
+      <c r="H2058">
+        <v>0</v>
+      </c>
+      <c r="I2058">
+        <v>0</v>
+      </c>
+      <c r="J2058">
+        <v>5</v>
+      </c>
+      <c r="K2058" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2059" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2059" t="s">
+        <v>919</v>
+      </c>
+      <c r="B2059" t="s">
+        <v>414</v>
+      </c>
+      <c r="C2059" t="s">
+        <v>386</v>
+      </c>
+      <c r="D2059" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2059">
+        <v>15</v>
+      </c>
+      <c r="F2059">
+        <v>0</v>
+      </c>
+      <c r="G2059">
+        <v>5</v>
+      </c>
+      <c r="H2059">
+        <v>0</v>
+      </c>
+      <c r="I2059">
+        <v>0</v>
+      </c>
+      <c r="J2059">
+        <v>5</v>
+      </c>
+      <c r="K2059" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2060" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2060" t="s">
+        <v>919</v>
+      </c>
+      <c r="B2060" t="s">
+        <v>415</v>
+      </c>
+      <c r="C2060" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2060" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2060">
+        <v>15</v>
+      </c>
+      <c r="F2060">
+        <v>0</v>
+      </c>
+      <c r="G2060">
+        <v>6</v>
+      </c>
+      <c r="H2060">
+        <v>0</v>
+      </c>
+      <c r="I2060">
+        <v>0</v>
+      </c>
+      <c r="J2060">
+        <v>4</v>
+      </c>
+      <c r="K2060" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2061" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2061" t="s">
+        <v>919</v>
+      </c>
+      <c r="B2061" t="s">
+        <v>416</v>
+      </c>
+      <c r="C2061" t="s">
+        <v>417</v>
+      </c>
+      <c r="D2061" t="s">
+        <v>145</v>
+      </c>
+      <c r="E2061">
+        <v>3</v>
+      </c>
+      <c r="F2061">
+        <v>0</v>
+      </c>
+      <c r="G2061">
+        <v>1</v>
+      </c>
+      <c r="H2061">
+        <v>0</v>
+      </c>
+      <c r="I2061">
+        <v>0</v>
+      </c>
+      <c r="J2061">
+        <v>1</v>
+      </c>
+      <c r="K2061" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2062" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2062" t="s">
+        <v>900</v>
+      </c>
+      <c r="B2062" t="s">
+        <v>603</v>
+      </c>
+      <c r="C2062" t="s">
+        <v>604</v>
+      </c>
+      <c r="D2062" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2062">
+        <v>15</v>
+      </c>
+      <c r="F2062">
+        <v>0</v>
+      </c>
+      <c r="G2062">
+        <v>6</v>
+      </c>
+      <c r="H2062">
+        <v>3</v>
+      </c>
+      <c r="I2062">
+        <v>0</v>
+      </c>
+      <c r="J2062">
+        <v>5</v>
+      </c>
+      <c r="K2062" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2063" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2063" t="s">
+        <v>900</v>
+      </c>
+      <c r="B2063" t="s">
+        <v>605</v>
+      </c>
+      <c r="C2063" t="s">
+        <v>606</v>
+      </c>
+      <c r="D2063" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2063">
+        <v>15</v>
+      </c>
+      <c r="F2063">
+        <v>0</v>
+      </c>
+      <c r="G2063">
+        <v>6</v>
+      </c>
+      <c r="H2063">
+        <v>3</v>
+      </c>
+      <c r="I2063">
+        <v>0</v>
+      </c>
+      <c r="J2063">
+        <v>5</v>
+      </c>
+      <c r="K2063" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2064" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2064" t="s">
+        <v>897</v>
+      </c>
+      <c r="B2064" t="s">
+        <v>607</v>
+      </c>
+      <c r="C2064" t="s">
+        <v>608</v>
+      </c>
+      <c r="D2064" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2064">
+        <v>15</v>
+      </c>
+      <c r="F2064">
+        <v>0</v>
+      </c>
+      <c r="G2064">
+        <v>6</v>
+      </c>
+      <c r="H2064">
+        <v>3</v>
+      </c>
+      <c r="I2064">
+        <v>0</v>
+      </c>
+      <c r="J2064">
+        <v>7</v>
+      </c>
+      <c r="K2064" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2065" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2065" t="s">
+        <v>897</v>
+      </c>
+      <c r="B2065" t="s">
+        <v>612</v>
+      </c>
+      <c r="C2065" t="s">
+        <v>613</v>
+      </c>
+      <c r="D2065" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2065">
+        <v>15</v>
+      </c>
+      <c r="F2065">
+        <v>0</v>
+      </c>
+      <c r="G2065">
+        <v>6</v>
+      </c>
+      <c r="H2065">
+        <v>3</v>
+      </c>
+      <c r="I2065">
+        <v>0</v>
+      </c>
+      <c r="J2065">
+        <v>7</v>
+      </c>
+      <c r="K2065" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2066" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2066" t="s">
+        <v>897</v>
+      </c>
+      <c r="B2066" t="s">
+        <v>614</v>
+      </c>
+      <c r="C2066" t="s">
+        <v>571</v>
+      </c>
+      <c r="D2066" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2066">
+        <v>15</v>
+      </c>
+      <c r="F2066">
+        <v>0</v>
+      </c>
+      <c r="G2066">
+        <v>6</v>
+      </c>
+      <c r="H2066">
+        <v>3</v>
+      </c>
+      <c r="I2066">
+        <v>0</v>
+      </c>
+      <c r="J2066">
+        <v>6</v>
+      </c>
+      <c r="K2066" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2067" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2067" t="s">
+        <v>896</v>
+      </c>
+      <c r="B2067" t="s">
+        <v>615</v>
+      </c>
+      <c r="C2067" t="s">
+        <v>616</v>
+      </c>
+      <c r="D2067" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2067">
+        <v>15</v>
+      </c>
+      <c r="F2067">
+        <v>0</v>
+      </c>
+      <c r="G2067">
+        <v>6</v>
+      </c>
+      <c r="H2067">
+        <v>3</v>
+      </c>
+      <c r="I2067">
+        <v>0</v>
+      </c>
+      <c r="J2067">
+        <v>6</v>
+      </c>
+      <c r="K2067" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2068" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2068" t="s">
+        <v>896</v>
+      </c>
+      <c r="B2068" t="s">
+        <v>621</v>
+      </c>
+      <c r="C2068" t="s">
+        <v>622</v>
+      </c>
+      <c r="D2068" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2068">
+        <v>15</v>
+      </c>
+      <c r="F2068">
+        <v>0</v>
+      </c>
+      <c r="G2068">
+        <v>6</v>
+      </c>
+      <c r="H2068">
+        <v>3</v>
+      </c>
+      <c r="I2068">
+        <v>0</v>
+      </c>
+      <c r="J2068">
+        <v>6</v>
+      </c>
+      <c r="K2068" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2069" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2069" t="s">
+        <v>896</v>
+      </c>
+      <c r="B2069" t="s">
+        <v>623</v>
+      </c>
+      <c r="C2069" t="s">
+        <v>624</v>
+      </c>
+      <c r="D2069" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2069">
+        <v>8</v>
+      </c>
+      <c r="F2069">
+        <v>0</v>
+      </c>
+      <c r="G2069">
+        <v>4</v>
+      </c>
+      <c r="H2069">
+        <v>2</v>
+      </c>
+      <c r="I2069">
+        <v>0</v>
+      </c>
+      <c r="J2069">
+        <v>3</v>
+      </c>
+      <c r="K2069" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2070" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2070" t="s">
+        <v>920</v>
+      </c>
+      <c r="B2070" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2070" t="s">
+        <v>393</v>
+      </c>
+      <c r="D2070" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2070">
+        <v>22</v>
+      </c>
+      <c r="F2070">
+        <v>0</v>
+      </c>
+      <c r="G2070">
+        <v>9</v>
+      </c>
+      <c r="H2070">
+        <v>0</v>
+      </c>
+      <c r="I2070">
+        <v>0</v>
+      </c>
+      <c r="J2070">
+        <v>10</v>
+      </c>
+      <c r="K2070" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2071" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2071" t="s">
         <v>921</v>
       </c>
-      <c r="B2055" t="s">
+      <c r="B2071" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2071" t="s">
+        <v>393</v>
+      </c>
+      <c r="D2071" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2071">
+        <v>0</v>
+      </c>
+      <c r="F2071">
+        <v>9</v>
+      </c>
+      <c r="G2071">
+        <v>0</v>
+      </c>
+      <c r="H2071">
+        <v>0</v>
+      </c>
+      <c r="I2071">
+        <v>11</v>
+      </c>
+      <c r="J2071">
+        <v>5</v>
+      </c>
+      <c r="K2071" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2072" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2072" t="s">
+        <v>919</v>
+      </c>
+      <c r="B2072" t="s">
+        <v>577</v>
+      </c>
+      <c r="C2072" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2072" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2072">
+        <v>9</v>
+      </c>
+      <c r="F2072">
+        <v>0</v>
+      </c>
+      <c r="G2072">
+        <v>4</v>
+      </c>
+      <c r="H2072">
+        <v>0</v>
+      </c>
+      <c r="I2072">
+        <v>0</v>
+      </c>
+      <c r="J2072">
+        <v>3</v>
+      </c>
+      <c r="K2072" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2073" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2073" t="s">
+        <v>911</v>
+      </c>
+      <c r="B2073" t="s">
+        <v>577</v>
+      </c>
+      <c r="C2073" t="s">
+        <v>578</v>
+      </c>
+      <c r="D2073" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2073">
+        <v>0</v>
+      </c>
+      <c r="F2073">
+        <v>4</v>
+      </c>
+      <c r="G2073">
+        <v>0</v>
+      </c>
+      <c r="H2073">
+        <v>0</v>
+      </c>
+      <c r="I2073">
+        <v>4</v>
+      </c>
+      <c r="J2073">
+        <v>2</v>
+      </c>
+      <c r="K2073" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2074" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2074" t="s">
+        <v>922</v>
+      </c>
+      <c r="B2074" t="s">
+        <v>408</v>
+      </c>
+      <c r="C2074" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2074" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2074">
+        <v>15</v>
+      </c>
+      <c r="F2074">
+        <v>0</v>
+      </c>
+      <c r="G2074">
+        <v>6</v>
+      </c>
+      <c r="H2074">
+        <v>0</v>
+      </c>
+      <c r="I2074">
+        <v>0</v>
+      </c>
+      <c r="J2074">
+        <v>5</v>
+      </c>
+      <c r="K2074" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2075" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2075" t="s">
+        <v>922</v>
+      </c>
+      <c r="B2075" t="s">
+        <v>409</v>
+      </c>
+      <c r="C2075" t="s">
+        <v>410</v>
+      </c>
+      <c r="D2075" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2075">
+        <v>15</v>
+      </c>
+      <c r="F2075">
+        <v>0</v>
+      </c>
+      <c r="G2075">
+        <v>6</v>
+      </c>
+      <c r="H2075">
+        <v>0</v>
+      </c>
+      <c r="I2075">
+        <v>0</v>
+      </c>
+      <c r="J2075">
+        <v>5</v>
+      </c>
+      <c r="K2075" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2076" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2076" t="s">
+        <v>922</v>
+      </c>
+      <c r="B2076" t="s">
+        <v>411</v>
+      </c>
+      <c r="C2076" t="s">
+        <v>239</v>
+      </c>
+      <c r="D2076" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2076">
+        <v>15</v>
+      </c>
+      <c r="F2076">
+        <v>0</v>
+      </c>
+      <c r="G2076">
+        <v>6</v>
+      </c>
+      <c r="H2076">
+        <v>0</v>
+      </c>
+      <c r="I2076">
+        <v>0</v>
+      </c>
+      <c r="J2076">
+        <v>5</v>
+      </c>
+      <c r="K2076" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2077" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2077" t="s">
+        <v>922</v>
+      </c>
+      <c r="B2077" t="s">
+        <v>418</v>
+      </c>
+      <c r="C2077" t="s">
+        <v>419</v>
+      </c>
+      <c r="D2077" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2077">
+        <v>7</v>
+      </c>
+      <c r="F2077">
+        <v>0</v>
+      </c>
+      <c r="G2077">
+        <v>3</v>
+      </c>
+      <c r="H2077">
+        <v>0</v>
+      </c>
+      <c r="I2077">
+        <v>0</v>
+      </c>
+      <c r="J2077">
+        <v>2</v>
+      </c>
+      <c r="K2077" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2078" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2078" t="s">
+        <v>903</v>
+      </c>
+      <c r="B2078" t="s">
+        <v>461</v>
+      </c>
+      <c r="C2078" t="s">
+        <v>462</v>
+      </c>
+      <c r="D2078" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2078">
+        <v>15</v>
+      </c>
+      <c r="F2078">
+        <v>0</v>
+      </c>
+      <c r="G2078">
+        <v>6</v>
+      </c>
+      <c r="H2078">
+        <v>0</v>
+      </c>
+      <c r="I2078">
+        <v>0</v>
+      </c>
+      <c r="J2078">
+        <v>5</v>
+      </c>
+      <c r="K2078" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2079" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2079" t="s">
+        <v>903</v>
+      </c>
+      <c r="B2079" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2079" t="s">
+        <v>300</v>
+      </c>
+      <c r="D2079" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2079">
+        <v>15</v>
+      </c>
+      <c r="F2079">
+        <v>0</v>
+      </c>
+      <c r="G2079">
+        <v>6</v>
+      </c>
+      <c r="H2079">
+        <v>0</v>
+      </c>
+      <c r="I2079">
+        <v>0</v>
+      </c>
+      <c r="J2079">
+        <v>5</v>
+      </c>
+      <c r="K2079" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2080" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2080" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2080" t="s">
+        <v>464</v>
+      </c>
+      <c r="C2080" t="s">
+        <v>300</v>
+      </c>
+      <c r="D2080" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2080">
+        <v>0</v>
+      </c>
+      <c r="F2080">
+        <v>6</v>
+      </c>
+      <c r="G2080">
+        <v>0</v>
+      </c>
+      <c r="H2080">
+        <v>0</v>
+      </c>
+      <c r="I2080">
+        <v>7</v>
+      </c>
+      <c r="J2080">
+        <v>3</v>
+      </c>
+      <c r="K2080" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2081" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2081" t="s">
+        <v>903</v>
+      </c>
+      <c r="B2081" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2081" t="s">
+        <v>466</v>
+      </c>
+      <c r="D2081" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2081">
+        <v>15</v>
+      </c>
+      <c r="F2081">
+        <v>0</v>
+      </c>
+      <c r="G2081">
+        <v>6</v>
+      </c>
+      <c r="H2081">
+        <v>0</v>
+      </c>
+      <c r="I2081">
+        <v>0</v>
+      </c>
+      <c r="J2081">
+        <v>5</v>
+      </c>
+      <c r="K2081" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2082" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2082" t="s">
+        <v>924</v>
+      </c>
+      <c r="B2082" t="s">
+        <v>465</v>
+      </c>
+      <c r="C2082" t="s">
+        <v>466</v>
+      </c>
+      <c r="D2082" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2082">
+        <v>0</v>
+      </c>
+      <c r="F2082">
+        <v>6</v>
+      </c>
+      <c r="G2082">
+        <v>0</v>
+      </c>
+      <c r="H2082">
+        <v>0</v>
+      </c>
+      <c r="I2082">
+        <v>7</v>
+      </c>
+      <c r="J2082">
+        <v>3</v>
+      </c>
+      <c r="K2082" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2083" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2083" t="s">
+        <v>924</v>
+      </c>
+      <c r="B2083" t="s">
+        <v>477</v>
+      </c>
+      <c r="C2083" t="s">
+        <v>478</v>
+      </c>
+      <c r="D2083" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2083">
+        <v>15</v>
+      </c>
+      <c r="F2083">
+        <v>0</v>
+      </c>
+      <c r="G2083">
+        <v>6</v>
+      </c>
+      <c r="H2083">
+        <v>0</v>
+      </c>
+      <c r="I2083">
+        <v>0</v>
+      </c>
+      <c r="J2083">
+        <v>5</v>
+      </c>
+      <c r="K2083" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2084" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2084" t="s">
+        <v>924</v>
+      </c>
+      <c r="B2084" t="s">
+        <v>479</v>
+      </c>
+      <c r="C2084" t="s">
+        <v>466</v>
+      </c>
+      <c r="D2084" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2084">
+        <v>15</v>
+      </c>
+      <c r="F2084">
+        <v>0</v>
+      </c>
+      <c r="G2084">
+        <v>6</v>
+      </c>
+      <c r="H2084">
+        <v>0</v>
+      </c>
+      <c r="I2084">
+        <v>0</v>
+      </c>
+      <c r="J2084">
+        <v>5</v>
+      </c>
+      <c r="K2084" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2085" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2085" t="s">
+        <v>924</v>
+      </c>
+      <c r="B2085" t="s">
+        <v>480</v>
+      </c>
+      <c r="C2085" t="s">
+        <v>440</v>
+      </c>
+      <c r="D2085" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2085">
+        <v>15</v>
+      </c>
+      <c r="F2085">
+        <v>0</v>
+      </c>
+      <c r="G2085">
+        <v>6</v>
+      </c>
+      <c r="H2085">
+        <v>0</v>
+      </c>
+      <c r="I2085">
+        <v>0</v>
+      </c>
+      <c r="J2085">
+        <v>5</v>
+      </c>
+      <c r="K2085" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2086" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2086" t="s">
+        <v>924</v>
+      </c>
+      <c r="B2086" t="s">
+        <v>481</v>
+      </c>
+      <c r="C2086" t="s">
+        <v>482</v>
+      </c>
+      <c r="D2086" t="s">
+        <v>463</v>
+      </c>
+      <c r="E2086">
+        <v>8</v>
+      </c>
+      <c r="F2086">
+        <v>0</v>
+      </c>
+      <c r="G2086">
+        <v>3</v>
+      </c>
+      <c r="H2086">
+        <v>0</v>
+      </c>
+      <c r="I2086">
+        <v>0</v>
+      </c>
+      <c r="J2086">
+        <v>3</v>
+      </c>
+      <c r="K2086" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2087" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2087" t="s">
+        <v>925</v>
+      </c>
+      <c r="B2087" t="s">
+        <v>443</v>
+      </c>
+      <c r="C2087" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2087" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2087">
+        <v>15</v>
+      </c>
+      <c r="F2087">
+        <v>0</v>
+      </c>
+      <c r="G2087">
+        <v>0</v>
+      </c>
+      <c r="H2087">
+        <v>0</v>
+      </c>
+      <c r="I2087">
+        <v>0</v>
+      </c>
+      <c r="J2087">
+        <v>3</v>
+      </c>
+      <c r="K2087" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2088" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2088" t="s">
+        <v>925</v>
+      </c>
+      <c r="B2088" t="s">
+        <v>434</v>
+      </c>
+      <c r="C2088" t="s">
+        <v>435</v>
+      </c>
+      <c r="D2088" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2088">
+        <v>15</v>
+      </c>
+      <c r="F2088">
+        <v>0</v>
+      </c>
+      <c r="G2088">
+        <v>0</v>
+      </c>
+      <c r="H2088">
+        <v>0</v>
+      </c>
+      <c r="I2088">
+        <v>0</v>
+      </c>
+      <c r="J2088">
+        <v>3</v>
+      </c>
+      <c r="K2088" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2089" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2089" t="s">
+        <v>916</v>
+      </c>
+      <c r="B2089" t="s">
+        <v>436</v>
+      </c>
+      <c r="C2089" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2089" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2089">
+        <v>15</v>
+      </c>
+      <c r="F2089">
+        <v>0</v>
+      </c>
+      <c r="G2089">
+        <v>0</v>
+      </c>
+      <c r="H2089">
+        <v>0</v>
+      </c>
+      <c r="I2089">
+        <v>0</v>
+      </c>
+      <c r="J2089">
+        <v>3</v>
+      </c>
+      <c r="K2089" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2090" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2090" t="s">
+        <v>916</v>
+      </c>
+      <c r="B2090" t="s">
+        <v>790</v>
+      </c>
+      <c r="C2090" t="s">
+        <v>384</v>
+      </c>
+      <c r="D2090" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2090">
+        <v>15</v>
+      </c>
+      <c r="F2090">
+        <v>0</v>
+      </c>
+      <c r="G2090">
+        <v>0</v>
+      </c>
+      <c r="H2090">
+        <v>0</v>
+      </c>
+      <c r="I2090">
+        <v>0</v>
+      </c>
+      <c r="J2090">
+        <v>3</v>
+      </c>
+      <c r="K2090" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2091" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2091" t="s">
+        <v>925</v>
+      </c>
+      <c r="B2091" t="s">
+        <v>373</v>
+      </c>
+      <c r="C2091" t="s">
+        <v>374</v>
+      </c>
+      <c r="D2091" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2091">
+        <v>15</v>
+      </c>
+      <c r="F2091">
+        <v>0</v>
+      </c>
+      <c r="G2091">
+        <v>0</v>
+      </c>
+      <c r="H2091">
+        <v>0</v>
+      </c>
+      <c r="I2091">
+        <v>0</v>
+      </c>
+      <c r="J2091">
+        <v>3</v>
+      </c>
+      <c r="K2091" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2092" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2092" t="s">
+        <v>925</v>
+      </c>
+      <c r="B2092" t="s">
+        <v>394</v>
+      </c>
+      <c r="C2092" t="s">
+        <v>395</v>
+      </c>
+      <c r="D2092" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2092">
+        <v>15</v>
+      </c>
+      <c r="F2092">
+        <v>0</v>
+      </c>
+      <c r="G2092">
+        <v>0</v>
+      </c>
+      <c r="H2092">
+        <v>0</v>
+      </c>
+      <c r="I2092">
+        <v>0</v>
+      </c>
+      <c r="J2092">
+        <v>3</v>
+      </c>
+      <c r="K2092" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2093" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2093" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2093" t="s">
+        <v>396</v>
+      </c>
+      <c r="C2093" t="s">
+        <v>299</v>
+      </c>
+      <c r="D2093" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2093">
+        <v>15</v>
+      </c>
+      <c r="F2093">
+        <v>0</v>
+      </c>
+      <c r="G2093">
+        <v>6</v>
+      </c>
+      <c r="H2093">
+        <v>0</v>
+      </c>
+      <c r="I2093">
+        <v>0</v>
+      </c>
+      <c r="J2093">
+        <v>4</v>
+      </c>
+      <c r="K2093" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2094" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2094" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2094" t="s">
+        <v>397</v>
+      </c>
+      <c r="C2094" t="s">
+        <v>229</v>
+      </c>
+      <c r="D2094" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2094">
+        <v>15</v>
+      </c>
+      <c r="F2094">
+        <v>0</v>
+      </c>
+      <c r="G2094">
+        <v>6</v>
+      </c>
+      <c r="H2094">
+        <v>0</v>
+      </c>
+      <c r="I2094">
+        <v>0</v>
+      </c>
+      <c r="J2094">
+        <v>4</v>
+      </c>
+      <c r="K2094" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2095" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2095" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2095" t="s">
+        <v>398</v>
+      </c>
+      <c r="C2095" t="s">
+        <v>399</v>
+      </c>
+      <c r="D2095" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2095">
+        <v>5</v>
+      </c>
+      <c r="F2095">
+        <v>0</v>
+      </c>
+      <c r="G2095">
+        <v>2</v>
+      </c>
+      <c r="H2095">
+        <v>0</v>
+      </c>
+      <c r="I2095">
+        <v>0</v>
+      </c>
+      <c r="J2095">
+        <v>1</v>
+      </c>
+      <c r="K2095" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2096" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2096" t="s">
+        <v>912</v>
+      </c>
+      <c r="B2096" t="s">
+        <v>534</v>
+      </c>
+      <c r="C2096" t="s">
+        <v>535</v>
+      </c>
+      <c r="D2096" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2096">
+        <v>15</v>
+      </c>
+      <c r="F2096">
+        <v>0</v>
+      </c>
+      <c r="G2096">
+        <v>0</v>
+      </c>
+      <c r="H2096">
+        <v>0</v>
+      </c>
+      <c r="I2096">
+        <v>0</v>
+      </c>
+      <c r="J2096">
+        <v>3</v>
+      </c>
+      <c r="K2096" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2097" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2097" t="s">
+        <v>912</v>
+      </c>
+      <c r="B2097" t="s">
+        <v>532</v>
+      </c>
+      <c r="C2097" t="s">
+        <v>533</v>
+      </c>
+      <c r="D2097" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2097">
+        <v>15</v>
+      </c>
+      <c r="F2097">
+        <v>0</v>
+      </c>
+      <c r="G2097">
+        <v>0</v>
+      </c>
+      <c r="H2097">
+        <v>0</v>
+      </c>
+      <c r="I2097">
+        <v>0</v>
+      </c>
+      <c r="J2097">
+        <v>3</v>
+      </c>
+      <c r="K2097" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2098" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2098" t="s">
+        <v>912</v>
+      </c>
+      <c r="B2098" t="s">
+        <v>528</v>
+      </c>
+      <c r="C2098" t="s">
+        <v>529</v>
+      </c>
+      <c r="D2098" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2098">
+        <v>15</v>
+      </c>
+      <c r="F2098">
+        <v>0</v>
+      </c>
+      <c r="G2098">
+        <v>0</v>
+      </c>
+      <c r="H2098">
+        <v>0</v>
+      </c>
+      <c r="I2098">
+        <v>0</v>
+      </c>
+      <c r="J2098">
+        <v>3</v>
+      </c>
+      <c r="K2098" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2099" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2099" t="s">
+        <v>926</v>
+      </c>
+      <c r="B2099" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2099" t="s">
+        <v>276</v>
+      </c>
+      <c r="D2099" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2099">
+        <v>15</v>
+      </c>
+      <c r="F2099">
+        <v>0</v>
+      </c>
+      <c r="G2099">
+        <v>6</v>
+      </c>
+      <c r="H2099">
+        <v>3</v>
+      </c>
+      <c r="I2099">
+        <v>0</v>
+      </c>
+      <c r="J2099">
+        <v>5</v>
+      </c>
+      <c r="K2099" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2100" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2100" t="s">
+        <v>926</v>
+      </c>
+      <c r="B2100" t="s">
+        <v>38</v>
+      </c>
+      <c r="C2100" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2100" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2100">
+        <v>15</v>
+      </c>
+      <c r="F2100">
+        <v>0</v>
+      </c>
+      <c r="G2100">
+        <v>6</v>
+      </c>
+      <c r="H2100">
+        <v>3</v>
+      </c>
+      <c r="I2100">
+        <v>0</v>
+      </c>
+      <c r="J2100">
+        <v>6</v>
+      </c>
+      <c r="K2100" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2101" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2101" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2101" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2101" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2101">
+        <v>0</v>
+      </c>
+      <c r="F2101">
+        <v>6</v>
+      </c>
+      <c r="G2101">
+        <v>0</v>
+      </c>
+      <c r="H2101">
+        <v>0</v>
+      </c>
+      <c r="I2101">
+        <v>7</v>
+      </c>
+      <c r="J2101">
+        <v>3</v>
+      </c>
+      <c r="K2101" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2102" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2102" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2102" t="s">
+        <v>28</v>
+      </c>
+      <c r="C2102" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2102" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2102">
+        <v>0</v>
+      </c>
+      <c r="F2102">
+        <v>6</v>
+      </c>
+      <c r="G2102">
+        <v>0</v>
+      </c>
+      <c r="H2102">
+        <v>0</v>
+      </c>
+      <c r="I2102">
+        <v>7</v>
+      </c>
+      <c r="J2102">
+        <v>3</v>
+      </c>
+      <c r="K2102" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2103" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2103" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2103" t="s">
+        <v>30</v>
+      </c>
+      <c r="C2103" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2103">
+        <v>0</v>
+      </c>
+      <c r="F2103">
+        <v>6</v>
+      </c>
+      <c r="G2103">
+        <v>0</v>
+      </c>
+      <c r="H2103">
+        <v>0</v>
+      </c>
+      <c r="I2103">
+        <v>7</v>
+      </c>
+      <c r="J2103">
+        <v>2</v>
+      </c>
+      <c r="K2103" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2104" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2104" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2104" t="s">
+        <v>65</v>
+      </c>
+      <c r="C2104" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2104" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2104">
+        <v>0</v>
+      </c>
+      <c r="F2104">
+        <v>6</v>
+      </c>
+      <c r="G2104">
+        <v>0</v>
+      </c>
+      <c r="H2104">
+        <v>0</v>
+      </c>
+      <c r="I2104">
+        <v>7</v>
+      </c>
+      <c r="J2104">
+        <v>3</v>
+      </c>
+      <c r="K2104" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2105" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2105" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2105" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2105" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2105">
+        <v>0</v>
+      </c>
+      <c r="F2105">
+        <v>6</v>
+      </c>
+      <c r="G2105">
+        <v>0</v>
+      </c>
+      <c r="H2105">
+        <v>0</v>
+      </c>
+      <c r="I2105">
+        <v>7</v>
+      </c>
+      <c r="J2105">
+        <v>3</v>
+      </c>
+      <c r="K2105" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2106" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2106" t="s">
+        <v>923</v>
+      </c>
+      <c r="B2106" t="s">
         <v>67</v>
       </c>
-      <c r="C2055" t="s">
+      <c r="C2106" t="s">
         <v>292</v>
       </c>
-      <c r="D2055" t="s">
+      <c r="D2106" t="s">
         <v>13</v>
       </c>
-      <c r="E2055">
-        <v>0</v>
-      </c>
-      <c r="F2055">
-        <v>6</v>
-      </c>
-      <c r="G2055">
-        <v>0</v>
-      </c>
-      <c r="H2055">
-        <v>0</v>
-      </c>
-      <c r="I2055">
+      <c r="E2106">
+        <v>0</v>
+      </c>
+      <c r="F2106">
+        <v>6</v>
+      </c>
+      <c r="G2106">
+        <v>0</v>
+      </c>
+      <c r="H2106">
+        <v>0</v>
+      </c>
+      <c r="I2106">
         <v>7</v>
       </c>
-      <c r="J2055">
-        <v>3</v>
-      </c>
-      <c r="K2055" t="s">
-        <v>891</v>
+      <c r="J2106">
+        <v>3</v>
+      </c>
+      <c r="K2106" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2107" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2107" t="s">
+        <v>927</v>
+      </c>
+      <c r="B2107" t="s">
+        <v>102</v>
+      </c>
+      <c r="C2107" t="s">
+        <v>676</v>
+      </c>
+      <c r="D2107" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2107">
+        <v>15</v>
+      </c>
+      <c r="F2107">
+        <v>0</v>
+      </c>
+      <c r="G2107">
+        <v>6</v>
+      </c>
+      <c r="H2107">
+        <v>0</v>
+      </c>
+      <c r="I2107">
+        <v>0</v>
+      </c>
+      <c r="J2107">
+        <v>5</v>
+      </c>
+      <c r="K2107" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2108" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2108" t="s">
+        <v>927</v>
+      </c>
+      <c r="B2108" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2108" t="s">
+        <v>155</v>
+      </c>
+      <c r="D2108" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2108">
+        <v>15</v>
+      </c>
+      <c r="F2108">
+        <v>0</v>
+      </c>
+      <c r="G2108">
+        <v>6</v>
+      </c>
+      <c r="H2108">
+        <v>0</v>
+      </c>
+      <c r="I2108">
+        <v>0</v>
+      </c>
+      <c r="J2108">
+        <v>5</v>
+      </c>
+      <c r="K2108" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2109" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2109" t="s">
+        <v>927</v>
+      </c>
+      <c r="B2109" t="s">
+        <v>110</v>
+      </c>
+      <c r="C2109" t="s">
+        <v>928</v>
+      </c>
+      <c r="D2109" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2109">
+        <v>15</v>
+      </c>
+      <c r="F2109">
+        <v>0</v>
+      </c>
+      <c r="G2109">
+        <v>6</v>
+      </c>
+      <c r="H2109">
+        <v>0</v>
+      </c>
+      <c r="I2109">
+        <v>0</v>
+      </c>
+      <c r="J2109">
+        <v>4</v>
+      </c>
+      <c r="K2109" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2110" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2110" t="s">
+        <v>927</v>
+      </c>
+      <c r="B2110" t="s">
+        <v>207</v>
+      </c>
+      <c r="C2110" t="s">
+        <v>208</v>
+      </c>
+      <c r="D2110" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2110">
+        <v>15</v>
+      </c>
+      <c r="F2110">
+        <v>0</v>
+      </c>
+      <c r="G2110">
+        <v>6</v>
+      </c>
+      <c r="H2110">
+        <v>0</v>
+      </c>
+      <c r="I2110">
+        <v>0</v>
+      </c>
+      <c r="J2110">
+        <v>5</v>
+      </c>
+      <c r="K2110" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2111" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2111" t="s">
+        <v>929</v>
+      </c>
+      <c r="B2111" t="s">
+        <v>31</v>
+      </c>
+      <c r="C2111" t="s">
+        <v>244</v>
+      </c>
+      <c r="D2111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2111">
+        <v>0</v>
+      </c>
+      <c r="F2111">
+        <v>6</v>
+      </c>
+      <c r="G2111">
+        <v>0</v>
+      </c>
+      <c r="H2111">
+        <v>0</v>
+      </c>
+      <c r="I2111">
+        <v>7</v>
+      </c>
+      <c r="J2111">
+        <v>3</v>
+      </c>
+      <c r="K2111" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2112" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2112" t="s">
+        <v>929</v>
+      </c>
+      <c r="B2112" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2112" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2112" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2112">
+        <v>0</v>
+      </c>
+      <c r="F2112">
+        <v>6</v>
+      </c>
+      <c r="G2112">
+        <v>0</v>
+      </c>
+      <c r="H2112">
+        <v>0</v>
+      </c>
+      <c r="I2112">
+        <v>7</v>
+      </c>
+      <c r="J2112">
+        <v>3</v>
+      </c>
+      <c r="K2112" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2113" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2113" t="s">
+        <v>929</v>
+      </c>
+      <c r="B2113" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2113" t="s">
+        <v>265</v>
+      </c>
+      <c r="D2113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2113">
+        <v>0</v>
+      </c>
+      <c r="F2113">
+        <v>6</v>
+      </c>
+      <c r="G2113">
+        <v>0</v>
+      </c>
+      <c r="H2113">
+        <v>0</v>
+      </c>
+      <c r="I2113">
+        <v>7</v>
+      </c>
+      <c r="J2113">
+        <v>3</v>
+      </c>
+      <c r="K2113" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2114" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2114" t="s">
+        <v>929</v>
+      </c>
+      <c r="B2114" t="s">
+        <v>35</v>
+      </c>
+      <c r="C2114" t="s">
+        <v>266</v>
+      </c>
+      <c r="D2114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2114">
+        <v>0</v>
+      </c>
+      <c r="F2114">
+        <v>1</v>
+      </c>
+      <c r="G2114">
+        <v>0</v>
+      </c>
+      <c r="H2114">
+        <v>0</v>
+      </c>
+      <c r="I2114">
+        <v>2</v>
+      </c>
+      <c r="J2114">
+        <v>1</v>
+      </c>
+      <c r="K2114" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2115" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2115" t="s">
+        <v>930</v>
+      </c>
+      <c r="B2115" t="s">
+        <v>111</v>
+      </c>
+      <c r="C2115" t="s">
+        <v>928</v>
+      </c>
+      <c r="D2115" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2115">
+        <v>15</v>
+      </c>
+      <c r="F2115">
+        <v>0</v>
+      </c>
+      <c r="G2115">
+        <v>6</v>
+      </c>
+      <c r="H2115">
+        <v>0</v>
+      </c>
+      <c r="I2115">
+        <v>0</v>
+      </c>
+      <c r="J2115">
+        <v>5</v>
+      </c>
+      <c r="K2115" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2116" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2116" t="s">
+        <v>930</v>
+      </c>
+      <c r="B2116" t="s">
+        <v>112</v>
+      </c>
+      <c r="C2116" t="s">
+        <v>545</v>
+      </c>
+      <c r="D2116" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2116">
+        <v>15</v>
+      </c>
+      <c r="F2116">
+        <v>0</v>
+      </c>
+      <c r="G2116">
+        <v>6</v>
+      </c>
+      <c r="H2116">
+        <v>0</v>
+      </c>
+      <c r="I2116">
+        <v>0</v>
+      </c>
+      <c r="J2116">
+        <v>5</v>
+      </c>
+      <c r="K2116" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2117" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2117" t="s">
+        <v>930</v>
+      </c>
+      <c r="B2117" t="s">
+        <v>36</v>
+      </c>
+      <c r="C2117" t="s">
+        <v>218</v>
+      </c>
+      <c r="D2117" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2117">
+        <v>0</v>
+      </c>
+      <c r="F2117">
+        <v>6</v>
+      </c>
+      <c r="G2117">
+        <v>0</v>
+      </c>
+      <c r="H2117">
+        <v>0</v>
+      </c>
+      <c r="I2117">
+        <v>7</v>
+      </c>
+      <c r="J2117">
+        <v>3</v>
+      </c>
+      <c r="K2117" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2118" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2118" t="s">
+        <v>930</v>
+      </c>
+      <c r="B2118" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2118" t="s">
+        <v>268</v>
+      </c>
+      <c r="D2118" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2118">
+        <v>0</v>
+      </c>
+      <c r="F2118">
+        <v>6</v>
+      </c>
+      <c r="G2118">
+        <v>0</v>
+      </c>
+      <c r="H2118">
+        <v>0</v>
+      </c>
+      <c r="I2118">
+        <v>7</v>
+      </c>
+      <c r="J2118">
+        <v>3</v>
+      </c>
+      <c r="K2118" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2119" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2119" t="s">
+        <v>931</v>
+      </c>
+      <c r="B2119" t="s">
+        <v>196</v>
+      </c>
+      <c r="C2119" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2119" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2119">
+        <v>15</v>
+      </c>
+      <c r="F2119">
+        <v>0</v>
+      </c>
+      <c r="G2119">
+        <v>6</v>
+      </c>
+      <c r="H2119">
+        <v>0</v>
+      </c>
+      <c r="I2119">
+        <v>0</v>
+      </c>
+      <c r="J2119">
+        <v>5</v>
+      </c>
+      <c r="K2119" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2120" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2120" t="s">
+        <v>931</v>
+      </c>
+      <c r="B2120" t="s">
+        <v>174</v>
+      </c>
+      <c r="C2120" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2120" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2120">
+        <v>15</v>
+      </c>
+      <c r="F2120">
+        <v>0</v>
+      </c>
+      <c r="G2120">
+        <v>6</v>
+      </c>
+      <c r="H2120">
+        <v>0</v>
+      </c>
+      <c r="I2120">
+        <v>0</v>
+      </c>
+      <c r="J2120">
+        <v>5</v>
+      </c>
+      <c r="K2120" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2121" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2121" t="s">
+        <v>931</v>
+      </c>
+      <c r="B2121" t="s">
+        <v>172</v>
+      </c>
+      <c r="C2121" t="s">
+        <v>173</v>
+      </c>
+      <c r="D2121" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2121">
+        <v>15</v>
+      </c>
+      <c r="F2121">
+        <v>0</v>
+      </c>
+      <c r="G2121">
+        <v>6</v>
+      </c>
+      <c r="H2121">
+        <v>0</v>
+      </c>
+      <c r="I2121">
+        <v>0</v>
+      </c>
+      <c r="J2121">
+        <v>4</v>
+      </c>
+      <c r="K2121" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2122" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2122" t="s">
+        <v>931</v>
+      </c>
+      <c r="B2122" t="s">
+        <v>170</v>
+      </c>
+      <c r="C2122" t="s">
+        <v>932</v>
+      </c>
+      <c r="D2122" t="s">
+        <v>72</v>
+      </c>
+      <c r="E2122">
+        <v>3</v>
+      </c>
+      <c r="F2122">
+        <v>0</v>
+      </c>
+      <c r="G2122">
+        <v>1</v>
+      </c>
+      <c r="H2122">
+        <v>0</v>
+      </c>
+      <c r="I2122">
+        <v>0</v>
+      </c>
+      <c r="J2122">
+        <v>1</v>
+      </c>
+      <c r="K2122" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2123" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2123" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2123" t="s">
+        <v>117</v>
+      </c>
+      <c r="C2123" t="s">
+        <v>466</v>
+      </c>
+      <c r="D2123" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2123">
+        <v>15</v>
+      </c>
+      <c r="F2123">
+        <v>0</v>
+      </c>
+      <c r="G2123">
+        <v>6</v>
+      </c>
+      <c r="H2123">
+        <v>0</v>
+      </c>
+      <c r="I2123">
+        <v>0</v>
+      </c>
+      <c r="J2123">
+        <v>5</v>
+      </c>
+      <c r="K2123" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2124" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2124" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2124" t="s">
+        <v>118</v>
+      </c>
+      <c r="C2124" t="s">
+        <v>220</v>
+      </c>
+      <c r="D2124" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2124">
+        <v>15</v>
+      </c>
+      <c r="F2124">
+        <v>0</v>
+      </c>
+      <c r="G2124">
+        <v>6</v>
+      </c>
+      <c r="H2124">
+        <v>0</v>
+      </c>
+      <c r="I2124">
+        <v>0</v>
+      </c>
+      <c r="J2124">
+        <v>4</v>
+      </c>
+      <c r="K2124" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2125" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2125" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2125" t="s">
+        <v>119</v>
+      </c>
+      <c r="C2125" t="s">
+        <v>934</v>
+      </c>
+      <c r="D2125" t="s">
+        <v>79</v>
+      </c>
+      <c r="E2125">
+        <v>8</v>
+      </c>
+      <c r="F2125">
+        <v>0</v>
+      </c>
+      <c r="G2125">
+        <v>4</v>
+      </c>
+      <c r="H2125">
+        <v>0</v>
+      </c>
+      <c r="I2125">
+        <v>0</v>
+      </c>
+      <c r="J2125">
+        <v>3</v>
+      </c>
+      <c r="K2125" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2126" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2126" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2126" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2126" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2126" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2126">
+        <v>0</v>
+      </c>
+      <c r="F2126">
+        <v>6</v>
+      </c>
+      <c r="G2126">
+        <v>0</v>
+      </c>
+      <c r="H2126">
+        <v>0</v>
+      </c>
+      <c r="I2126">
+        <v>7</v>
+      </c>
+      <c r="J2126">
+        <v>3</v>
+      </c>
+      <c r="K2126" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2127" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2127" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2127" t="s">
+        <v>44</v>
+      </c>
+      <c r="C2127" t="s">
+        <v>269</v>
+      </c>
+      <c r="D2127" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2127">
+        <v>0</v>
+      </c>
+      <c r="F2127">
+        <v>6</v>
+      </c>
+      <c r="G2127">
+        <v>0</v>
+      </c>
+      <c r="H2127">
+        <v>0</v>
+      </c>
+      <c r="I2127">
+        <v>7</v>
+      </c>
+      <c r="J2127">
+        <v>2</v>
+      </c>
+      <c r="K2127" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="2128" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="A2128" t="s">
+        <v>933</v>
+      </c>
+      <c r="B2128" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2128" t="s">
+        <v>421</v>
+      </c>
+      <c r="D2128" t="s">
+        <v>87</v>
+      </c>
+      <c r="E2128">
+        <v>0</v>
+      </c>
+      <c r="F2128">
+        <v>1</v>
+      </c>
+      <c r="G2128">
+        <v>0</v>
+      </c>
+      <c r="H2128">
+        <v>0</v>
+      </c>
+      <c r="I2128">
+        <v>2</v>
+      </c>
+      <c r="J2128">
+        <v>1</v>
+      </c>
+      <c r="K2128" t="s">
+        <v>893</v>
       </c>
     </row>
   </sheetData>
